--- a/docs/damping_curve_RAx8.xlsx
+++ b/docs/damping_curve_RAx8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\damping-rx-sync-20261026\native\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF63139-4438-4B24-989E-C0A88151CC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733267B6-4D59-444D-B8E3-208505955454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -316,11 +316,11 @@
   </si>
   <si>
     <t>RA88</t>
-    <phoneticPr fontId="75" type="noConversion"/>
+    <phoneticPr fontId="74" type="noConversion"/>
   </si>
   <si>
     <t>Type-A</t>
-    <phoneticPr fontId="75" type="noConversion"/>
+    <phoneticPr fontId="74" type="noConversion"/>
   </si>
   <si>
     <t>Rally</t>
@@ -338,7 +338,7 @@
     <numFmt numFmtId="177" formatCode="0&quot; mm&quot;"/>
     <numFmt numFmtId="178" formatCode="0&quot; clicks&quot;"/>
   </numFmts>
-  <fonts count="76">
+  <fonts count="75">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -665,13 +665,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="20"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
@@ -821,7 +814,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="70">
+  <fills count="69">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1040,11 +1033,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF31475E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -1169,7 +1157,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="67">
+  <borders count="66">
     <border>
       <left/>
       <right/>
@@ -1571,13 +1559,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FFDCE4EB"/>
       </bottom>
@@ -1716,11 +1697,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="43" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1735,7 +1716,7 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1747,10 +1728,10 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1765,10 +1746,10 @@
     <xf numFmtId="178" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1828,8 +1809,11 @@
     <xf numFmtId="0" fontId="45" fillId="37" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="52" fillId="44" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="53" fillId="45" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="46" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1841,7 +1825,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="49" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="50" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1853,60 +1837,57 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="53" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="54" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="63" fillId="55" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="64" fillId="56" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="65" fillId="57" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="58" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="59" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="67" fillId="59" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="68" fillId="60" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="69" fillId="61" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="70" fillId="62" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="63" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="64" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="65" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="66" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="66" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="67" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="67" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="68" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="67" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="69" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="66" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="68" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="69" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="67" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="68" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1918,26 +1899,56 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="44" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="43" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="62" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="61" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1945,53 +1956,8 @@
     <xf numFmtId="0" fontId="40" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="42" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="33" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2007,6 +1973,18 @@
     </xf>
     <xf numFmtId="0" fontId="48" fillId="40" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="42" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2174,64 +2152,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>135</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>270</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>405</c:v>
-                </c:pt>
                 <c:pt idx="4">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>540</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>675</c:v>
-                </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>720.00000000000011</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>810</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>919.07999999999993</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1010.8800000000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1102.68</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>1206.98</c:v>
+                  <c:v>975</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1311.2800000000002</c:v>
+                  <c:v>1140.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1415.58</c:v>
+                  <c:v>1305</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1519.88</c:v>
+                  <c:v>1470</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1624.1799999999998</c:v>
+                  <c:v>1635</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1728.48</c:v>
+                  <c:v>1800</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1832.7800000000002</c:v>
+                  <c:v>1965.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1937.0800000000002</c:v>
+                  <c:v>2130</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2041.3800000000003</c:v>
+                  <c:v>2295</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2145.6799999999998</c:v>
+                  <c:v>2460</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2249.98</c:v>
+                  <c:v>2625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2350,64 +2328,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>157.5</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>315</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>472.5</c:v>
+                  <c:v>357</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>630</c:v>
+                  <c:v>474</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>787.5</c:v>
+                  <c:v>591</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>945</c:v>
+                  <c:v>708</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1070.3699999999999</c:v>
+                  <c:v>824.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1174.32</c:v>
+                  <c:v>942.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1278.27</c:v>
+                  <c:v>1059</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1394.72</c:v>
+                  <c:v>1251</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1511.17</c:v>
+                  <c:v>1443.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1627.62</c:v>
+                  <c:v>1635</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1744.0700000000002</c:v>
+                  <c:v>1827</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1860.52</c:v>
+                  <c:v>2019</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1976.97</c:v>
+                  <c:v>2211</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2093.42</c:v>
+                  <c:v>2403</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2209.87</c:v>
+                  <c:v>2595</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2326.3200000000002</c:v>
+                  <c:v>2787</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2442.7699999999995</c:v>
+                  <c:v>2979</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2559.2199999999998</c:v>
+                  <c:v>3171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2526,64 +2504,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>180</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>540</c:v>
+                  <c:v>442.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>720</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>900</c:v>
+                  <c:v>727.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1080</c:v>
+                  <c:v>870</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1221.1199999999999</c:v>
+                  <c:v>1012.4999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1336.3200000000002</c:v>
+                  <c:v>1155</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1451.52</c:v>
+                  <c:v>1297.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1579.22</c:v>
+                  <c:v>1515</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1706.92</c:v>
+                  <c:v>1732.5000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1834.62</c:v>
+                  <c:v>1950</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1962.3200000000002</c:v>
+                  <c:v>2167.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2090.02</c:v>
+                  <c:v>2385</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2217.7200000000003</c:v>
+                  <c:v>2602.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2345.42</c:v>
+                  <c:v>2820</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2473.12</c:v>
+                  <c:v>3037.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2600.8200000000002</c:v>
+                  <c:v>3255</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2728.5199999999995</c:v>
+                  <c:v>3472.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2856.22</c:v>
+                  <c:v>3690</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2702,64 +2680,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>202.5</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>405</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>607.5</c:v>
+                  <c:v>526.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>810</c:v>
+                  <c:v>693</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1012.5</c:v>
+                  <c:v>859.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1215</c:v>
+                  <c:v>1026</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1371.33</c:v>
+                  <c:v>1192.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1496.88</c:v>
+                  <c:v>1359</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1622.43</c:v>
+                  <c:v>1525.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1760.48</c:v>
+                  <c:v>1767</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1898.5300000000002</c:v>
+                  <c:v>2008.5000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2036.58</c:v>
+                  <c:v>2250</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2174.63</c:v>
+                  <c:v>2491.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2312.6799999999998</c:v>
+                  <c:v>2733</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2450.73</c:v>
+                  <c:v>2974.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2588.7800000000002</c:v>
+                  <c:v>3216</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2726.83</c:v>
+                  <c:v>3457.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2864.88</c:v>
+                  <c:v>3699</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3002.93</c:v>
+                  <c:v>3940.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3140.9799999999996</c:v>
+                  <c:v>4182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2878,64 +2856,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>225</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>450</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>675</c:v>
+                  <c:v>609</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>798</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1125</c:v>
+                  <c:v>987</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1350</c:v>
+                  <c:v>1176</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1521</c:v>
+                  <c:v>1365</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1656</c:v>
+                  <c:v>1554.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1791</c:v>
+                  <c:v>1743</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1938.5</c:v>
+                  <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2086</c:v>
+                  <c:v>2271</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2233.5</c:v>
+                  <c:v>2535</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2381</c:v>
+                  <c:v>2799</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2528.5</c:v>
+                  <c:v>3063</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2676</c:v>
+                  <c:v>3327</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2823.5</c:v>
+                  <c:v>3591.0000000000005</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2971</c:v>
+                  <c:v>3855</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3118.5</c:v>
+                  <c:v>4119</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3266</c:v>
+                  <c:v>4383</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3413.5</c:v>
+                  <c:v>4647</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3254,64 +3232,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>195</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>390</c:v>
+                  <c:v>340</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>585</c:v>
+                  <c:v>498.66666666666663</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>780</c:v>
+                  <c:v>657.33333333333337</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>931.31999999999994</c:v>
+                  <c:v>816</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1053.52</c:v>
+                  <c:v>974.66666666666663</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1175.72</c:v>
+                  <c:v>1133.3333333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1297.92</c:v>
+                  <c:v>1292.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1420.12</c:v>
+                  <c:v>1451.6666666666667</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1554.8200000000002</c:v>
+                  <c:v>1615.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1689.5200000000002</c:v>
+                  <c:v>1779.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1824.22</c:v>
+                  <c:v>1942.6666666666667</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1958.92</c:v>
+                  <c:v>2106.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2093.62</c:v>
+                  <c:v>2270</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2228.3200000000002</c:v>
+                  <c:v>2433.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2363.0200000000004</c:v>
+                  <c:v>2597.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2497.7200000000003</c:v>
+                  <c:v>2761</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2632.42</c:v>
+                  <c:v>2924.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2767.12</c:v>
+                  <c:v>3088.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2901.82</c:v>
+                  <c:v>3252</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3430,64 +3408,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>195</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>390</c:v>
+                  <c:v>340</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>585</c:v>
+                  <c:v>498.66666666666663</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>780</c:v>
+                  <c:v>657.33333333333337</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>975</c:v>
+                  <c:v>816</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1126.32</c:v>
+                  <c:v>974.66666666666663</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1248.52</c:v>
+                  <c:v>1133.3333333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1370.72</c:v>
+                  <c:v>1292.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1492.92</c:v>
+                  <c:v>1454.6666666666667</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1627.62</c:v>
+                  <c:v>1653.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1762.3200000000002</c:v>
+                  <c:v>1852.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1897.02</c:v>
+                  <c:v>2050.6666666666665</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2031.72</c:v>
+                  <c:v>2249.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2166.42</c:v>
+                  <c:v>2448</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2301.12</c:v>
+                  <c:v>2646.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2435.8200000000002</c:v>
+                  <c:v>2845.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2570.52</c:v>
+                  <c:v>3044</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2705.2200000000003</c:v>
+                  <c:v>3242.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2839.92</c:v>
+                  <c:v>3441.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2974.62</c:v>
+                  <c:v>3640</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3606,64 +3584,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>195</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>390</c:v>
+                  <c:v>340</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>585</c:v>
+                  <c:v>498.66666666666663</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>780</c:v>
+                  <c:v>657.33333333333337</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>975</c:v>
+                  <c:v>816</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1170</c:v>
+                  <c:v>974.66666666666663</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1321.32</c:v>
+                  <c:v>1133.3333333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1443.52</c:v>
+                  <c:v>1292.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1565.72</c:v>
+                  <c:v>1450.6666666666667</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1700.42</c:v>
+                  <c:v>1684.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1835.1200000000001</c:v>
+                  <c:v>1918.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1969.82</c:v>
+                  <c:v>2151.6666666666665</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2104.52</c:v>
+                  <c:v>2385.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2239.2199999999998</c:v>
+                  <c:v>2619</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2373.92</c:v>
+                  <c:v>2852.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2508.62</c:v>
+                  <c:v>3086.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2643.32</c:v>
+                  <c:v>3320</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2778.0200000000004</c:v>
+                  <c:v>3553.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2912.72</c:v>
+                  <c:v>3787.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3047.42</c:v>
+                  <c:v>4021</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3782,64 +3760,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>195</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>390</c:v>
+                  <c:v>340</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>585</c:v>
+                  <c:v>498.66666666666663</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>780</c:v>
+                  <c:v>657.33333333333337</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>975</c:v>
+                  <c:v>816</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1170</c:v>
+                  <c:v>974.66666666666663</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1365</c:v>
+                  <c:v>1133.3333333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1516.3200000000002</c:v>
+                  <c:v>1292.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1638.52</c:v>
+                  <c:v>1450.6666666666667</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1773.22</c:v>
+                  <c:v>1708.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1907.92</c:v>
+                  <c:v>1977.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2042.62</c:v>
+                  <c:v>2245.6666666666665</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2177.3200000000002</c:v>
+                  <c:v>2514.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2312.02</c:v>
+                  <c:v>2783</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2446.7200000000003</c:v>
+                  <c:v>3051.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2581.42</c:v>
+                  <c:v>3320.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2716.12</c:v>
+                  <c:v>3589</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2850.82</c:v>
+                  <c:v>3857.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2985.52</c:v>
+                  <c:v>4126.333333333333</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3120.2200000000003</c:v>
+                  <c:v>4395</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3958,64 +3936,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>195</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>390</c:v>
+                  <c:v>340</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>585</c:v>
+                  <c:v>498.66666666666663</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>780</c:v>
+                  <c:v>657.33333333333337</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>975</c:v>
+                  <c:v>816</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1170</c:v>
+                  <c:v>974.66666666666663</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1365</c:v>
+                  <c:v>1133.3333333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1560</c:v>
+                  <c:v>1292.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1711.3200000000002</c:v>
+                  <c:v>1450.6666666666667</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1846.02</c:v>
+                  <c:v>1725.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1980.7200000000003</c:v>
+                  <c:v>2029.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2115.42</c:v>
+                  <c:v>2332.6666666666665</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2250.12</c:v>
+                  <c:v>2636.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2384.8199999999997</c:v>
+                  <c:v>2940</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2519.52</c:v>
+                  <c:v>3243.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2654.2200000000003</c:v>
+                  <c:v>3547.3333333333335</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2788.92</c:v>
+                  <c:v>3851</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2923.62</c:v>
+                  <c:v>4154.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3058.32</c:v>
+                  <c:v>4458.333333333333</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3193.0200000000004</c:v>
+                  <c:v>4762</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4334,64 +4312,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>450</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>714</c:v>
+                  <c:v>497.59999999999997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>828</c:v>
+                  <c:v>591.59999999999991</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>942</c:v>
+                  <c:v>685.59999999999991</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1056</c:v>
+                  <c:v>779.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1170</c:v>
+                  <c:v>873.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1284</c:v>
+                  <c:v>967.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1398</c:v>
+                  <c:v>1061.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1512</c:v>
+                  <c:v>1155.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1626</c:v>
+                  <c:v>1249.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1739.9999999999998</c:v>
+                  <c:v>1343.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1854</c:v>
+                  <c:v>1437.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1968.0000000000002</c:v>
+                  <c:v>1531.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2082</c:v>
+                  <c:v>1625.6</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2196</c:v>
+                  <c:v>1719.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2310</c:v>
+                  <c:v>1813.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2424</c:v>
+                  <c:v>1907.6000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4510,64 +4488,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>175</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>350</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>525</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>700</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>850.5</c:v>
+                  <c:v>625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>976.5</c:v>
+                  <c:v>739.875</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1102.5</c:v>
+                  <c:v>853.625</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1228.5</c:v>
+                  <c:v>967.375</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1354.5</c:v>
+                  <c:v>1081.125</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1480.5</c:v>
+                  <c:v>1194.875</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1606.5</c:v>
+                  <c:v>1308.625</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1732.5</c:v>
+                  <c:v>1422.375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1858.5</c:v>
+                  <c:v>1536.125</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1984.5</c:v>
+                  <c:v>1649.875</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2110.5</c:v>
+                  <c:v>1763.625</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2236.5</c:v>
+                  <c:v>1877.375</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2362.5</c:v>
+                  <c:v>1991.125</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2488.5</c:v>
+                  <c:v>2104.875</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2614.5</c:v>
+                  <c:v>2218.625</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2740.5</c:v>
+                  <c:v>2332.375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4686,64 +4664,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>200</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>400</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>600</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>800</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>1000</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1136</c:v>
+                  <c:v>892.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1272</c:v>
+                  <c:v>1024.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1408</c:v>
+                  <c:v>1156.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1544</c:v>
+                  <c:v>1288.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1680</c:v>
+                  <c:v>1420.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1816</c:v>
+                  <c:v>1552.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1952</c:v>
+                  <c:v>1684.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2088</c:v>
+                  <c:v>1816.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2224</c:v>
+                  <c:v>1948.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2360</c:v>
+                  <c:v>2080.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2496</c:v>
+                  <c:v>2212.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2632</c:v>
+                  <c:v>2344.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2768</c:v>
+                  <c:v>2476.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2904</c:v>
+                  <c:v>2608.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3040</c:v>
+                  <c:v>2740.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4862,64 +4840,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>225</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>450</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>675</c:v>
+                  <c:v>525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>700</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1125</c:v>
+                  <c:v>875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1309.5</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1453.5</c:v>
+                  <c:v>1201.375</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1597.5</c:v>
+                  <c:v>1350.1250000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1741.5</c:v>
+                  <c:v>1498.875</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1885.5</c:v>
+                  <c:v>1647.625</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2029.5</c:v>
+                  <c:v>1796.3750000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2173.5</c:v>
+                  <c:v>1945.125</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2317.5</c:v>
+                  <c:v>2093.875</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2461.5</c:v>
+                  <c:v>2242.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2605.5</c:v>
+                  <c:v>2391.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2749.5</c:v>
+                  <c:v>2540.125</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2893.5</c:v>
+                  <c:v>2688.875</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3037.5</c:v>
+                  <c:v>2837.625</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3181.5</c:v>
+                  <c:v>2986.375</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3325.5</c:v>
+                  <c:v>3135.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5038,64 +5016,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>250</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>500</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>750</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>1250</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>1500</c:v>
+                  <c:v>1200</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1650</c:v>
+                  <c:v>1385.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1800</c:v>
+                  <c:v>1549.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1950</c:v>
+                  <c:v>1713.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2100</c:v>
+                  <c:v>1877.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2250</c:v>
+                  <c:v>2041.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2400</c:v>
+                  <c:v>2205.6</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2550</c:v>
+                  <c:v>2369.6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2700</c:v>
+                  <c:v>2533.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2850</c:v>
+                  <c:v>2697.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3000</c:v>
+                  <c:v>2861.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3150</c:v>
+                  <c:v>3025.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3300</c:v>
+                  <c:v>3189.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3450</c:v>
+                  <c:v>3353.5999999999995</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3600</c:v>
+                  <c:v>3517.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5407,64 +5385,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>135</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>270</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>405</c:v>
-                </c:pt>
                 <c:pt idx="4">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>540</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>649.08000000000004</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>740.88</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>832.68</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>924.48</c:v>
+                  <c:v>720.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1016.2800000000001</c:v>
+                  <c:v>811</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1120.5800000000002</c:v>
+                  <c:v>906</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1224.8800000000001</c:v>
+                  <c:v>1001.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1329.18</c:v>
+                  <c:v>1096</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1433.48</c:v>
+                  <c:v>1191</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1537.7800000000002</c:v>
+                  <c:v>1286</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1642.0800000000002</c:v>
+                  <c:v>1381</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1746.3800000000003</c:v>
+                  <c:v>1476.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1850.68</c:v>
+                  <c:v>1571</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1954.9800000000002</c:v>
+                  <c:v>1666</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2059.2800000000002</c:v>
+                  <c:v>1761</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2163.58</c:v>
+                  <c:v>1856</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5583,64 +5561,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>157.5</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>315</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>472.5</c:v>
+                  <c:v>357</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>630</c:v>
+                  <c:v>474</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>787.5</c:v>
+                  <c:v>591</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>912.86999999999989</c:v>
+                  <c:v>708</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1016.8199999999999</c:v>
+                  <c:v>824.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1120.77</c:v>
+                  <c:v>942.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1224.72</c:v>
+                  <c:v>1063</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1341.17</c:v>
+                  <c:v>1220</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1457.62</c:v>
+                  <c:v>1377.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1574.07</c:v>
+                  <c:v>1534</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1690.52</c:v>
+                  <c:v>1691</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1806.9699999999998</c:v>
+                  <c:v>1848</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1923.42</c:v>
+                  <c:v>2005</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2039.8700000000001</c:v>
+                  <c:v>2162.0000000000005</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2156.3199999999997</c:v>
+                  <c:v>2319</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2272.77</c:v>
+                  <c:v>2476</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2389.2199999999998</c:v>
+                  <c:v>2633</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2505.67</c:v>
+                  <c:v>2790</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5759,64 +5737,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>180</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>540</c:v>
+                  <c:v>442.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>720</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>900</c:v>
+                  <c:v>727.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1080</c:v>
+                  <c:v>870</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1221.1199999999999</c:v>
+                  <c:v>1012.4999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1336.3200000000002</c:v>
+                  <c:v>1155</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1451.52</c:v>
+                  <c:v>1297.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1579.22</c:v>
+                  <c:v>1515</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1706.92</c:v>
+                  <c:v>1732.5000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1834.62</c:v>
+                  <c:v>1950</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1962.3200000000002</c:v>
+                  <c:v>2167.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2090.02</c:v>
+                  <c:v>2385</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2217.7200000000003</c:v>
+                  <c:v>2602.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2345.42</c:v>
+                  <c:v>2820</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2473.12</c:v>
+                  <c:v>3037.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2600.8200000000002</c:v>
+                  <c:v>3255</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2728.5199999999995</c:v>
+                  <c:v>3472.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2856.22</c:v>
+                  <c:v>3690</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5935,64 +5913,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>202.5</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>405</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>607.5</c:v>
+                  <c:v>526.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>810</c:v>
+                  <c:v>693</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1012.5</c:v>
+                  <c:v>859.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1215</c:v>
+                  <c:v>1026</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1417.5</c:v>
+                  <c:v>1192.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1573.8300000000002</c:v>
+                  <c:v>1359</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1699.38</c:v>
+                  <c:v>1525.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1837.43</c:v>
+                  <c:v>1791</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1975.48</c:v>
+                  <c:v>2067.5000000000005</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2113.5299999999997</c:v>
+                  <c:v>2344</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2251.58</c:v>
+                  <c:v>2620.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2389.63</c:v>
+                  <c:v>2897</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2527.6800000000003</c:v>
+                  <c:v>3173.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2665.73</c:v>
+                  <c:v>3450</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2803.7799999999997</c:v>
+                  <c:v>3726.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2941.83</c:v>
+                  <c:v>4003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3079.88</c:v>
+                  <c:v>4279.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3217.9300000000003</c:v>
+                  <c:v>4556</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6111,64 +6089,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>225</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>450</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>675</c:v>
+                  <c:v>609</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>798</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1125</c:v>
+                  <c:v>987</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1350</c:v>
+                  <c:v>1176</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1575</c:v>
+                  <c:v>1365</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1800</c:v>
+                  <c:v>1554.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1971</c:v>
+                  <c:v>1743</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2118.5</c:v>
+                  <c:v>2048</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2266</c:v>
+                  <c:v>2382</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2413.5</c:v>
+                  <c:v>2716</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2561</c:v>
+                  <c:v>3050</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2708.5</c:v>
+                  <c:v>3384</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2856</c:v>
+                  <c:v>3718</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3003.5</c:v>
+                  <c:v>4052.0000000000005</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3151</c:v>
+                  <c:v>4386</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3298.5</c:v>
+                  <c:v>4720</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3446</c:v>
+                  <c:v>5054</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3593.5</c:v>
+                  <c:v>5388</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6287,64 +6265,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-150</c:v>
+                  <c:v>-100</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>-200</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>-300</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>-450</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>-600</c:v>
+                  <c:v>-400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-714</c:v>
+                  <c:v>-497.59999999999997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-828</c:v>
+                  <c:v>-591.59999999999991</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-942</c:v>
+                  <c:v>-685.59999999999991</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1056</c:v>
+                  <c:v>-779.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1170</c:v>
+                  <c:v>-873.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1284</c:v>
+                  <c:v>-967.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1398</c:v>
+                  <c:v>-1061.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1512</c:v>
+                  <c:v>-1155.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1626</c:v>
+                  <c:v>-1249.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1739.9999999999998</c:v>
+                  <c:v>-1343.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1854</c:v>
+                  <c:v>-1437.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1968.0000000000002</c:v>
+                  <c:v>-1531.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2082</c:v>
+                  <c:v>-1625.6</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2196</c:v>
+                  <c:v>-1719.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2310</c:v>
+                  <c:v>-1813.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2424</c:v>
+                  <c:v>-1907.6000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6463,64 +6441,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-175</c:v>
+                  <c:v>-125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-350</c:v>
+                  <c:v>-250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-525</c:v>
+                  <c:v>-375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-700</c:v>
+                  <c:v>-500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-850.5</c:v>
+                  <c:v>-625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-976.5</c:v>
+                  <c:v>-739.875</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1102.5</c:v>
+                  <c:v>-853.625</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1228.5</c:v>
+                  <c:v>-967.375</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1354.5</c:v>
+                  <c:v>-1081.125</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1480.5</c:v>
+                  <c:v>-1194.875</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1606.5</c:v>
+                  <c:v>-1308.625</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1732.5</c:v>
+                  <c:v>-1422.375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1858.5</c:v>
+                  <c:v>-1536.125</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1984.5</c:v>
+                  <c:v>-1649.875</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2110.5</c:v>
+                  <c:v>-1763.625</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2236.5</c:v>
+                  <c:v>-1877.375</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2362.5</c:v>
+                  <c:v>-1991.125</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2488.5</c:v>
+                  <c:v>-2104.875</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2614.5</c:v>
+                  <c:v>-2218.625</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2740.5</c:v>
+                  <c:v>-2332.375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6639,64 +6617,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-200</c:v>
+                  <c:v>-150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-400</c:v>
+                  <c:v>-300</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>-450</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>-600</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>-800</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1000</c:v>
+                  <c:v>-750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1136</c:v>
+                  <c:v>-892.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1272</c:v>
+                  <c:v>-1024.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1408</c:v>
+                  <c:v>-1156.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1544</c:v>
+                  <c:v>-1288.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1680</c:v>
+                  <c:v>-1420.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1816</c:v>
+                  <c:v>-1552.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1952</c:v>
+                  <c:v>-1684.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-2088</c:v>
+                  <c:v>-1816.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-2224</c:v>
+                  <c:v>-1948.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2360</c:v>
+                  <c:v>-2080.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2496</c:v>
+                  <c:v>-2212.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2632</c:v>
+                  <c:v>-2344.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2768</c:v>
+                  <c:v>-2476.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2904</c:v>
+                  <c:v>-2608.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-3040</c:v>
+                  <c:v>-2740.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6815,64 +6793,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-225</c:v>
+                  <c:v>-175</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-450</c:v>
+                  <c:v>-350</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-675</c:v>
+                  <c:v>-525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-900</c:v>
+                  <c:v>-700</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1125</c:v>
+                  <c:v>-875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1309.5</c:v>
+                  <c:v>-1050</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1453.5</c:v>
+                  <c:v>-1201.375</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1597.5</c:v>
+                  <c:v>-1350.1250000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1741.5</c:v>
+                  <c:v>-1498.875</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1885.5</c:v>
+                  <c:v>-1647.625</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2029.5</c:v>
+                  <c:v>-1796.3750000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2173.5</c:v>
+                  <c:v>-1945.125</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-2317.5</c:v>
+                  <c:v>-2093.875</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-2461.5</c:v>
+                  <c:v>-2242.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2605.5</c:v>
+                  <c:v>-2391.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2749.5</c:v>
+                  <c:v>-2540.125</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2893.5</c:v>
+                  <c:v>-2688.875</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-3037.5</c:v>
+                  <c:v>-2837.625</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-3181.5</c:v>
+                  <c:v>-2986.375</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-3325.5</c:v>
+                  <c:v>-3135.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6991,64 +6969,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-250</c:v>
+                  <c:v>-200</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-500</c:v>
+                  <c:v>-400</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-750</c:v>
+                  <c:v>-600</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>-800</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>-1000</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>-1250</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1500</c:v>
+                  <c:v>-1200</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1650</c:v>
+                  <c:v>-1385.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1800</c:v>
+                  <c:v>-1549.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1950</c:v>
+                  <c:v>-1713.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2100</c:v>
+                  <c:v>-1877.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2250</c:v>
+                  <c:v>-2041.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2400</c:v>
+                  <c:v>-2205.6</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-2550</c:v>
+                  <c:v>-2369.6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-2700</c:v>
+                  <c:v>-2533.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2850</c:v>
+                  <c:v>-2697.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-3000</c:v>
+                  <c:v>-2861.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-3150</c:v>
+                  <c:v>-3025.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-3300</c:v>
+                  <c:v>-3189.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-3450</c:v>
+                  <c:v>-3353.5999999999995</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-3600</c:v>
+                  <c:v>-3517.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7591,14 +7569,14 @@
     </row>
     <row r="2" spans="1:8" ht="35" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -7643,7 +7621,7 @@
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="73" t="s">
+      <c r="B6" s="72" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="6"/>
@@ -7660,7 +7638,7 @@
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="73"/>
+      <c r="B7" s="72"/>
       <c r="C7" s="6"/>
       <c r="D7" s="10" t="s">
         <v>4</v>
@@ -7781,30 +7759,30 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="25" customHeight="1">
@@ -7855,7 +7833,7 @@
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
   </mergeCells>
-  <phoneticPr fontId="75" type="noConversion"/>
+  <phoneticPr fontId="74" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7894,20 +7872,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -7937,15 +7915,15 @@
         <v>92</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -7976,13 +7954,13 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="82" t="s">
+      <c r="F6" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -8020,16 +7998,16 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="81" t="s">
+      <c r="F8" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="78"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="85">
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="78">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>4021</v>
       </c>
-      <c r="J8" s="86"/>
+      <c r="J8" s="79"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -8067,16 +8045,16 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="81" t="s">
+      <c r="F10" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="85">
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="78">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>2579.2479999999996</v>
       </c>
-      <c r="J10" s="86"/>
+      <c r="J10" s="79"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -8128,13 +8106,13 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="82" t="s">
+      <c r="F13" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="75"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -8152,11 +8130,11 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
       <c r="I14" s="29">
         <f>Samples!F165</f>
         <v>3400</v>
@@ -8181,11 +8159,11 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="78" t="s">
+      <c r="F15" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
       <c r="I15" s="30">
         <f>Samples!I165</f>
         <v>3173.3333333333335</v>
@@ -8205,11 +8183,11 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="80" t="s">
+      <c r="F16" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
       <c r="I16" s="29">
         <f>Samples!J165</f>
         <v>1500</v>
@@ -8229,11 +8207,11 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="81" t="s">
+      <c r="F17" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="82"/>
       <c r="I17" s="30">
         <f>Samples!L165</f>
         <v>4673.3333333333339</v>
@@ -8275,11 +8253,11 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="76" t="s">
+      <c r="F19" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
       <c r="I19" s="29">
         <f>Samples!M165</f>
         <v>2800</v>
@@ -8299,11 +8277,11 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="78" t="s">
+      <c r="F20" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="82"/>
       <c r="I20" s="30">
         <f>Samples!P165</f>
         <v>2497.6</v>
@@ -8340,11 +8318,11 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="80" t="s">
+      <c r="F22" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
       <c r="I22" s="32">
         <f>Samples!G165</f>
         <v>0.1</v>
@@ -8364,11 +8342,11 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="81" t="s">
+      <c r="F23" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
+      <c r="G23" s="82"/>
+      <c r="H23" s="82"/>
       <c r="I23" s="33">
         <f>Samples!K165</f>
         <v>0.45</v>
@@ -8388,11 +8366,11 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="76" t="s">
+      <c r="F24" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
       <c r="I24" s="32">
         <f>Samples!N165</f>
         <v>0.27</v>
@@ -8442,20 +8420,20 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="75"/>
-      <c r="D27" s="75"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="75"/>
-      <c r="J27" s="75"/>
-      <c r="K27" s="75"/>
-      <c r="L27" s="75"/>
-      <c r="M27" s="75"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="85"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="85"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
@@ -8716,6 +8694,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -8723,19 +8712,8 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
   </mergeCells>
-  <phoneticPr fontId="75" type="noConversion"/>
+  <phoneticPr fontId="74" type="noConversion"/>
   <dataValidations count="5">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -8790,20 +8768,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -8830,18 +8808,18 @@
         <v>11</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -8871,15 +8849,15 @@
         <v>-10</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -9463,18 +9441,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="87"/>
-      <c r="G41" s="87"/>
-      <c r="H41" s="87"/>
-      <c r="I41" s="87"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="87"/>
+      <c r="B41" s="86"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="86"/>
+      <c r="E41" s="86"/>
+      <c r="F41" s="86"/>
+      <c r="G41" s="86"/>
+      <c r="H41" s="86"/>
+      <c r="I41" s="86"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="86"/>
+      <c r="L41" s="86"/>
+      <c r="M41" s="86"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -9502,7 +9480,7 @@
     <mergeCell ref="E6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="75" type="noConversion"/>
+  <phoneticPr fontId="74" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -9548,20 +9526,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -9588,18 +9566,18 @@
         <v>11</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -9629,15 +9607,15 @@
         <v>-8</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -10221,18 +10199,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="87"/>
-      <c r="G41" s="87"/>
-      <c r="H41" s="87"/>
-      <c r="I41" s="87"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="87"/>
+      <c r="B41" s="86"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="86"/>
+      <c r="E41" s="86"/>
+      <c r="F41" s="86"/>
+      <c r="G41" s="86"/>
+      <c r="H41" s="86"/>
+      <c r="I41" s="86"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="86"/>
+      <c r="L41" s="86"/>
+      <c r="M41" s="86"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -10260,7 +10238,7 @@
     <mergeCell ref="E6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="75" type="noConversion"/>
+  <phoneticPr fontId="74" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -10306,20 +10284,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -10346,18 +10324,18 @@
         <v>11</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -10380,18 +10358,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -10975,18 +10953,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="87"/>
-      <c r="G41" s="87"/>
-      <c r="H41" s="87"/>
-      <c r="I41" s="87"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="87"/>
+      <c r="B41" s="86"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="86"/>
+      <c r="E41" s="86"/>
+      <c r="F41" s="86"/>
+      <c r="G41" s="86"/>
+      <c r="H41" s="86"/>
+      <c r="I41" s="86"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="86"/>
+      <c r="L41" s="86"/>
+      <c r="M41" s="86"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -11014,7 +10992,7 @@
     <mergeCell ref="B6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="75" type="noConversion"/>
+  <phoneticPr fontId="74" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -11056,20 +11034,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -11096,18 +11074,18 @@
         <v>11</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -11130,18 +11108,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -11725,18 +11703,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="87"/>
-      <c r="G41" s="87"/>
-      <c r="H41" s="87"/>
-      <c r="I41" s="87"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="87"/>
+      <c r="B41" s="86"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="86"/>
+      <c r="E41" s="86"/>
+      <c r="F41" s="86"/>
+      <c r="G41" s="86"/>
+      <c r="H41" s="86"/>
+      <c r="I41" s="86"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="86"/>
+      <c r="L41" s="86"/>
+      <c r="M41" s="86"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -11764,7 +11742,7 @@
     <mergeCell ref="B6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="75" type="noConversion"/>
+  <phoneticPr fontId="74" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -11810,40 +11788,40 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -11867,21 +11845,21 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="83" t="s">
+      <c r="D5" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="83" t="s">
+      <c r="J5" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="83"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="83"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -12515,73 +12493,73 @@
     </row>
     <row r="22" spans="1:15" ht="32" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="82" t="s">
+      <c r="B22" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="83"/>
-      <c r="G22" s="83"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="83"/>
-      <c r="J22" s="83"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="83"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="75"/>
+      <c r="L22" s="75"/>
+      <c r="M22" s="75"/>
+      <c r="N22" s="75"/>
       <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:15" ht="29" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="80" t="s">
+      <c r="B23" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="77"/>
+      <c r="C23" s="81"/>
       <c r="D23" s="26">
         <v>24</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="94" t="s">
+      <c r="F23" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="95"/>
-      <c r="H23" s="95"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="95"/>
-      <c r="K23" s="95"/>
-      <c r="L23" s="95"/>
-      <c r="M23" s="95"/>
-      <c r="N23" s="95"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="90"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="90"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="90"/>
       <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:15" ht="29" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="81" t="s">
+      <c r="B24" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="79"/>
+      <c r="C24" s="82"/>
       <c r="D24" s="28">
         <v>20</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="95"/>
-      <c r="G24" s="95"/>
-      <c r="H24" s="95"/>
-      <c r="I24" s="95"/>
-      <c r="J24" s="95"/>
-      <c r="K24" s="95"/>
-      <c r="L24" s="95"/>
-      <c r="M24" s="95"/>
-      <c r="N24" s="95"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="90"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="90"/>
       <c r="O24" s="2"/>
     </row>
     <row r="25" spans="1:15" ht="29" customHeight="1">
       <c r="A25" s="2"/>
-      <c r="B25" s="80" t="s">
+      <c r="B25" s="83" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="77"/>
+      <c r="C25" s="81"/>
       <c r="D25" s="26">
         <v>40</v>
       </c>
@@ -12599,33 +12577,33 @@
     </row>
     <row r="26" spans="1:15" ht="29" customHeight="1">
       <c r="A26" s="2"/>
-      <c r="B26" s="78" t="s">
+      <c r="B26" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="79"/>
+      <c r="C26" s="82"/>
       <c r="D26" s="28">
         <v>40</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="96" t="s">
+      <c r="F26" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="G26" s="93"/>
-      <c r="H26" s="93"/>
-      <c r="I26" s="93"/>
-      <c r="J26" s="93"/>
-      <c r="K26" s="93"/>
-      <c r="L26" s="93"/>
-      <c r="M26" s="93"/>
-      <c r="N26" s="93"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="88"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="88"/>
+      <c r="K26" s="88"/>
+      <c r="L26" s="88"/>
+      <c r="M26" s="88"/>
+      <c r="N26" s="88"/>
       <c r="O26" s="2"/>
     </row>
     <row r="27" spans="1:15" ht="29" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="81" t="s">
+      <c r="B27" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="79"/>
+      <c r="C27" s="82"/>
       <c r="D27" s="28">
         <v>10</v>
       </c>
@@ -12643,140 +12621,140 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="89" t="s">
+      <c r="B28" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="90"/>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="90"/>
-      <c r="J28" s="90"/>
-      <c r="K28" s="90"/>
-      <c r="L28" s="90"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="90"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="94"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="94"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="94"/>
+      <c r="J28" s="94"/>
+      <c r="K28" s="94"/>
+      <c r="L28" s="94"/>
+      <c r="M28" s="94"/>
+      <c r="N28" s="94"/>
       <c r="O28" s="2"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="2"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="88"/>
-      <c r="N29" s="88"/>
+      <c r="B29" s="92"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="92"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="92"/>
+      <c r="J29" s="92"/>
+      <c r="K29" s="92"/>
+      <c r="L29" s="92"/>
+      <c r="M29" s="92"/>
+      <c r="N29" s="92"/>
       <c r="O29" s="2"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="91"/>
-      <c r="C30" s="91"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="91"/>
-      <c r="F30" s="91"/>
-      <c r="G30" s="91"/>
-      <c r="H30" s="91"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="91"/>
-      <c r="K30" s="91"/>
-      <c r="L30" s="91"/>
-      <c r="M30" s="91"/>
-      <c r="N30" s="91"/>
+      <c r="B30" s="95"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="95"/>
+      <c r="N30" s="95"/>
       <c r="O30" s="2"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="88"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
-      <c r="L31" s="88"/>
-      <c r="M31" s="88"/>
-      <c r="N31" s="88"/>
+      <c r="B31" s="92"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="92"/>
+      <c r="K31" s="92"/>
+      <c r="L31" s="92"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
       <c r="O31" s="2"/>
     </row>
     <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="2"/>
-      <c r="B32" s="88"/>
-      <c r="C32" s="88"/>
-      <c r="D32" s="88"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="88"/>
-      <c r="G32" s="88"/>
-      <c r="H32" s="88"/>
-      <c r="I32" s="88"/>
-      <c r="J32" s="88"/>
-      <c r="K32" s="88"/>
-      <c r="L32" s="88"/>
-      <c r="M32" s="88"/>
-      <c r="N32" s="88"/>
+      <c r="B32" s="92"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="92"/>
+      <c r="J32" s="92"/>
+      <c r="K32" s="92"/>
+      <c r="L32" s="92"/>
+      <c r="M32" s="92"/>
+      <c r="N32" s="92"/>
       <c r="O32" s="2"/>
     </row>
     <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="88"/>
-      <c r="C33" s="88"/>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="88"/>
-      <c r="J33" s="88"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="88"/>
-      <c r="N33" s="88"/>
+      <c r="B33" s="92"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
       <c r="O33" s="2"/>
     </row>
     <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="88"/>
-      <c r="C34" s="88"/>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="88"/>
-      <c r="G34" s="88"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="88"/>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="88"/>
-      <c r="M34" s="88"/>
-      <c r="N34" s="88"/>
+      <c r="B34" s="92"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="92"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="92"/>
+      <c r="J34" s="92"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="92"/>
+      <c r="M34" s="92"/>
+      <c r="N34" s="92"/>
       <c r="O34" s="2"/>
     </row>
     <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="2"/>
-      <c r="B35" s="88"/>
-      <c r="C35" s="88"/>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="88"/>
-      <c r="G35" s="88"/>
-      <c r="H35" s="88"/>
-      <c r="I35" s="88"/>
-      <c r="J35" s="88"/>
-      <c r="K35" s="88"/>
-      <c r="L35" s="88"/>
-      <c r="M35" s="88"/>
-      <c r="N35" s="88"/>
+      <c r="B35" s="92"/>
+      <c r="C35" s="92"/>
+      <c r="D35" s="92"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="92"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="92"/>
+      <c r="L35" s="92"/>
+      <c r="M35" s="92"/>
+      <c r="N35" s="92"/>
       <c r="O35" s="2"/>
     </row>
     <row r="36" spans="1:15" ht="23.15" customHeight="1">
@@ -12883,6 +12861,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -12895,16 +12881,8 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
   </mergeCells>
-  <phoneticPr fontId="75" type="noConversion"/>
+  <phoneticPr fontId="74" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13082,23 +13060,23 @@
       </c>
       <c r="F5" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q5)+(INDEX(Parameters!$J$10:$N$10,1,Q5+1)-INDEX(Parameters!$J$10:$N$10,1,Q5))*T5,INDEX(Parameters!$D$10:$H$10,1,Q5)+(INDEX(Parameters!$D$10:$H$10,1,Q5+1)-INDEX(Parameters!$D$10:$H$10,1,Q5))*T5)</f>
-        <v>2700</v>
+        <v>1800</v>
       </c>
       <c r="G5" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R5)+(INDEX(Parameters!$J$11:$N$11,1,R5+1)-INDEX(Parameters!$J$11:$N$11,1,R5))*U5,INDEX(Parameters!$D$11:$H$11,1,Q5)+(INDEX(Parameters!$D$11:$H$11,1,Q5+1)-INDEX(Parameters!$D$11:$H$11,1,Q5))*T5)</f>
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="H5" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q5)+(INDEX(Parameters!$J$12:$N$12,1,Q5+1)-INDEX(Parameters!$J$12:$N$12,1,Q5))*T5,INDEX(Parameters!$D$12:$H$12,1,Q5)+(INDEX(Parameters!$D$12:$H$12,1,Q5+1)-INDEX(Parameters!$D$12:$H$12,1,Q5))*T5)</f>
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="I5" s="42">
         <f>F5*H5</f>
-        <v>1836.0000000000002</v>
+        <v>1800</v>
       </c>
       <c r="J5" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="K5" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
@@ -13106,23 +13084,23 @@
       </c>
       <c r="L5" s="42">
         <f>I5+J5</f>
-        <v>2086</v>
+        <v>3300</v>
       </c>
       <c r="M5" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="N5" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S5)+(INDEX(Parameters!$J$18:$N$18,1,S5+1)-INDEX(Parameters!$J$18:$N$18,1,S5))*V5,INDEX(Parameters!$D$18:$H$18,1,S5)+(INDEX(Parameters!$D$18:$H$18,1,S5+1)-INDEX(Parameters!$D$18:$H$18,1,S5))*V5)</f>
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="O5" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S5)+(INDEX(Parameters!$J$19:$N$19,1,S5+1)-INDEX(Parameters!$J$19:$N$19,1,S5))*V5,INDEX(Parameters!$D$19:$H$19,1,S5)+(INDEX(Parameters!$D$19:$H$19,1,S5+1)-INDEX(Parameters!$D$19:$H$19,1,S5))*V5)</f>
-        <v>0.76</v>
+        <v>0.94</v>
       </c>
       <c r="P5" s="43">
         <f>M5*O5</f>
-        <v>2280</v>
+        <v>1880</v>
       </c>
       <c r="Q5" s="43">
         <f>MIN(4,MAX(1,INT((1+C5/Parameters!$D$23)*4)+1))</f>
@@ -13169,23 +13147,23 @@
       </c>
       <c r="F6" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q6)+(INDEX(Parameters!$J$10:$N$10,1,Q6+1)-INDEX(Parameters!$J$10:$N$10,1,Q6))*T6,INDEX(Parameters!$D$10:$H$10,1,Q6)+(INDEX(Parameters!$D$10:$H$10,1,Q6+1)-INDEX(Parameters!$D$10:$H$10,1,Q6))*T6)</f>
-        <v>3150</v>
+        <v>2400</v>
       </c>
       <c r="G6" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R6)+(INDEX(Parameters!$J$11:$N$11,1,R6+1)-INDEX(Parameters!$J$11:$N$11,1,R6))*U6,INDEX(Parameters!$D$11:$H$11,1,Q6)+(INDEX(Parameters!$D$11:$H$11,1,Q6+1)-INDEX(Parameters!$D$11:$H$11,1,Q6))*T6)</f>
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="H6" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q6)+(INDEX(Parameters!$J$12:$N$12,1,Q6+1)-INDEX(Parameters!$J$12:$N$12,1,Q6))*T6,INDEX(Parameters!$D$12:$H$12,1,Q6)+(INDEX(Parameters!$D$12:$H$12,1,Q6+1)-INDEX(Parameters!$D$12:$H$12,1,Q6))*T6)</f>
-        <v>0.66</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I6" s="44">
         <f>F6*H6</f>
-        <v>2079</v>
+        <v>2340</v>
       </c>
       <c r="J6" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="K6" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
@@ -13193,23 +13171,23 @@
       </c>
       <c r="L6" s="44">
         <f>I6+J6</f>
-        <v>2329</v>
+        <v>3840</v>
       </c>
       <c r="M6" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="N6" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S6)+(INDEX(Parameters!$J$18:$N$18,1,S6+1)-INDEX(Parameters!$J$18:$N$18,1,S6))*V6,INDEX(Parameters!$D$18:$H$18,1,S6)+(INDEX(Parameters!$D$18:$H$18,1,S6+1)-INDEX(Parameters!$D$18:$H$18,1,S6))*V6)</f>
-        <v>0.22500000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="O6" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S6)+(INDEX(Parameters!$J$19:$N$19,1,S6+1)-INDEX(Parameters!$J$19:$N$19,1,S6))*V6,INDEX(Parameters!$D$19:$H$19,1,S6)+(INDEX(Parameters!$D$19:$H$19,1,S6+1)-INDEX(Parameters!$D$19:$H$19,1,S6))*V6)</f>
-        <v>0.72</v>
+        <v>0.90999999999999992</v>
       </c>
       <c r="P6" s="45">
         <f>M6*O6</f>
-        <v>2520</v>
+        <v>2275</v>
       </c>
       <c r="Q6" s="45">
         <f>MIN(4,MAX(1,INT((1+C6/Parameters!$D$23)*4)+1))</f>
@@ -13256,23 +13234,23 @@
       </c>
       <c r="F7" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q7)+(INDEX(Parameters!$J$10:$N$10,1,Q7+1)-INDEX(Parameters!$J$10:$N$10,1,Q7))*T7,INDEX(Parameters!$D$10:$H$10,1,Q7)+(INDEX(Parameters!$D$10:$H$10,1,Q7+1)-INDEX(Parameters!$D$10:$H$10,1,Q7))*T7)</f>
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="G7" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R7)+(INDEX(Parameters!$J$11:$N$11,1,R7+1)-INDEX(Parameters!$J$11:$N$11,1,R7))*U7,INDEX(Parameters!$D$11:$H$11,1,Q7)+(INDEX(Parameters!$D$11:$H$11,1,Q7+1)-INDEX(Parameters!$D$11:$H$11,1,Q7))*T7)</f>
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="H7" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q7)+(INDEX(Parameters!$J$12:$N$12,1,Q7+1)-INDEX(Parameters!$J$12:$N$12,1,Q7))*T7,INDEX(Parameters!$D$12:$H$12,1,Q7)+(INDEX(Parameters!$D$12:$H$12,1,Q7+1)-INDEX(Parameters!$D$12:$H$12,1,Q7))*T7)</f>
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="I7" s="42">
         <f>F7*H7</f>
-        <v>2304</v>
+        <v>2850</v>
       </c>
       <c r="J7" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="K7" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
@@ -13280,23 +13258,23 @@
       </c>
       <c r="L7" s="42">
         <f>I7+J7</f>
-        <v>2554</v>
+        <v>4350</v>
       </c>
       <c r="M7" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="N7" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S7)+(INDEX(Parameters!$J$18:$N$18,1,S7+1)-INDEX(Parameters!$J$18:$N$18,1,S7))*V7,INDEX(Parameters!$D$18:$H$18,1,S7)+(INDEX(Parameters!$D$18:$H$18,1,S7+1)-INDEX(Parameters!$D$18:$H$18,1,S7))*V7)</f>
-        <v>0.25</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O7" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S7)+(INDEX(Parameters!$J$19:$N$19,1,S7+1)-INDEX(Parameters!$J$19:$N$19,1,S7))*V7,INDEX(Parameters!$D$19:$H$19,1,S7)+(INDEX(Parameters!$D$19:$H$19,1,S7+1)-INDEX(Parameters!$D$19:$H$19,1,S7))*V7)</f>
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="P7" s="43">
         <f>M7*O7</f>
-        <v>2720</v>
+        <v>2640</v>
       </c>
       <c r="Q7" s="43">
         <f>MIN(4,MAX(1,INT((1+C7/Parameters!$D$23)*4)+1))</f>
@@ -13343,23 +13321,23 @@
       </c>
       <c r="F8" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q8)+(INDEX(Parameters!$J$10:$N$10,1,Q8+1)-INDEX(Parameters!$J$10:$N$10,1,Q8))*T8,INDEX(Parameters!$D$10:$H$10,1,Q8)+(INDEX(Parameters!$D$10:$H$10,1,Q8+1)-INDEX(Parameters!$D$10:$H$10,1,Q8))*T8)</f>
-        <v>4050</v>
+        <v>3600</v>
       </c>
       <c r="G8" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R8)+(INDEX(Parameters!$J$11:$N$11,1,R8+1)-INDEX(Parameters!$J$11:$N$11,1,R8))*U8,INDEX(Parameters!$D$11:$H$11,1,Q8)+(INDEX(Parameters!$D$11:$H$11,1,Q8+1)-INDEX(Parameters!$D$11:$H$11,1,Q8))*T8)</f>
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="H8" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q8)+(INDEX(Parameters!$J$12:$N$12,1,Q8+1)-INDEX(Parameters!$J$12:$N$12,1,Q8))*T8,INDEX(Parameters!$D$12:$H$12,1,Q8)+(INDEX(Parameters!$D$12:$H$12,1,Q8+1)-INDEX(Parameters!$D$12:$H$12,1,Q8))*T8)</f>
-        <v>0.62</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="I8" s="44">
         <f>F8*H8</f>
-        <v>2511</v>
+        <v>3330</v>
       </c>
       <c r="J8" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="K8" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
@@ -13367,23 +13345,23 @@
       </c>
       <c r="L8" s="44">
         <f>I8+J8</f>
-        <v>2761</v>
+        <v>4830</v>
       </c>
       <c r="M8" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="N8" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S8)+(INDEX(Parameters!$J$18:$N$18,1,S8+1)-INDEX(Parameters!$J$18:$N$18,1,S8))*V8,INDEX(Parameters!$D$18:$H$18,1,S8)+(INDEX(Parameters!$D$18:$H$18,1,S8+1)-INDEX(Parameters!$D$18:$H$18,1,S8))*V8)</f>
-        <v>0.27500000000000002</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="O8" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S8)+(INDEX(Parameters!$J$19:$N$19,1,S8+1)-INDEX(Parameters!$J$19:$N$19,1,S8))*V8,INDEX(Parameters!$D$19:$H$19,1,S8)+(INDEX(Parameters!$D$19:$H$19,1,S8+1)-INDEX(Parameters!$D$19:$H$19,1,S8))*V8)</f>
-        <v>0.64</v>
+        <v>0.85</v>
       </c>
       <c r="P8" s="45">
         <f>M8*O8</f>
-        <v>2880</v>
+        <v>2975</v>
       </c>
       <c r="Q8" s="45">
         <f>MIN(4,MAX(1,INT((1+C8/Parameters!$D$23)*4)+1))</f>
@@ -13430,23 +13408,23 @@
       </c>
       <c r="F9" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q9)+(INDEX(Parameters!$J$10:$N$10,1,Q9+1)-INDEX(Parameters!$J$10:$N$10,1,Q9))*T9,INDEX(Parameters!$D$10:$H$10,1,Q9)+(INDEX(Parameters!$D$10:$H$10,1,Q9+1)-INDEX(Parameters!$D$10:$H$10,1,Q9))*T9)</f>
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="G9" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R9)+(INDEX(Parameters!$J$11:$N$11,1,R9+1)-INDEX(Parameters!$J$11:$N$11,1,R9))*U9,INDEX(Parameters!$D$11:$H$11,1,Q9)+(INDEX(Parameters!$D$11:$H$11,1,Q9+1)-INDEX(Parameters!$D$11:$H$11,1,Q9))*T9)</f>
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="H9" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q9)+(INDEX(Parameters!$J$12:$N$12,1,Q9+1)-INDEX(Parameters!$J$12:$N$12,1,Q9))*T9,INDEX(Parameters!$D$12:$H$12,1,Q9)+(INDEX(Parameters!$D$12:$H$12,1,Q9+1)-INDEX(Parameters!$D$12:$H$12,1,Q9))*T9)</f>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I9" s="42">
         <f>F9*H9</f>
-        <v>2700</v>
+        <v>3780</v>
       </c>
       <c r="J9" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="K9" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
@@ -13454,23 +13432,23 @@
       </c>
       <c r="L9" s="42">
         <f>I9+J9</f>
-        <v>2950</v>
+        <v>5280</v>
       </c>
       <c r="M9" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="N9" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S9)+(INDEX(Parameters!$J$18:$N$18,1,S9+1)-INDEX(Parameters!$J$18:$N$18,1,S9))*V9,INDEX(Parameters!$D$18:$H$18,1,S9)+(INDEX(Parameters!$D$18:$H$18,1,S9+1)-INDEX(Parameters!$D$18:$H$18,1,S9))*V9)</f>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="O9" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S9)+(INDEX(Parameters!$J$19:$N$19,1,S9+1)-INDEX(Parameters!$J$19:$N$19,1,S9))*V9,INDEX(Parameters!$D$19:$H$19,1,S9)+(INDEX(Parameters!$D$19:$H$19,1,S9+1)-INDEX(Parameters!$D$19:$H$19,1,S9))*V9)</f>
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="P9" s="43">
         <f>M9*O9</f>
-        <v>3000</v>
+        <v>3280</v>
       </c>
       <c r="Q9" s="43">
         <f>MIN(4,MAX(1,INT((1+C9/Parameters!$D$23)*4)+1))</f>
@@ -13658,23 +13636,23 @@
       </c>
       <c r="C15" s="49">
         <f t="shared" si="0"/>
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="D15" s="49">
         <f t="shared" si="1"/>
-        <v>157.5</v>
+        <v>120</v>
       </c>
       <c r="E15" s="49">
         <f t="shared" si="2"/>
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F15" s="49">
         <f t="shared" si="3"/>
-        <v>202.5</v>
+        <v>180</v>
       </c>
       <c r="G15" s="49">
         <f t="shared" si="4"/>
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -13699,23 +13677,23 @@
       </c>
       <c r="C16" s="48">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="D16" s="48">
         <f t="shared" si="1"/>
-        <v>315</v>
+        <v>240</v>
       </c>
       <c r="E16" s="48">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="F16" s="48">
         <f t="shared" si="3"/>
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="G16" s="48">
         <f t="shared" si="4"/>
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -13740,23 +13718,23 @@
       </c>
       <c r="C17" s="49">
         <f t="shared" si="0"/>
-        <v>405</v>
+        <v>270</v>
       </c>
       <c r="D17" s="49">
         <f t="shared" si="1"/>
-        <v>472.5</v>
+        <v>357</v>
       </c>
       <c r="E17" s="49">
         <f t="shared" si="2"/>
-        <v>540</v>
+        <v>442.5</v>
       </c>
       <c r="F17" s="49">
         <f t="shared" si="3"/>
-        <v>607.5</v>
+        <v>526.5</v>
       </c>
       <c r="G17" s="49">
         <f t="shared" si="4"/>
-        <v>675</v>
+        <v>609</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -13781,23 +13759,23 @@
       </c>
       <c r="C18" s="48">
         <f t="shared" si="0"/>
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="D18" s="48">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>474</v>
       </c>
       <c r="E18" s="48">
         <f t="shared" si="2"/>
-        <v>720</v>
+        <v>585</v>
       </c>
       <c r="F18" s="48">
         <f t="shared" si="3"/>
-        <v>810</v>
+        <v>693</v>
       </c>
       <c r="G18" s="48">
         <f t="shared" si="4"/>
-        <v>900</v>
+        <v>798</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -13822,23 +13800,23 @@
       </c>
       <c r="C19" s="49">
         <f t="shared" si="0"/>
-        <v>675</v>
+        <v>450</v>
       </c>
       <c r="D19" s="49">
         <f t="shared" si="1"/>
-        <v>787.5</v>
+        <v>591</v>
       </c>
       <c r="E19" s="49">
         <f t="shared" si="2"/>
-        <v>900</v>
+        <v>727.5</v>
       </c>
       <c r="F19" s="49">
         <f t="shared" si="3"/>
-        <v>1012.5</v>
+        <v>859.5</v>
       </c>
       <c r="G19" s="49">
         <f t="shared" si="4"/>
-        <v>1125</v>
+        <v>987</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -13863,23 +13841,23 @@
       </c>
       <c r="C20" s="48">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>540</v>
       </c>
       <c r="D20" s="48">
         <f t="shared" si="1"/>
-        <v>945</v>
+        <v>708</v>
       </c>
       <c r="E20" s="48">
         <f t="shared" si="2"/>
-        <v>1080</v>
+        <v>870</v>
       </c>
       <c r="F20" s="48">
         <f t="shared" si="3"/>
-        <v>1215</v>
+        <v>1026</v>
       </c>
       <c r="G20" s="48">
         <f t="shared" si="4"/>
-        <v>1350</v>
+        <v>1176</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -13904,23 +13882,23 @@
       </c>
       <c r="C21" s="49">
         <f t="shared" si="0"/>
-        <v>919.07999999999993</v>
+        <v>630</v>
       </c>
       <c r="D21" s="49">
         <f t="shared" si="1"/>
-        <v>1070.3699999999999</v>
+        <v>824.99999999999989</v>
       </c>
       <c r="E21" s="49">
         <f t="shared" si="2"/>
-        <v>1221.1199999999999</v>
+        <v>1012.4999999999999</v>
       </c>
       <c r="F21" s="49">
         <f t="shared" si="3"/>
-        <v>1371.33</v>
+        <v>1192.5</v>
       </c>
       <c r="G21" s="49">
         <f t="shared" si="4"/>
-        <v>1521</v>
+        <v>1365</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -13945,23 +13923,23 @@
       </c>
       <c r="C22" s="48">
         <f t="shared" si="0"/>
-        <v>1010.8800000000001</v>
+        <v>720.00000000000011</v>
       </c>
       <c r="D22" s="48">
         <f t="shared" si="1"/>
-        <v>1174.32</v>
+        <v>942.00000000000011</v>
       </c>
       <c r="E22" s="48">
         <f t="shared" si="2"/>
-        <v>1336.3200000000002</v>
+        <v>1155</v>
       </c>
       <c r="F22" s="48">
         <f t="shared" si="3"/>
-        <v>1496.88</v>
+        <v>1359</v>
       </c>
       <c r="G22" s="48">
         <f t="shared" si="4"/>
-        <v>1656</v>
+        <v>1554.0000000000002</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -13986,23 +13964,23 @@
       </c>
       <c r="C23" s="49">
         <f t="shared" si="0"/>
-        <v>1102.68</v>
+        <v>810</v>
       </c>
       <c r="D23" s="49">
         <f t="shared" si="1"/>
-        <v>1278.27</v>
+        <v>1059</v>
       </c>
       <c r="E23" s="49">
         <f t="shared" si="2"/>
-        <v>1451.52</v>
+        <v>1297.5</v>
       </c>
       <c r="F23" s="49">
         <f t="shared" si="3"/>
-        <v>1622.43</v>
+        <v>1525.5</v>
       </c>
       <c r="G23" s="49">
         <f t="shared" si="4"/>
-        <v>1791</v>
+        <v>1743</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -14027,23 +14005,23 @@
       </c>
       <c r="C24" s="48">
         <f t="shared" si="0"/>
-        <v>1206.98</v>
+        <v>975</v>
       </c>
       <c r="D24" s="48">
         <f t="shared" si="1"/>
-        <v>1394.72</v>
+        <v>1251</v>
       </c>
       <c r="E24" s="48">
         <f t="shared" si="2"/>
-        <v>1579.22</v>
+        <v>1515</v>
       </c>
       <c r="F24" s="48">
         <f t="shared" si="3"/>
-        <v>1760.48</v>
+        <v>1767</v>
       </c>
       <c r="G24" s="48">
         <f t="shared" si="4"/>
-        <v>1938.5</v>
+        <v>2007</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -14068,23 +14046,23 @@
       </c>
       <c r="C25" s="49">
         <f t="shared" si="0"/>
-        <v>1311.2800000000002</v>
+        <v>1140.0000000000002</v>
       </c>
       <c r="D25" s="49">
         <f t="shared" si="1"/>
-        <v>1511.17</v>
+        <v>1443.0000000000002</v>
       </c>
       <c r="E25" s="49">
         <f t="shared" si="2"/>
-        <v>1706.92</v>
+        <v>1732.5000000000002</v>
       </c>
       <c r="F25" s="49">
         <f t="shared" si="3"/>
-        <v>1898.5300000000002</v>
+        <v>2008.5000000000002</v>
       </c>
       <c r="G25" s="49">
         <f t="shared" si="4"/>
-        <v>2086</v>
+        <v>2271</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -14109,23 +14087,23 @@
       </c>
       <c r="C26" s="48">
         <f t="shared" si="0"/>
-        <v>1415.58</v>
+        <v>1305</v>
       </c>
       <c r="D26" s="48">
         <f t="shared" si="1"/>
-        <v>1627.62</v>
+        <v>1635</v>
       </c>
       <c r="E26" s="48">
         <f t="shared" si="2"/>
-        <v>1834.62</v>
+        <v>1950</v>
       </c>
       <c r="F26" s="48">
         <f t="shared" si="3"/>
-        <v>2036.58</v>
+        <v>2250</v>
       </c>
       <c r="G26" s="48">
         <f t="shared" si="4"/>
-        <v>2233.5</v>
+        <v>2535</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -14150,23 +14128,23 @@
       </c>
       <c r="C27" s="49">
         <f t="shared" si="0"/>
-        <v>1519.88</v>
+        <v>1470</v>
       </c>
       <c r="D27" s="49">
         <f t="shared" si="1"/>
-        <v>1744.0700000000002</v>
+        <v>1827</v>
       </c>
       <c r="E27" s="49">
         <f t="shared" si="2"/>
-        <v>1962.3200000000002</v>
+        <v>2167.5</v>
       </c>
       <c r="F27" s="49">
         <f t="shared" si="3"/>
-        <v>2174.63</v>
+        <v>2491.5</v>
       </c>
       <c r="G27" s="49">
         <f t="shared" si="4"/>
-        <v>2381</v>
+        <v>2799</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -14191,23 +14169,23 @@
       </c>
       <c r="C28" s="48">
         <f t="shared" si="0"/>
-        <v>1624.1799999999998</v>
+        <v>1635</v>
       </c>
       <c r="D28" s="48">
         <f t="shared" si="1"/>
-        <v>1860.52</v>
+        <v>2019</v>
       </c>
       <c r="E28" s="48">
         <f t="shared" si="2"/>
-        <v>2090.02</v>
+        <v>2385</v>
       </c>
       <c r="F28" s="48">
         <f t="shared" si="3"/>
-        <v>2312.6799999999998</v>
+        <v>2733</v>
       </c>
       <c r="G28" s="48">
         <f t="shared" si="4"/>
-        <v>2528.5</v>
+        <v>3063</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -14232,23 +14210,23 @@
       </c>
       <c r="C29" s="49">
         <f t="shared" si="0"/>
-        <v>1728.48</v>
+        <v>1800</v>
       </c>
       <c r="D29" s="49">
         <f t="shared" si="1"/>
-        <v>1976.97</v>
+        <v>2211</v>
       </c>
       <c r="E29" s="49">
         <f t="shared" si="2"/>
-        <v>2217.7200000000003</v>
+        <v>2602.5</v>
       </c>
       <c r="F29" s="49">
         <f t="shared" si="3"/>
-        <v>2450.73</v>
+        <v>2974.5</v>
       </c>
       <c r="G29" s="49">
         <f t="shared" si="4"/>
-        <v>2676</v>
+        <v>3327</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -14273,23 +14251,23 @@
       </c>
       <c r="C30" s="48">
         <f t="shared" si="0"/>
-        <v>1832.7800000000002</v>
+        <v>1965.0000000000002</v>
       </c>
       <c r="D30" s="48">
         <f t="shared" si="1"/>
-        <v>2093.42</v>
+        <v>2403</v>
       </c>
       <c r="E30" s="48">
         <f t="shared" si="2"/>
-        <v>2345.42</v>
+        <v>2820</v>
       </c>
       <c r="F30" s="48">
         <f t="shared" si="3"/>
-        <v>2588.7800000000002</v>
+        <v>3216</v>
       </c>
       <c r="G30" s="48">
         <f t="shared" si="4"/>
-        <v>2823.5</v>
+        <v>3591.0000000000005</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -14314,23 +14292,23 @@
       </c>
       <c r="C31" s="49">
         <f t="shared" si="0"/>
-        <v>1937.0800000000002</v>
+        <v>2130</v>
       </c>
       <c r="D31" s="49">
         <f t="shared" si="1"/>
-        <v>2209.87</v>
+        <v>2595</v>
       </c>
       <c r="E31" s="49">
         <f t="shared" si="2"/>
-        <v>2473.12</v>
+        <v>3037.5</v>
       </c>
       <c r="F31" s="49">
         <f t="shared" si="3"/>
-        <v>2726.83</v>
+        <v>3457.5</v>
       </c>
       <c r="G31" s="49">
         <f t="shared" si="4"/>
-        <v>2971</v>
+        <v>3855</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -14355,23 +14333,23 @@
       </c>
       <c r="C32" s="48">
         <f t="shared" si="0"/>
-        <v>2041.3800000000003</v>
+        <v>2295</v>
       </c>
       <c r="D32" s="48">
         <f t="shared" si="1"/>
-        <v>2326.3200000000002</v>
+        <v>2787</v>
       </c>
       <c r="E32" s="48">
         <f t="shared" si="2"/>
-        <v>2600.8200000000002</v>
+        <v>3255</v>
       </c>
       <c r="F32" s="48">
         <f t="shared" si="3"/>
-        <v>2864.88</v>
+        <v>3699</v>
       </c>
       <c r="G32" s="48">
         <f t="shared" si="4"/>
-        <v>3118.5</v>
+        <v>4119</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -14396,23 +14374,23 @@
       </c>
       <c r="C33" s="49">
         <f t="shared" si="0"/>
-        <v>2145.6799999999998</v>
+        <v>2460</v>
       </c>
       <c r="D33" s="49">
         <f t="shared" si="1"/>
-        <v>2442.7699999999995</v>
+        <v>2979</v>
       </c>
       <c r="E33" s="49">
         <f t="shared" si="2"/>
-        <v>2728.5199999999995</v>
+        <v>3472.5</v>
       </c>
       <c r="F33" s="49">
         <f t="shared" si="3"/>
-        <v>3002.93</v>
+        <v>3940.5</v>
       </c>
       <c r="G33" s="49">
         <f t="shared" si="4"/>
-        <v>3266</v>
+        <v>4383</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -14437,23 +14415,23 @@
       </c>
       <c r="C34" s="48">
         <f t="shared" si="0"/>
-        <v>2249.98</v>
+        <v>2625</v>
       </c>
       <c r="D34" s="48">
         <f t="shared" si="1"/>
-        <v>2559.2199999999998</v>
+        <v>3171</v>
       </c>
       <c r="E34" s="48">
         <f t="shared" si="2"/>
-        <v>2856.22</v>
+        <v>3690</v>
       </c>
       <c r="F34" s="48">
         <f t="shared" si="3"/>
-        <v>3140.9799999999996</v>
+        <v>4182</v>
       </c>
       <c r="G34" s="48">
         <f t="shared" si="4"/>
-        <v>3413.5</v>
+        <v>4647</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -14772,47 +14750,47 @@
       </c>
       <c r="F45" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q45)+(INDEX(Parameters!$J$10:$N$10,1,Q45+1)-INDEX(Parameters!$J$10:$N$10,1,Q45))*T45,INDEX(Parameters!$D$10:$H$10,1,Q45)+(INDEX(Parameters!$D$10:$H$10,1,Q45+1)-INDEX(Parameters!$D$10:$H$10,1,Q45))*T45)</f>
-        <v>3900</v>
+        <v>3400</v>
       </c>
       <c r="G45" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R45)+(INDEX(Parameters!$J$11:$N$11,1,R45+1)-INDEX(Parameters!$J$11:$N$11,1,R45))*U45,INDEX(Parameters!$D$11:$H$11,1,Q45)+(INDEX(Parameters!$D$11:$H$11,1,Q45+1)-INDEX(Parameters!$D$11:$H$11,1,Q45))*T45)</f>
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="H45" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q45)+(INDEX(Parameters!$J$12:$N$12,1,Q45+1)-INDEX(Parameters!$J$12:$N$12,1,Q45))*T45,INDEX(Parameters!$D$12:$H$12,1,Q45)+(INDEX(Parameters!$D$12:$H$12,1,Q45+1)-INDEX(Parameters!$D$12:$H$12,1,Q45))*T45)</f>
-        <v>0.62666666666666671</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="I45" s="43">
         <f>F45*H45</f>
-        <v>2444</v>
+        <v>3173.3333333333335</v>
       </c>
       <c r="J45" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K45" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="L45" s="43">
         <f>I45+J45</f>
-        <v>2694</v>
+        <v>3273.3333333333335</v>
       </c>
       <c r="M45" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="N45" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S45)+(INDEX(Parameters!$J$18:$N$18,1,S45+1)-INDEX(Parameters!$J$18:$N$18,1,S45))*V45,INDEX(Parameters!$D$18:$H$18,1,S45)+(INDEX(Parameters!$D$18:$H$18,1,S45+1)-INDEX(Parameters!$D$18:$H$18,1,S45))*V45)</f>
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="O45" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S45)+(INDEX(Parameters!$J$19:$N$19,1,S45+1)-INDEX(Parameters!$J$19:$N$19,1,S45))*V45,INDEX(Parameters!$D$19:$H$19,1,S45)+(INDEX(Parameters!$D$19:$H$19,1,S45+1)-INDEX(Parameters!$D$19:$H$19,1,S45))*V45)</f>
-        <v>0.76</v>
+        <v>0.94</v>
       </c>
       <c r="P45" s="43">
         <f>M45*O45</f>
-        <v>2280</v>
+        <v>1880</v>
       </c>
       <c r="Q45" s="43">
         <f>MIN(4,MAX(1,INT((1+C45/Parameters!$D$23)*4)+1))</f>
@@ -14858,47 +14836,47 @@
       </c>
       <c r="F46" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q46)+(INDEX(Parameters!$J$10:$N$10,1,Q46+1)-INDEX(Parameters!$J$10:$N$10,1,Q46))*T46,INDEX(Parameters!$D$10:$H$10,1,Q46)+(INDEX(Parameters!$D$10:$H$10,1,Q46+1)-INDEX(Parameters!$D$10:$H$10,1,Q46))*T46)</f>
-        <v>3900</v>
+        <v>3400</v>
       </c>
       <c r="G46" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R46)+(INDEX(Parameters!$J$11:$N$11,1,R46+1)-INDEX(Parameters!$J$11:$N$11,1,R46))*U46,INDEX(Parameters!$D$11:$H$11,1,Q46)+(INDEX(Parameters!$D$11:$H$11,1,Q46+1)-INDEX(Parameters!$D$11:$H$11,1,Q46))*T46)</f>
-        <v>0.27</v>
+        <v>0.1</v>
       </c>
       <c r="H46" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q46)+(INDEX(Parameters!$J$12:$N$12,1,Q46+1)-INDEX(Parameters!$J$12:$N$12,1,Q46))*T46,INDEX(Parameters!$D$12:$H$12,1,Q46)+(INDEX(Parameters!$D$12:$H$12,1,Q46+1)-INDEX(Parameters!$D$12:$H$12,1,Q46))*T46)</f>
-        <v>0.62666666666666671</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="I46" s="45">
         <f>F46*H46</f>
-        <v>2444</v>
+        <v>3173.3333333333335</v>
       </c>
       <c r="J46" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="K46" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
-        <v>0.45</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="L46" s="45">
         <f>I46+J46</f>
-        <v>2694</v>
+        <v>3973.3333333333335</v>
       </c>
       <c r="M46" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="N46" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S46)+(INDEX(Parameters!$J$18:$N$18,1,S46+1)-INDEX(Parameters!$J$18:$N$18,1,S46))*V46,INDEX(Parameters!$D$18:$H$18,1,S46)+(INDEX(Parameters!$D$18:$H$18,1,S46+1)-INDEX(Parameters!$D$18:$H$18,1,S46))*V46)</f>
-        <v>0.22500000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="O46" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S46)+(INDEX(Parameters!$J$19:$N$19,1,S46+1)-INDEX(Parameters!$J$19:$N$19,1,S46))*V46,INDEX(Parameters!$D$19:$H$19,1,S46)+(INDEX(Parameters!$D$19:$H$19,1,S46+1)-INDEX(Parameters!$D$19:$H$19,1,S46))*V46)</f>
-        <v>0.72</v>
+        <v>0.90999999999999992</v>
       </c>
       <c r="P46" s="45">
         <f>M46*O46</f>
-        <v>2520</v>
+        <v>2275</v>
       </c>
       <c r="Q46" s="45">
         <f>MIN(4,MAX(1,INT((1+C46/Parameters!$D$23)*4)+1))</f>
@@ -14944,23 +14922,23 @@
       </c>
       <c r="F47" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q47)+(INDEX(Parameters!$J$10:$N$10,1,Q47+1)-INDEX(Parameters!$J$10:$N$10,1,Q47))*T47,INDEX(Parameters!$D$10:$H$10,1,Q47)+(INDEX(Parameters!$D$10:$H$10,1,Q47+1)-INDEX(Parameters!$D$10:$H$10,1,Q47))*T47)</f>
-        <v>3900</v>
+        <v>3400</v>
       </c>
       <c r="G47" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R47)+(INDEX(Parameters!$J$11:$N$11,1,R47+1)-INDEX(Parameters!$J$11:$N$11,1,R47))*U47,INDEX(Parameters!$D$11:$H$11,1,Q47)+(INDEX(Parameters!$D$11:$H$11,1,Q47+1)-INDEX(Parameters!$D$11:$H$11,1,Q47))*T47)</f>
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="H47" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q47)+(INDEX(Parameters!$J$12:$N$12,1,Q47+1)-INDEX(Parameters!$J$12:$N$12,1,Q47))*T47,INDEX(Parameters!$D$12:$H$12,1,Q47)+(INDEX(Parameters!$D$12:$H$12,1,Q47+1)-INDEX(Parameters!$D$12:$H$12,1,Q47))*T47)</f>
-        <v>0.62666666666666671</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="I47" s="43">
         <f>F47*H47</f>
-        <v>2444</v>
+        <v>3173.3333333333335</v>
       </c>
       <c r="J47" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="K47" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
@@ -14968,23 +14946,23 @@
       </c>
       <c r="L47" s="43">
         <f>I47+J47</f>
-        <v>2694</v>
+        <v>4673.3333333333339</v>
       </c>
       <c r="M47" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="N47" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S47)+(INDEX(Parameters!$J$18:$N$18,1,S47+1)-INDEX(Parameters!$J$18:$N$18,1,S47))*V47,INDEX(Parameters!$D$18:$H$18,1,S47)+(INDEX(Parameters!$D$18:$H$18,1,S47+1)-INDEX(Parameters!$D$18:$H$18,1,S47))*V47)</f>
-        <v>0.25</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O47" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S47)+(INDEX(Parameters!$J$19:$N$19,1,S47+1)-INDEX(Parameters!$J$19:$N$19,1,S47))*V47,INDEX(Parameters!$D$19:$H$19,1,S47)+(INDEX(Parameters!$D$19:$H$19,1,S47+1)-INDEX(Parameters!$D$19:$H$19,1,S47))*V47)</f>
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="P47" s="43">
         <f>M47*O47</f>
-        <v>2720</v>
+        <v>2640</v>
       </c>
       <c r="Q47" s="43">
         <f>MIN(4,MAX(1,INT((1+C47/Parameters!$D$23)*4)+1))</f>
@@ -15030,47 +15008,47 @@
       </c>
       <c r="F48" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q48)+(INDEX(Parameters!$J$10:$N$10,1,Q48+1)-INDEX(Parameters!$J$10:$N$10,1,Q48))*T48,INDEX(Parameters!$D$10:$H$10,1,Q48)+(INDEX(Parameters!$D$10:$H$10,1,Q48+1)-INDEX(Parameters!$D$10:$H$10,1,Q48))*T48)</f>
-        <v>3900</v>
+        <v>3400</v>
       </c>
       <c r="G48" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R48)+(INDEX(Parameters!$J$11:$N$11,1,R48+1)-INDEX(Parameters!$J$11:$N$11,1,R48))*U48,INDEX(Parameters!$D$11:$H$11,1,Q48)+(INDEX(Parameters!$D$11:$H$11,1,Q48+1)-INDEX(Parameters!$D$11:$H$11,1,Q48))*T48)</f>
-        <v>0.37</v>
+        <v>0.1</v>
       </c>
       <c r="H48" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q48)+(INDEX(Parameters!$J$12:$N$12,1,Q48+1)-INDEX(Parameters!$J$12:$N$12,1,Q48))*T48,INDEX(Parameters!$D$12:$H$12,1,Q48)+(INDEX(Parameters!$D$12:$H$12,1,Q48+1)-INDEX(Parameters!$D$12:$H$12,1,Q48))*T48)</f>
-        <v>0.62666666666666671</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="I48" s="45">
         <f>F48*H48</f>
-        <v>2444</v>
+        <v>3173.3333333333335</v>
       </c>
       <c r="J48" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>250</v>
+        <v>2200</v>
       </c>
       <c r="K48" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
-        <v>0.45</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="L48" s="45">
         <f>I48+J48</f>
-        <v>2694</v>
+        <v>5373.3333333333339</v>
       </c>
       <c r="M48" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="N48" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S48)+(INDEX(Parameters!$J$18:$N$18,1,S48+1)-INDEX(Parameters!$J$18:$N$18,1,S48))*V48,INDEX(Parameters!$D$18:$H$18,1,S48)+(INDEX(Parameters!$D$18:$H$18,1,S48+1)-INDEX(Parameters!$D$18:$H$18,1,S48))*V48)</f>
-        <v>0.27500000000000002</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="O48" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S48)+(INDEX(Parameters!$J$19:$N$19,1,S48+1)-INDEX(Parameters!$J$19:$N$19,1,S48))*V48,INDEX(Parameters!$D$19:$H$19,1,S48)+(INDEX(Parameters!$D$19:$H$19,1,S48+1)-INDEX(Parameters!$D$19:$H$19,1,S48))*V48)</f>
-        <v>0.64</v>
+        <v>0.85</v>
       </c>
       <c r="P48" s="45">
         <f>M48*O48</f>
-        <v>2880</v>
+        <v>2975</v>
       </c>
       <c r="Q48" s="45">
         <f>MIN(4,MAX(1,INT((1+C48/Parameters!$D$23)*4)+1))</f>
@@ -15116,47 +15094,47 @@
       </c>
       <c r="F49" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q49)+(INDEX(Parameters!$J$10:$N$10,1,Q49+1)-INDEX(Parameters!$J$10:$N$10,1,Q49))*T49,INDEX(Parameters!$D$10:$H$10,1,Q49)+(INDEX(Parameters!$D$10:$H$10,1,Q49+1)-INDEX(Parameters!$D$10:$H$10,1,Q49))*T49)</f>
-        <v>3900</v>
+        <v>3400</v>
       </c>
       <c r="G49" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R49)+(INDEX(Parameters!$J$11:$N$11,1,R49+1)-INDEX(Parameters!$J$11:$N$11,1,R49))*U49,INDEX(Parameters!$D$11:$H$11,1,Q49)+(INDEX(Parameters!$D$11:$H$11,1,Q49+1)-INDEX(Parameters!$D$11:$H$11,1,Q49))*T49)</f>
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="H49" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q49)+(INDEX(Parameters!$J$12:$N$12,1,Q49+1)-INDEX(Parameters!$J$12:$N$12,1,Q49))*T49,INDEX(Parameters!$D$12:$H$12,1,Q49)+(INDEX(Parameters!$D$12:$H$12,1,Q49+1)-INDEX(Parameters!$D$12:$H$12,1,Q49))*T49)</f>
-        <v>0.62666666666666671</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="I49" s="43">
         <f>F49*H49</f>
-        <v>2444</v>
+        <v>3173.3333333333335</v>
       </c>
       <c r="J49" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>250</v>
+        <v>2900</v>
       </c>
       <c r="K49" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="L49" s="43">
         <f>I49+J49</f>
-        <v>2694</v>
+        <v>6073.3333333333339</v>
       </c>
       <c r="M49" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="N49" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S49)+(INDEX(Parameters!$J$18:$N$18,1,S49+1)-INDEX(Parameters!$J$18:$N$18,1,S49))*V49,INDEX(Parameters!$D$18:$H$18,1,S49)+(INDEX(Parameters!$D$18:$H$18,1,S49+1)-INDEX(Parameters!$D$18:$H$18,1,S49))*V49)</f>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="O49" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S49)+(INDEX(Parameters!$J$19:$N$19,1,S49+1)-INDEX(Parameters!$J$19:$N$19,1,S49))*V49,INDEX(Parameters!$D$19:$H$19,1,S49)+(INDEX(Parameters!$D$19:$H$19,1,S49+1)-INDEX(Parameters!$D$19:$H$19,1,S49))*V49)</f>
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="P49" s="43">
         <f>M49*O49</f>
-        <v>3000</v>
+        <v>3280</v>
       </c>
       <c r="Q49" s="43">
         <f>MIN(4,MAX(1,INT((1+C49/Parameters!$D$23)*4)+1))</f>
@@ -15338,23 +15316,23 @@
       </c>
       <c r="C55" s="53">
         <f t="shared" si="5"/>
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="D55" s="53">
         <f t="shared" si="6"/>
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="E55" s="53">
         <f t="shared" si="7"/>
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="F55" s="53">
         <f t="shared" si="8"/>
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="G55" s="53">
         <f t="shared" si="9"/>
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
@@ -15378,23 +15356,23 @@
       </c>
       <c r="C56" s="52">
         <f t="shared" si="5"/>
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="D56" s="52">
         <f t="shared" si="6"/>
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="E56" s="52">
         <f t="shared" si="7"/>
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="F56" s="52">
         <f t="shared" si="8"/>
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="G56" s="52">
         <f t="shared" si="9"/>
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
@@ -15418,23 +15396,23 @@
       </c>
       <c r="C57" s="53">
         <f t="shared" si="5"/>
-        <v>585</v>
+        <v>498.66666666666663</v>
       </c>
       <c r="D57" s="53">
         <f t="shared" si="6"/>
-        <v>585</v>
+        <v>498.66666666666663</v>
       </c>
       <c r="E57" s="53">
         <f t="shared" si="7"/>
-        <v>585</v>
+        <v>498.66666666666663</v>
       </c>
       <c r="F57" s="53">
         <f t="shared" si="8"/>
-        <v>585</v>
+        <v>498.66666666666663</v>
       </c>
       <c r="G57" s="53">
         <f t="shared" si="9"/>
-        <v>585</v>
+        <v>498.66666666666663</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -15458,23 +15436,23 @@
       </c>
       <c r="C58" s="52">
         <f t="shared" si="5"/>
-        <v>780</v>
+        <v>657.33333333333337</v>
       </c>
       <c r="D58" s="52">
         <f t="shared" si="6"/>
-        <v>780</v>
+        <v>657.33333333333337</v>
       </c>
       <c r="E58" s="52">
         <f t="shared" si="7"/>
-        <v>780</v>
+        <v>657.33333333333337</v>
       </c>
       <c r="F58" s="52">
         <f t="shared" si="8"/>
-        <v>780</v>
+        <v>657.33333333333337</v>
       </c>
       <c r="G58" s="52">
         <f t="shared" si="9"/>
-        <v>780</v>
+        <v>657.33333333333337</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
@@ -15498,23 +15476,23 @@
       </c>
       <c r="C59" s="53">
         <f t="shared" si="5"/>
-        <v>931.31999999999994</v>
+        <v>816</v>
       </c>
       <c r="D59" s="53">
         <f t="shared" si="6"/>
-        <v>975</v>
+        <v>816</v>
       </c>
       <c r="E59" s="53">
         <f t="shared" si="7"/>
-        <v>975</v>
+        <v>816</v>
       </c>
       <c r="F59" s="53">
         <f t="shared" si="8"/>
-        <v>975</v>
+        <v>816</v>
       </c>
       <c r="G59" s="53">
         <f t="shared" si="9"/>
-        <v>975</v>
+        <v>816</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
@@ -15538,23 +15516,23 @@
       </c>
       <c r="C60" s="52">
         <f t="shared" si="5"/>
-        <v>1053.52</v>
+        <v>974.66666666666663</v>
       </c>
       <c r="D60" s="52">
         <f t="shared" si="6"/>
-        <v>1126.32</v>
+        <v>974.66666666666663</v>
       </c>
       <c r="E60" s="52">
         <f t="shared" si="7"/>
-        <v>1170</v>
+        <v>974.66666666666663</v>
       </c>
       <c r="F60" s="52">
         <f t="shared" si="8"/>
-        <v>1170</v>
+        <v>974.66666666666663</v>
       </c>
       <c r="G60" s="52">
         <f t="shared" si="9"/>
-        <v>1170</v>
+        <v>974.66666666666663</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
@@ -15578,23 +15556,23 @@
       </c>
       <c r="C61" s="53">
         <f t="shared" si="5"/>
-        <v>1175.72</v>
+        <v>1133.3333333333333</v>
       </c>
       <c r="D61" s="53">
         <f t="shared" si="6"/>
-        <v>1248.52</v>
+        <v>1133.3333333333333</v>
       </c>
       <c r="E61" s="53">
         <f t="shared" si="7"/>
-        <v>1321.32</v>
+        <v>1133.3333333333333</v>
       </c>
       <c r="F61" s="53">
         <f t="shared" si="8"/>
-        <v>1365</v>
+        <v>1133.3333333333333</v>
       </c>
       <c r="G61" s="53">
         <f t="shared" si="9"/>
-        <v>1365</v>
+        <v>1133.3333333333333</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
@@ -15618,23 +15596,23 @@
       </c>
       <c r="C62" s="52">
         <f t="shared" si="5"/>
-        <v>1297.92</v>
+        <v>1292.0000000000002</v>
       </c>
       <c r="D62" s="52">
         <f t="shared" si="6"/>
-        <v>1370.72</v>
+        <v>1292.0000000000002</v>
       </c>
       <c r="E62" s="52">
         <f t="shared" si="7"/>
-        <v>1443.52</v>
+        <v>1292.0000000000002</v>
       </c>
       <c r="F62" s="52">
         <f t="shared" si="8"/>
-        <v>1516.3200000000002</v>
+        <v>1292.0000000000002</v>
       </c>
       <c r="G62" s="52">
         <f t="shared" si="9"/>
-        <v>1560</v>
+        <v>1292.0000000000002</v>
       </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
@@ -15658,23 +15636,23 @@
       </c>
       <c r="C63" s="53">
         <f t="shared" si="5"/>
-        <v>1420.12</v>
+        <v>1451.6666666666667</v>
       </c>
       <c r="D63" s="53">
         <f t="shared" si="6"/>
-        <v>1492.92</v>
+        <v>1454.6666666666667</v>
       </c>
       <c r="E63" s="53">
         <f t="shared" si="7"/>
-        <v>1565.72</v>
+        <v>1450.6666666666667</v>
       </c>
       <c r="F63" s="53">
         <f t="shared" si="8"/>
-        <v>1638.52</v>
+        <v>1450.6666666666667</v>
       </c>
       <c r="G63" s="53">
         <f t="shared" si="9"/>
-        <v>1711.3200000000002</v>
+        <v>1450.6666666666667</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
@@ -15698,23 +15676,23 @@
       </c>
       <c r="C64" s="52">
         <f t="shared" si="5"/>
-        <v>1554.8200000000002</v>
+        <v>1615.3333333333335</v>
       </c>
       <c r="D64" s="52">
         <f t="shared" si="6"/>
-        <v>1627.62</v>
+        <v>1653.3333333333335</v>
       </c>
       <c r="E64" s="52">
         <f t="shared" si="7"/>
-        <v>1700.42</v>
+        <v>1684.3333333333335</v>
       </c>
       <c r="F64" s="52">
         <f t="shared" si="8"/>
-        <v>1773.22</v>
+        <v>1708.3333333333335</v>
       </c>
       <c r="G64" s="52">
         <f t="shared" si="9"/>
-        <v>1846.02</v>
+        <v>1725.3333333333335</v>
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
@@ -15738,23 +15716,23 @@
       </c>
       <c r="C65" s="53">
         <f t="shared" si="5"/>
-        <v>1689.5200000000002</v>
+        <v>1779.0000000000002</v>
       </c>
       <c r="D65" s="53">
         <f t="shared" si="6"/>
-        <v>1762.3200000000002</v>
+        <v>1852.0000000000002</v>
       </c>
       <c r="E65" s="53">
         <f t="shared" si="7"/>
-        <v>1835.1200000000001</v>
+        <v>1918.0000000000002</v>
       </c>
       <c r="F65" s="53">
         <f t="shared" si="8"/>
-        <v>1907.92</v>
+        <v>1977.0000000000002</v>
       </c>
       <c r="G65" s="53">
         <f t="shared" si="9"/>
-        <v>1980.7200000000003</v>
+        <v>2029.0000000000002</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -15778,23 +15756,23 @@
       </c>
       <c r="C66" s="52">
         <f t="shared" si="5"/>
-        <v>1824.22</v>
+        <v>1942.6666666666667</v>
       </c>
       <c r="D66" s="52">
         <f t="shared" si="6"/>
-        <v>1897.02</v>
+        <v>2050.6666666666665</v>
       </c>
       <c r="E66" s="52">
         <f t="shared" si="7"/>
-        <v>1969.82</v>
+        <v>2151.6666666666665</v>
       </c>
       <c r="F66" s="52">
         <f t="shared" si="8"/>
-        <v>2042.62</v>
+        <v>2245.6666666666665</v>
       </c>
       <c r="G66" s="52">
         <f t="shared" si="9"/>
-        <v>2115.42</v>
+        <v>2332.6666666666665</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -15818,23 +15796,23 @@
       </c>
       <c r="C67" s="53">
         <f t="shared" si="5"/>
-        <v>1958.92</v>
+        <v>2106.3333333333335</v>
       </c>
       <c r="D67" s="53">
         <f t="shared" si="6"/>
-        <v>2031.72</v>
+        <v>2249.3333333333335</v>
       </c>
       <c r="E67" s="53">
         <f t="shared" si="7"/>
-        <v>2104.52</v>
+        <v>2385.3333333333335</v>
       </c>
       <c r="F67" s="53">
         <f t="shared" si="8"/>
-        <v>2177.3200000000002</v>
+        <v>2514.3333333333335</v>
       </c>
       <c r="G67" s="53">
         <f t="shared" si="9"/>
-        <v>2250.12</v>
+        <v>2636.3333333333335</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -15858,23 +15836,23 @@
       </c>
       <c r="C68" s="52">
         <f t="shared" si="5"/>
-        <v>2093.62</v>
+        <v>2270</v>
       </c>
       <c r="D68" s="52">
         <f t="shared" si="6"/>
-        <v>2166.42</v>
+        <v>2448</v>
       </c>
       <c r="E68" s="52">
         <f t="shared" si="7"/>
-        <v>2239.2199999999998</v>
+        <v>2619</v>
       </c>
       <c r="F68" s="52">
         <f t="shared" si="8"/>
-        <v>2312.02</v>
+        <v>2783</v>
       </c>
       <c r="G68" s="52">
         <f t="shared" si="9"/>
-        <v>2384.8199999999997</v>
+        <v>2940</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -15898,23 +15876,23 @@
       </c>
       <c r="C69" s="53">
         <f t="shared" si="5"/>
-        <v>2228.3200000000002</v>
+        <v>2433.666666666667</v>
       </c>
       <c r="D69" s="53">
         <f t="shared" si="6"/>
-        <v>2301.12</v>
+        <v>2646.666666666667</v>
       </c>
       <c r="E69" s="53">
         <f t="shared" si="7"/>
-        <v>2373.92</v>
+        <v>2852.666666666667</v>
       </c>
       <c r="F69" s="53">
         <f t="shared" si="8"/>
-        <v>2446.7200000000003</v>
+        <v>3051.666666666667</v>
       </c>
       <c r="G69" s="53">
         <f t="shared" si="9"/>
-        <v>2519.52</v>
+        <v>3243.666666666667</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -15938,23 +15916,23 @@
       </c>
       <c r="C70" s="52">
         <f t="shared" si="5"/>
-        <v>2363.0200000000004</v>
+        <v>2597.3333333333335</v>
       </c>
       <c r="D70" s="52">
         <f t="shared" si="6"/>
-        <v>2435.8200000000002</v>
+        <v>2845.3333333333335</v>
       </c>
       <c r="E70" s="52">
         <f t="shared" si="7"/>
-        <v>2508.62</v>
+        <v>3086.3333333333335</v>
       </c>
       <c r="F70" s="52">
         <f t="shared" si="8"/>
-        <v>2581.42</v>
+        <v>3320.3333333333335</v>
       </c>
       <c r="G70" s="52">
         <f t="shared" si="9"/>
-        <v>2654.2200000000003</v>
+        <v>3547.3333333333335</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -15978,23 +15956,23 @@
       </c>
       <c r="C71" s="53">
         <f t="shared" si="5"/>
-        <v>2497.7200000000003</v>
+        <v>2761</v>
       </c>
       <c r="D71" s="53">
         <f t="shared" si="6"/>
-        <v>2570.52</v>
+        <v>3044</v>
       </c>
       <c r="E71" s="53">
         <f t="shared" si="7"/>
-        <v>2643.32</v>
+        <v>3320</v>
       </c>
       <c r="F71" s="53">
         <f t="shared" si="8"/>
-        <v>2716.12</v>
+        <v>3589</v>
       </c>
       <c r="G71" s="53">
         <f t="shared" si="9"/>
-        <v>2788.92</v>
+        <v>3851</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -16018,23 +15996,23 @@
       </c>
       <c r="C72" s="52">
         <f t="shared" si="5"/>
-        <v>2632.42</v>
+        <v>2924.666666666667</v>
       </c>
       <c r="D72" s="52">
         <f t="shared" si="6"/>
-        <v>2705.2200000000003</v>
+        <v>3242.666666666667</v>
       </c>
       <c r="E72" s="52">
         <f t="shared" si="7"/>
-        <v>2778.0200000000004</v>
+        <v>3553.666666666667</v>
       </c>
       <c r="F72" s="52">
         <f t="shared" si="8"/>
-        <v>2850.82</v>
+        <v>3857.666666666667</v>
       </c>
       <c r="G72" s="52">
         <f t="shared" si="9"/>
-        <v>2923.62</v>
+        <v>4154.666666666667</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -16058,23 +16036,23 @@
       </c>
       <c r="C73" s="53">
         <f t="shared" si="5"/>
-        <v>2767.12</v>
+        <v>3088.3333333333335</v>
       </c>
       <c r="D73" s="53">
         <f t="shared" si="6"/>
-        <v>2839.92</v>
+        <v>3441.3333333333335</v>
       </c>
       <c r="E73" s="53">
         <f t="shared" si="7"/>
-        <v>2912.72</v>
+        <v>3787.3333333333335</v>
       </c>
       <c r="F73" s="53">
         <f t="shared" si="8"/>
-        <v>2985.52</v>
+        <v>4126.333333333333</v>
       </c>
       <c r="G73" s="53">
         <f t="shared" si="9"/>
-        <v>3058.32</v>
+        <v>4458.333333333333</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -16098,23 +16076,23 @@
       </c>
       <c r="C74" s="52">
         <f t="shared" si="5"/>
-        <v>2901.82</v>
+        <v>3252</v>
       </c>
       <c r="D74" s="52">
         <f t="shared" si="6"/>
-        <v>2974.62</v>
+        <v>3640</v>
       </c>
       <c r="E74" s="52">
         <f t="shared" si="7"/>
-        <v>3047.42</v>
+        <v>4021</v>
       </c>
       <c r="F74" s="52">
         <f t="shared" si="8"/>
-        <v>3120.2200000000003</v>
+        <v>4395</v>
       </c>
       <c r="G74" s="52">
         <f t="shared" si="9"/>
-        <v>3193.0200000000004</v>
+        <v>4762</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -16425,47 +16403,47 @@
       </c>
       <c r="F85" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q85)+(INDEX(Parameters!$J$10:$N$10,1,Q85+1)-INDEX(Parameters!$J$10:$N$10,1,Q85))*T85,INDEX(Parameters!$D$10:$H$10,1,Q85)+(INDEX(Parameters!$D$10:$H$10,1,Q85+1)-INDEX(Parameters!$D$10:$H$10,1,Q85))*T85)</f>
-        <v>2700</v>
+        <v>1800</v>
       </c>
       <c r="G85" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R85)+(INDEX(Parameters!$J$11:$N$11,1,R85+1)-INDEX(Parameters!$J$11:$N$11,1,R85))*U85,INDEX(Parameters!$D$11:$H$11,1,Q85)+(INDEX(Parameters!$D$11:$H$11,1,Q85+1)-INDEX(Parameters!$D$11:$H$11,1,Q85))*T85)</f>
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="H85" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q85)+(INDEX(Parameters!$J$12:$N$12,1,Q85+1)-INDEX(Parameters!$J$12:$N$12,1,Q85))*T85,INDEX(Parameters!$D$12:$H$12,1,Q85)+(INDEX(Parameters!$D$12:$H$12,1,Q85+1)-INDEX(Parameters!$D$12:$H$12,1,Q85))*T85)</f>
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="I85" s="43">
         <f>F85*H85</f>
-        <v>1836.0000000000002</v>
+        <v>1800</v>
       </c>
       <c r="J85" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R85)+(INDEX(Parameters!$J$13:$N$13,1,R85+1)-INDEX(Parameters!$J$13:$N$13,1,R85))*U85,INDEX(Parameters!$D$13:$H$13,1,R85)+(INDEX(Parameters!$D$13:$H$13,1,R85+1)-INDEX(Parameters!$D$13:$H$13,1,R85))*U85)</f>
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K85" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R85)+(INDEX(Parameters!$D$14:$H$14,1,R85+1)-INDEX(Parameters!$D$14:$H$14,1,R85))*U85)</f>
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="L85" s="43">
         <f>I85+J85</f>
-        <v>2086</v>
+        <v>1900</v>
       </c>
       <c r="M85" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S85)+(INDEX(Parameters!$J$17:$N$17,1,S85+1)-INDEX(Parameters!$J$17:$N$17,1,S85))*V85,INDEX(Parameters!$D$17:$H$17,1,S85)+(INDEX(Parameters!$D$17:$H$17,1,S85+1)-INDEX(Parameters!$D$17:$H$17,1,S85))*V85)</f>
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="N85" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S85)+(INDEX(Parameters!$J$18:$N$18,1,S85+1)-INDEX(Parameters!$J$18:$N$18,1,S85))*V85,INDEX(Parameters!$D$18:$H$18,1,S85)+(INDEX(Parameters!$D$18:$H$18,1,S85+1)-INDEX(Parameters!$D$18:$H$18,1,S85))*V85)</f>
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="O85" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S85)+(INDEX(Parameters!$J$19:$N$19,1,S85+1)-INDEX(Parameters!$J$19:$N$19,1,S85))*V85,INDEX(Parameters!$D$19:$H$19,1,S85)+(INDEX(Parameters!$D$19:$H$19,1,S85+1)-INDEX(Parameters!$D$19:$H$19,1,S85))*V85)</f>
-        <v>0.76</v>
+        <v>0.94</v>
       </c>
       <c r="P85" s="43">
         <f>M85*O85</f>
-        <v>2280</v>
+        <v>1880</v>
       </c>
       <c r="Q85" s="43">
         <f>MIN(4,MAX(1,INT((1+C85/Parameters!$D$23)*4)+1))</f>
@@ -16511,47 +16489,47 @@
       </c>
       <c r="F86" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q86)+(INDEX(Parameters!$J$10:$N$10,1,Q86+1)-INDEX(Parameters!$J$10:$N$10,1,Q86))*T86,INDEX(Parameters!$D$10:$H$10,1,Q86)+(INDEX(Parameters!$D$10:$H$10,1,Q86+1)-INDEX(Parameters!$D$10:$H$10,1,Q86))*T86)</f>
-        <v>3150</v>
+        <v>2400</v>
       </c>
       <c r="G86" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R86)+(INDEX(Parameters!$J$11:$N$11,1,R86+1)-INDEX(Parameters!$J$11:$N$11,1,R86))*U86,INDEX(Parameters!$D$11:$H$11,1,Q86)+(INDEX(Parameters!$D$11:$H$11,1,Q86+1)-INDEX(Parameters!$D$11:$H$11,1,Q86))*T86)</f>
-        <v>0.27</v>
+        <v>0.1</v>
       </c>
       <c r="H86" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q86)+(INDEX(Parameters!$J$12:$N$12,1,Q86+1)-INDEX(Parameters!$J$12:$N$12,1,Q86))*T86,INDEX(Parameters!$D$12:$H$12,1,Q86)+(INDEX(Parameters!$D$12:$H$12,1,Q86+1)-INDEX(Parameters!$D$12:$H$12,1,Q86))*T86)</f>
-        <v>0.66</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I86" s="45">
         <f>F86*H86</f>
-        <v>2079</v>
+        <v>2340</v>
       </c>
       <c r="J86" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R86)+(INDEX(Parameters!$J$13:$N$13,1,R86+1)-INDEX(Parameters!$J$13:$N$13,1,R86))*U86,INDEX(Parameters!$D$13:$H$13,1,R86)+(INDEX(Parameters!$D$13:$H$13,1,R86+1)-INDEX(Parameters!$D$13:$H$13,1,R86))*U86)</f>
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="K86" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R86)+(INDEX(Parameters!$D$14:$H$14,1,R86+1)-INDEX(Parameters!$D$14:$H$14,1,R86))*U86)</f>
-        <v>0.45</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="L86" s="45">
         <f>I86+J86</f>
-        <v>2329</v>
+        <v>3140</v>
       </c>
       <c r="M86" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="N86" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S86)+(INDEX(Parameters!$J$18:$N$18,1,S86+1)-INDEX(Parameters!$J$18:$N$18,1,S86))*V86,INDEX(Parameters!$D$18:$H$18,1,S86)+(INDEX(Parameters!$D$18:$H$18,1,S86+1)-INDEX(Parameters!$D$18:$H$18,1,S86))*V86)</f>
-        <v>0.22500000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="O86" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S86)+(INDEX(Parameters!$J$19:$N$19,1,S86+1)-INDEX(Parameters!$J$19:$N$19,1,S86))*V86,INDEX(Parameters!$D$19:$H$19,1,S86)+(INDEX(Parameters!$D$19:$H$19,1,S86+1)-INDEX(Parameters!$D$19:$H$19,1,S86))*V86)</f>
-        <v>0.72</v>
+        <v>0.90999999999999992</v>
       </c>
       <c r="P86" s="45">
         <f>M86*O86</f>
-        <v>2520</v>
+        <v>2275</v>
       </c>
       <c r="Q86" s="45">
         <f>MIN(4,MAX(1,INT((1+C86/Parameters!$D$23)*4)+1))</f>
@@ -16597,23 +16575,23 @@
       </c>
       <c r="F87" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q87)+(INDEX(Parameters!$J$10:$N$10,1,Q87+1)-INDEX(Parameters!$J$10:$N$10,1,Q87))*T87,INDEX(Parameters!$D$10:$H$10,1,Q87)+(INDEX(Parameters!$D$10:$H$10,1,Q87+1)-INDEX(Parameters!$D$10:$H$10,1,Q87))*T87)</f>
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="G87" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R87)+(INDEX(Parameters!$J$11:$N$11,1,R87+1)-INDEX(Parameters!$J$11:$N$11,1,R87))*U87,INDEX(Parameters!$D$11:$H$11,1,Q87)+(INDEX(Parameters!$D$11:$H$11,1,Q87+1)-INDEX(Parameters!$D$11:$H$11,1,Q87))*T87)</f>
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="H87" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q87)+(INDEX(Parameters!$J$12:$N$12,1,Q87+1)-INDEX(Parameters!$J$12:$N$12,1,Q87))*T87,INDEX(Parameters!$D$12:$H$12,1,Q87)+(INDEX(Parameters!$D$12:$H$12,1,Q87+1)-INDEX(Parameters!$D$12:$H$12,1,Q87))*T87)</f>
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="I87" s="43">
         <f>F87*H87</f>
-        <v>2304</v>
+        <v>2850</v>
       </c>
       <c r="J87" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R87)+(INDEX(Parameters!$J$13:$N$13,1,R87+1)-INDEX(Parameters!$J$13:$N$13,1,R87))*U87,INDEX(Parameters!$D$13:$H$13,1,R87)+(INDEX(Parameters!$D$13:$H$13,1,R87+1)-INDEX(Parameters!$D$13:$H$13,1,R87))*U87)</f>
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="K87" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R87)+(INDEX(Parameters!$D$14:$H$14,1,R87+1)-INDEX(Parameters!$D$14:$H$14,1,R87))*U87)</f>
@@ -16621,23 +16599,23 @@
       </c>
       <c r="L87" s="43">
         <f>I87+J87</f>
-        <v>2554</v>
+        <v>4350</v>
       </c>
       <c r="M87" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S87)+(INDEX(Parameters!$J$17:$N$17,1,S87+1)-INDEX(Parameters!$J$17:$N$17,1,S87))*V87,INDEX(Parameters!$D$17:$H$17,1,S87)+(INDEX(Parameters!$D$17:$H$17,1,S87+1)-INDEX(Parameters!$D$17:$H$17,1,S87))*V87)</f>
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="N87" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S87)+(INDEX(Parameters!$J$18:$N$18,1,S87+1)-INDEX(Parameters!$J$18:$N$18,1,S87))*V87,INDEX(Parameters!$D$18:$H$18,1,S87)+(INDEX(Parameters!$D$18:$H$18,1,S87+1)-INDEX(Parameters!$D$18:$H$18,1,S87))*V87)</f>
-        <v>0.25</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O87" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S87)+(INDEX(Parameters!$J$19:$N$19,1,S87+1)-INDEX(Parameters!$J$19:$N$19,1,S87))*V87,INDEX(Parameters!$D$19:$H$19,1,S87)+(INDEX(Parameters!$D$19:$H$19,1,S87+1)-INDEX(Parameters!$D$19:$H$19,1,S87))*V87)</f>
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="P87" s="43">
         <f>M87*O87</f>
-        <v>2720</v>
+        <v>2640</v>
       </c>
       <c r="Q87" s="43">
         <f>MIN(4,MAX(1,INT((1+C87/Parameters!$D$23)*4)+1))</f>
@@ -16683,47 +16661,47 @@
       </c>
       <c r="F88" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q88)+(INDEX(Parameters!$J$10:$N$10,1,Q88+1)-INDEX(Parameters!$J$10:$N$10,1,Q88))*T88,INDEX(Parameters!$D$10:$H$10,1,Q88)+(INDEX(Parameters!$D$10:$H$10,1,Q88+1)-INDEX(Parameters!$D$10:$H$10,1,Q88))*T88)</f>
-        <v>4050</v>
+        <v>3600</v>
       </c>
       <c r="G88" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R88)+(INDEX(Parameters!$J$11:$N$11,1,R88+1)-INDEX(Parameters!$J$11:$N$11,1,R88))*U88,INDEX(Parameters!$D$11:$H$11,1,Q88)+(INDEX(Parameters!$D$11:$H$11,1,Q88+1)-INDEX(Parameters!$D$11:$H$11,1,Q88))*T88)</f>
-        <v>0.37</v>
+        <v>0.1</v>
       </c>
       <c r="H88" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q88)+(INDEX(Parameters!$J$12:$N$12,1,Q88+1)-INDEX(Parameters!$J$12:$N$12,1,Q88))*T88,INDEX(Parameters!$D$12:$H$12,1,Q88)+(INDEX(Parameters!$D$12:$H$12,1,Q88+1)-INDEX(Parameters!$D$12:$H$12,1,Q88))*T88)</f>
-        <v>0.62</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="I88" s="45">
         <f>F88*H88</f>
-        <v>2511</v>
+        <v>3330</v>
       </c>
       <c r="J88" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R88)+(INDEX(Parameters!$J$13:$N$13,1,R88+1)-INDEX(Parameters!$J$13:$N$13,1,R88))*U88,INDEX(Parameters!$D$13:$H$13,1,R88)+(INDEX(Parameters!$D$13:$H$13,1,R88+1)-INDEX(Parameters!$D$13:$H$13,1,R88))*U88)</f>
-        <v>250</v>
+        <v>2200</v>
       </c>
       <c r="K88" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R88)+(INDEX(Parameters!$D$14:$H$14,1,R88+1)-INDEX(Parameters!$D$14:$H$14,1,R88))*U88)</f>
-        <v>0.45</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="L88" s="45">
         <f>I88+J88</f>
-        <v>2761</v>
+        <v>5530</v>
       </c>
       <c r="M88" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="N88" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S88)+(INDEX(Parameters!$J$18:$N$18,1,S88+1)-INDEX(Parameters!$J$18:$N$18,1,S88))*V88,INDEX(Parameters!$D$18:$H$18,1,S88)+(INDEX(Parameters!$D$18:$H$18,1,S88+1)-INDEX(Parameters!$D$18:$H$18,1,S88))*V88)</f>
-        <v>0.27500000000000002</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="O88" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S88)+(INDEX(Parameters!$J$19:$N$19,1,S88+1)-INDEX(Parameters!$J$19:$N$19,1,S88))*V88,INDEX(Parameters!$D$19:$H$19,1,S88)+(INDEX(Parameters!$D$19:$H$19,1,S88+1)-INDEX(Parameters!$D$19:$H$19,1,S88))*V88)</f>
-        <v>0.64</v>
+        <v>0.85</v>
       </c>
       <c r="P88" s="45">
         <f>M88*O88</f>
-        <v>2880</v>
+        <v>2975</v>
       </c>
       <c r="Q88" s="45">
         <f>MIN(4,MAX(1,INT((1+C88/Parameters!$D$23)*4)+1))</f>
@@ -16769,47 +16747,47 @@
       </c>
       <c r="F89" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q89)+(INDEX(Parameters!$J$10:$N$10,1,Q89+1)-INDEX(Parameters!$J$10:$N$10,1,Q89))*T89,INDEX(Parameters!$D$10:$H$10,1,Q89)+(INDEX(Parameters!$D$10:$H$10,1,Q89+1)-INDEX(Parameters!$D$10:$H$10,1,Q89))*T89)</f>
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="G89" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R89)+(INDEX(Parameters!$J$11:$N$11,1,R89+1)-INDEX(Parameters!$J$11:$N$11,1,R89))*U89,INDEX(Parameters!$D$11:$H$11,1,Q89)+(INDEX(Parameters!$D$11:$H$11,1,Q89+1)-INDEX(Parameters!$D$11:$H$11,1,Q89))*T89)</f>
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="H89" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q89)+(INDEX(Parameters!$J$12:$N$12,1,Q89+1)-INDEX(Parameters!$J$12:$N$12,1,Q89))*T89,INDEX(Parameters!$D$12:$H$12,1,Q89)+(INDEX(Parameters!$D$12:$H$12,1,Q89+1)-INDEX(Parameters!$D$12:$H$12,1,Q89))*T89)</f>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I89" s="43">
         <f>F89*H89</f>
-        <v>2700</v>
+        <v>3780</v>
       </c>
       <c r="J89" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R89)+(INDEX(Parameters!$J$13:$N$13,1,R89+1)-INDEX(Parameters!$J$13:$N$13,1,R89))*U89,INDEX(Parameters!$D$13:$H$13,1,R89)+(INDEX(Parameters!$D$13:$H$13,1,R89+1)-INDEX(Parameters!$D$13:$H$13,1,R89))*U89)</f>
-        <v>250</v>
+        <v>2900</v>
       </c>
       <c r="K89" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R89)+(INDEX(Parameters!$D$14:$H$14,1,R89+1)-INDEX(Parameters!$D$14:$H$14,1,R89))*U89)</f>
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="L89" s="43">
         <f>I89+J89</f>
-        <v>2950</v>
+        <v>6680</v>
       </c>
       <c r="M89" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="N89" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S89)+(INDEX(Parameters!$J$18:$N$18,1,S89+1)-INDEX(Parameters!$J$18:$N$18,1,S89))*V89,INDEX(Parameters!$D$18:$H$18,1,S89)+(INDEX(Parameters!$D$18:$H$18,1,S89+1)-INDEX(Parameters!$D$18:$H$18,1,S89))*V89)</f>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="O89" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S89)+(INDEX(Parameters!$J$19:$N$19,1,S89+1)-INDEX(Parameters!$J$19:$N$19,1,S89))*V89,INDEX(Parameters!$D$19:$H$19,1,S89)+(INDEX(Parameters!$D$19:$H$19,1,S89+1)-INDEX(Parameters!$D$19:$H$19,1,S89))*V89)</f>
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="P89" s="43">
         <f>M89*O89</f>
-        <v>3000</v>
+        <v>3280</v>
       </c>
       <c r="Q89" s="43">
         <f>MIN(4,MAX(1,INT((1+C89/Parameters!$D$23)*4)+1))</f>
@@ -16991,23 +16969,23 @@
       </c>
       <c r="C95" s="53">
         <f t="shared" si="10"/>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D95" s="53">
         <f t="shared" si="11"/>
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="E95" s="53">
         <f t="shared" si="12"/>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F95" s="53">
         <f t="shared" si="13"/>
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="G95" s="53">
         <f t="shared" si="14"/>
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
@@ -17031,23 +17009,23 @@
       </c>
       <c r="C96" s="52">
         <f t="shared" si="10"/>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D96" s="52">
         <f t="shared" si="11"/>
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E96" s="52">
         <f t="shared" si="12"/>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F96" s="52">
         <f t="shared" si="13"/>
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="G96" s="52">
         <f t="shared" si="14"/>
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
@@ -17071,23 +17049,23 @@
       </c>
       <c r="C97" s="53">
         <f t="shared" si="10"/>
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="D97" s="53">
         <f t="shared" si="11"/>
-        <v>525</v>
+        <v>375</v>
       </c>
       <c r="E97" s="53">
         <f t="shared" si="12"/>
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="F97" s="53">
         <f t="shared" si="13"/>
-        <v>675</v>
+        <v>525</v>
       </c>
       <c r="G97" s="53">
         <f t="shared" si="14"/>
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
@@ -17111,23 +17089,23 @@
       </c>
       <c r="C98" s="52">
         <f t="shared" si="10"/>
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="D98" s="52">
         <f t="shared" si="11"/>
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E98" s="52">
         <f t="shared" si="12"/>
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F98" s="52">
         <f t="shared" si="13"/>
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="G98" s="52">
         <f t="shared" si="14"/>
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
@@ -17151,23 +17129,23 @@
       </c>
       <c r="C99" s="53">
         <f t="shared" si="10"/>
-        <v>714</v>
+        <v>497.59999999999997</v>
       </c>
       <c r="D99" s="53">
         <f t="shared" si="11"/>
-        <v>850.5</v>
+        <v>625</v>
       </c>
       <c r="E99" s="53">
         <f t="shared" si="12"/>
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="F99" s="53">
         <f t="shared" si="13"/>
-        <v>1125</v>
+        <v>875</v>
       </c>
       <c r="G99" s="53">
         <f t="shared" si="14"/>
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
@@ -17191,23 +17169,23 @@
       </c>
       <c r="C100" s="52">
         <f t="shared" si="10"/>
-        <v>828</v>
+        <v>591.59999999999991</v>
       </c>
       <c r="D100" s="52">
         <f t="shared" si="11"/>
-        <v>976.5</v>
+        <v>739.875</v>
       </c>
       <c r="E100" s="52">
         <f t="shared" si="12"/>
-        <v>1136</v>
+        <v>892.8</v>
       </c>
       <c r="F100" s="52">
         <f t="shared" si="13"/>
-        <v>1309.5</v>
+        <v>1050</v>
       </c>
       <c r="G100" s="52">
         <f t="shared" si="14"/>
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
@@ -17231,23 +17209,23 @@
       </c>
       <c r="C101" s="53">
         <f t="shared" si="10"/>
-        <v>942</v>
+        <v>685.59999999999991</v>
       </c>
       <c r="D101" s="53">
         <f t="shared" si="11"/>
-        <v>1102.5</v>
+        <v>853.625</v>
       </c>
       <c r="E101" s="53">
         <f t="shared" si="12"/>
-        <v>1272</v>
+        <v>1024.8</v>
       </c>
       <c r="F101" s="53">
         <f t="shared" si="13"/>
-        <v>1453.5</v>
+        <v>1201.375</v>
       </c>
       <c r="G101" s="53">
         <f t="shared" si="14"/>
-        <v>1650</v>
+        <v>1385.6</v>
       </c>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
@@ -17271,23 +17249,23 @@
       </c>
       <c r="C102" s="52">
         <f t="shared" si="10"/>
-        <v>1056</v>
+        <v>779.6</v>
       </c>
       <c r="D102" s="52">
         <f t="shared" si="11"/>
-        <v>1228.5</v>
+        <v>967.375</v>
       </c>
       <c r="E102" s="52">
         <f t="shared" si="12"/>
-        <v>1408</v>
+        <v>1156.8000000000002</v>
       </c>
       <c r="F102" s="52">
         <f t="shared" si="13"/>
-        <v>1597.5</v>
+        <v>1350.1250000000002</v>
       </c>
       <c r="G102" s="52">
         <f t="shared" si="14"/>
-        <v>1800</v>
+        <v>1549.6</v>
       </c>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
@@ -17311,23 +17289,23 @@
       </c>
       <c r="C103" s="53">
         <f t="shared" si="10"/>
-        <v>1170</v>
+        <v>873.6</v>
       </c>
       <c r="D103" s="53">
         <f t="shared" si="11"/>
-        <v>1354.5</v>
+        <v>1081.125</v>
       </c>
       <c r="E103" s="53">
         <f t="shared" si="12"/>
-        <v>1544</v>
+        <v>1288.8000000000002</v>
       </c>
       <c r="F103" s="53">
         <f t="shared" si="13"/>
-        <v>1741.5</v>
+        <v>1498.875</v>
       </c>
       <c r="G103" s="53">
         <f t="shared" si="14"/>
-        <v>1950</v>
+        <v>1713.6</v>
       </c>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
@@ -17351,23 +17329,23 @@
       </c>
       <c r="C104" s="52">
         <f t="shared" si="10"/>
-        <v>1284</v>
+        <v>967.6</v>
       </c>
       <c r="D104" s="52">
         <f t="shared" si="11"/>
-        <v>1480.5</v>
+        <v>1194.875</v>
       </c>
       <c r="E104" s="52">
         <f t="shared" si="12"/>
-        <v>1680</v>
+        <v>1420.8000000000002</v>
       </c>
       <c r="F104" s="52">
         <f t="shared" si="13"/>
-        <v>1885.5</v>
+        <v>1647.625</v>
       </c>
       <c r="G104" s="52">
         <f t="shared" si="14"/>
-        <v>2100</v>
+        <v>1877.6</v>
       </c>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
@@ -17391,23 +17369,23 @@
       </c>
       <c r="C105" s="53">
         <f t="shared" si="10"/>
-        <v>1398</v>
+        <v>1061.6000000000001</v>
       </c>
       <c r="D105" s="53">
         <f t="shared" si="11"/>
-        <v>1606.5</v>
+        <v>1308.625</v>
       </c>
       <c r="E105" s="53">
         <f t="shared" si="12"/>
-        <v>1816</v>
+        <v>1552.8000000000002</v>
       </c>
       <c r="F105" s="53">
         <f t="shared" si="13"/>
-        <v>2029.5</v>
+        <v>1796.3750000000002</v>
       </c>
       <c r="G105" s="53">
         <f t="shared" si="14"/>
-        <v>2250</v>
+        <v>2041.6000000000001</v>
       </c>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
@@ -17431,23 +17409,23 @@
       </c>
       <c r="C106" s="52">
         <f t="shared" si="10"/>
-        <v>1512</v>
+        <v>1155.5999999999999</v>
       </c>
       <c r="D106" s="52">
         <f t="shared" si="11"/>
-        <v>1732.5</v>
+        <v>1422.375</v>
       </c>
       <c r="E106" s="52">
         <f t="shared" si="12"/>
-        <v>1952</v>
+        <v>1684.8</v>
       </c>
       <c r="F106" s="52">
         <f t="shared" si="13"/>
-        <v>2173.5</v>
+        <v>1945.125</v>
       </c>
       <c r="G106" s="52">
         <f t="shared" si="14"/>
-        <v>2400</v>
+        <v>2205.6</v>
       </c>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
@@ -17471,23 +17449,23 @@
       </c>
       <c r="C107" s="53">
         <f t="shared" si="10"/>
-        <v>1626</v>
+        <v>1249.5999999999999</v>
       </c>
       <c r="D107" s="53">
         <f t="shared" si="11"/>
-        <v>1858.5</v>
+        <v>1536.125</v>
       </c>
       <c r="E107" s="53">
         <f t="shared" si="12"/>
-        <v>2088</v>
+        <v>1816.8000000000002</v>
       </c>
       <c r="F107" s="53">
         <f t="shared" si="13"/>
-        <v>2317.5</v>
+        <v>2093.875</v>
       </c>
       <c r="G107" s="53">
         <f t="shared" si="14"/>
-        <v>2550</v>
+        <v>2369.6</v>
       </c>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
@@ -17511,23 +17489,23 @@
       </c>
       <c r="C108" s="52">
         <f t="shared" si="10"/>
-        <v>1739.9999999999998</v>
+        <v>1343.6</v>
       </c>
       <c r="D108" s="52">
         <f t="shared" si="11"/>
-        <v>1984.5</v>
+        <v>1649.875</v>
       </c>
       <c r="E108" s="52">
         <f t="shared" si="12"/>
-        <v>2224</v>
+        <v>1948.7999999999997</v>
       </c>
       <c r="F108" s="52">
         <f t="shared" si="13"/>
-        <v>2461.5</v>
+        <v>2242.625</v>
       </c>
       <c r="G108" s="52">
         <f t="shared" si="14"/>
-        <v>2700</v>
+        <v>2533.6</v>
       </c>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
@@ -17551,23 +17529,23 @@
       </c>
       <c r="C109" s="53">
         <f t="shared" si="10"/>
-        <v>1854</v>
+        <v>1437.6</v>
       </c>
       <c r="D109" s="53">
         <f t="shared" si="11"/>
-        <v>2110.5</v>
+        <v>1763.625</v>
       </c>
       <c r="E109" s="53">
         <f t="shared" si="12"/>
-        <v>2360</v>
+        <v>2080.8000000000002</v>
       </c>
       <c r="F109" s="53">
         <f t="shared" si="13"/>
-        <v>2605.5</v>
+        <v>2391.375</v>
       </c>
       <c r="G109" s="53">
         <f t="shared" si="14"/>
-        <v>2850</v>
+        <v>2697.6</v>
       </c>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
@@ -17591,23 +17569,23 @@
       </c>
       <c r="C110" s="52">
         <f t="shared" si="10"/>
-        <v>1968.0000000000002</v>
+        <v>1531.6000000000001</v>
       </c>
       <c r="D110" s="52">
         <f t="shared" si="11"/>
-        <v>2236.5</v>
+        <v>1877.375</v>
       </c>
       <c r="E110" s="52">
         <f t="shared" si="12"/>
-        <v>2496</v>
+        <v>2212.8000000000002</v>
       </c>
       <c r="F110" s="52">
         <f t="shared" si="13"/>
-        <v>2749.5</v>
+        <v>2540.125</v>
       </c>
       <c r="G110" s="52">
         <f t="shared" si="14"/>
-        <v>3000</v>
+        <v>2861.6000000000004</v>
       </c>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
@@ -17631,23 +17609,23 @@
       </c>
       <c r="C111" s="53">
         <f t="shared" si="10"/>
-        <v>2082</v>
+        <v>1625.6</v>
       </c>
       <c r="D111" s="53">
         <f t="shared" si="11"/>
-        <v>2362.5</v>
+        <v>1991.125</v>
       </c>
       <c r="E111" s="53">
         <f t="shared" si="12"/>
-        <v>2632</v>
+        <v>2344.8000000000002</v>
       </c>
       <c r="F111" s="53">
         <f t="shared" si="13"/>
-        <v>2893.5</v>
+        <v>2688.875</v>
       </c>
       <c r="G111" s="53">
         <f t="shared" si="14"/>
-        <v>3150</v>
+        <v>3025.6000000000004</v>
       </c>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
@@ -17671,23 +17649,23 @@
       </c>
       <c r="C112" s="52">
         <f t="shared" si="10"/>
-        <v>2196</v>
+        <v>1719.6000000000001</v>
       </c>
       <c r="D112" s="52">
         <f t="shared" si="11"/>
-        <v>2488.5</v>
+        <v>2104.875</v>
       </c>
       <c r="E112" s="52">
         <f t="shared" si="12"/>
-        <v>2768</v>
+        <v>2476.8000000000002</v>
       </c>
       <c r="F112" s="52">
         <f t="shared" si="13"/>
-        <v>3037.5</v>
+        <v>2837.625</v>
       </c>
       <c r="G112" s="52">
         <f t="shared" si="14"/>
-        <v>3300</v>
+        <v>3189.6000000000004</v>
       </c>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
@@ -17711,23 +17689,23 @@
       </c>
       <c r="C113" s="53">
         <f t="shared" si="10"/>
-        <v>2310</v>
+        <v>1813.6</v>
       </c>
       <c r="D113" s="53">
         <f t="shared" si="11"/>
-        <v>2614.5</v>
+        <v>2218.625</v>
       </c>
       <c r="E113" s="53">
         <f t="shared" si="12"/>
-        <v>2904</v>
+        <v>2608.7999999999997</v>
       </c>
       <c r="F113" s="53">
         <f t="shared" si="13"/>
-        <v>3181.5</v>
+        <v>2986.375</v>
       </c>
       <c r="G113" s="53">
         <f t="shared" si="14"/>
-        <v>3450</v>
+        <v>3353.5999999999995</v>
       </c>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
@@ -17751,23 +17729,23 @@
       </c>
       <c r="C114" s="52">
         <f t="shared" si="10"/>
-        <v>2424</v>
+        <v>1907.6000000000001</v>
       </c>
       <c r="D114" s="52">
         <f t="shared" si="11"/>
-        <v>2740.5</v>
+        <v>2332.375</v>
       </c>
       <c r="E114" s="52">
         <f t="shared" si="12"/>
-        <v>3040</v>
+        <v>2740.8</v>
       </c>
       <c r="F114" s="52">
         <f t="shared" si="13"/>
-        <v>3325.5</v>
+        <v>3135.125</v>
       </c>
       <c r="G114" s="52">
         <f t="shared" si="14"/>
-        <v>3600</v>
+        <v>3517.6</v>
       </c>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
@@ -18078,47 +18056,47 @@
       </c>
       <c r="F125" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q125)+(INDEX(Parameters!$J$10:$N$10,1,Q125+1)-INDEX(Parameters!$J$10:$N$10,1,Q125))*T125,INDEX(Parameters!$D$10:$H$10,1,Q125)+(INDEX(Parameters!$D$10:$H$10,1,Q125+1)-INDEX(Parameters!$D$10:$H$10,1,Q125))*T125)</f>
-        <v>2700</v>
+        <v>1800</v>
       </c>
       <c r="G125" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R125)+(INDEX(Parameters!$J$11:$N$11,1,R125+1)-INDEX(Parameters!$J$11:$N$11,1,R125))*U125,INDEX(Parameters!$D$11:$H$11,1,Q125)+(INDEX(Parameters!$D$11:$H$11,1,Q125+1)-INDEX(Parameters!$D$11:$H$11,1,Q125))*T125)</f>
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="H125" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q125)+(INDEX(Parameters!$J$12:$N$12,1,Q125+1)-INDEX(Parameters!$J$12:$N$12,1,Q125))*T125,INDEX(Parameters!$D$12:$H$12,1,Q125)+(INDEX(Parameters!$D$12:$H$12,1,Q125+1)-INDEX(Parameters!$D$12:$H$12,1,Q125))*T125)</f>
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="I125" s="43">
         <f>F125*H125</f>
-        <v>1836.0000000000002</v>
+        <v>1800</v>
       </c>
       <c r="J125" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R125)+(INDEX(Parameters!$J$13:$N$13,1,R125+1)-INDEX(Parameters!$J$13:$N$13,1,R125))*U125,INDEX(Parameters!$D$13:$H$13,1,R125)+(INDEX(Parameters!$D$13:$H$13,1,R125+1)-INDEX(Parameters!$D$13:$H$13,1,R125))*U125)</f>
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K125" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R125)+(INDEX(Parameters!$D$14:$H$14,1,R125+1)-INDEX(Parameters!$D$14:$H$14,1,R125))*U125)</f>
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="L125" s="43">
         <f>I125+J125</f>
-        <v>2086</v>
+        <v>1900</v>
       </c>
       <c r="M125" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S125)+(INDEX(Parameters!$J$17:$N$17,1,S125+1)-INDEX(Parameters!$J$17:$N$17,1,S125))*V125,INDEX(Parameters!$D$17:$H$17,1,S125)+(INDEX(Parameters!$D$17:$H$17,1,S125+1)-INDEX(Parameters!$D$17:$H$17,1,S125))*V125)</f>
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="N125" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S125)+(INDEX(Parameters!$J$18:$N$18,1,S125+1)-INDEX(Parameters!$J$18:$N$18,1,S125))*V125,INDEX(Parameters!$D$18:$H$18,1,S125)+(INDEX(Parameters!$D$18:$H$18,1,S125+1)-INDEX(Parameters!$D$18:$H$18,1,S125))*V125)</f>
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="O125" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S125)+(INDEX(Parameters!$J$19:$N$19,1,S125+1)-INDEX(Parameters!$J$19:$N$19,1,S125))*V125,INDEX(Parameters!$D$19:$H$19,1,S125)+(INDEX(Parameters!$D$19:$H$19,1,S125+1)-INDEX(Parameters!$D$19:$H$19,1,S125))*V125)</f>
-        <v>0.76</v>
+        <v>0.94</v>
       </c>
       <c r="P125" s="43">
         <f>M125*O125</f>
-        <v>2280</v>
+        <v>1880</v>
       </c>
       <c r="Q125" s="43">
         <f>MIN(4,MAX(1,INT((1+C125/Parameters!$D$23)*4)+1))</f>
@@ -18164,47 +18142,47 @@
       </c>
       <c r="F126" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q126)+(INDEX(Parameters!$J$10:$N$10,1,Q126+1)-INDEX(Parameters!$J$10:$N$10,1,Q126))*T126,INDEX(Parameters!$D$10:$H$10,1,Q126)+(INDEX(Parameters!$D$10:$H$10,1,Q126+1)-INDEX(Parameters!$D$10:$H$10,1,Q126))*T126)</f>
-        <v>3150</v>
+        <v>2400</v>
       </c>
       <c r="G126" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R126)+(INDEX(Parameters!$J$11:$N$11,1,R126+1)-INDEX(Parameters!$J$11:$N$11,1,R126))*U126,INDEX(Parameters!$D$11:$H$11,1,Q126)+(INDEX(Parameters!$D$11:$H$11,1,Q126+1)-INDEX(Parameters!$D$11:$H$11,1,Q126))*T126)</f>
-        <v>0.27</v>
+        <v>0.1</v>
       </c>
       <c r="H126" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q126)+(INDEX(Parameters!$J$12:$N$12,1,Q126+1)-INDEX(Parameters!$J$12:$N$12,1,Q126))*T126,INDEX(Parameters!$D$12:$H$12,1,Q126)+(INDEX(Parameters!$D$12:$H$12,1,Q126+1)-INDEX(Parameters!$D$12:$H$12,1,Q126))*T126)</f>
-        <v>0.66</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I126" s="45">
         <f>F126*H126</f>
-        <v>2079</v>
+        <v>2340</v>
       </c>
       <c r="J126" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R126)+(INDEX(Parameters!$J$13:$N$13,1,R126+1)-INDEX(Parameters!$J$13:$N$13,1,R126))*U126,INDEX(Parameters!$D$13:$H$13,1,R126)+(INDEX(Parameters!$D$13:$H$13,1,R126+1)-INDEX(Parameters!$D$13:$H$13,1,R126))*U126)</f>
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="K126" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R126)+(INDEX(Parameters!$D$14:$H$14,1,R126+1)-INDEX(Parameters!$D$14:$H$14,1,R126))*U126)</f>
-        <v>0.45</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="L126" s="45">
         <f>I126+J126</f>
-        <v>2329</v>
+        <v>3140</v>
       </c>
       <c r="M126" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="N126" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S126)+(INDEX(Parameters!$J$18:$N$18,1,S126+1)-INDEX(Parameters!$J$18:$N$18,1,S126))*V126,INDEX(Parameters!$D$18:$H$18,1,S126)+(INDEX(Parameters!$D$18:$H$18,1,S126+1)-INDEX(Parameters!$D$18:$H$18,1,S126))*V126)</f>
-        <v>0.22500000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="O126" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S126)+(INDEX(Parameters!$J$19:$N$19,1,S126+1)-INDEX(Parameters!$J$19:$N$19,1,S126))*V126,INDEX(Parameters!$D$19:$H$19,1,S126)+(INDEX(Parameters!$D$19:$H$19,1,S126+1)-INDEX(Parameters!$D$19:$H$19,1,S126))*V126)</f>
-        <v>0.72</v>
+        <v>0.90999999999999992</v>
       </c>
       <c r="P126" s="45">
         <f>M126*O126</f>
-        <v>2520</v>
+        <v>2275</v>
       </c>
       <c r="Q126" s="45">
         <f>MIN(4,MAX(1,INT((1+C126/Parameters!$D$23)*4)+1))</f>
@@ -18250,23 +18228,23 @@
       </c>
       <c r="F127" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q127)+(INDEX(Parameters!$J$10:$N$10,1,Q127+1)-INDEX(Parameters!$J$10:$N$10,1,Q127))*T127,INDEX(Parameters!$D$10:$H$10,1,Q127)+(INDEX(Parameters!$D$10:$H$10,1,Q127+1)-INDEX(Parameters!$D$10:$H$10,1,Q127))*T127)</f>
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="G127" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R127)+(INDEX(Parameters!$J$11:$N$11,1,R127+1)-INDEX(Parameters!$J$11:$N$11,1,R127))*U127,INDEX(Parameters!$D$11:$H$11,1,Q127)+(INDEX(Parameters!$D$11:$H$11,1,Q127+1)-INDEX(Parameters!$D$11:$H$11,1,Q127))*T127)</f>
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="H127" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q127)+(INDEX(Parameters!$J$12:$N$12,1,Q127+1)-INDEX(Parameters!$J$12:$N$12,1,Q127))*T127,INDEX(Parameters!$D$12:$H$12,1,Q127)+(INDEX(Parameters!$D$12:$H$12,1,Q127+1)-INDEX(Parameters!$D$12:$H$12,1,Q127))*T127)</f>
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="I127" s="43">
         <f>F127*H127</f>
-        <v>2304</v>
+        <v>2850</v>
       </c>
       <c r="J127" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R127)+(INDEX(Parameters!$J$13:$N$13,1,R127+1)-INDEX(Parameters!$J$13:$N$13,1,R127))*U127,INDEX(Parameters!$D$13:$H$13,1,R127)+(INDEX(Parameters!$D$13:$H$13,1,R127+1)-INDEX(Parameters!$D$13:$H$13,1,R127))*U127)</f>
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="K127" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R127)+(INDEX(Parameters!$D$14:$H$14,1,R127+1)-INDEX(Parameters!$D$14:$H$14,1,R127))*U127)</f>
@@ -18274,23 +18252,23 @@
       </c>
       <c r="L127" s="43">
         <f>I127+J127</f>
-        <v>2554</v>
+        <v>4350</v>
       </c>
       <c r="M127" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S127)+(INDEX(Parameters!$J$17:$N$17,1,S127+1)-INDEX(Parameters!$J$17:$N$17,1,S127))*V127,INDEX(Parameters!$D$17:$H$17,1,S127)+(INDEX(Parameters!$D$17:$H$17,1,S127+1)-INDEX(Parameters!$D$17:$H$17,1,S127))*V127)</f>
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="N127" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S127)+(INDEX(Parameters!$J$18:$N$18,1,S127+1)-INDEX(Parameters!$J$18:$N$18,1,S127))*V127,INDEX(Parameters!$D$18:$H$18,1,S127)+(INDEX(Parameters!$D$18:$H$18,1,S127+1)-INDEX(Parameters!$D$18:$H$18,1,S127))*V127)</f>
-        <v>0.25</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O127" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S127)+(INDEX(Parameters!$J$19:$N$19,1,S127+1)-INDEX(Parameters!$J$19:$N$19,1,S127))*V127,INDEX(Parameters!$D$19:$H$19,1,S127)+(INDEX(Parameters!$D$19:$H$19,1,S127+1)-INDEX(Parameters!$D$19:$H$19,1,S127))*V127)</f>
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="P127" s="43">
         <f>M127*O127</f>
-        <v>2720</v>
+        <v>2640</v>
       </c>
       <c r="Q127" s="43">
         <f>MIN(4,MAX(1,INT((1+C127/Parameters!$D$23)*4)+1))</f>
@@ -18336,47 +18314,47 @@
       </c>
       <c r="F128" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q128)+(INDEX(Parameters!$J$10:$N$10,1,Q128+1)-INDEX(Parameters!$J$10:$N$10,1,Q128))*T128,INDEX(Parameters!$D$10:$H$10,1,Q128)+(INDEX(Parameters!$D$10:$H$10,1,Q128+1)-INDEX(Parameters!$D$10:$H$10,1,Q128))*T128)</f>
-        <v>4050</v>
+        <v>3600</v>
       </c>
       <c r="G128" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R128)+(INDEX(Parameters!$J$11:$N$11,1,R128+1)-INDEX(Parameters!$J$11:$N$11,1,R128))*U128,INDEX(Parameters!$D$11:$H$11,1,Q128)+(INDEX(Parameters!$D$11:$H$11,1,Q128+1)-INDEX(Parameters!$D$11:$H$11,1,Q128))*T128)</f>
-        <v>0.37</v>
+        <v>0.1</v>
       </c>
       <c r="H128" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q128)+(INDEX(Parameters!$J$12:$N$12,1,Q128+1)-INDEX(Parameters!$J$12:$N$12,1,Q128))*T128,INDEX(Parameters!$D$12:$H$12,1,Q128)+(INDEX(Parameters!$D$12:$H$12,1,Q128+1)-INDEX(Parameters!$D$12:$H$12,1,Q128))*T128)</f>
-        <v>0.62</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="I128" s="45">
         <f>F128*H128</f>
-        <v>2511</v>
+        <v>3330</v>
       </c>
       <c r="J128" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R128)+(INDEX(Parameters!$J$13:$N$13,1,R128+1)-INDEX(Parameters!$J$13:$N$13,1,R128))*U128,INDEX(Parameters!$D$13:$H$13,1,R128)+(INDEX(Parameters!$D$13:$H$13,1,R128+1)-INDEX(Parameters!$D$13:$H$13,1,R128))*U128)</f>
-        <v>250</v>
+        <v>2200</v>
       </c>
       <c r="K128" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R128)+(INDEX(Parameters!$D$14:$H$14,1,R128+1)-INDEX(Parameters!$D$14:$H$14,1,R128))*U128)</f>
-        <v>0.45</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="L128" s="45">
         <f>I128+J128</f>
-        <v>2761</v>
+        <v>5530</v>
       </c>
       <c r="M128" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="N128" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S128)+(INDEX(Parameters!$J$18:$N$18,1,S128+1)-INDEX(Parameters!$J$18:$N$18,1,S128))*V128,INDEX(Parameters!$D$18:$H$18,1,S128)+(INDEX(Parameters!$D$18:$H$18,1,S128+1)-INDEX(Parameters!$D$18:$H$18,1,S128))*V128)</f>
-        <v>0.27500000000000002</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="O128" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S128)+(INDEX(Parameters!$J$19:$N$19,1,S128+1)-INDEX(Parameters!$J$19:$N$19,1,S128))*V128,INDEX(Parameters!$D$19:$H$19,1,S128)+(INDEX(Parameters!$D$19:$H$19,1,S128+1)-INDEX(Parameters!$D$19:$H$19,1,S128))*V128)</f>
-        <v>0.64</v>
+        <v>0.85</v>
       </c>
       <c r="P128" s="45">
         <f>M128*O128</f>
-        <v>2880</v>
+        <v>2975</v>
       </c>
       <c r="Q128" s="45">
         <f>MIN(4,MAX(1,INT((1+C128/Parameters!$D$23)*4)+1))</f>
@@ -18422,47 +18400,47 @@
       </c>
       <c r="F129" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q129)+(INDEX(Parameters!$J$10:$N$10,1,Q129+1)-INDEX(Parameters!$J$10:$N$10,1,Q129))*T129,INDEX(Parameters!$D$10:$H$10,1,Q129)+(INDEX(Parameters!$D$10:$H$10,1,Q129+1)-INDEX(Parameters!$D$10:$H$10,1,Q129))*T129)</f>
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="G129" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R129)+(INDEX(Parameters!$J$11:$N$11,1,R129+1)-INDEX(Parameters!$J$11:$N$11,1,R129))*U129,INDEX(Parameters!$D$11:$H$11,1,Q129)+(INDEX(Parameters!$D$11:$H$11,1,Q129+1)-INDEX(Parameters!$D$11:$H$11,1,Q129))*T129)</f>
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="H129" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q129)+(INDEX(Parameters!$J$12:$N$12,1,Q129+1)-INDEX(Parameters!$J$12:$N$12,1,Q129))*T129,INDEX(Parameters!$D$12:$H$12,1,Q129)+(INDEX(Parameters!$D$12:$H$12,1,Q129+1)-INDEX(Parameters!$D$12:$H$12,1,Q129))*T129)</f>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I129" s="43">
         <f>F129*H129</f>
-        <v>2700</v>
+        <v>3780</v>
       </c>
       <c r="J129" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R129)+(INDEX(Parameters!$J$13:$N$13,1,R129+1)-INDEX(Parameters!$J$13:$N$13,1,R129))*U129,INDEX(Parameters!$D$13:$H$13,1,R129)+(INDEX(Parameters!$D$13:$H$13,1,R129+1)-INDEX(Parameters!$D$13:$H$13,1,R129))*U129)</f>
-        <v>250</v>
+        <v>2900</v>
       </c>
       <c r="K129" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R129)+(INDEX(Parameters!$D$14:$H$14,1,R129+1)-INDEX(Parameters!$D$14:$H$14,1,R129))*U129)</f>
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="L129" s="43">
         <f>I129+J129</f>
-        <v>2950</v>
+        <v>6680</v>
       </c>
       <c r="M129" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="N129" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S129)+(INDEX(Parameters!$J$18:$N$18,1,S129+1)-INDEX(Parameters!$J$18:$N$18,1,S129))*V129,INDEX(Parameters!$D$18:$H$18,1,S129)+(INDEX(Parameters!$D$18:$H$18,1,S129+1)-INDEX(Parameters!$D$18:$H$18,1,S129))*V129)</f>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="O129" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S129)+(INDEX(Parameters!$J$19:$N$19,1,S129+1)-INDEX(Parameters!$J$19:$N$19,1,S129))*V129,INDEX(Parameters!$D$19:$H$19,1,S129)+(INDEX(Parameters!$D$19:$H$19,1,S129+1)-INDEX(Parameters!$D$19:$H$19,1,S129))*V129)</f>
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="P129" s="43">
         <f>M129*O129</f>
-        <v>3000</v>
+        <v>3280</v>
       </c>
       <c r="Q129" s="43">
         <f>MIN(4,MAX(1,INT((1+C129/Parameters!$D$23)*4)+1))</f>
@@ -18674,43 +18652,43 @@
       </c>
       <c r="C135" s="53">
         <f t="shared" si="15"/>
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="D135" s="53">
         <f t="shared" si="16"/>
-        <v>157.5</v>
+        <v>120</v>
       </c>
       <c r="E135" s="53">
         <f t="shared" si="17"/>
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F135" s="53">
         <f t="shared" si="18"/>
-        <v>202.5</v>
+        <v>180</v>
       </c>
       <c r="G135" s="53">
         <f t="shared" si="19"/>
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="H135" s="53">
         <f t="shared" si="20"/>
-        <v>-150</v>
+        <v>-100</v>
       </c>
       <c r="I135" s="53">
         <f t="shared" si="21"/>
-        <v>-175</v>
+        <v>-125</v>
       </c>
       <c r="J135" s="53">
         <f t="shared" si="22"/>
-        <v>-200</v>
+        <v>-150</v>
       </c>
       <c r="K135" s="53">
         <f t="shared" si="23"/>
-        <v>-225</v>
+        <v>-175</v>
       </c>
       <c r="L135" s="53">
         <f t="shared" si="24"/>
-        <v>-250</v>
+        <v>-200</v>
       </c>
       <c r="M135" s="4"/>
       <c r="N135" s="4"/>
@@ -18729,43 +18707,43 @@
       </c>
       <c r="C136" s="52">
         <f t="shared" si="15"/>
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="D136" s="52">
         <f t="shared" si="16"/>
-        <v>315</v>
+        <v>240</v>
       </c>
       <c r="E136" s="52">
         <f t="shared" si="17"/>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="F136" s="52">
         <f t="shared" si="18"/>
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="G136" s="52">
         <f t="shared" si="19"/>
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="H136" s="52">
         <f t="shared" si="20"/>
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="I136" s="52">
         <f t="shared" si="21"/>
-        <v>-350</v>
+        <v>-250</v>
       </c>
       <c r="J136" s="52">
         <f t="shared" si="22"/>
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="K136" s="52">
         <f t="shared" si="23"/>
-        <v>-450</v>
+        <v>-350</v>
       </c>
       <c r="L136" s="52">
         <f t="shared" si="24"/>
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="M136" s="4"/>
       <c r="N136" s="4"/>
@@ -18784,43 +18762,43 @@
       </c>
       <c r="C137" s="53">
         <f t="shared" si="15"/>
-        <v>405</v>
+        <v>270</v>
       </c>
       <c r="D137" s="53">
         <f t="shared" si="16"/>
-        <v>472.5</v>
+        <v>357</v>
       </c>
       <c r="E137" s="53">
         <f t="shared" si="17"/>
-        <v>540</v>
+        <v>442.5</v>
       </c>
       <c r="F137" s="53">
         <f t="shared" si="18"/>
-        <v>607.5</v>
+        <v>526.5</v>
       </c>
       <c r="G137" s="53">
         <f t="shared" si="19"/>
-        <v>675</v>
+        <v>609</v>
       </c>
       <c r="H137" s="53">
         <f t="shared" si="20"/>
-        <v>-450</v>
+        <v>-300</v>
       </c>
       <c r="I137" s="53">
         <f t="shared" si="21"/>
-        <v>-525</v>
+        <v>-375</v>
       </c>
       <c r="J137" s="53">
         <f t="shared" si="22"/>
-        <v>-600</v>
+        <v>-450</v>
       </c>
       <c r="K137" s="53">
         <f t="shared" si="23"/>
-        <v>-675</v>
+        <v>-525</v>
       </c>
       <c r="L137" s="53">
         <f t="shared" si="24"/>
-        <v>-750</v>
+        <v>-600</v>
       </c>
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
@@ -18839,43 +18817,43 @@
       </c>
       <c r="C138" s="52">
         <f t="shared" si="15"/>
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="D138" s="52">
         <f t="shared" si="16"/>
-        <v>630</v>
+        <v>474</v>
       </c>
       <c r="E138" s="52">
         <f t="shared" si="17"/>
-        <v>720</v>
+        <v>585</v>
       </c>
       <c r="F138" s="52">
         <f t="shared" si="18"/>
-        <v>810</v>
+        <v>693</v>
       </c>
       <c r="G138" s="52">
         <f t="shared" si="19"/>
-        <v>900</v>
+        <v>798</v>
       </c>
       <c r="H138" s="52">
         <f t="shared" si="20"/>
-        <v>-600</v>
+        <v>-400</v>
       </c>
       <c r="I138" s="52">
         <f t="shared" si="21"/>
-        <v>-700</v>
+        <v>-500</v>
       </c>
       <c r="J138" s="52">
         <f t="shared" si="22"/>
-        <v>-800</v>
+        <v>-600</v>
       </c>
       <c r="K138" s="52">
         <f t="shared" si="23"/>
-        <v>-900</v>
+        <v>-700</v>
       </c>
       <c r="L138" s="52">
         <f t="shared" si="24"/>
-        <v>-1000</v>
+        <v>-800</v>
       </c>
       <c r="M138" s="4"/>
       <c r="N138" s="4"/>
@@ -18894,43 +18872,43 @@
       </c>
       <c r="C139" s="53">
         <f t="shared" si="15"/>
-        <v>649.08000000000004</v>
+        <v>450</v>
       </c>
       <c r="D139" s="53">
         <f t="shared" si="16"/>
-        <v>787.5</v>
+        <v>591</v>
       </c>
       <c r="E139" s="53">
         <f t="shared" si="17"/>
-        <v>900</v>
+        <v>727.5</v>
       </c>
       <c r="F139" s="53">
         <f t="shared" si="18"/>
-        <v>1012.5</v>
+        <v>859.5</v>
       </c>
       <c r="G139" s="53">
         <f t="shared" si="19"/>
-        <v>1125</v>
+        <v>987</v>
       </c>
       <c r="H139" s="53">
         <f t="shared" si="20"/>
-        <v>-714</v>
+        <v>-497.59999999999997</v>
       </c>
       <c r="I139" s="53">
         <f t="shared" si="21"/>
-        <v>-850.5</v>
+        <v>-625</v>
       </c>
       <c r="J139" s="53">
         <f t="shared" si="22"/>
-        <v>-1000</v>
+        <v>-750</v>
       </c>
       <c r="K139" s="53">
         <f t="shared" si="23"/>
-        <v>-1125</v>
+        <v>-875</v>
       </c>
       <c r="L139" s="53">
         <f t="shared" si="24"/>
-        <v>-1250</v>
+        <v>-1000</v>
       </c>
       <c r="M139" s="4"/>
       <c r="N139" s="4"/>
@@ -18949,43 +18927,43 @@
       </c>
       <c r="C140" s="52">
         <f t="shared" si="15"/>
-        <v>740.88</v>
+        <v>540</v>
       </c>
       <c r="D140" s="52">
         <f t="shared" si="16"/>
-        <v>912.86999999999989</v>
+        <v>708</v>
       </c>
       <c r="E140" s="52">
         <f t="shared" si="17"/>
-        <v>1080</v>
+        <v>870</v>
       </c>
       <c r="F140" s="52">
         <f t="shared" si="18"/>
-        <v>1215</v>
+        <v>1026</v>
       </c>
       <c r="G140" s="52">
         <f t="shared" si="19"/>
-        <v>1350</v>
+        <v>1176</v>
       </c>
       <c r="H140" s="52">
         <f t="shared" si="20"/>
-        <v>-828</v>
+        <v>-591.59999999999991</v>
       </c>
       <c r="I140" s="52">
         <f t="shared" si="21"/>
-        <v>-976.5</v>
+        <v>-739.875</v>
       </c>
       <c r="J140" s="52">
         <f t="shared" si="22"/>
-        <v>-1136</v>
+        <v>-892.8</v>
       </c>
       <c r="K140" s="52">
         <f t="shared" si="23"/>
-        <v>-1309.5</v>
+        <v>-1050</v>
       </c>
       <c r="L140" s="52">
         <f t="shared" si="24"/>
-        <v>-1500</v>
+        <v>-1200</v>
       </c>
       <c r="M140" s="4"/>
       <c r="N140" s="4"/>
@@ -19004,43 +18982,43 @@
       </c>
       <c r="C141" s="53">
         <f t="shared" si="15"/>
-        <v>832.68</v>
+        <v>630</v>
       </c>
       <c r="D141" s="53">
         <f t="shared" si="16"/>
-        <v>1016.8199999999999</v>
+        <v>824.99999999999989</v>
       </c>
       <c r="E141" s="53">
         <f t="shared" si="17"/>
-        <v>1221.1199999999999</v>
+        <v>1012.4999999999999</v>
       </c>
       <c r="F141" s="53">
         <f t="shared" si="18"/>
-        <v>1417.5</v>
+        <v>1192.5</v>
       </c>
       <c r="G141" s="53">
         <f t="shared" si="19"/>
-        <v>1575</v>
+        <v>1365</v>
       </c>
       <c r="H141" s="53">
         <f t="shared" si="20"/>
-        <v>-942</v>
+        <v>-685.59999999999991</v>
       </c>
       <c r="I141" s="53">
         <f t="shared" si="21"/>
-        <v>-1102.5</v>
+        <v>-853.625</v>
       </c>
       <c r="J141" s="53">
         <f t="shared" si="22"/>
-        <v>-1272</v>
+        <v>-1024.8</v>
       </c>
       <c r="K141" s="53">
         <f t="shared" si="23"/>
-        <v>-1453.5</v>
+        <v>-1201.375</v>
       </c>
       <c r="L141" s="53">
         <f t="shared" si="24"/>
-        <v>-1650</v>
+        <v>-1385.6</v>
       </c>
       <c r="M141" s="4"/>
       <c r="N141" s="4"/>
@@ -19059,43 +19037,43 @@
       </c>
       <c r="C142" s="52">
         <f t="shared" si="15"/>
-        <v>924.48</v>
+        <v>720.00000000000011</v>
       </c>
       <c r="D142" s="52">
         <f t="shared" si="16"/>
-        <v>1120.77</v>
+        <v>942.00000000000011</v>
       </c>
       <c r="E142" s="52">
         <f t="shared" si="17"/>
-        <v>1336.3200000000002</v>
+        <v>1155</v>
       </c>
       <c r="F142" s="52">
         <f t="shared" si="18"/>
-        <v>1573.8300000000002</v>
+        <v>1359</v>
       </c>
       <c r="G142" s="52">
         <f t="shared" si="19"/>
-        <v>1800</v>
+        <v>1554.0000000000002</v>
       </c>
       <c r="H142" s="52">
         <f t="shared" si="20"/>
-        <v>-1056</v>
+        <v>-779.6</v>
       </c>
       <c r="I142" s="52">
         <f t="shared" si="21"/>
-        <v>-1228.5</v>
+        <v>-967.375</v>
       </c>
       <c r="J142" s="52">
         <f t="shared" si="22"/>
-        <v>-1408</v>
+        <v>-1156.8000000000002</v>
       </c>
       <c r="K142" s="52">
         <f t="shared" si="23"/>
-        <v>-1597.5</v>
+        <v>-1350.1250000000002</v>
       </c>
       <c r="L142" s="52">
         <f t="shared" si="24"/>
-        <v>-1800</v>
+        <v>-1549.6</v>
       </c>
       <c r="M142" s="4"/>
       <c r="N142" s="4"/>
@@ -19114,43 +19092,43 @@
       </c>
       <c r="C143" s="53">
         <f t="shared" si="15"/>
-        <v>1016.2800000000001</v>
+        <v>811</v>
       </c>
       <c r="D143" s="53">
         <f t="shared" si="16"/>
-        <v>1224.72</v>
+        <v>1063</v>
       </c>
       <c r="E143" s="53">
         <f t="shared" si="17"/>
-        <v>1451.52</v>
+        <v>1297.5</v>
       </c>
       <c r="F143" s="53">
         <f t="shared" si="18"/>
-        <v>1699.38</v>
+        <v>1525.5</v>
       </c>
       <c r="G143" s="53">
         <f t="shared" si="19"/>
-        <v>1971</v>
+        <v>1743</v>
       </c>
       <c r="H143" s="53">
         <f t="shared" si="20"/>
-        <v>-1170</v>
+        <v>-873.6</v>
       </c>
       <c r="I143" s="53">
         <f t="shared" si="21"/>
-        <v>-1354.5</v>
+        <v>-1081.125</v>
       </c>
       <c r="J143" s="53">
         <f t="shared" si="22"/>
-        <v>-1544</v>
+        <v>-1288.8000000000002</v>
       </c>
       <c r="K143" s="53">
         <f t="shared" si="23"/>
-        <v>-1741.5</v>
+        <v>-1498.875</v>
       </c>
       <c r="L143" s="53">
         <f t="shared" si="24"/>
-        <v>-1950</v>
+        <v>-1713.6</v>
       </c>
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
@@ -19169,43 +19147,43 @@
       </c>
       <c r="C144" s="52">
         <f t="shared" si="15"/>
-        <v>1120.5800000000002</v>
+        <v>906</v>
       </c>
       <c r="D144" s="52">
         <f t="shared" si="16"/>
-        <v>1341.17</v>
+        <v>1220</v>
       </c>
       <c r="E144" s="52">
         <f t="shared" si="17"/>
-        <v>1579.22</v>
+        <v>1515</v>
       </c>
       <c r="F144" s="52">
         <f t="shared" si="18"/>
-        <v>1837.43</v>
+        <v>1791</v>
       </c>
       <c r="G144" s="52">
         <f t="shared" si="19"/>
-        <v>2118.5</v>
+        <v>2048</v>
       </c>
       <c r="H144" s="52">
         <f t="shared" si="20"/>
-        <v>-1284</v>
+        <v>-967.6</v>
       </c>
       <c r="I144" s="52">
         <f t="shared" si="21"/>
-        <v>-1480.5</v>
+        <v>-1194.875</v>
       </c>
       <c r="J144" s="52">
         <f t="shared" si="22"/>
-        <v>-1680</v>
+        <v>-1420.8000000000002</v>
       </c>
       <c r="K144" s="52">
         <f t="shared" si="23"/>
-        <v>-1885.5</v>
+        <v>-1647.625</v>
       </c>
       <c r="L144" s="52">
         <f t="shared" si="24"/>
-        <v>-2100</v>
+        <v>-1877.6</v>
       </c>
       <c r="M144" s="4"/>
       <c r="N144" s="4"/>
@@ -19224,43 +19202,43 @@
       </c>
       <c r="C145" s="53">
         <f t="shared" si="15"/>
-        <v>1224.8800000000001</v>
+        <v>1001.0000000000001</v>
       </c>
       <c r="D145" s="53">
         <f t="shared" si="16"/>
-        <v>1457.62</v>
+        <v>1377.0000000000002</v>
       </c>
       <c r="E145" s="53">
         <f t="shared" si="17"/>
-        <v>1706.92</v>
+        <v>1732.5000000000002</v>
       </c>
       <c r="F145" s="53">
         <f t="shared" si="18"/>
-        <v>1975.48</v>
+        <v>2067.5000000000005</v>
       </c>
       <c r="G145" s="53">
         <f t="shared" si="19"/>
-        <v>2266</v>
+        <v>2382</v>
       </c>
       <c r="H145" s="53">
         <f t="shared" si="20"/>
-        <v>-1398</v>
+        <v>-1061.6000000000001</v>
       </c>
       <c r="I145" s="53">
         <f t="shared" si="21"/>
-        <v>-1606.5</v>
+        <v>-1308.625</v>
       </c>
       <c r="J145" s="53">
         <f t="shared" si="22"/>
-        <v>-1816</v>
+        <v>-1552.8000000000002</v>
       </c>
       <c r="K145" s="53">
         <f t="shared" si="23"/>
-        <v>-2029.5</v>
+        <v>-1796.3750000000002</v>
       </c>
       <c r="L145" s="53">
         <f t="shared" si="24"/>
-        <v>-2250</v>
+        <v>-2041.6000000000001</v>
       </c>
       <c r="M145" s="4"/>
       <c r="N145" s="4"/>
@@ -19279,43 +19257,43 @@
       </c>
       <c r="C146" s="52">
         <f t="shared" si="15"/>
-        <v>1329.18</v>
+        <v>1096</v>
       </c>
       <c r="D146" s="52">
         <f t="shared" si="16"/>
-        <v>1574.07</v>
+        <v>1534</v>
       </c>
       <c r="E146" s="52">
         <f t="shared" si="17"/>
-        <v>1834.62</v>
+        <v>1950</v>
       </c>
       <c r="F146" s="52">
         <f t="shared" si="18"/>
-        <v>2113.5299999999997</v>
+        <v>2344</v>
       </c>
       <c r="G146" s="52">
         <f t="shared" si="19"/>
-        <v>2413.5</v>
+        <v>2716</v>
       </c>
       <c r="H146" s="52">
         <f t="shared" si="20"/>
-        <v>-1512</v>
+        <v>-1155.5999999999999</v>
       </c>
       <c r="I146" s="52">
         <f t="shared" si="21"/>
-        <v>-1732.5</v>
+        <v>-1422.375</v>
       </c>
       <c r="J146" s="52">
         <f t="shared" si="22"/>
-        <v>-1952</v>
+        <v>-1684.8</v>
       </c>
       <c r="K146" s="52">
         <f t="shared" si="23"/>
-        <v>-2173.5</v>
+        <v>-1945.125</v>
       </c>
       <c r="L146" s="52">
         <f t="shared" si="24"/>
-        <v>-2400</v>
+        <v>-2205.6</v>
       </c>
       <c r="M146" s="4"/>
       <c r="N146" s="4"/>
@@ -19334,43 +19312,43 @@
       </c>
       <c r="C147" s="53">
         <f t="shared" si="15"/>
-        <v>1433.48</v>
+        <v>1191</v>
       </c>
       <c r="D147" s="53">
         <f t="shared" si="16"/>
-        <v>1690.52</v>
+        <v>1691</v>
       </c>
       <c r="E147" s="53">
         <f t="shared" si="17"/>
-        <v>1962.3200000000002</v>
+        <v>2167.5</v>
       </c>
       <c r="F147" s="53">
         <f t="shared" si="18"/>
-        <v>2251.58</v>
+        <v>2620.5</v>
       </c>
       <c r="G147" s="53">
         <f t="shared" si="19"/>
-        <v>2561</v>
+        <v>3050</v>
       </c>
       <c r="H147" s="53">
         <f t="shared" si="20"/>
-        <v>-1626</v>
+        <v>-1249.5999999999999</v>
       </c>
       <c r="I147" s="53">
         <f t="shared" si="21"/>
-        <v>-1858.5</v>
+        <v>-1536.125</v>
       </c>
       <c r="J147" s="53">
         <f t="shared" si="22"/>
-        <v>-2088</v>
+        <v>-1816.8000000000002</v>
       </c>
       <c r="K147" s="53">
         <f t="shared" si="23"/>
-        <v>-2317.5</v>
+        <v>-2093.875</v>
       </c>
       <c r="L147" s="53">
         <f t="shared" si="24"/>
-        <v>-2550</v>
+        <v>-2369.6</v>
       </c>
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
@@ -19389,43 +19367,43 @@
       </c>
       <c r="C148" s="52">
         <f t="shared" si="15"/>
-        <v>1537.7800000000002</v>
+        <v>1286</v>
       </c>
       <c r="D148" s="52">
         <f t="shared" si="16"/>
-        <v>1806.9699999999998</v>
+        <v>1848</v>
       </c>
       <c r="E148" s="52">
         <f t="shared" si="17"/>
-        <v>2090.02</v>
+        <v>2385</v>
       </c>
       <c r="F148" s="52">
         <f t="shared" si="18"/>
-        <v>2389.63</v>
+        <v>2897</v>
       </c>
       <c r="G148" s="52">
         <f t="shared" si="19"/>
-        <v>2708.5</v>
+        <v>3384</v>
       </c>
       <c r="H148" s="52">
         <f t="shared" si="20"/>
-        <v>-1739.9999999999998</v>
+        <v>-1343.6</v>
       </c>
       <c r="I148" s="52">
         <f t="shared" si="21"/>
-        <v>-1984.5</v>
+        <v>-1649.875</v>
       </c>
       <c r="J148" s="52">
         <f t="shared" si="22"/>
-        <v>-2224</v>
+        <v>-1948.7999999999997</v>
       </c>
       <c r="K148" s="52">
         <f t="shared" si="23"/>
-        <v>-2461.5</v>
+        <v>-2242.625</v>
       </c>
       <c r="L148" s="52">
         <f t="shared" si="24"/>
-        <v>-2700</v>
+        <v>-2533.6</v>
       </c>
       <c r="M148" s="4"/>
       <c r="N148" s="4"/>
@@ -19444,43 +19422,43 @@
       </c>
       <c r="C149" s="53">
         <f t="shared" si="15"/>
-        <v>1642.0800000000002</v>
+        <v>1381</v>
       </c>
       <c r="D149" s="53">
         <f t="shared" si="16"/>
-        <v>1923.42</v>
+        <v>2005</v>
       </c>
       <c r="E149" s="53">
         <f t="shared" si="17"/>
-        <v>2217.7200000000003</v>
+        <v>2602.5</v>
       </c>
       <c r="F149" s="53">
         <f t="shared" si="18"/>
-        <v>2527.6800000000003</v>
+        <v>3173.5</v>
       </c>
       <c r="G149" s="53">
         <f t="shared" si="19"/>
-        <v>2856</v>
+        <v>3718</v>
       </c>
       <c r="H149" s="53">
         <f t="shared" si="20"/>
-        <v>-1854</v>
+        <v>-1437.6</v>
       </c>
       <c r="I149" s="53">
         <f t="shared" si="21"/>
-        <v>-2110.5</v>
+        <v>-1763.625</v>
       </c>
       <c r="J149" s="53">
         <f t="shared" si="22"/>
-        <v>-2360</v>
+        <v>-2080.8000000000002</v>
       </c>
       <c r="K149" s="53">
         <f t="shared" si="23"/>
-        <v>-2605.5</v>
+        <v>-2391.375</v>
       </c>
       <c r="L149" s="53">
         <f t="shared" si="24"/>
-        <v>-2850</v>
+        <v>-2697.6</v>
       </c>
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
@@ -19499,43 +19477,43 @@
       </c>
       <c r="C150" s="52">
         <f t="shared" si="15"/>
-        <v>1746.3800000000003</v>
+        <v>1476.0000000000002</v>
       </c>
       <c r="D150" s="52">
         <f t="shared" si="16"/>
-        <v>2039.8700000000001</v>
+        <v>2162.0000000000005</v>
       </c>
       <c r="E150" s="52">
         <f t="shared" si="17"/>
-        <v>2345.42</v>
+        <v>2820</v>
       </c>
       <c r="F150" s="52">
         <f t="shared" si="18"/>
-        <v>2665.73</v>
+        <v>3450</v>
       </c>
       <c r="G150" s="52">
         <f t="shared" si="19"/>
-        <v>3003.5</v>
+        <v>4052.0000000000005</v>
       </c>
       <c r="H150" s="52">
         <f t="shared" si="20"/>
-        <v>-1968.0000000000002</v>
+        <v>-1531.6000000000001</v>
       </c>
       <c r="I150" s="52">
         <f t="shared" si="21"/>
-        <v>-2236.5</v>
+        <v>-1877.375</v>
       </c>
       <c r="J150" s="52">
         <f t="shared" si="22"/>
-        <v>-2496</v>
+        <v>-2212.8000000000002</v>
       </c>
       <c r="K150" s="52">
         <f t="shared" si="23"/>
-        <v>-2749.5</v>
+        <v>-2540.125</v>
       </c>
       <c r="L150" s="52">
         <f t="shared" si="24"/>
-        <v>-3000</v>
+        <v>-2861.6000000000004</v>
       </c>
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
@@ -19554,43 +19532,43 @@
       </c>
       <c r="C151" s="53">
         <f t="shared" si="15"/>
-        <v>1850.68</v>
+        <v>1571</v>
       </c>
       <c r="D151" s="53">
         <f t="shared" si="16"/>
-        <v>2156.3199999999997</v>
+        <v>2319</v>
       </c>
       <c r="E151" s="53">
         <f t="shared" si="17"/>
-        <v>2473.12</v>
+        <v>3037.5</v>
       </c>
       <c r="F151" s="53">
         <f t="shared" si="18"/>
-        <v>2803.7799999999997</v>
+        <v>3726.5</v>
       </c>
       <c r="G151" s="53">
         <f t="shared" si="19"/>
-        <v>3151</v>
+        <v>4386</v>
       </c>
       <c r="H151" s="53">
         <f t="shared" si="20"/>
-        <v>-2082</v>
+        <v>-1625.6</v>
       </c>
       <c r="I151" s="53">
         <f t="shared" si="21"/>
-        <v>-2362.5</v>
+        <v>-1991.125</v>
       </c>
       <c r="J151" s="53">
         <f t="shared" si="22"/>
-        <v>-2632</v>
+        <v>-2344.8000000000002</v>
       </c>
       <c r="K151" s="53">
         <f t="shared" si="23"/>
-        <v>-2893.5</v>
+        <v>-2688.875</v>
       </c>
       <c r="L151" s="53">
         <f t="shared" si="24"/>
-        <v>-3150</v>
+        <v>-3025.6000000000004</v>
       </c>
       <c r="M151" s="4"/>
       <c r="N151" s="4"/>
@@ -19609,43 +19587,43 @@
       </c>
       <c r="C152" s="52">
         <f t="shared" si="15"/>
-        <v>1954.9800000000002</v>
+        <v>1666</v>
       </c>
       <c r="D152" s="52">
         <f t="shared" si="16"/>
-        <v>2272.77</v>
+        <v>2476</v>
       </c>
       <c r="E152" s="52">
         <f t="shared" si="17"/>
-        <v>2600.8200000000002</v>
+        <v>3255</v>
       </c>
       <c r="F152" s="52">
         <f t="shared" si="18"/>
-        <v>2941.83</v>
+        <v>4003</v>
       </c>
       <c r="G152" s="52">
         <f t="shared" si="19"/>
-        <v>3298.5</v>
+        <v>4720</v>
       </c>
       <c r="H152" s="52">
         <f t="shared" si="20"/>
-        <v>-2196</v>
+        <v>-1719.6000000000001</v>
       </c>
       <c r="I152" s="52">
         <f t="shared" si="21"/>
-        <v>-2488.5</v>
+        <v>-2104.875</v>
       </c>
       <c r="J152" s="52">
         <f t="shared" si="22"/>
-        <v>-2768</v>
+        <v>-2476.8000000000002</v>
       </c>
       <c r="K152" s="52">
         <f t="shared" si="23"/>
-        <v>-3037.5</v>
+        <v>-2837.625</v>
       </c>
       <c r="L152" s="52">
         <f t="shared" si="24"/>
-        <v>-3300</v>
+        <v>-3189.6000000000004</v>
       </c>
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
@@ -19664,43 +19642,43 @@
       </c>
       <c r="C153" s="53">
         <f t="shared" si="15"/>
-        <v>2059.2800000000002</v>
+        <v>1761</v>
       </c>
       <c r="D153" s="53">
         <f t="shared" si="16"/>
-        <v>2389.2199999999998</v>
+        <v>2633</v>
       </c>
       <c r="E153" s="53">
         <f t="shared" si="17"/>
-        <v>2728.5199999999995</v>
+        <v>3472.5</v>
       </c>
       <c r="F153" s="53">
         <f t="shared" si="18"/>
-        <v>3079.88</v>
+        <v>4279.5</v>
       </c>
       <c r="G153" s="53">
         <f t="shared" si="19"/>
-        <v>3446</v>
+        <v>5054</v>
       </c>
       <c r="H153" s="53">
         <f t="shared" si="20"/>
-        <v>-2310</v>
+        <v>-1813.6</v>
       </c>
       <c r="I153" s="53">
         <f t="shared" si="21"/>
-        <v>-2614.5</v>
+        <v>-2218.625</v>
       </c>
       <c r="J153" s="53">
         <f t="shared" si="22"/>
-        <v>-2904</v>
+        <v>-2608.7999999999997</v>
       </c>
       <c r="K153" s="53">
         <f t="shared" si="23"/>
-        <v>-3181.5</v>
+        <v>-2986.375</v>
       </c>
       <c r="L153" s="53">
         <f t="shared" si="24"/>
-        <v>-3450</v>
+        <v>-3353.5999999999995</v>
       </c>
       <c r="M153" s="4"/>
       <c r="N153" s="4"/>
@@ -19719,43 +19697,43 @@
       </c>
       <c r="C154" s="52">
         <f t="shared" si="15"/>
-        <v>2163.58</v>
+        <v>1856</v>
       </c>
       <c r="D154" s="52">
         <f t="shared" si="16"/>
-        <v>2505.67</v>
+        <v>2790</v>
       </c>
       <c r="E154" s="52">
         <f t="shared" si="17"/>
-        <v>2856.22</v>
+        <v>3690</v>
       </c>
       <c r="F154" s="52">
         <f t="shared" si="18"/>
-        <v>3217.9300000000003</v>
+        <v>4556</v>
       </c>
       <c r="G154" s="52">
         <f t="shared" si="19"/>
-        <v>3593.5</v>
+        <v>5388</v>
       </c>
       <c r="H154" s="52">
         <f t="shared" si="20"/>
-        <v>-2424</v>
+        <v>-1907.6000000000001</v>
       </c>
       <c r="I154" s="52">
         <f t="shared" si="21"/>
-        <v>-2740.5</v>
+        <v>-2332.375</v>
       </c>
       <c r="J154" s="52">
         <f t="shared" si="22"/>
-        <v>-3040</v>
+        <v>-2740.8</v>
       </c>
       <c r="K154" s="52">
         <f t="shared" si="23"/>
-        <v>-3325.5</v>
+        <v>-3135.125</v>
       </c>
       <c r="L154" s="52">
         <f t="shared" si="24"/>
-        <v>-3600</v>
+        <v>-3517.6</v>
       </c>
       <c r="M154" s="4"/>
       <c r="N154" s="4"/>
@@ -20018,7 +19996,7 @@
     <mergeCell ref="B121:V121"/>
     <mergeCell ref="B161:V161"/>
   </mergeCells>
-  <phoneticPr fontId="75" type="noConversion"/>
+  <phoneticPr fontId="74" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/damping_curve_RAx8.xlsx
+++ b/docs/damping_curve_RAx8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733267B6-4D59-444D-B8E3-208505955454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CBF6F6-2AE7-47D5-AAD1-A0F0E997B519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -1716,25 +1716,25 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="7" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1746,13 +1746,13 @@
     <xf numFmtId="178" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1893,32 +1893,53 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="43" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="61" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1926,38 +1947,23 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="24" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="25" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="42" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="33" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1974,21 +1980,15 @@
     <xf numFmtId="0" fontId="48" fillId="40" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="51" fillId="43" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="42" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="69" fillId="61" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2006,7 +2006,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3096,7 +3096,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4176,7 +4176,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -5249,7 +5249,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -7548,7 +7548,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -7567,7 +7567,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="35" customHeight="1">
+    <row r="2" spans="1:8" ht="35.1" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="70" t="s">
         <v>69</v>
@@ -7579,7 +7579,7 @@
       <c r="G2" s="71"/>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" ht="25" customHeight="1">
+    <row r="3" spans="1:8" ht="24.95" customHeight="1">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -7589,7 +7589,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" ht="32" customHeight="1">
+    <row r="4" spans="1:8" ht="32.1" customHeight="1">
       <c r="A4" s="6"/>
       <c r="B4" s="16"/>
       <c r="C4" s="6"/>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:8" ht="31" customHeight="1">
+    <row r="5" spans="1:8" ht="30.95" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="16"/>
       <c r="C5" s="6"/>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" ht="31" customHeight="1">
+    <row r="6" spans="1:8" ht="30.95" customHeight="1">
       <c r="A6" s="6"/>
       <c r="B6" s="72" t="s">
         <v>2</v>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" ht="31" customHeight="1">
+    <row r="7" spans="1:8" ht="30.95" customHeight="1">
       <c r="A7" s="6"/>
       <c r="B7" s="72"/>
       <c r="C7" s="6"/>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="31" customHeight="1">
+    <row r="8" spans="1:8" ht="30.95" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="65" t="s">
         <v>93</v>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:8" ht="31" customHeight="1">
+    <row r="9" spans="1:8" ht="30.95" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="66" t="s">
         <v>74</v>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" ht="31" customHeight="1">
+    <row r="10" spans="1:8" ht="30.95" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="6"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" ht="31" customHeight="1">
+    <row r="11" spans="1:8" ht="30.95" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="6"/>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" ht="31" customHeight="1">
+    <row r="12" spans="1:8" ht="30.95" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="6"/>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" ht="31" customHeight="1">
+    <row r="13" spans="1:8" ht="30.95" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="6"/>
@@ -7745,7 +7745,7 @@
       <c r="F13" s="18"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="25" customHeight="1">
+    <row r="14" spans="1:8" ht="24.95" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -7755,7 +7755,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" ht="22" customHeight="1">
+    <row r="15" spans="1:8" ht="21.95" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -7765,7 +7765,7 @@
       <c r="G15" s="69"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" ht="22" customHeight="1">
+    <row r="16" spans="1:8" ht="21.95" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -7775,7 +7775,7 @@
       <c r="G16" s="69"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" ht="22" customHeight="1">
+    <row r="17" spans="1:8" ht="21.95" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -7785,7 +7785,7 @@
       <c r="G17" s="69"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="25" customHeight="1">
+    <row r="18" spans="1:8" ht="24.95" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -7795,7 +7795,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="25" customHeight="1">
+    <row r="19" spans="1:8" ht="24.95" customHeight="1">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -7805,7 +7805,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="25" customHeight="1">
+    <row r="20" spans="1:8" ht="24.95" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7815,7 +7815,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="25" customHeight="1">
+    <row r="21" spans="1:8" ht="24.95" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -7844,7 +7844,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -7870,7 +7870,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -7906,7 +7906,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -7915,19 +7915,19 @@
         <v>92</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="14" customHeight="1">
+    <row r="5" spans="1:15" ht="14.1" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -7944,7 +7944,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="32" customHeight="1">
+    <row r="6" spans="1:15" ht="32.1" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="22" t="s">
         <v>12</v>
@@ -7954,20 +7954,20 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="74" t="s">
+      <c r="F6" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="28" customHeight="1">
+    <row r="7" spans="1:15" ht="27.95" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="23" t="s">
         <v>14</v>
@@ -7988,7 +7988,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="28" customHeight="1">
+    <row r="8" spans="1:15" ht="27.95" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="20" t="s">
         <v>15</v>
@@ -7998,23 +7998,23 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="76" t="s">
+      <c r="F8" s="80" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="77"/>
       <c r="H8" s="77"/>
-      <c r="I8" s="78">
+      <c r="I8" s="83">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>4021</v>
       </c>
-      <c r="J8" s="79"/>
+      <c r="J8" s="84"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="28" customHeight="1">
+    <row r="9" spans="1:15" ht="27.95" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="23" t="s">
         <v>17</v>
@@ -8035,7 +8035,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="28" customHeight="1">
+    <row r="10" spans="1:15" ht="27.95" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="22" t="s">
         <v>18</v>
@@ -8045,23 +8045,23 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="76" t="s">
+      <c r="F10" s="80" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="77"/>
       <c r="H10" s="77"/>
-      <c r="I10" s="78">
+      <c r="I10" s="83">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>2579.2479999999996</v>
       </c>
-      <c r="J10" s="79"/>
+      <c r="J10" s="84"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="23.15" customHeight="1">
+    <row r="11" spans="1:15" ht="23.1" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -8078,7 +8078,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="23.15" customHeight="1">
+    <row r="12" spans="1:15" ht="23.1" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -8095,7 +8095,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="32" customHeight="1">
+    <row r="13" spans="1:15" ht="32.1" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="22" t="s">
         <v>20</v>
@@ -8106,20 +8106,20 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="74" t="s">
+      <c r="F13" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="28" customHeight="1">
+    <row r="14" spans="1:15" ht="27.95" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="27" t="s">
         <v>22</v>
@@ -8130,11 +8130,11 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="80" t="s">
+      <c r="F14" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
       <c r="I14" s="29">
         <f>Samples!F165</f>
         <v>3400</v>
@@ -8148,7 +8148,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="28" customHeight="1">
+    <row r="15" spans="1:15" ht="27.95" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="22" t="s">
         <v>25</v>
@@ -8162,8 +8162,8 @@
       <c r="F15" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="82"/>
-      <c r="H15" s="82"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="78"/>
       <c r="I15" s="30">
         <f>Samples!I165</f>
         <v>3173.3333333333335</v>
@@ -8177,17 +8177,17 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="28" customHeight="1">
+    <row r="16" spans="1:15" ht="27.95" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="83" t="s">
+      <c r="F16" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
       <c r="I16" s="29">
         <f>Samples!J165</f>
         <v>1500</v>
@@ -8201,17 +8201,17 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="28" customHeight="1">
+    <row r="17" spans="1:15" ht="27.95" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="76" t="s">
+      <c r="F17" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="82"/>
-      <c r="H17" s="82"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
       <c r="I17" s="30">
         <f>Samples!L165</f>
         <v>4673.3333333333339</v>
@@ -8225,7 +8225,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="28" customHeight="1">
+    <row r="18" spans="1:15" ht="27.95" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="22" t="s">
         <v>29</v>
@@ -8247,17 +8247,17 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="28" customHeight="1">
+    <row r="19" spans="1:15" ht="27.95" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="80" t="s">
+      <c r="F19" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="76"/>
       <c r="I19" s="29">
         <f>Samples!M165</f>
         <v>2800</v>
@@ -8271,7 +8271,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="28" customHeight="1">
+    <row r="20" spans="1:15" ht="27.95" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -8280,8 +8280,8 @@
       <c r="F20" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="82"/>
-      <c r="H20" s="82"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
       <c r="I20" s="30">
         <f>Samples!P165</f>
         <v>2497.6</v>
@@ -8295,7 +8295,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" ht="28" customHeight="1">
+    <row r="21" spans="1:15" ht="27.95" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -8312,17 +8312,17 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="28" customHeight="1">
+    <row r="22" spans="1:15" ht="27.95" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="83" t="s">
+      <c r="F22" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
       <c r="I22" s="32">
         <f>Samples!G165</f>
         <v>0.1</v>
@@ -8336,17 +8336,17 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="28" customHeight="1">
+    <row r="23" spans="1:15" ht="27.95" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="76" t="s">
+      <c r="F23" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="82"/>
-      <c r="H23" s="82"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
       <c r="I23" s="33">
         <f>Samples!K165</f>
         <v>0.45</v>
@@ -8360,17 +8360,17 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="28" customHeight="1">
+    <row r="24" spans="1:15" ht="27.95" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="80" t="s">
+      <c r="F24" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
       <c r="I24" s="32">
         <f>Samples!N165</f>
         <v>0.27</v>
@@ -8384,7 +8384,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="23.15" customHeight="1">
+    <row r="25" spans="1:15" ht="23.1" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -8401,7 +8401,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="23.15" customHeight="1">
+    <row r="26" spans="1:15" ht="23.1" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -8418,26 +8418,26 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="23.15" customHeight="1">
+    <row r="27" spans="1:15" ht="23.1" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="84" t="s">
+      <c r="B27" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="85"/>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="85"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="85"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="74"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" ht="23.15" customHeight="1">
+    <row r="28" spans="1:15" ht="23.1" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -8454,7 +8454,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -8471,7 +8471,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="23.15" customHeight="1">
+    <row r="30" spans="1:15" ht="23.1" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -8488,7 +8488,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -8505,7 +8505,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -8522,7 +8522,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -8539,7 +8539,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -8556,7 +8556,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -8573,7 +8573,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -8590,7 +8590,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -8607,7 +8607,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -8624,7 +8624,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -8641,7 +8641,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -8658,7 +8658,7 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -8675,7 +8675,7 @@
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" ht="23.15" customHeight="1">
+    <row r="42" spans="1:15" ht="23.1" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -8694,17 +8694,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -8712,6 +8701,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="74" type="noConversion"/>
   <dataValidations count="5">
@@ -8743,7 +8743,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -8766,7 +8766,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>79</v>
@@ -8802,7 +8802,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8811,19 +8811,19 @@
         <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="14" customHeight="1">
+    <row r="5" spans="1:15" ht="14.1" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -8840,7 +8840,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="28" customHeight="1">
+    <row r="6" spans="1:15" ht="27.95" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="22" t="s">
         <v>37</v>
@@ -8861,7 +8861,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="23.15" customHeight="1">
+    <row r="7" spans="1:15" ht="23.1" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -8878,7 +8878,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="23.15" customHeight="1">
+    <row r="8" spans="1:15" ht="23.1" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -8895,7 +8895,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="23.15" customHeight="1">
+    <row r="9" spans="1:15" ht="23.1" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -8912,7 +8912,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="23.15" customHeight="1">
+    <row r="10" spans="1:15" ht="23.1" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -8929,7 +8929,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="23.15" customHeight="1">
+    <row r="11" spans="1:15" ht="23.1" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -8946,7 +8946,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="23.15" customHeight="1">
+    <row r="12" spans="1:15" ht="23.1" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -8963,7 +8963,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="23.15" customHeight="1">
+    <row r="13" spans="1:15" ht="23.1" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -8980,7 +8980,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="23.15" customHeight="1">
+    <row r="14" spans="1:15" ht="23.1" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -8997,7 +8997,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="23.15" customHeight="1">
+    <row r="15" spans="1:15" ht="23.1" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -9014,7 +9014,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="23.15" customHeight="1">
+    <row r="16" spans="1:15" ht="23.1" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -9031,7 +9031,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="23.15" customHeight="1">
+    <row r="17" spans="1:15" ht="23.1" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -9048,7 +9048,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="23.15" customHeight="1">
+    <row r="18" spans="1:15" ht="23.1" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -9065,7 +9065,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="23.15" customHeight="1">
+    <row r="19" spans="1:15" ht="23.1" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -9082,7 +9082,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="23.15" customHeight="1">
+    <row r="20" spans="1:15" ht="23.1" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -9099,7 +9099,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" ht="23.15" customHeight="1">
+    <row r="21" spans="1:15" ht="23.1" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -9116,7 +9116,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="23.15" customHeight="1">
+    <row r="22" spans="1:15" ht="23.1" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -9133,7 +9133,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="23.15" customHeight="1">
+    <row r="23" spans="1:15" ht="23.1" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -9150,7 +9150,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="23.15" customHeight="1">
+    <row r="24" spans="1:15" ht="23.1" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -9167,7 +9167,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="23.15" customHeight="1">
+    <row r="25" spans="1:15" ht="23.1" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -9184,7 +9184,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="23.15" customHeight="1">
+    <row r="26" spans="1:15" ht="23.1" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -9201,7 +9201,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="23.15" customHeight="1">
+    <row r="27" spans="1:15" ht="23.1" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -9218,7 +9218,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" ht="23.15" customHeight="1">
+    <row r="28" spans="1:15" ht="23.1" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -9235,7 +9235,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -9252,7 +9252,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="23.15" customHeight="1">
+    <row r="30" spans="1:15" ht="23.1" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -9269,7 +9269,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -9286,7 +9286,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -9303,7 +9303,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -9320,7 +9320,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -9337,7 +9337,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -9354,7 +9354,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -9371,7 +9371,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -9388,7 +9388,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -9405,7 +9405,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -9422,7 +9422,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -9439,24 +9439,24 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="86"/>
-      <c r="E41" s="86"/>
-      <c r="F41" s="86"/>
-      <c r="G41" s="86"/>
-      <c r="H41" s="86"/>
-      <c r="I41" s="86"/>
-      <c r="J41" s="86"/>
-      <c r="K41" s="86"/>
-      <c r="L41" s="86"/>
-      <c r="M41" s="86"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="68"/>
+      <c r="M41" s="68"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" ht="23.15" customHeight="1">
+    <row r="42" spans="1:15" ht="23.1" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -9501,7 +9501,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -9524,7 +9524,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>80</v>
@@ -9560,7 +9560,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -9569,19 +9569,19 @@
         <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="14" customHeight="1">
+    <row r="5" spans="1:15" ht="14.1" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -9598,7 +9598,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="28" customHeight="1">
+    <row r="6" spans="1:15" ht="27.95" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="22" t="s">
         <v>38</v>
@@ -9619,7 +9619,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="23.15" customHeight="1">
+    <row r="7" spans="1:15" ht="23.1" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -9636,7 +9636,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="23.15" customHeight="1">
+    <row r="8" spans="1:15" ht="23.1" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -9653,7 +9653,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="23.15" customHeight="1">
+    <row r="9" spans="1:15" ht="23.1" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -9670,7 +9670,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="23.15" customHeight="1">
+    <row r="10" spans="1:15" ht="23.1" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -9687,7 +9687,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="23.15" customHeight="1">
+    <row r="11" spans="1:15" ht="23.1" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -9704,7 +9704,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="23.15" customHeight="1">
+    <row r="12" spans="1:15" ht="23.1" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -9721,7 +9721,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="23.15" customHeight="1">
+    <row r="13" spans="1:15" ht="23.1" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -9738,7 +9738,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="23.15" customHeight="1">
+    <row r="14" spans="1:15" ht="23.1" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -9755,7 +9755,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="23.15" customHeight="1">
+    <row r="15" spans="1:15" ht="23.1" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -9772,7 +9772,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="23.15" customHeight="1">
+    <row r="16" spans="1:15" ht="23.1" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -9789,7 +9789,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="23.15" customHeight="1">
+    <row r="17" spans="1:15" ht="23.1" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -9806,7 +9806,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="23.15" customHeight="1">
+    <row r="18" spans="1:15" ht="23.1" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -9823,7 +9823,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="23.15" customHeight="1">
+    <row r="19" spans="1:15" ht="23.1" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -9840,7 +9840,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="23.15" customHeight="1">
+    <row r="20" spans="1:15" ht="23.1" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -9857,7 +9857,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" ht="23.15" customHeight="1">
+    <row r="21" spans="1:15" ht="23.1" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -9874,7 +9874,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="23.15" customHeight="1">
+    <row r="22" spans="1:15" ht="23.1" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -9891,7 +9891,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="23.15" customHeight="1">
+    <row r="23" spans="1:15" ht="23.1" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -9908,7 +9908,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="23.15" customHeight="1">
+    <row r="24" spans="1:15" ht="23.1" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -9925,7 +9925,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="23.15" customHeight="1">
+    <row r="25" spans="1:15" ht="23.1" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -9942,7 +9942,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="23.15" customHeight="1">
+    <row r="26" spans="1:15" ht="23.1" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -9959,7 +9959,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="23.15" customHeight="1">
+    <row r="27" spans="1:15" ht="23.1" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -9976,7 +9976,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" ht="23.15" customHeight="1">
+    <row r="28" spans="1:15" ht="23.1" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -9993,7 +9993,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -10010,7 +10010,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="23.15" customHeight="1">
+    <row r="30" spans="1:15" ht="23.1" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -10027,7 +10027,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -10044,7 +10044,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -10061,7 +10061,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -10078,7 +10078,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -10095,7 +10095,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -10112,7 +10112,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -10129,7 +10129,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -10146,7 +10146,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -10163,7 +10163,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -10180,7 +10180,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -10197,24 +10197,24 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="86"/>
-      <c r="E41" s="86"/>
-      <c r="F41" s="86"/>
-      <c r="G41" s="86"/>
-      <c r="H41" s="86"/>
-      <c r="I41" s="86"/>
-      <c r="J41" s="86"/>
-      <c r="K41" s="86"/>
-      <c r="L41" s="86"/>
-      <c r="M41" s="86"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="68"/>
+      <c r="M41" s="68"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" ht="23.15" customHeight="1">
+    <row r="42" spans="1:15" ht="23.1" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -10259,7 +10259,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -10282,7 +10282,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>81</v>
@@ -10318,7 +10318,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -10327,19 +10327,19 @@
         <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="14" customHeight="1">
+    <row r="5" spans="1:15" ht="14.1" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -10356,7 +10356,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="28" customHeight="1">
+    <row r="6" spans="1:15" ht="27.95" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -10373,7 +10373,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="23.15" customHeight="1">
+    <row r="7" spans="1:15" ht="23.1" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -10390,7 +10390,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="23.15" customHeight="1">
+    <row r="8" spans="1:15" ht="23.1" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -10407,7 +10407,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="23.15" customHeight="1">
+    <row r="9" spans="1:15" ht="23.1" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -10424,7 +10424,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="23.15" customHeight="1">
+    <row r="10" spans="1:15" ht="23.1" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -10441,7 +10441,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="23.15" customHeight="1">
+    <row r="11" spans="1:15" ht="23.1" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -10458,7 +10458,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="23.15" customHeight="1">
+    <row r="12" spans="1:15" ht="23.1" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -10475,7 +10475,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="23.15" customHeight="1">
+    <row r="13" spans="1:15" ht="23.1" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -10492,7 +10492,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="23.15" customHeight="1">
+    <row r="14" spans="1:15" ht="23.1" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -10509,7 +10509,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="23.15" customHeight="1">
+    <row r="15" spans="1:15" ht="23.1" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -10526,7 +10526,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="23.15" customHeight="1">
+    <row r="16" spans="1:15" ht="23.1" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -10543,7 +10543,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="23.15" customHeight="1">
+    <row r="17" spans="1:15" ht="23.1" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -10560,7 +10560,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="23.15" customHeight="1">
+    <row r="18" spans="1:15" ht="23.1" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -10577,7 +10577,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="23.15" customHeight="1">
+    <row r="19" spans="1:15" ht="23.1" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -10594,7 +10594,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="23.15" customHeight="1">
+    <row r="20" spans="1:15" ht="23.1" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -10611,7 +10611,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" ht="23.15" customHeight="1">
+    <row r="21" spans="1:15" ht="23.1" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -10628,7 +10628,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="23.15" customHeight="1">
+    <row r="22" spans="1:15" ht="23.1" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -10645,7 +10645,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="23.15" customHeight="1">
+    <row r="23" spans="1:15" ht="23.1" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -10662,7 +10662,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="23.15" customHeight="1">
+    <row r="24" spans="1:15" ht="23.1" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -10679,7 +10679,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="23.15" customHeight="1">
+    <row r="25" spans="1:15" ht="23.1" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -10696,7 +10696,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="23.15" customHeight="1">
+    <row r="26" spans="1:15" ht="23.1" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -10713,7 +10713,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="23.15" customHeight="1">
+    <row r="27" spans="1:15" ht="23.1" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -10730,7 +10730,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" ht="23.15" customHeight="1">
+    <row r="28" spans="1:15" ht="23.1" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -10747,7 +10747,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -10764,7 +10764,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="23.15" customHeight="1">
+    <row r="30" spans="1:15" ht="23.1" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -10781,7 +10781,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -10798,7 +10798,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -10815,7 +10815,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -10832,7 +10832,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -10849,7 +10849,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -10866,7 +10866,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -10883,7 +10883,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -10900,7 +10900,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -10917,7 +10917,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -10934,7 +10934,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -10951,24 +10951,24 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="86"/>
-      <c r="E41" s="86"/>
-      <c r="F41" s="86"/>
-      <c r="G41" s="86"/>
-      <c r="H41" s="86"/>
-      <c r="I41" s="86"/>
-      <c r="J41" s="86"/>
-      <c r="K41" s="86"/>
-      <c r="L41" s="86"/>
-      <c r="M41" s="86"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="68"/>
+      <c r="M41" s="68"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" ht="23.15" customHeight="1">
+    <row r="42" spans="1:15" ht="23.1" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -11009,7 +11009,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -11032,7 +11032,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>82</v>
@@ -11068,7 +11068,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -11077,19 +11077,19 @@
         <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="14" customHeight="1">
+    <row r="5" spans="1:15" ht="14.1" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -11106,7 +11106,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="28" customHeight="1">
+    <row r="6" spans="1:15" ht="27.95" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -11123,7 +11123,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="23.15" customHeight="1">
+    <row r="7" spans="1:15" ht="23.1" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -11140,7 +11140,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="23.15" customHeight="1">
+    <row r="8" spans="1:15" ht="23.1" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -11157,7 +11157,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="23.15" customHeight="1">
+    <row r="9" spans="1:15" ht="23.1" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -11174,7 +11174,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="23.15" customHeight="1">
+    <row r="10" spans="1:15" ht="23.1" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -11191,7 +11191,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="23.15" customHeight="1">
+    <row r="11" spans="1:15" ht="23.1" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -11208,7 +11208,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="23.15" customHeight="1">
+    <row r="12" spans="1:15" ht="23.1" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -11225,7 +11225,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="23.15" customHeight="1">
+    <row r="13" spans="1:15" ht="23.1" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -11242,7 +11242,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="23.15" customHeight="1">
+    <row r="14" spans="1:15" ht="23.1" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -11259,7 +11259,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="23.15" customHeight="1">
+    <row r="15" spans="1:15" ht="23.1" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -11276,7 +11276,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="23.15" customHeight="1">
+    <row r="16" spans="1:15" ht="23.1" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -11293,7 +11293,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="23.15" customHeight="1">
+    <row r="17" spans="1:15" ht="23.1" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -11310,7 +11310,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="23.15" customHeight="1">
+    <row r="18" spans="1:15" ht="23.1" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -11327,7 +11327,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="23.15" customHeight="1">
+    <row r="19" spans="1:15" ht="23.1" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -11344,7 +11344,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="23.15" customHeight="1">
+    <row r="20" spans="1:15" ht="23.1" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -11361,7 +11361,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" ht="23.15" customHeight="1">
+    <row r="21" spans="1:15" ht="23.1" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -11378,7 +11378,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="23.15" customHeight="1">
+    <row r="22" spans="1:15" ht="23.1" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -11395,7 +11395,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="23.15" customHeight="1">
+    <row r="23" spans="1:15" ht="23.1" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -11412,7 +11412,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="23.15" customHeight="1">
+    <row r="24" spans="1:15" ht="23.1" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -11429,7 +11429,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="23.15" customHeight="1">
+    <row r="25" spans="1:15" ht="23.1" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -11446,7 +11446,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="23.15" customHeight="1">
+    <row r="26" spans="1:15" ht="23.1" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -11463,7 +11463,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="23.15" customHeight="1">
+    <row r="27" spans="1:15" ht="23.1" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -11480,7 +11480,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" ht="23.15" customHeight="1">
+    <row r="28" spans="1:15" ht="23.1" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -11497,7 +11497,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -11514,7 +11514,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="23.15" customHeight="1">
+    <row r="30" spans="1:15" ht="23.1" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -11531,7 +11531,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -11548,7 +11548,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -11565,7 +11565,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -11582,7 +11582,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -11599,7 +11599,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -11616,7 +11616,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -11633,7 +11633,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -11650,7 +11650,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -11667,7 +11667,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -11684,7 +11684,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -11701,24 +11701,24 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="86"/>
-      <c r="E41" s="86"/>
-      <c r="F41" s="86"/>
-      <c r="G41" s="86"/>
-      <c r="H41" s="86"/>
-      <c r="I41" s="86"/>
-      <c r="J41" s="86"/>
-      <c r="K41" s="86"/>
-      <c r="L41" s="86"/>
-      <c r="M41" s="86"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="68"/>
+      <c r="M41" s="68"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" ht="23.15" customHeight="1">
+    <row r="42" spans="1:15" ht="23.1" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -11759,7 +11759,7 @@
     <tabColor rgb="FFC49A32"/>
   </sheetPr>
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -11786,7 +11786,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>83</v>
@@ -11807,24 +11807,24 @@
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -11841,25 +11841,25 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="32" customHeight="1">
+    <row r="5" spans="1:15" ht="32.1" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="75" t="s">
+      <c r="D5" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="75" t="s">
+      <c r="J5" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="82"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="29" customHeight="1">
+    <row r="7" spans="1:15" ht="29.1" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="20" t="s">
         <v>14</v>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="29" customHeight="1">
+    <row r="8" spans="1:15" ht="29.1" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="23" t="s">
         <v>15</v>
@@ -12027,7 +12027,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="29" customHeight="1">
+    <row r="10" spans="1:15" ht="29.1" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="20" t="s">
         <v>23</v>
@@ -12072,7 +12072,7 @@
       </c>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="29" customHeight="1">
+    <row r="11" spans="1:15" ht="29.1" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="27" t="s">
         <v>32</v>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="29" customHeight="1">
+    <row r="12" spans="1:15" ht="29.1" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="20" t="s">
         <v>44</v>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="29" customHeight="1">
+    <row r="13" spans="1:15" ht="29.1" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="27" t="s">
         <v>27</v>
@@ -12207,7 +12207,7 @@
       </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="29" customHeight="1">
+    <row r="14" spans="1:15" ht="29.1" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="22" t="s">
         <v>34</v>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="29" customHeight="1">
+    <row r="17" spans="1:15" ht="29.1" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="20" t="s">
         <v>30</v>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="29" customHeight="1">
+    <row r="18" spans="1:15" ht="29.1" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="23" t="s">
         <v>35</v>
@@ -12412,7 +12412,7 @@
       </c>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="29" customHeight="1">
+    <row r="19" spans="1:15" ht="29.1" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="20" t="s">
         <v>46</v>
@@ -12491,75 +12491,75 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="32" customHeight="1">
+    <row r="22" spans="1:15" ht="32.1" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="75"/>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
-      <c r="M22" s="75"/>
-      <c r="N22" s="75"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="82"/>
+      <c r="K22" s="82"/>
+      <c r="L22" s="82"/>
+      <c r="M22" s="82"/>
+      <c r="N22" s="82"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="29" customHeight="1">
+    <row r="23" spans="1:15" ht="29.1" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="81"/>
+      <c r="C23" s="76"/>
       <c r="D23" s="26">
         <v>24</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="89" t="s">
+      <c r="F23" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="90"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="90"/>
-      <c r="K23" s="90"/>
-      <c r="L23" s="90"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="90"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="92"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="92"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="29" customHeight="1">
+    <row r="24" spans="1:15" ht="29.1" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="82"/>
+      <c r="C24" s="78"/>
       <c r="D24" s="28">
         <v>20</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="90"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="90"/>
-      <c r="K24" s="90"/>
-      <c r="L24" s="90"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="90"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="92"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="92"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="29" customHeight="1">
+    <row r="25" spans="1:15" ht="29.1" customHeight="1">
       <c r="A25" s="2"/>
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="81"/>
+      <c r="C25" s="76"/>
       <c r="D25" s="26">
         <v>40</v>
       </c>
@@ -12575,35 +12575,35 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="29" customHeight="1">
+    <row r="26" spans="1:15" ht="29.1" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="82"/>
+      <c r="C26" s="78"/>
       <c r="D26" s="28">
         <v>40</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="91" t="s">
+      <c r="F26" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="G26" s="88"/>
-      <c r="H26" s="88"/>
-      <c r="I26" s="88"/>
-      <c r="J26" s="88"/>
-      <c r="K26" s="88"/>
-      <c r="L26" s="88"/>
-      <c r="M26" s="88"/>
-      <c r="N26" s="88"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="90"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="90"/>
+      <c r="K26" s="90"/>
+      <c r="L26" s="90"/>
+      <c r="M26" s="90"/>
+      <c r="N26" s="90"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="29" customHeight="1">
+    <row r="27" spans="1:15" ht="29.1" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="82"/>
+      <c r="C27" s="78"/>
       <c r="D27" s="28">
         <v>10</v>
       </c>
@@ -12621,143 +12621,143 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="93" t="s">
+      <c r="B28" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="94"/>
-      <c r="D28" s="94"/>
-      <c r="E28" s="94"/>
-      <c r="F28" s="94"/>
-      <c r="G28" s="94"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="94"/>
-      <c r="K28" s="94"/>
-      <c r="L28" s="94"/>
-      <c r="M28" s="94"/>
-      <c r="N28" s="94"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="87"/>
+      <c r="J28" s="87"/>
+      <c r="K28" s="87"/>
+      <c r="L28" s="87"/>
+      <c r="M28" s="87"/>
+      <c r="N28" s="87"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="2"/>
-      <c r="B29" s="92"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="92"/>
-      <c r="H29" s="92"/>
-      <c r="I29" s="92"/>
-      <c r="J29" s="92"/>
-      <c r="K29" s="92"/>
-      <c r="L29" s="92"/>
-      <c r="M29" s="92"/>
-      <c r="N29" s="92"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+      <c r="G29" s="85"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="85"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="85"/>
+      <c r="N29" s="85"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="31" customHeight="1">
+    <row r="30" spans="1:15" ht="30.95" customHeight="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="95"/>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
-      <c r="I30" s="95"/>
-      <c r="J30" s="95"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="95"/>
-      <c r="M30" s="95"/>
-      <c r="N30" s="95"/>
+      <c r="B30" s="88"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="88"/>
+      <c r="I30" s="88"/>
+      <c r="J30" s="88"/>
+      <c r="K30" s="88"/>
+      <c r="L30" s="88"/>
+      <c r="M30" s="88"/>
+      <c r="N30" s="88"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="92"/>
-      <c r="C31" s="92"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="92"/>
-      <c r="H31" s="92"/>
-      <c r="I31" s="92"/>
-      <c r="J31" s="92"/>
-      <c r="K31" s="92"/>
-      <c r="L31" s="92"/>
-      <c r="M31" s="92"/>
-      <c r="N31" s="92"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="2"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="92"/>
-      <c r="G32" s="92"/>
-      <c r="H32" s="92"/>
-      <c r="I32" s="92"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92"/>
-      <c r="M32" s="92"/>
-      <c r="N32" s="92"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="85"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="85"/>
+      <c r="G32" s="85"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="85"/>
+      <c r="J32" s="85"/>
+      <c r="K32" s="85"/>
+      <c r="L32" s="85"/>
+      <c r="M32" s="85"/>
+      <c r="N32" s="85"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="92"/>
-      <c r="G33" s="92"/>
-      <c r="H33" s="92"/>
-      <c r="I33" s="92"/>
-      <c r="J33" s="92"/>
-      <c r="K33" s="92"/>
-      <c r="L33" s="92"/>
-      <c r="M33" s="92"/>
-      <c r="N33" s="92"/>
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+      <c r="G33" s="85"/>
+      <c r="H33" s="85"/>
+      <c r="I33" s="85"/>
+      <c r="J33" s="85"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="85"/>
+      <c r="N33" s="85"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="92"/>
-      <c r="G34" s="92"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="92"/>
-      <c r="J34" s="92"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="92"/>
-      <c r="M34" s="92"/>
-      <c r="N34" s="92"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="85"/>
+      <c r="G34" s="85"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
+      <c r="K34" s="85"/>
+      <c r="L34" s="85"/>
+      <c r="M34" s="85"/>
+      <c r="N34" s="85"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="2"/>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="92"/>
-      <c r="H35" s="92"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="92"/>
-      <c r="M35" s="92"/>
-      <c r="N35" s="92"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="85"/>
+      <c r="D35" s="85"/>
+      <c r="E35" s="85"/>
+      <c r="F35" s="85"/>
+      <c r="G35" s="85"/>
+      <c r="H35" s="85"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="85"/>
+      <c r="K35" s="85"/>
+      <c r="L35" s="85"/>
+      <c r="M35" s="85"/>
+      <c r="N35" s="85"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -12774,7 +12774,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -12791,7 +12791,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -12808,7 +12808,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -12825,7 +12825,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -12842,7 +12842,7 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -12861,14 +12861,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -12881,6 +12873,14 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
   </mergeCells>
   <phoneticPr fontId="74" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12893,14 +12893,14 @@
     <tabColor rgb="FF93A0AC"/>
   </sheetPr>
   <dimension ref="A1:V165"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="22" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="32" customHeight="1">
+    <row r="1" spans="1:22" ht="32.1" customHeight="1">
       <c r="A1" s="2"/>
       <c r="B1" s="1" t="s">
         <v>50</v>
@@ -12918,15 +12918,15 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-    </row>
-    <row r="2" spans="1:22" ht="22" customHeight="1">
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
+      <c r="R1" s="94"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="94"/>
+      <c r="V1" s="94"/>
+    </row>
+    <row r="2" spans="1:22" ht="21.95" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -12950,7 +12950,7 @@
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
     </row>
-    <row r="3" spans="1:22" ht="22" customHeight="1">
+    <row r="3" spans="1:22" ht="21.95" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -12974,7 +12974,7 @@
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
     </row>
-    <row r="4" spans="1:22" ht="44" customHeight="1">
+    <row r="4" spans="1:22" ht="44.1" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="38" t="s">
         <v>51</v>
@@ -13040,7 +13040,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="25" customHeight="1">
+    <row r="5" spans="1:22" ht="24.95" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="42" t="str">
         <f>"c "&amp;C5</f>
@@ -13127,7 +13127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="25" customHeight="1">
+    <row r="6" spans="1:22" ht="24.95" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="44" t="str">
         <f>"c "&amp;C6</f>
@@ -13214,7 +13214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="25" customHeight="1">
+    <row r="7" spans="1:22" ht="24.95" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="42" t="str">
         <f>"c "&amp;C7</f>
@@ -13301,7 +13301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="25" customHeight="1">
+    <row r="8" spans="1:22" ht="24.95" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="44" t="str">
         <f>"c "&amp;C8</f>
@@ -13388,7 +13388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="25" customHeight="1">
+    <row r="9" spans="1:22" ht="24.95" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="42" t="str">
         <f>"c "&amp;C9</f>
@@ -13475,7 +13475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="22" customHeight="1">
+    <row r="10" spans="1:22" ht="21.95" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -13499,7 +13499,7 @@
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
     </row>
-    <row r="11" spans="1:22" ht="22" customHeight="1">
+    <row r="11" spans="1:22" ht="21.95" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -13523,7 +13523,7 @@
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
     </row>
-    <row r="12" spans="1:22" ht="22" customHeight="1">
+    <row r="12" spans="1:22" ht="21.95" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -13588,7 +13588,7 @@
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
     </row>
-    <row r="14" spans="1:22" ht="25" customHeight="1">
+    <row r="14" spans="1:22" ht="24.95" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="48">
         <v>0</v>
@@ -13629,7 +13629,7 @@
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
     </row>
-    <row r="15" spans="1:22" ht="25" customHeight="1">
+    <row r="15" spans="1:22" ht="24.95" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="49">
         <v>0.05</v>
@@ -13670,7 +13670,7 @@
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
     </row>
-    <row r="16" spans="1:22" ht="25" customHeight="1">
+    <row r="16" spans="1:22" ht="24.95" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="48">
         <v>0.1</v>
@@ -13711,7 +13711,7 @@
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
     </row>
-    <row r="17" spans="1:22" ht="25" customHeight="1">
+    <row r="17" spans="1:22" ht="24.95" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="49">
         <v>0.15</v>
@@ -13752,7 +13752,7 @@
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
     </row>
-    <row r="18" spans="1:22" ht="25" customHeight="1">
+    <row r="18" spans="1:22" ht="24.95" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="48">
         <v>0.2</v>
@@ -13793,7 +13793,7 @@
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
     </row>
-    <row r="19" spans="1:22" ht="25" customHeight="1">
+    <row r="19" spans="1:22" ht="24.95" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="49">
         <v>0.25</v>
@@ -13834,7 +13834,7 @@
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
     </row>
-    <row r="20" spans="1:22" ht="25" customHeight="1">
+    <row r="20" spans="1:22" ht="24.95" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="48">
         <v>0.3</v>
@@ -13875,7 +13875,7 @@
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
     </row>
-    <row r="21" spans="1:22" ht="25" customHeight="1">
+    <row r="21" spans="1:22" ht="24.95" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="49">
         <v>0.35</v>
@@ -13916,7 +13916,7 @@
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
     </row>
-    <row r="22" spans="1:22" ht="25" customHeight="1">
+    <row r="22" spans="1:22" ht="24.95" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="48">
         <v>0.4</v>
@@ -13957,7 +13957,7 @@
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
     </row>
-    <row r="23" spans="1:22" ht="25" customHeight="1">
+    <row r="23" spans="1:22" ht="24.95" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="49">
         <v>0.45</v>
@@ -13998,7 +13998,7 @@
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
     </row>
-    <row r="24" spans="1:22" ht="25" customHeight="1">
+    <row r="24" spans="1:22" ht="24.95" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="48">
         <v>0.5</v>
@@ -14039,7 +14039,7 @@
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
     </row>
-    <row r="25" spans="1:22" ht="25" customHeight="1">
+    <row r="25" spans="1:22" ht="24.95" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="49">
         <v>0.55000000000000004</v>
@@ -14080,7 +14080,7 @@
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
     </row>
-    <row r="26" spans="1:22" ht="25" customHeight="1">
+    <row r="26" spans="1:22" ht="24.95" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="48">
         <v>0.6</v>
@@ -14121,7 +14121,7 @@
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
     </row>
-    <row r="27" spans="1:22" ht="25" customHeight="1">
+    <row r="27" spans="1:22" ht="24.95" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="49">
         <v>0.65</v>
@@ -14162,7 +14162,7 @@
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
     </row>
-    <row r="28" spans="1:22" ht="25" customHeight="1">
+    <row r="28" spans="1:22" ht="24.95" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="48">
         <v>0.7</v>
@@ -14203,7 +14203,7 @@
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
     </row>
-    <row r="29" spans="1:22" ht="25" customHeight="1">
+    <row r="29" spans="1:22" ht="24.95" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="49">
         <v>0.75</v>
@@ -14244,7 +14244,7 @@
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
     </row>
-    <row r="30" spans="1:22" ht="25" customHeight="1">
+    <row r="30" spans="1:22" ht="24.95" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="48">
         <v>0.8</v>
@@ -14285,7 +14285,7 @@
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
     </row>
-    <row r="31" spans="1:22" ht="25" customHeight="1">
+    <row r="31" spans="1:22" ht="24.95" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="49">
         <v>0.85</v>
@@ -14326,7 +14326,7 @@
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
     </row>
-    <row r="32" spans="1:22" ht="25" customHeight="1">
+    <row r="32" spans="1:22" ht="24.95" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="48">
         <v>0.9</v>
@@ -14367,7 +14367,7 @@
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
     </row>
-    <row r="33" spans="1:22" ht="25" customHeight="1">
+    <row r="33" spans="1:22" ht="24.95" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="49">
         <v>0.95</v>
@@ -14408,7 +14408,7 @@
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
     </row>
-    <row r="34" spans="1:22" ht="25" customHeight="1">
+    <row r="34" spans="1:22" ht="24.95" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="48">
         <v>1</v>
@@ -14449,7 +14449,7 @@
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
     </row>
-    <row r="35" spans="1:22" ht="22" customHeight="1">
+    <row r="35" spans="1:22" ht="21.95" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -14473,7 +14473,7 @@
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
     </row>
-    <row r="36" spans="1:22" ht="22" customHeight="1">
+    <row r="36" spans="1:22" ht="21.95" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -14497,7 +14497,7 @@
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
     </row>
-    <row r="37" spans="1:22" ht="22" customHeight="1">
+    <row r="37" spans="1:22" ht="21.95" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -14521,7 +14521,7 @@
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
     </row>
-    <row r="38" spans="1:22" ht="22" customHeight="1">
+    <row r="38" spans="1:22" ht="21.95" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -14545,7 +14545,7 @@
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
     </row>
-    <row r="39" spans="1:22" ht="22" customHeight="1">
+    <row r="39" spans="1:22" ht="21.95" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -14569,7 +14569,7 @@
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
     </row>
-    <row r="40" spans="1:22" ht="22" customHeight="1">
+    <row r="40" spans="1:22" ht="21.95" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -14593,7 +14593,7 @@
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
     </row>
-    <row r="41" spans="1:22" ht="32" customHeight="1">
+    <row r="41" spans="1:22" ht="32.1" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="1" t="s">
         <v>65</v>
@@ -14611,15 +14611,15 @@
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
-      <c r="P41" s="67"/>
-      <c r="Q41" s="67"/>
-      <c r="R41" s="67"/>
-      <c r="S41" s="67"/>
-      <c r="T41" s="67"/>
-      <c r="U41" s="67"/>
-      <c r="V41" s="67"/>
-    </row>
-    <row r="42" spans="1:22" ht="22" customHeight="1">
+      <c r="P41" s="94"/>
+      <c r="Q41" s="94"/>
+      <c r="R41" s="94"/>
+      <c r="S41" s="94"/>
+      <c r="T41" s="94"/>
+      <c r="U41" s="94"/>
+      <c r="V41" s="94"/>
+    </row>
+    <row r="42" spans="1:22" ht="21.95" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -14643,7 +14643,7 @@
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
     </row>
-    <row r="43" spans="1:22" ht="22" customHeight="1">
+    <row r="43" spans="1:22" ht="21.95" customHeight="1">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -14666,7 +14666,7 @@
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
     </row>
-    <row r="44" spans="1:22" ht="44" customHeight="1">
+    <row r="44" spans="1:22" ht="44.1" customHeight="1">
       <c r="B44" s="41" t="s">
         <v>51</v>
       </c>
@@ -14731,7 +14731,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:22" ht="25" customHeight="1">
+    <row r="45" spans="1:22" ht="24.95" customHeight="1">
       <c r="B45" s="43" t="str">
         <f>"C "&amp;D45</f>
         <v>C -20</v>
@@ -14817,7 +14817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="25" customHeight="1">
+    <row r="46" spans="1:22" ht="24.95" customHeight="1">
       <c r="B46" s="45" t="str">
         <f>"C "&amp;D46</f>
         <v>C -15</v>
@@ -14903,7 +14903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="25" customHeight="1">
+    <row r="47" spans="1:22" ht="24.95" customHeight="1">
       <c r="B47" s="43" t="str">
         <f>"C "&amp;D47</f>
         <v>C -10</v>
@@ -14989,7 +14989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:22" ht="25" customHeight="1">
+    <row r="48" spans="1:22" ht="24.95" customHeight="1">
       <c r="B48" s="45" t="str">
         <f>"C "&amp;D48</f>
         <v>C -5</v>
@@ -15075,7 +15075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22" ht="25" customHeight="1">
+    <row r="49" spans="2:22" ht="24.95" customHeight="1">
       <c r="B49" s="43" t="str">
         <f>"C "&amp;D49</f>
         <v>C 0</v>
@@ -15161,7 +15161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:22" ht="22" customHeight="1">
+    <row r="50" spans="2:22" ht="21.95" customHeight="1">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -15184,7 +15184,7 @@
       <c r="U50" s="4"/>
       <c r="V50" s="4"/>
     </row>
-    <row r="51" spans="2:22" ht="22" customHeight="1">
+    <row r="51" spans="2:22" ht="21.95" customHeight="1">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -15207,7 +15207,7 @@
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
     </row>
-    <row r="52" spans="2:22" ht="22" customHeight="1">
+    <row r="52" spans="2:22" ht="21.95" customHeight="1">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -15270,7 +15270,7 @@
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
     </row>
-    <row r="54" spans="2:22" ht="25" customHeight="1">
+    <row r="54" spans="2:22" ht="24.95" customHeight="1">
       <c r="B54" s="52">
         <v>0</v>
       </c>
@@ -15310,7 +15310,7 @@
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
     </row>
-    <row r="55" spans="2:22" ht="25" customHeight="1">
+    <row r="55" spans="2:22" ht="24.95" customHeight="1">
       <c r="B55" s="53">
         <v>0.05</v>
       </c>
@@ -15350,7 +15350,7 @@
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
     </row>
-    <row r="56" spans="2:22" ht="25" customHeight="1">
+    <row r="56" spans="2:22" ht="24.95" customHeight="1">
       <c r="B56" s="52">
         <v>0.1</v>
       </c>
@@ -15390,7 +15390,7 @@
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
     </row>
-    <row r="57" spans="2:22" ht="25" customHeight="1">
+    <row r="57" spans="2:22" ht="24.95" customHeight="1">
       <c r="B57" s="53">
         <v>0.15</v>
       </c>
@@ -15430,7 +15430,7 @@
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
     </row>
-    <row r="58" spans="2:22" ht="25" customHeight="1">
+    <row r="58" spans="2:22" ht="24.95" customHeight="1">
       <c r="B58" s="52">
         <v>0.2</v>
       </c>
@@ -15470,7 +15470,7 @@
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
     </row>
-    <row r="59" spans="2:22" ht="25" customHeight="1">
+    <row r="59" spans="2:22" ht="24.95" customHeight="1">
       <c r="B59" s="53">
         <v>0.25</v>
       </c>
@@ -15510,7 +15510,7 @@
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
     </row>
-    <row r="60" spans="2:22" ht="25" customHeight="1">
+    <row r="60" spans="2:22" ht="24.95" customHeight="1">
       <c r="B60" s="52">
         <v>0.3</v>
       </c>
@@ -15550,7 +15550,7 @@
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
     </row>
-    <row r="61" spans="2:22" ht="25" customHeight="1">
+    <row r="61" spans="2:22" ht="24.95" customHeight="1">
       <c r="B61" s="53">
         <v>0.35</v>
       </c>
@@ -15590,7 +15590,7 @@
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
     </row>
-    <row r="62" spans="2:22" ht="25" customHeight="1">
+    <row r="62" spans="2:22" ht="24.95" customHeight="1">
       <c r="B62" s="52">
         <v>0.4</v>
       </c>
@@ -15630,7 +15630,7 @@
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
     </row>
-    <row r="63" spans="2:22" ht="25" customHeight="1">
+    <row r="63" spans="2:22" ht="24.95" customHeight="1">
       <c r="B63" s="53">
         <v>0.45</v>
       </c>
@@ -15670,7 +15670,7 @@
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
     </row>
-    <row r="64" spans="2:22" ht="25" customHeight="1">
+    <row r="64" spans="2:22" ht="24.95" customHeight="1">
       <c r="B64" s="52">
         <v>0.5</v>
       </c>
@@ -15710,7 +15710,7 @@
       <c r="U64" s="4"/>
       <c r="V64" s="4"/>
     </row>
-    <row r="65" spans="2:22" ht="25" customHeight="1">
+    <row r="65" spans="2:22" ht="24.95" customHeight="1">
       <c r="B65" s="53">
         <v>0.55000000000000004</v>
       </c>
@@ -15750,7 +15750,7 @@
       <c r="U65" s="4"/>
       <c r="V65" s="4"/>
     </row>
-    <row r="66" spans="2:22" ht="25" customHeight="1">
+    <row r="66" spans="2:22" ht="24.95" customHeight="1">
       <c r="B66" s="52">
         <v>0.6</v>
       </c>
@@ -15790,7 +15790,7 @@
       <c r="U66" s="4"/>
       <c r="V66" s="4"/>
     </row>
-    <row r="67" spans="2:22" ht="25" customHeight="1">
+    <row r="67" spans="2:22" ht="24.95" customHeight="1">
       <c r="B67" s="53">
         <v>0.65</v>
       </c>
@@ -15830,7 +15830,7 @@
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
     </row>
-    <row r="68" spans="2:22" ht="25" customHeight="1">
+    <row r="68" spans="2:22" ht="24.95" customHeight="1">
       <c r="B68" s="52">
         <v>0.7</v>
       </c>
@@ -15870,7 +15870,7 @@
       <c r="U68" s="4"/>
       <c r="V68" s="4"/>
     </row>
-    <row r="69" spans="2:22" ht="25" customHeight="1">
+    <row r="69" spans="2:22" ht="24.95" customHeight="1">
       <c r="B69" s="53">
         <v>0.75</v>
       </c>
@@ -15910,7 +15910,7 @@
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
     </row>
-    <row r="70" spans="2:22" ht="25" customHeight="1">
+    <row r="70" spans="2:22" ht="24.95" customHeight="1">
       <c r="B70" s="52">
         <v>0.8</v>
       </c>
@@ -15950,7 +15950,7 @@
       <c r="U70" s="4"/>
       <c r="V70" s="4"/>
     </row>
-    <row r="71" spans="2:22" ht="25" customHeight="1">
+    <row r="71" spans="2:22" ht="24.95" customHeight="1">
       <c r="B71" s="53">
         <v>0.85</v>
       </c>
@@ -15990,7 +15990,7 @@
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
     </row>
-    <row r="72" spans="2:22" ht="25" customHeight="1">
+    <row r="72" spans="2:22" ht="24.95" customHeight="1">
       <c r="B72" s="52">
         <v>0.9</v>
       </c>
@@ -16030,7 +16030,7 @@
       <c r="U72" s="4"/>
       <c r="V72" s="4"/>
     </row>
-    <row r="73" spans="2:22" ht="25" customHeight="1">
+    <row r="73" spans="2:22" ht="24.95" customHeight="1">
       <c r="B73" s="53">
         <v>0.95</v>
       </c>
@@ -16070,7 +16070,7 @@
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
     </row>
-    <row r="74" spans="2:22" ht="25" customHeight="1">
+    <row r="74" spans="2:22" ht="24.95" customHeight="1">
       <c r="B74" s="52">
         <v>1</v>
       </c>
@@ -16110,7 +16110,7 @@
       <c r="U74" s="4"/>
       <c r="V74" s="4"/>
     </row>
-    <row r="75" spans="2:22" ht="22" customHeight="1">
+    <row r="75" spans="2:22" ht="21.95" customHeight="1">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -16133,7 +16133,7 @@
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
     </row>
-    <row r="76" spans="2:22" ht="22" customHeight="1">
+    <row r="76" spans="2:22" ht="21.95" customHeight="1">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -16156,7 +16156,7 @@
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
     </row>
-    <row r="77" spans="2:22" ht="22" customHeight="1">
+    <row r="77" spans="2:22" ht="21.95" customHeight="1">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -16179,7 +16179,7 @@
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
     </row>
-    <row r="78" spans="2:22" ht="22" customHeight="1">
+    <row r="78" spans="2:22" ht="21.95" customHeight="1">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -16202,7 +16202,7 @@
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
     </row>
-    <row r="79" spans="2:22" ht="22" customHeight="1">
+    <row r="79" spans="2:22" ht="21.95" customHeight="1">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -16225,7 +16225,7 @@
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
     </row>
-    <row r="80" spans="2:22" ht="22" customHeight="1">
+    <row r="80" spans="2:22" ht="21.95" customHeight="1">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -16248,32 +16248,32 @@
       <c r="U80" s="4"/>
       <c r="V80" s="4"/>
     </row>
-    <row r="81" spans="2:22" ht="32" customHeight="1">
-      <c r="B81" s="67" t="s">
+    <row r="81" spans="2:22" ht="32.1" customHeight="1">
+      <c r="B81" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="C81" s="67"/>
-      <c r="D81" s="67"/>
-      <c r="E81" s="67"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="67"/>
-      <c r="H81" s="67"/>
-      <c r="I81" s="67"/>
-      <c r="J81" s="67"/>
-      <c r="K81" s="67"/>
-      <c r="L81" s="67"/>
-      <c r="M81" s="67"/>
-      <c r="N81" s="67"/>
-      <c r="O81" s="67"/>
-      <c r="P81" s="67"/>
-      <c r="Q81" s="67"/>
-      <c r="R81" s="67"/>
-      <c r="S81" s="67"/>
-      <c r="T81" s="67"/>
-      <c r="U81" s="67"/>
-      <c r="V81" s="67"/>
-    </row>
-    <row r="82" spans="2:22" ht="22" customHeight="1">
+      <c r="C81" s="94"/>
+      <c r="D81" s="94"/>
+      <c r="E81" s="94"/>
+      <c r="F81" s="94"/>
+      <c r="G81" s="94"/>
+      <c r="H81" s="94"/>
+      <c r="I81" s="94"/>
+      <c r="J81" s="94"/>
+      <c r="K81" s="94"/>
+      <c r="L81" s="94"/>
+      <c r="M81" s="94"/>
+      <c r="N81" s="94"/>
+      <c r="O81" s="94"/>
+      <c r="P81" s="94"/>
+      <c r="Q81" s="94"/>
+      <c r="R81" s="94"/>
+      <c r="S81" s="94"/>
+      <c r="T81" s="94"/>
+      <c r="U81" s="94"/>
+      <c r="V81" s="94"/>
+    </row>
+    <row r="82" spans="2:22" ht="21.95" customHeight="1">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -16296,7 +16296,7 @@
       <c r="U82" s="4"/>
       <c r="V82" s="4"/>
     </row>
-    <row r="83" spans="2:22" ht="22" customHeight="1">
+    <row r="83" spans="2:22" ht="21.95" customHeight="1">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -16319,7 +16319,7 @@
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
     </row>
-    <row r="84" spans="2:22" ht="44" customHeight="1">
+    <row r="84" spans="2:22" ht="44.1" customHeight="1">
       <c r="B84" s="41" t="s">
         <v>51</v>
       </c>
@@ -16384,7 +16384,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="2:22" ht="25" customHeight="1">
+    <row r="85" spans="2:22" ht="24.95" customHeight="1">
       <c r="B85" s="43" t="str">
         <f>"R "&amp;E85</f>
         <v>R -40</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:22" ht="25" customHeight="1">
+    <row r="86" spans="2:22" ht="24.95" customHeight="1">
       <c r="B86" s="45" t="str">
         <f>"R "&amp;E86</f>
         <v>R -30</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:22" ht="25" customHeight="1">
+    <row r="87" spans="2:22" ht="24.95" customHeight="1">
       <c r="B87" s="43" t="str">
         <f>"R "&amp;E87</f>
         <v>R -20</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:22" ht="25" customHeight="1">
+    <row r="88" spans="2:22" ht="24.95" customHeight="1">
       <c r="B88" s="45" t="str">
         <f>"R "&amp;E88</f>
         <v>R -10</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:22" ht="25" customHeight="1">
+    <row r="89" spans="2:22" ht="24.95" customHeight="1">
       <c r="B89" s="43" t="str">
         <f>"R "&amp;E89</f>
         <v>R 0</v>
@@ -16814,7 +16814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:22" ht="22" customHeight="1">
+    <row r="90" spans="2:22" ht="21.95" customHeight="1">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -16837,7 +16837,7 @@
       <c r="U90" s="4"/>
       <c r="V90" s="4"/>
     </row>
-    <row r="91" spans="2:22" ht="22" customHeight="1">
+    <row r="91" spans="2:22" ht="21.95" customHeight="1">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -16860,7 +16860,7 @@
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
     </row>
-    <row r="92" spans="2:22" ht="22" customHeight="1">
+    <row r="92" spans="2:22" ht="21.95" customHeight="1">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -16923,7 +16923,7 @@
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
     </row>
-    <row r="94" spans="2:22" ht="25" customHeight="1">
+    <row r="94" spans="2:22" ht="24.95" customHeight="1">
       <c r="B94" s="52">
         <v>0</v>
       </c>
@@ -16963,7 +16963,7 @@
       <c r="U94" s="4"/>
       <c r="V94" s="4"/>
     </row>
-    <row r="95" spans="2:22" ht="25" customHeight="1">
+    <row r="95" spans="2:22" ht="24.95" customHeight="1">
       <c r="B95" s="53">
         <v>0.05</v>
       </c>
@@ -17003,7 +17003,7 @@
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
     </row>
-    <row r="96" spans="2:22" ht="25" customHeight="1">
+    <row r="96" spans="2:22" ht="24.95" customHeight="1">
       <c r="B96" s="52">
         <v>0.1</v>
       </c>
@@ -17043,7 +17043,7 @@
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
     </row>
-    <row r="97" spans="2:22" ht="25" customHeight="1">
+    <row r="97" spans="2:22" ht="24.95" customHeight="1">
       <c r="B97" s="53">
         <v>0.15</v>
       </c>
@@ -17083,7 +17083,7 @@
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
     </row>
-    <row r="98" spans="2:22" ht="25" customHeight="1">
+    <row r="98" spans="2:22" ht="24.95" customHeight="1">
       <c r="B98" s="52">
         <v>0.2</v>
       </c>
@@ -17123,7 +17123,7 @@
       <c r="U98" s="4"/>
       <c r="V98" s="4"/>
     </row>
-    <row r="99" spans="2:22" ht="25" customHeight="1">
+    <row r="99" spans="2:22" ht="24.95" customHeight="1">
       <c r="B99" s="53">
         <v>0.25</v>
       </c>
@@ -17163,7 +17163,7 @@
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
     </row>
-    <row r="100" spans="2:22" ht="25" customHeight="1">
+    <row r="100" spans="2:22" ht="24.95" customHeight="1">
       <c r="B100" s="52">
         <v>0.3</v>
       </c>
@@ -17203,7 +17203,7 @@
       <c r="U100" s="4"/>
       <c r="V100" s="4"/>
     </row>
-    <row r="101" spans="2:22" ht="25" customHeight="1">
+    <row r="101" spans="2:22" ht="24.95" customHeight="1">
       <c r="B101" s="53">
         <v>0.35</v>
       </c>
@@ -17243,7 +17243,7 @@
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
     </row>
-    <row r="102" spans="2:22" ht="25" customHeight="1">
+    <row r="102" spans="2:22" ht="24.95" customHeight="1">
       <c r="B102" s="52">
         <v>0.4</v>
       </c>
@@ -17283,7 +17283,7 @@
       <c r="U102" s="4"/>
       <c r="V102" s="4"/>
     </row>
-    <row r="103" spans="2:22" ht="25" customHeight="1">
+    <row r="103" spans="2:22" ht="24.95" customHeight="1">
       <c r="B103" s="53">
         <v>0.45</v>
       </c>
@@ -17323,7 +17323,7 @@
       <c r="U103" s="4"/>
       <c r="V103" s="4"/>
     </row>
-    <row r="104" spans="2:22" ht="25" customHeight="1">
+    <row r="104" spans="2:22" ht="24.95" customHeight="1">
       <c r="B104" s="52">
         <v>0.5</v>
       </c>
@@ -17363,7 +17363,7 @@
       <c r="U104" s="4"/>
       <c r="V104" s="4"/>
     </row>
-    <row r="105" spans="2:22" ht="25" customHeight="1">
+    <row r="105" spans="2:22" ht="24.95" customHeight="1">
       <c r="B105" s="53">
         <v>0.55000000000000004</v>
       </c>
@@ -17403,7 +17403,7 @@
       <c r="U105" s="4"/>
       <c r="V105" s="4"/>
     </row>
-    <row r="106" spans="2:22" ht="25" customHeight="1">
+    <row r="106" spans="2:22" ht="24.95" customHeight="1">
       <c r="B106" s="52">
         <v>0.6</v>
       </c>
@@ -17443,7 +17443,7 @@
       <c r="U106" s="4"/>
       <c r="V106" s="4"/>
     </row>
-    <row r="107" spans="2:22" ht="25" customHeight="1">
+    <row r="107" spans="2:22" ht="24.95" customHeight="1">
       <c r="B107" s="53">
         <v>0.65</v>
       </c>
@@ -17483,7 +17483,7 @@
       <c r="U107" s="4"/>
       <c r="V107" s="4"/>
     </row>
-    <row r="108" spans="2:22" ht="25" customHeight="1">
+    <row r="108" spans="2:22" ht="24.95" customHeight="1">
       <c r="B108" s="52">
         <v>0.7</v>
       </c>
@@ -17523,7 +17523,7 @@
       <c r="U108" s="4"/>
       <c r="V108" s="4"/>
     </row>
-    <row r="109" spans="2:22" ht="25" customHeight="1">
+    <row r="109" spans="2:22" ht="24.95" customHeight="1">
       <c r="B109" s="53">
         <v>0.75</v>
       </c>
@@ -17563,7 +17563,7 @@
       <c r="U109" s="4"/>
       <c r="V109" s="4"/>
     </row>
-    <row r="110" spans="2:22" ht="25" customHeight="1">
+    <row r="110" spans="2:22" ht="24.95" customHeight="1">
       <c r="B110" s="52">
         <v>0.8</v>
       </c>
@@ -17603,7 +17603,7 @@
       <c r="U110" s="4"/>
       <c r="V110" s="4"/>
     </row>
-    <row r="111" spans="2:22" ht="25" customHeight="1">
+    <row r="111" spans="2:22" ht="24.95" customHeight="1">
       <c r="B111" s="53">
         <v>0.85</v>
       </c>
@@ -17643,7 +17643,7 @@
       <c r="U111" s="4"/>
       <c r="V111" s="4"/>
     </row>
-    <row r="112" spans="2:22" ht="25" customHeight="1">
+    <row r="112" spans="2:22" ht="24.95" customHeight="1">
       <c r="B112" s="52">
         <v>0.9</v>
       </c>
@@ -17683,7 +17683,7 @@
       <c r="U112" s="4"/>
       <c r="V112" s="4"/>
     </row>
-    <row r="113" spans="2:22" ht="25" customHeight="1">
+    <row r="113" spans="2:22" ht="24.95" customHeight="1">
       <c r="B113" s="53">
         <v>0.95</v>
       </c>
@@ -17723,7 +17723,7 @@
       <c r="U113" s="4"/>
       <c r="V113" s="4"/>
     </row>
-    <row r="114" spans="2:22" ht="25" customHeight="1">
+    <row r="114" spans="2:22" ht="24.95" customHeight="1">
       <c r="B114" s="52">
         <v>1</v>
       </c>
@@ -17763,7 +17763,7 @@
       <c r="U114" s="4"/>
       <c r="V114" s="4"/>
     </row>
-    <row r="115" spans="2:22" ht="22" customHeight="1">
+    <row r="115" spans="2:22" ht="21.95" customHeight="1">
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
@@ -17786,7 +17786,7 @@
       <c r="U115" s="4"/>
       <c r="V115" s="4"/>
     </row>
-    <row r="116" spans="2:22" ht="22" customHeight="1">
+    <row r="116" spans="2:22" ht="21.95" customHeight="1">
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
@@ -17809,7 +17809,7 @@
       <c r="U116" s="4"/>
       <c r="V116" s="4"/>
     </row>
-    <row r="117" spans="2:22" ht="22" customHeight="1">
+    <row r="117" spans="2:22" ht="21.95" customHeight="1">
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
@@ -17832,7 +17832,7 @@
       <c r="U117" s="4"/>
       <c r="V117" s="4"/>
     </row>
-    <row r="118" spans="2:22" ht="22" customHeight="1">
+    <row r="118" spans="2:22" ht="21.95" customHeight="1">
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
@@ -17855,7 +17855,7 @@
       <c r="U118" s="4"/>
       <c r="V118" s="4"/>
     </row>
-    <row r="119" spans="2:22" ht="22" customHeight="1">
+    <row r="119" spans="2:22" ht="21.95" customHeight="1">
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
@@ -17878,7 +17878,7 @@
       <c r="U119" s="4"/>
       <c r="V119" s="4"/>
     </row>
-    <row r="120" spans="2:22" ht="22" customHeight="1">
+    <row r="120" spans="2:22" ht="21.95" customHeight="1">
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
@@ -17901,32 +17901,32 @@
       <c r="U120" s="4"/>
       <c r="V120" s="4"/>
     </row>
-    <row r="121" spans="2:22" ht="32" customHeight="1">
-      <c r="B121" s="67" t="s">
+    <row r="121" spans="2:22" ht="32.1" customHeight="1">
+      <c r="B121" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="C121" s="67"/>
-      <c r="D121" s="67"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="67"/>
-      <c r="G121" s="67"/>
-      <c r="H121" s="67"/>
-      <c r="I121" s="67"/>
-      <c r="J121" s="67"/>
-      <c r="K121" s="67"/>
-      <c r="L121" s="67"/>
-      <c r="M121" s="67"/>
-      <c r="N121" s="67"/>
-      <c r="O121" s="67"/>
-      <c r="P121" s="67"/>
-      <c r="Q121" s="67"/>
-      <c r="R121" s="67"/>
-      <c r="S121" s="67"/>
-      <c r="T121" s="67"/>
-      <c r="U121" s="67"/>
-      <c r="V121" s="67"/>
-    </row>
-    <row r="122" spans="2:22" ht="22" customHeight="1">
+      <c r="C121" s="94"/>
+      <c r="D121" s="94"/>
+      <c r="E121" s="94"/>
+      <c r="F121" s="94"/>
+      <c r="G121" s="94"/>
+      <c r="H121" s="94"/>
+      <c r="I121" s="94"/>
+      <c r="J121" s="94"/>
+      <c r="K121" s="94"/>
+      <c r="L121" s="94"/>
+      <c r="M121" s="94"/>
+      <c r="N121" s="94"/>
+      <c r="O121" s="94"/>
+      <c r="P121" s="94"/>
+      <c r="Q121" s="94"/>
+      <c r="R121" s="94"/>
+      <c r="S121" s="94"/>
+      <c r="T121" s="94"/>
+      <c r="U121" s="94"/>
+      <c r="V121" s="94"/>
+    </row>
+    <row r="122" spans="2:22" ht="21.95" customHeight="1">
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
@@ -17949,7 +17949,7 @@
       <c r="U122" s="4"/>
       <c r="V122" s="4"/>
     </row>
-    <row r="123" spans="2:22" ht="22" customHeight="1">
+    <row r="123" spans="2:22" ht="21.95" customHeight="1">
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
@@ -17972,7 +17972,7 @@
       <c r="U123" s="4"/>
       <c r="V123" s="4"/>
     </row>
-    <row r="124" spans="2:22" ht="44" customHeight="1">
+    <row r="124" spans="2:22" ht="44.1" customHeight="1">
       <c r="B124" s="41" t="s">
         <v>51</v>
       </c>
@@ -18037,7 +18037,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="125" spans="2:22" ht="25" customHeight="1">
+    <row r="125" spans="2:22" ht="24.95" customHeight="1">
       <c r="B125" s="43" t="str">
         <f>"c "&amp;C125&amp;" / C "&amp;D125</f>
         <v>c -24 / C -20</v>
@@ -18123,7 +18123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="2:22" ht="25" customHeight="1">
+    <row r="126" spans="2:22" ht="24.95" customHeight="1">
       <c r="B126" s="45" t="str">
         <f>"c "&amp;C126&amp;" / C "&amp;D126</f>
         <v>c -18 / C -15</v>
@@ -18209,7 +18209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="2:22" ht="25" customHeight="1">
+    <row r="127" spans="2:22" ht="24.95" customHeight="1">
       <c r="B127" s="43" t="str">
         <f>"c "&amp;C127&amp;" / C "&amp;D127</f>
         <v>c -12 / C -10</v>
@@ -18295,7 +18295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="2:22" ht="25" customHeight="1">
+    <row r="128" spans="2:22" ht="24.95" customHeight="1">
       <c r="B128" s="45" t="str">
         <f>"c "&amp;C128&amp;" / C "&amp;D128</f>
         <v>c -6 / C -5</v>
@@ -18381,7 +18381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="2:22" ht="25" customHeight="1">
+    <row r="129" spans="2:22" ht="24.95" customHeight="1">
       <c r="B129" s="43" t="str">
         <f>"c "&amp;C129&amp;" / C "&amp;D129</f>
         <v>c 0 / C 0</v>
@@ -18467,7 +18467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="2:22" ht="22" customHeight="1">
+    <row r="130" spans="2:22" ht="21.95" customHeight="1">
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
@@ -18490,7 +18490,7 @@
       <c r="U130" s="4"/>
       <c r="V130" s="4"/>
     </row>
-    <row r="131" spans="2:22" ht="22" customHeight="1">
+    <row r="131" spans="2:22" ht="21.95" customHeight="1">
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
@@ -18513,7 +18513,7 @@
       <c r="U131" s="4"/>
       <c r="V131" s="4"/>
     </row>
-    <row r="132" spans="2:22" ht="22" customHeight="1">
+    <row r="132" spans="2:22" ht="21.95" customHeight="1">
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
@@ -18591,7 +18591,7 @@
       <c r="U133" s="4"/>
       <c r="V133" s="4"/>
     </row>
-    <row r="134" spans="2:22" ht="25" customHeight="1">
+    <row r="134" spans="2:22" ht="24.95" customHeight="1">
       <c r="B134" s="52">
         <v>0</v>
       </c>
@@ -18646,7 +18646,7 @@
       <c r="U134" s="4"/>
       <c r="V134" s="4"/>
     </row>
-    <row r="135" spans="2:22" ht="25" customHeight="1">
+    <row r="135" spans="2:22" ht="24.95" customHeight="1">
       <c r="B135" s="53">
         <v>0.05</v>
       </c>
@@ -18701,7 +18701,7 @@
       <c r="U135" s="4"/>
       <c r="V135" s="4"/>
     </row>
-    <row r="136" spans="2:22" ht="25" customHeight="1">
+    <row r="136" spans="2:22" ht="24.95" customHeight="1">
       <c r="B136" s="52">
         <v>0.1</v>
       </c>
@@ -18756,7 +18756,7 @@
       <c r="U136" s="4"/>
       <c r="V136" s="4"/>
     </row>
-    <row r="137" spans="2:22" ht="25" customHeight="1">
+    <row r="137" spans="2:22" ht="24.95" customHeight="1">
       <c r="B137" s="53">
         <v>0.15</v>
       </c>
@@ -18811,7 +18811,7 @@
       <c r="U137" s="4"/>
       <c r="V137" s="4"/>
     </row>
-    <row r="138" spans="2:22" ht="25" customHeight="1">
+    <row r="138" spans="2:22" ht="24.95" customHeight="1">
       <c r="B138" s="52">
         <v>0.2</v>
       </c>
@@ -18866,7 +18866,7 @@
       <c r="U138" s="4"/>
       <c r="V138" s="4"/>
     </row>
-    <row r="139" spans="2:22" ht="25" customHeight="1">
+    <row r="139" spans="2:22" ht="24.95" customHeight="1">
       <c r="B139" s="53">
         <v>0.25</v>
       </c>
@@ -18921,7 +18921,7 @@
       <c r="U139" s="4"/>
       <c r="V139" s="4"/>
     </row>
-    <row r="140" spans="2:22" ht="25" customHeight="1">
+    <row r="140" spans="2:22" ht="24.95" customHeight="1">
       <c r="B140" s="52">
         <v>0.3</v>
       </c>
@@ -18976,7 +18976,7 @@
       <c r="U140" s="4"/>
       <c r="V140" s="4"/>
     </row>
-    <row r="141" spans="2:22" ht="25" customHeight="1">
+    <row r="141" spans="2:22" ht="24.95" customHeight="1">
       <c r="B141" s="53">
         <v>0.35</v>
       </c>
@@ -19031,7 +19031,7 @@
       <c r="U141" s="4"/>
       <c r="V141" s="4"/>
     </row>
-    <row r="142" spans="2:22" ht="25" customHeight="1">
+    <row r="142" spans="2:22" ht="24.95" customHeight="1">
       <c r="B142" s="52">
         <v>0.4</v>
       </c>
@@ -19086,7 +19086,7 @@
       <c r="U142" s="4"/>
       <c r="V142" s="4"/>
     </row>
-    <row r="143" spans="2:22" ht="25" customHeight="1">
+    <row r="143" spans="2:22" ht="24.95" customHeight="1">
       <c r="B143" s="53">
         <v>0.45</v>
       </c>
@@ -19141,7 +19141,7 @@
       <c r="U143" s="4"/>
       <c r="V143" s="4"/>
     </row>
-    <row r="144" spans="2:22" ht="25" customHeight="1">
+    <row r="144" spans="2:22" ht="24.95" customHeight="1">
       <c r="B144" s="52">
         <v>0.5</v>
       </c>
@@ -19196,7 +19196,7 @@
       <c r="U144" s="4"/>
       <c r="V144" s="4"/>
     </row>
-    <row r="145" spans="2:22" ht="25" customHeight="1">
+    <row r="145" spans="2:22" ht="24.95" customHeight="1">
       <c r="B145" s="53">
         <v>0.55000000000000004</v>
       </c>
@@ -19251,7 +19251,7 @@
       <c r="U145" s="4"/>
       <c r="V145" s="4"/>
     </row>
-    <row r="146" spans="2:22" ht="25" customHeight="1">
+    <row r="146" spans="2:22" ht="24.95" customHeight="1">
       <c r="B146" s="52">
         <v>0.6</v>
       </c>
@@ -19306,7 +19306,7 @@
       <c r="U146" s="4"/>
       <c r="V146" s="4"/>
     </row>
-    <row r="147" spans="2:22" ht="25" customHeight="1">
+    <row r="147" spans="2:22" ht="24.95" customHeight="1">
       <c r="B147" s="53">
         <v>0.65</v>
       </c>
@@ -19361,7 +19361,7 @@
       <c r="U147" s="4"/>
       <c r="V147" s="4"/>
     </row>
-    <row r="148" spans="2:22" ht="25" customHeight="1">
+    <row r="148" spans="2:22" ht="24.95" customHeight="1">
       <c r="B148" s="52">
         <v>0.7</v>
       </c>
@@ -19416,7 +19416,7 @@
       <c r="U148" s="4"/>
       <c r="V148" s="4"/>
     </row>
-    <row r="149" spans="2:22" ht="25" customHeight="1">
+    <row r="149" spans="2:22" ht="24.95" customHeight="1">
       <c r="B149" s="53">
         <v>0.75</v>
       </c>
@@ -19471,7 +19471,7 @@
       <c r="U149" s="4"/>
       <c r="V149" s="4"/>
     </row>
-    <row r="150" spans="2:22" ht="25" customHeight="1">
+    <row r="150" spans="2:22" ht="24.95" customHeight="1">
       <c r="B150" s="52">
         <v>0.8</v>
       </c>
@@ -19526,7 +19526,7 @@
       <c r="U150" s="4"/>
       <c r="V150" s="4"/>
     </row>
-    <row r="151" spans="2:22" ht="25" customHeight="1">
+    <row r="151" spans="2:22" ht="24.95" customHeight="1">
       <c r="B151" s="53">
         <v>0.85</v>
       </c>
@@ -19581,7 +19581,7 @@
       <c r="U151" s="4"/>
       <c r="V151" s="4"/>
     </row>
-    <row r="152" spans="2:22" ht="25" customHeight="1">
+    <row r="152" spans="2:22" ht="24.95" customHeight="1">
       <c r="B152" s="52">
         <v>0.9</v>
       </c>
@@ -19636,7 +19636,7 @@
       <c r="U152" s="4"/>
       <c r="V152" s="4"/>
     </row>
-    <row r="153" spans="2:22" ht="25" customHeight="1">
+    <row r="153" spans="2:22" ht="24.95" customHeight="1">
       <c r="B153" s="53">
         <v>0.95</v>
       </c>
@@ -19691,7 +19691,7 @@
       <c r="U153" s="4"/>
       <c r="V153" s="4"/>
     </row>
-    <row r="154" spans="2:22" ht="25" customHeight="1">
+    <row r="154" spans="2:22" ht="24.95" customHeight="1">
       <c r="B154" s="52">
         <v>1</v>
       </c>
@@ -19746,7 +19746,7 @@
       <c r="U154" s="4"/>
       <c r="V154" s="4"/>
     </row>
-    <row r="155" spans="2:22" ht="22" customHeight="1">
+    <row r="155" spans="2:22" ht="21.95" customHeight="1">
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
@@ -19769,7 +19769,7 @@
       <c r="U155" s="4"/>
       <c r="V155" s="4"/>
     </row>
-    <row r="156" spans="2:22" ht="22" customHeight="1">
+    <row r="156" spans="2:22" ht="21.95" customHeight="1">
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
@@ -19792,7 +19792,7 @@
       <c r="U156" s="4"/>
       <c r="V156" s="4"/>
     </row>
-    <row r="157" spans="2:22" ht="22" customHeight="1">
+    <row r="157" spans="2:22" ht="21.95" customHeight="1">
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -19815,32 +19815,32 @@
       <c r="U157" s="4"/>
       <c r="V157" s="4"/>
     </row>
-    <row r="161" spans="2:22" ht="32" customHeight="1">
-      <c r="B161" s="68" t="s">
+    <row r="161" spans="2:22" ht="32.1" customHeight="1">
+      <c r="B161" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="C161" s="68"/>
-      <c r="D161" s="68"/>
-      <c r="E161" s="68"/>
-      <c r="F161" s="68"/>
-      <c r="G161" s="68"/>
-      <c r="H161" s="68"/>
-      <c r="I161" s="68"/>
-      <c r="J161" s="68"/>
-      <c r="K161" s="68"/>
-      <c r="L161" s="68"/>
-      <c r="M161" s="68"/>
-      <c r="N161" s="68"/>
-      <c r="O161" s="68"/>
-      <c r="P161" s="68"/>
-      <c r="Q161" s="68"/>
-      <c r="R161" s="68"/>
-      <c r="S161" s="68"/>
-      <c r="T161" s="68"/>
-      <c r="U161" s="68"/>
-      <c r="V161" s="68"/>
-    </row>
-    <row r="164" spans="2:22" ht="44" customHeight="1">
+      <c r="C161" s="95"/>
+      <c r="D161" s="95"/>
+      <c r="E161" s="95"/>
+      <c r="F161" s="95"/>
+      <c r="G161" s="95"/>
+      <c r="H161" s="95"/>
+      <c r="I161" s="95"/>
+      <c r="J161" s="95"/>
+      <c r="K161" s="95"/>
+      <c r="L161" s="95"/>
+      <c r="M161" s="95"/>
+      <c r="N161" s="95"/>
+      <c r="O161" s="95"/>
+      <c r="P161" s="95"/>
+      <c r="Q161" s="95"/>
+      <c r="R161" s="95"/>
+      <c r="S161" s="95"/>
+      <c r="T161" s="95"/>
+      <c r="U161" s="95"/>
+      <c r="V161" s="95"/>
+    </row>
+    <row r="164" spans="2:22" ht="44.1" customHeight="1">
       <c r="B164" s="54" t="s">
         <v>51</v>
       </c>
@@ -19905,7 +19905,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="165" spans="2:22" ht="25" customHeight="1">
+    <row r="165" spans="2:22" ht="24.95" customHeight="1">
       <c r="B165" s="57"/>
       <c r="C165" s="56">
         <f>Calculator!C7</f>

--- a/docs/damping_curve_RAx8.xlsx
+++ b/docs/damping_curve_RAx8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CBF6F6-2AE7-47D5-AAD1-A0F0E997B519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4075A77F-6E09-4DA1-9293-4EC61C2C99DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="94">
   <si>
     <t>规格</t>
   </si>
@@ -316,10 +316,6 @@
   </si>
   <si>
     <t>RA88</t>
-    <phoneticPr fontId="74" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type-A</t>
     <phoneticPr fontId="74" type="noConversion"/>
   </si>
   <si>
@@ -1917,11 +1913,23 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1929,41 +1937,17 @@
     <xf numFmtId="0" fontId="31" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="25" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="27" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="42" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="33" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1979,6 +1963,18 @@
     </xf>
     <xf numFmtId="0" fontId="48" fillId="40" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="42" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="43" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4312,64 +4308,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>200</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>300</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>400</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>497.59999999999997</c:v>
+                  <c:v>447.84</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>591.59999999999991</c:v>
+                  <c:v>532.43999999999994</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>685.59999999999991</c:v>
+                  <c:v>617.04</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>779.6</c:v>
+                  <c:v>701.6400000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>873.6</c:v>
+                  <c:v>786.24</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>967.6</c:v>
+                  <c:v>870.84</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1061.6000000000001</c:v>
+                  <c:v>955.44</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1155.5999999999999</c:v>
+                  <c:v>1040.04</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1249.5999999999999</c:v>
+                  <c:v>1124.6400000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1343.6</c:v>
+                  <c:v>1209.24</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1437.6</c:v>
+                  <c:v>1293.8400000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1531.6000000000001</c:v>
+                  <c:v>1378.44</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1625.6</c:v>
+                  <c:v>1463.04</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1719.6000000000001</c:v>
+                  <c:v>1547.64</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1813.6</c:v>
+                  <c:v>1632.24</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1907.6000000000001</c:v>
+                  <c:v>1716.84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4488,64 +4484,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>230</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>345</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>500</c:v>
+                  <c:v>460</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>625</c:v>
+                  <c:v>575</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>739.875</c:v>
+                  <c:v>680.68499999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>853.625</c:v>
+                  <c:v>785.33499999999992</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>967.375</c:v>
+                  <c:v>889.98500000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1081.125</c:v>
+                  <c:v>994.63499999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1194.875</c:v>
+                  <c:v>1099.2849999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1308.625</c:v>
+                  <c:v>1203.9349999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1422.375</c:v>
+                  <c:v>1308.585</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1536.125</c:v>
+                  <c:v>1413.2350000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1649.875</c:v>
+                  <c:v>1517.8849999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1763.625</c:v>
+                  <c:v>1622.5350000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1877.375</c:v>
+                  <c:v>1727.1850000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1991.125</c:v>
+                  <c:v>1831.835</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2104.875</c:v>
+                  <c:v>1936.4850000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2218.625</c:v>
+                  <c:v>2041.135</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2332.375</c:v>
+                  <c:v>2145.7849999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4664,64 +4660,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>140</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>280</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>560</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>700</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>892.8</c:v>
+                  <c:v>833.28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1024.8</c:v>
+                  <c:v>956.48</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1156.8000000000002</c:v>
+                  <c:v>1079.68</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1288.8000000000002</c:v>
+                  <c:v>1202.8800000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1420.8000000000002</c:v>
+                  <c:v>1326.08</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1552.8000000000002</c:v>
+                  <c:v>1449.2800000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1684.8</c:v>
+                  <c:v>1572.48</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1816.8000000000002</c:v>
+                  <c:v>1695.68</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1948.7999999999997</c:v>
+                  <c:v>1818.88</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2080.8000000000002</c:v>
+                  <c:v>1942.08</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2212.8000000000002</c:v>
+                  <c:v>2065.2800000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2344.8000000000002</c:v>
+                  <c:v>2188.48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2476.8000000000002</c:v>
+                  <c:v>2311.6800000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2608.7999999999997</c:v>
+                  <c:v>2434.88</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2740.8</c:v>
+                  <c:v>2558.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4840,64 +4836,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>175</c:v>
+                  <c:v>165</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>350</c:v>
+                  <c:v>330</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>525</c:v>
+                  <c:v>495</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>700</c:v>
+                  <c:v>660</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>875</c:v>
+                  <c:v>825</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1050</c:v>
+                  <c:v>990</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1201.375</c:v>
+                  <c:v>1132.7249999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1350.1250000000002</c:v>
+                  <c:v>1272.9749999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1498.875</c:v>
+                  <c:v>1413.2249999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1647.625</c:v>
+                  <c:v>1553.4749999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1796.3750000000002</c:v>
+                  <c:v>1693.7250000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1945.125</c:v>
+                  <c:v>1833.9749999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2093.875</c:v>
+                  <c:v>1974.2249999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2242.625</c:v>
+                  <c:v>2114.4749999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2391.375</c:v>
+                  <c:v>2254.7249999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2540.125</c:v>
+                  <c:v>2394.9749999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2688.875</c:v>
+                  <c:v>2535.2249999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2837.625</c:v>
+                  <c:v>2675.4749999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2986.375</c:v>
+                  <c:v>2815.7249999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3135.125</c:v>
+                  <c:v>2955.9749999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5016,64 +5012,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>200</c:v>
+                  <c:v>190</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>400</c:v>
+                  <c:v>380</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>600</c:v>
+                  <c:v>570</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>800</c:v>
+                  <c:v>760</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1000</c:v>
+                  <c:v>950</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1200</c:v>
+                  <c:v>1140</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1385.6</c:v>
+                  <c:v>1316.32</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1549.6</c:v>
+                  <c:v>1472.1200000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1713.6</c:v>
+                  <c:v>1627.92</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1877.6</c:v>
+                  <c:v>1783.7199999999998</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2041.6000000000001</c:v>
+                  <c:v>1939.52</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2205.6</c:v>
+                  <c:v>2095.3199999999997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2369.6</c:v>
+                  <c:v>2251.12</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2533.6</c:v>
+                  <c:v>2406.92</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2697.6</c:v>
+                  <c:v>2562.7200000000003</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2861.6000000000004</c:v>
+                  <c:v>2718.52</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3025.6000000000004</c:v>
+                  <c:v>2874.32</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3189.6000000000004</c:v>
+                  <c:v>3030.12</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3353.5999999999995</c:v>
+                  <c:v>3185.9199999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3517.6</c:v>
+                  <c:v>3341.72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6265,64 +6261,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-100</c:v>
+                  <c:v>-90</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-200</c:v>
+                  <c:v>-180</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-300</c:v>
+                  <c:v>-270</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-400</c:v>
+                  <c:v>-360</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-497.59999999999997</c:v>
+                  <c:v>-447.84</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-591.59999999999991</c:v>
+                  <c:v>-532.43999999999994</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-685.59999999999991</c:v>
+                  <c:v>-617.04</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-779.6</c:v>
+                  <c:v>-701.6400000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-873.6</c:v>
+                  <c:v>-786.24</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-967.6</c:v>
+                  <c:v>-870.84</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1061.6000000000001</c:v>
+                  <c:v>-955.44</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1155.5999999999999</c:v>
+                  <c:v>-1040.04</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1249.5999999999999</c:v>
+                  <c:v>-1124.6400000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1343.6</c:v>
+                  <c:v>-1209.24</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1437.6</c:v>
+                  <c:v>-1293.8400000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1531.6000000000001</c:v>
+                  <c:v>-1378.44</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1625.6</c:v>
+                  <c:v>-1463.04</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1719.6000000000001</c:v>
+                  <c:v>-1547.64</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1813.6</c:v>
+                  <c:v>-1632.24</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1907.6000000000001</c:v>
+                  <c:v>-1716.84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6441,64 +6437,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-125</c:v>
+                  <c:v>-115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-250</c:v>
+                  <c:v>-230</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-375</c:v>
+                  <c:v>-345</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-500</c:v>
+                  <c:v>-460</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-625</c:v>
+                  <c:v>-575</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-739.875</c:v>
+                  <c:v>-680.68499999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-853.625</c:v>
+                  <c:v>-785.33499999999992</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-967.375</c:v>
+                  <c:v>-889.98500000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1081.125</c:v>
+                  <c:v>-994.63499999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1194.875</c:v>
+                  <c:v>-1099.2849999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1308.625</c:v>
+                  <c:v>-1203.9349999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1422.375</c:v>
+                  <c:v>-1308.585</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1536.125</c:v>
+                  <c:v>-1413.2350000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1649.875</c:v>
+                  <c:v>-1517.8849999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1763.625</c:v>
+                  <c:v>-1622.5350000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1877.375</c:v>
+                  <c:v>-1727.1850000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1991.125</c:v>
+                  <c:v>-1831.835</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2104.875</c:v>
+                  <c:v>-1936.4850000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2218.625</c:v>
+                  <c:v>-2041.135</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2332.375</c:v>
+                  <c:v>-2145.7849999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6617,64 +6613,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-150</c:v>
+                  <c:v>-140</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-300</c:v>
+                  <c:v>-280</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-450</c:v>
+                  <c:v>-420</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-600</c:v>
+                  <c:v>-560</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-750</c:v>
+                  <c:v>-700</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-892.8</c:v>
+                  <c:v>-833.28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1024.8</c:v>
+                  <c:v>-956.48</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1156.8000000000002</c:v>
+                  <c:v>-1079.68</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1288.8000000000002</c:v>
+                  <c:v>-1202.8800000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1420.8000000000002</c:v>
+                  <c:v>-1326.08</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1552.8000000000002</c:v>
+                  <c:v>-1449.2800000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1684.8</c:v>
+                  <c:v>-1572.48</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1816.8000000000002</c:v>
+                  <c:v>-1695.68</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1948.7999999999997</c:v>
+                  <c:v>-1818.88</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2080.8000000000002</c:v>
+                  <c:v>-1942.08</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2212.8000000000002</c:v>
+                  <c:v>-2065.2800000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2344.8000000000002</c:v>
+                  <c:v>-2188.48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2476.8000000000002</c:v>
+                  <c:v>-2311.6800000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2608.7999999999997</c:v>
+                  <c:v>-2434.88</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2740.8</c:v>
+                  <c:v>-2558.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6793,64 +6789,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-175</c:v>
+                  <c:v>-165</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-350</c:v>
+                  <c:v>-330</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-525</c:v>
+                  <c:v>-495</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-700</c:v>
+                  <c:v>-660</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-875</c:v>
+                  <c:v>-825</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1050</c:v>
+                  <c:v>-990</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1201.375</c:v>
+                  <c:v>-1132.7249999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1350.1250000000002</c:v>
+                  <c:v>-1272.9749999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1498.875</c:v>
+                  <c:v>-1413.2249999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1647.625</c:v>
+                  <c:v>-1553.4749999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1796.3750000000002</c:v>
+                  <c:v>-1693.7250000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1945.125</c:v>
+                  <c:v>-1833.9749999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-2093.875</c:v>
+                  <c:v>-1974.2249999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-2242.625</c:v>
+                  <c:v>-2114.4749999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2391.375</c:v>
+                  <c:v>-2254.7249999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2540.125</c:v>
+                  <c:v>-2394.9749999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2688.875</c:v>
+                  <c:v>-2535.2249999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2837.625</c:v>
+                  <c:v>-2675.4749999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2986.375</c:v>
+                  <c:v>-2815.7249999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-3135.125</c:v>
+                  <c:v>-2955.9749999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6969,64 +6965,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-200</c:v>
+                  <c:v>-190</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-400</c:v>
+                  <c:v>-380</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-600</c:v>
+                  <c:v>-570</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-800</c:v>
+                  <c:v>-760</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1000</c:v>
+                  <c:v>-950</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1200</c:v>
+                  <c:v>-1140</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1385.6</c:v>
+                  <c:v>-1316.32</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1549.6</c:v>
+                  <c:v>-1472.1200000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1713.6</c:v>
+                  <c:v>-1627.92</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1877.6</c:v>
+                  <c:v>-1783.7199999999998</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2041.6000000000001</c:v>
+                  <c:v>-1939.52</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2205.6</c:v>
+                  <c:v>-2095.3199999999997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-2369.6</c:v>
+                  <c:v>-2251.12</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-2533.6</c:v>
+                  <c:v>-2406.92</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2697.6</c:v>
+                  <c:v>-2562.7200000000003</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2861.6000000000004</c:v>
+                  <c:v>-2718.52</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-3025.6000000000004</c:v>
+                  <c:v>-2874.32</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-3189.6000000000004</c:v>
+                  <c:v>-3030.12</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-3353.5999999999995</c:v>
+                  <c:v>-3185.9199999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-3517.6</c:v>
+                  <c:v>-3341.72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7632,7 +7628,7 @@
         <v>73</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H6" s="6"/>
     </row>
@@ -7656,7 +7652,7 @@
     <row r="8" spans="1:8" ht="30.95" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="11" t="s">
@@ -7912,7 +7908,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="67"/>
@@ -7954,13 +7950,13 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="81" t="s">
+      <c r="F6" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -7998,16 +7994,16 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="80" t="s">
+      <c r="F8" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="83">
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="77">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
-        <v>4021</v>
-      </c>
-      <c r="J8" s="84"/>
+        <v>2151.6666666666665</v>
+      </c>
+      <c r="J8" s="78"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -8041,20 +8037,20 @@
         <v>18</v>
       </c>
       <c r="C10" s="25">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="80" t="s">
+      <c r="F10" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="83">
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="77">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
-        <v>2579.2479999999996</v>
-      </c>
-      <c r="J10" s="84"/>
+        <v>1467.3359999999998</v>
+      </c>
+      <c r="J10" s="78"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -8106,13 +8102,13 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="81" t="s">
+      <c r="F13" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -8130,11 +8126,11 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
       <c r="I14" s="29">
         <f>Samples!F165</f>
         <v>3400</v>
@@ -8159,11 +8155,11 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="77" t="s">
+      <c r="F15" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
       <c r="I15" s="30">
         <f>Samples!I165</f>
         <v>3173.3333333333335</v>
@@ -8183,11 +8179,11 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="79" t="s">
+      <c r="F16" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="76"/>
-      <c r="H16" s="76"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
       <c r="I16" s="29">
         <f>Samples!J165</f>
         <v>1500</v>
@@ -8207,11 +8203,11 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="80" t="s">
+      <c r="F17" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
       <c r="I17" s="30">
         <f>Samples!L165</f>
         <v>4673.3333333333339</v>
@@ -8253,14 +8249,14 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="80"/>
       <c r="I19" s="29">
         <f>Samples!M165</f>
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="J19" s="20" t="s">
         <v>24</v>
@@ -8277,14 +8273,14 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="77" t="s">
+      <c r="F20" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
       <c r="I20" s="30">
         <f>Samples!P165</f>
-        <v>2497.6</v>
+        <v>2319.1999999999998</v>
       </c>
       <c r="J20" s="23" t="s">
         <v>24</v>
@@ -8318,11 +8314,11 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="79" t="s">
+      <c r="F22" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
       <c r="I22" s="32">
         <f>Samples!G165</f>
         <v>0.1</v>
@@ -8342,11 +8338,11 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="80" t="s">
+      <c r="F23" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
       <c r="I23" s="33">
         <f>Samples!K165</f>
         <v>0.45</v>
@@ -8366,11 +8362,11 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="75" t="s">
+      <c r="F24" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
       <c r="I24" s="32">
         <f>Samples!N165</f>
         <v>0.27</v>
@@ -8420,20 +8416,20 @@
     </row>
     <row r="27" spans="1:15" ht="23.1" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="73" t="s">
+      <c r="B27" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="74"/>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="74"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="74"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
@@ -8694,6 +8690,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -8701,17 +8708,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="74" type="noConversion"/>
   <dataValidations count="5">
@@ -11807,21 +11803,21 @@
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="86"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" ht="27.95" customHeight="1">
@@ -11845,21 +11841,21 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="82" t="s">
+      <c r="D5" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="82" t="s">
+      <c r="J5" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="82"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -12054,21 +12050,21 @@
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="58">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="K10" s="59">
         <f>(J10+L10)/2</f>
-        <v>3150</v>
+        <v>3050</v>
       </c>
       <c r="L10" s="58">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="M10" s="59">
         <f>(L10+N10)/2</f>
-        <v>4050</v>
+        <v>3950</v>
       </c>
       <c r="N10" s="58">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="O10" s="2"/>
     </row>
@@ -12331,39 +12327,39 @@
         <v>24</v>
       </c>
       <c r="D17" s="58">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="E17" s="63">
         <f>(D17+F17)/2</f>
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="F17" s="58">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="G17" s="63">
         <f>(F17+H17)/2</f>
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="H17" s="58">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="58">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="K17" s="63">
         <f>(J17+L17)/2</f>
+        <v>3000</v>
+      </c>
+      <c r="L17" s="58">
         <v>3500</v>
-      </c>
-      <c r="L17" s="58">
-        <v>4000</v>
       </c>
       <c r="M17" s="63">
         <f>(L17+N17)/2</f>
+        <v>4000</v>
+      </c>
+      <c r="N17" s="58">
         <v>4500</v>
-      </c>
-      <c r="N17" s="58">
-        <v>5000</v>
       </c>
       <c r="O17" s="2"/>
     </row>
@@ -12493,73 +12489,73 @@
     </row>
     <row r="22" spans="1:15" ht="32.1" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="82"/>
-      <c r="N22" s="82"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="74"/>
       <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:15" ht="29.1" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="76"/>
+      <c r="C23" s="80"/>
       <c r="D23" s="26">
         <v>24</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="91" t="s">
+      <c r="F23" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="92"/>
-      <c r="M23" s="92"/>
-      <c r="N23" s="92"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="88"/>
+      <c r="L23" s="88"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="88"/>
       <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:15" ht="29.1" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="78"/>
+      <c r="C24" s="81"/>
       <c r="D24" s="28">
         <v>20</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="92"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="92"/>
-      <c r="I24" s="92"/>
-      <c r="J24" s="92"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="92"/>
-      <c r="N24" s="92"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="88"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="88"/>
+      <c r="K24" s="88"/>
+      <c r="L24" s="88"/>
+      <c r="M24" s="88"/>
+      <c r="N24" s="88"/>
       <c r="O24" s="2"/>
     </row>
     <row r="25" spans="1:15" ht="29.1" customHeight="1">
       <c r="A25" s="2"/>
-      <c r="B25" s="79" t="s">
+      <c r="B25" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="76"/>
+      <c r="C25" s="80"/>
       <c r="D25" s="26">
         <v>40</v>
       </c>
@@ -12577,33 +12573,33 @@
     </row>
     <row r="26" spans="1:15" ht="29.1" customHeight="1">
       <c r="A26" s="2"/>
-      <c r="B26" s="77" t="s">
+      <c r="B26" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="78"/>
+      <c r="C26" s="81"/>
       <c r="D26" s="28">
         <v>40</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="93" t="s">
+      <c r="F26" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="G26" s="90"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="90"/>
-      <c r="J26" s="90"/>
-      <c r="K26" s="90"/>
-      <c r="L26" s="90"/>
-      <c r="M26" s="90"/>
-      <c r="N26" s="90"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
+      <c r="L26" s="86"/>
+      <c r="M26" s="86"/>
+      <c r="N26" s="86"/>
       <c r="O26" s="2"/>
     </row>
     <row r="27" spans="1:15" ht="29.1" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="80" t="s">
+      <c r="B27" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="78"/>
+      <c r="C27" s="81"/>
       <c r="D27" s="28">
         <v>10</v>
       </c>
@@ -12621,140 +12617,140 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="86" t="s">
+      <c r="B28" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="87"/>
-      <c r="D28" s="87"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="87"/>
-      <c r="G28" s="87"/>
-      <c r="H28" s="87"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="K28" s="87"/>
-      <c r="L28" s="87"/>
-      <c r="M28" s="87"/>
-      <c r="N28" s="87"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="92"/>
+      <c r="G28" s="92"/>
+      <c r="H28" s="92"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="92"/>
+      <c r="K28" s="92"/>
+      <c r="L28" s="92"/>
+      <c r="M28" s="92"/>
+      <c r="N28" s="92"/>
       <c r="O28" s="2"/>
     </row>
     <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="2"/>
-      <c r="B29" s="85"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="85"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90"/>
+      <c r="F29" s="90"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="90"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="90"/>
       <c r="O29" s="2"/>
     </row>
     <row r="30" spans="1:15" ht="30.95" customHeight="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="88"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="88"/>
-      <c r="H30" s="88"/>
-      <c r="I30" s="88"/>
-      <c r="J30" s="88"/>
-      <c r="K30" s="88"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="88"/>
-      <c r="N30" s="88"/>
+      <c r="B30" s="93"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="93"/>
+      <c r="N30" s="93"/>
       <c r="O30" s="2"/>
     </row>
     <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="85"/>
-      <c r="D31" s="85"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="85"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="85"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="90"/>
+      <c r="F31" s="90"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="90"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="90"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="90"/>
+      <c r="M31" s="90"/>
+      <c r="N31" s="90"/>
       <c r="O31" s="2"/>
     </row>
     <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="2"/>
-      <c r="B32" s="85"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="85"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="85"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="85"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="90"/>
+      <c r="E32" s="90"/>
+      <c r="F32" s="90"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="90"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
+      <c r="M32" s="90"/>
+      <c r="N32" s="90"/>
       <c r="O32" s="2"/>
     </row>
     <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="85"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="85"/>
-      <c r="E33" s="85"/>
-      <c r="F33" s="85"/>
-      <c r="G33" s="85"/>
-      <c r="H33" s="85"/>
-      <c r="I33" s="85"/>
-      <c r="J33" s="85"/>
-      <c r="K33" s="85"/>
-      <c r="L33" s="85"/>
-      <c r="M33" s="85"/>
-      <c r="N33" s="85"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="90"/>
+      <c r="F33" s="90"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="90"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="90"/>
+      <c r="K33" s="90"/>
+      <c r="L33" s="90"/>
+      <c r="M33" s="90"/>
+      <c r="N33" s="90"/>
       <c r="O33" s="2"/>
     </row>
     <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="85"/>
-      <c r="E34" s="85"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="85"/>
-      <c r="H34" s="85"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="85"/>
-      <c r="K34" s="85"/>
-      <c r="L34" s="85"/>
-      <c r="M34" s="85"/>
-      <c r="N34" s="85"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="90"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="90"/>
+      <c r="J34" s="90"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="90"/>
+      <c r="M34" s="90"/>
+      <c r="N34" s="90"/>
       <c r="O34" s="2"/>
     </row>
     <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="2"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="85"/>
-      <c r="D35" s="85"/>
-      <c r="E35" s="85"/>
-      <c r="F35" s="85"/>
-      <c r="G35" s="85"/>
-      <c r="H35" s="85"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="85"/>
-      <c r="K35" s="85"/>
-      <c r="L35" s="85"/>
-      <c r="M35" s="85"/>
-      <c r="N35" s="85"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="90"/>
+      <c r="F35" s="90"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="90"/>
+      <c r="I35" s="90"/>
+      <c r="J35" s="90"/>
+      <c r="K35" s="90"/>
+      <c r="L35" s="90"/>
+      <c r="M35" s="90"/>
+      <c r="N35" s="90"/>
       <c r="O35" s="2"/>
     </row>
     <row r="36" spans="1:15" ht="23.1" customHeight="1">
@@ -12861,6 +12857,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -12873,14 +12877,6 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
   </mergeCells>
   <phoneticPr fontId="74" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13088,7 +13084,7 @@
       </c>
       <c r="M5" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="N5" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S5)+(INDEX(Parameters!$J$18:$N$18,1,S5+1)-INDEX(Parameters!$J$18:$N$18,1,S5))*V5,INDEX(Parameters!$D$18:$H$18,1,S5)+(INDEX(Parameters!$D$18:$H$18,1,S5+1)-INDEX(Parameters!$D$18:$H$18,1,S5))*V5)</f>
@@ -13100,7 +13096,7 @@
       </c>
       <c r="P5" s="43">
         <f>M5*O5</f>
-        <v>1880</v>
+        <v>1692</v>
       </c>
       <c r="Q5" s="43">
         <f>MIN(4,MAX(1,INT((1+C5/Parameters!$D$23)*4)+1))</f>
@@ -13175,7 +13171,7 @@
       </c>
       <c r="M6" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="N6" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S6)+(INDEX(Parameters!$J$18:$N$18,1,S6+1)-INDEX(Parameters!$J$18:$N$18,1,S6))*V6,INDEX(Parameters!$D$18:$H$18,1,S6)+(INDEX(Parameters!$D$18:$H$18,1,S6+1)-INDEX(Parameters!$D$18:$H$18,1,S6))*V6)</f>
@@ -13187,7 +13183,7 @@
       </c>
       <c r="P6" s="45">
         <f>M6*O6</f>
-        <v>2275</v>
+        <v>2093</v>
       </c>
       <c r="Q6" s="45">
         <f>MIN(4,MAX(1,INT((1+C6/Parameters!$D$23)*4)+1))</f>
@@ -13262,7 +13258,7 @@
       </c>
       <c r="M7" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="N7" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S7)+(INDEX(Parameters!$J$18:$N$18,1,S7+1)-INDEX(Parameters!$J$18:$N$18,1,S7))*V7,INDEX(Parameters!$D$18:$H$18,1,S7)+(INDEX(Parameters!$D$18:$H$18,1,S7+1)-INDEX(Parameters!$D$18:$H$18,1,S7))*V7)</f>
@@ -13274,7 +13270,7 @@
       </c>
       <c r="P7" s="43">
         <f>M7*O7</f>
-        <v>2640</v>
+        <v>2464</v>
       </c>
       <c r="Q7" s="43">
         <f>MIN(4,MAX(1,INT((1+C7/Parameters!$D$23)*4)+1))</f>
@@ -13349,7 +13345,7 @@
       </c>
       <c r="M8" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="N8" s="44">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S8)+(INDEX(Parameters!$J$18:$N$18,1,S8+1)-INDEX(Parameters!$J$18:$N$18,1,S8))*V8,INDEX(Parameters!$D$18:$H$18,1,S8)+(INDEX(Parameters!$D$18:$H$18,1,S8+1)-INDEX(Parameters!$D$18:$H$18,1,S8))*V8)</f>
@@ -13361,7 +13357,7 @@
       </c>
       <c r="P8" s="45">
         <f>M8*O8</f>
-        <v>2975</v>
+        <v>2805</v>
       </c>
       <c r="Q8" s="45">
         <f>MIN(4,MAX(1,INT((1+C8/Parameters!$D$23)*4)+1))</f>
@@ -13436,7 +13432,7 @@
       </c>
       <c r="M9" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="N9" s="42">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S9)+(INDEX(Parameters!$J$18:$N$18,1,S9+1)-INDEX(Parameters!$J$18:$N$18,1,S9))*V9,INDEX(Parameters!$D$18:$H$18,1,S9)+(INDEX(Parameters!$D$18:$H$18,1,S9+1)-INDEX(Parameters!$D$18:$H$18,1,S9))*V9)</f>
@@ -13448,7 +13444,7 @@
       </c>
       <c r="P9" s="43">
         <f>M9*O9</f>
-        <v>3280</v>
+        <v>3116</v>
       </c>
       <c r="Q9" s="43">
         <f>MIN(4,MAX(1,INT((1+C9/Parameters!$D$23)*4)+1))</f>
@@ -14778,7 +14774,7 @@
       </c>
       <c r="M45" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="N45" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S45)+(INDEX(Parameters!$J$18:$N$18,1,S45+1)-INDEX(Parameters!$J$18:$N$18,1,S45))*V45,INDEX(Parameters!$D$18:$H$18,1,S45)+(INDEX(Parameters!$D$18:$H$18,1,S45+1)-INDEX(Parameters!$D$18:$H$18,1,S45))*V45)</f>
@@ -14790,7 +14786,7 @@
       </c>
       <c r="P45" s="43">
         <f>M45*O45</f>
-        <v>1880</v>
+        <v>1692</v>
       </c>
       <c r="Q45" s="43">
         <f>MIN(4,MAX(1,INT((1+C45/Parameters!$D$23)*4)+1))</f>
@@ -14864,7 +14860,7 @@
       </c>
       <c r="M46" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="N46" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S46)+(INDEX(Parameters!$J$18:$N$18,1,S46+1)-INDEX(Parameters!$J$18:$N$18,1,S46))*V46,INDEX(Parameters!$D$18:$H$18,1,S46)+(INDEX(Parameters!$D$18:$H$18,1,S46+1)-INDEX(Parameters!$D$18:$H$18,1,S46))*V46)</f>
@@ -14876,7 +14872,7 @@
       </c>
       <c r="P46" s="45">
         <f>M46*O46</f>
-        <v>2275</v>
+        <v>2093</v>
       </c>
       <c r="Q46" s="45">
         <f>MIN(4,MAX(1,INT((1+C46/Parameters!$D$23)*4)+1))</f>
@@ -14950,7 +14946,7 @@
       </c>
       <c r="M47" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="N47" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S47)+(INDEX(Parameters!$J$18:$N$18,1,S47+1)-INDEX(Parameters!$J$18:$N$18,1,S47))*V47,INDEX(Parameters!$D$18:$H$18,1,S47)+(INDEX(Parameters!$D$18:$H$18,1,S47+1)-INDEX(Parameters!$D$18:$H$18,1,S47))*V47)</f>
@@ -14962,7 +14958,7 @@
       </c>
       <c r="P47" s="43">
         <f>M47*O47</f>
-        <v>2640</v>
+        <v>2464</v>
       </c>
       <c r="Q47" s="43">
         <f>MIN(4,MAX(1,INT((1+C47/Parameters!$D$23)*4)+1))</f>
@@ -15036,7 +15032,7 @@
       </c>
       <c r="M48" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="N48" s="45">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S48)+(INDEX(Parameters!$J$18:$N$18,1,S48+1)-INDEX(Parameters!$J$18:$N$18,1,S48))*V48,INDEX(Parameters!$D$18:$H$18,1,S48)+(INDEX(Parameters!$D$18:$H$18,1,S48+1)-INDEX(Parameters!$D$18:$H$18,1,S48))*V48)</f>
@@ -15048,7 +15044,7 @@
       </c>
       <c r="P48" s="45">
         <f>M48*O48</f>
-        <v>2975</v>
+        <v>2805</v>
       </c>
       <c r="Q48" s="45">
         <f>MIN(4,MAX(1,INT((1+C48/Parameters!$D$23)*4)+1))</f>
@@ -15122,7 +15118,7 @@
       </c>
       <c r="M49" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="N49" s="43">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S49)+(INDEX(Parameters!$J$18:$N$18,1,S49+1)-INDEX(Parameters!$J$18:$N$18,1,S49))*V49,INDEX(Parameters!$D$18:$H$18,1,S49)+(INDEX(Parameters!$D$18:$H$18,1,S49+1)-INDEX(Parameters!$D$18:$H$18,1,S49))*V49)</f>
@@ -15134,7 +15130,7 @@
       </c>
       <c r="P49" s="43">
         <f>M49*O49</f>
-        <v>3280</v>
+        <v>3116</v>
       </c>
       <c r="Q49" s="43">
         <f>MIN(4,MAX(1,INT((1+C49/Parameters!$D$23)*4)+1))</f>
@@ -16431,7 +16427,7 @@
       </c>
       <c r="M85" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S85)+(INDEX(Parameters!$J$17:$N$17,1,S85+1)-INDEX(Parameters!$J$17:$N$17,1,S85))*V85,INDEX(Parameters!$D$17:$H$17,1,S85)+(INDEX(Parameters!$D$17:$H$17,1,S85+1)-INDEX(Parameters!$D$17:$H$17,1,S85))*V85)</f>
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="N85" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S85)+(INDEX(Parameters!$J$18:$N$18,1,S85+1)-INDEX(Parameters!$J$18:$N$18,1,S85))*V85,INDEX(Parameters!$D$18:$H$18,1,S85)+(INDEX(Parameters!$D$18:$H$18,1,S85+1)-INDEX(Parameters!$D$18:$H$18,1,S85))*V85)</f>
@@ -16443,7 +16439,7 @@
       </c>
       <c r="P85" s="43">
         <f>M85*O85</f>
-        <v>1880</v>
+        <v>1692</v>
       </c>
       <c r="Q85" s="43">
         <f>MIN(4,MAX(1,INT((1+C85/Parameters!$D$23)*4)+1))</f>
@@ -16517,7 +16513,7 @@
       </c>
       <c r="M86" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="N86" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S86)+(INDEX(Parameters!$J$18:$N$18,1,S86+1)-INDEX(Parameters!$J$18:$N$18,1,S86))*V86,INDEX(Parameters!$D$18:$H$18,1,S86)+(INDEX(Parameters!$D$18:$H$18,1,S86+1)-INDEX(Parameters!$D$18:$H$18,1,S86))*V86)</f>
@@ -16529,7 +16525,7 @@
       </c>
       <c r="P86" s="45">
         <f>M86*O86</f>
-        <v>2275</v>
+        <v>2093</v>
       </c>
       <c r="Q86" s="45">
         <f>MIN(4,MAX(1,INT((1+C86/Parameters!$D$23)*4)+1))</f>
@@ -16603,7 +16599,7 @@
       </c>
       <c r="M87" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S87)+(INDEX(Parameters!$J$17:$N$17,1,S87+1)-INDEX(Parameters!$J$17:$N$17,1,S87))*V87,INDEX(Parameters!$D$17:$H$17,1,S87)+(INDEX(Parameters!$D$17:$H$17,1,S87+1)-INDEX(Parameters!$D$17:$H$17,1,S87))*V87)</f>
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="N87" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S87)+(INDEX(Parameters!$J$18:$N$18,1,S87+1)-INDEX(Parameters!$J$18:$N$18,1,S87))*V87,INDEX(Parameters!$D$18:$H$18,1,S87)+(INDEX(Parameters!$D$18:$H$18,1,S87+1)-INDEX(Parameters!$D$18:$H$18,1,S87))*V87)</f>
@@ -16615,7 +16611,7 @@
       </c>
       <c r="P87" s="43">
         <f>M87*O87</f>
-        <v>2640</v>
+        <v>2464</v>
       </c>
       <c r="Q87" s="43">
         <f>MIN(4,MAX(1,INT((1+C87/Parameters!$D$23)*4)+1))</f>
@@ -16689,7 +16685,7 @@
       </c>
       <c r="M88" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="N88" s="45">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S88)+(INDEX(Parameters!$J$18:$N$18,1,S88+1)-INDEX(Parameters!$J$18:$N$18,1,S88))*V88,INDEX(Parameters!$D$18:$H$18,1,S88)+(INDEX(Parameters!$D$18:$H$18,1,S88+1)-INDEX(Parameters!$D$18:$H$18,1,S88))*V88)</f>
@@ -16701,7 +16697,7 @@
       </c>
       <c r="P88" s="45">
         <f>M88*O88</f>
-        <v>2975</v>
+        <v>2805</v>
       </c>
       <c r="Q88" s="45">
         <f>MIN(4,MAX(1,INT((1+C88/Parameters!$D$23)*4)+1))</f>
@@ -16775,7 +16771,7 @@
       </c>
       <c r="M89" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="N89" s="43">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S89)+(INDEX(Parameters!$J$18:$N$18,1,S89+1)-INDEX(Parameters!$J$18:$N$18,1,S89))*V89,INDEX(Parameters!$D$18:$H$18,1,S89)+(INDEX(Parameters!$D$18:$H$18,1,S89+1)-INDEX(Parameters!$D$18:$H$18,1,S89))*V89)</f>
@@ -16787,7 +16783,7 @@
       </c>
       <c r="P89" s="43">
         <f>M89*O89</f>
-        <v>3280</v>
+        <v>3116</v>
       </c>
       <c r="Q89" s="43">
         <f>MIN(4,MAX(1,INT((1+C89/Parameters!$D$23)*4)+1))</f>
@@ -16969,23 +16965,23 @@
       </c>
       <c r="C95" s="53">
         <f t="shared" si="10"/>
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D95" s="53">
         <f t="shared" si="11"/>
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E95" s="53">
         <f t="shared" si="12"/>
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F95" s="53">
         <f t="shared" si="13"/>
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="G95" s="53">
         <f t="shared" si="14"/>
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
@@ -17009,23 +17005,23 @@
       </c>
       <c r="C96" s="52">
         <f t="shared" si="10"/>
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D96" s="52">
         <f t="shared" si="11"/>
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E96" s="52">
         <f t="shared" si="12"/>
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="F96" s="52">
         <f t="shared" si="13"/>
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="G96" s="52">
         <f t="shared" si="14"/>
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
@@ -17049,23 +17045,23 @@
       </c>
       <c r="C97" s="53">
         <f t="shared" si="10"/>
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="D97" s="53">
         <f t="shared" si="11"/>
-        <v>375</v>
+        <v>345</v>
       </c>
       <c r="E97" s="53">
         <f t="shared" si="12"/>
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="F97" s="53">
         <f t="shared" si="13"/>
-        <v>525</v>
+        <v>495</v>
       </c>
       <c r="G97" s="53">
         <f t="shared" si="14"/>
-        <v>600</v>
+        <v>570</v>
       </c>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
@@ -17089,23 +17085,23 @@
       </c>
       <c r="C98" s="52">
         <f t="shared" si="10"/>
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="D98" s="52">
         <f t="shared" si="11"/>
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="E98" s="52">
         <f t="shared" si="12"/>
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="F98" s="52">
         <f t="shared" si="13"/>
-        <v>700</v>
+        <v>660</v>
       </c>
       <c r="G98" s="52">
         <f t="shared" si="14"/>
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
@@ -17129,23 +17125,23 @@
       </c>
       <c r="C99" s="53">
         <f t="shared" si="10"/>
-        <v>497.59999999999997</v>
+        <v>447.84</v>
       </c>
       <c r="D99" s="53">
         <f t="shared" si="11"/>
-        <v>625</v>
+        <v>575</v>
       </c>
       <c r="E99" s="53">
         <f t="shared" si="12"/>
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="F99" s="53">
         <f t="shared" si="13"/>
-        <v>875</v>
+        <v>825</v>
       </c>
       <c r="G99" s="53">
         <f t="shared" si="14"/>
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
@@ -17169,23 +17165,23 @@
       </c>
       <c r="C100" s="52">
         <f t="shared" si="10"/>
-        <v>591.59999999999991</v>
+        <v>532.43999999999994</v>
       </c>
       <c r="D100" s="52">
         <f t="shared" si="11"/>
-        <v>739.875</v>
+        <v>680.68499999999995</v>
       </c>
       <c r="E100" s="52">
         <f t="shared" si="12"/>
-        <v>892.8</v>
+        <v>833.28</v>
       </c>
       <c r="F100" s="52">
         <f t="shared" si="13"/>
-        <v>1050</v>
+        <v>990</v>
       </c>
       <c r="G100" s="52">
         <f t="shared" si="14"/>
-        <v>1200</v>
+        <v>1140</v>
       </c>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
@@ -17209,23 +17205,23 @@
       </c>
       <c r="C101" s="53">
         <f t="shared" si="10"/>
-        <v>685.59999999999991</v>
+        <v>617.04</v>
       </c>
       <c r="D101" s="53">
         <f t="shared" si="11"/>
-        <v>853.625</v>
+        <v>785.33499999999992</v>
       </c>
       <c r="E101" s="53">
         <f t="shared" si="12"/>
-        <v>1024.8</v>
+        <v>956.48</v>
       </c>
       <c r="F101" s="53">
         <f t="shared" si="13"/>
-        <v>1201.375</v>
+        <v>1132.7249999999999</v>
       </c>
       <c r="G101" s="53">
         <f t="shared" si="14"/>
-        <v>1385.6</v>
+        <v>1316.32</v>
       </c>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
@@ -17249,23 +17245,23 @@
       </c>
       <c r="C102" s="52">
         <f t="shared" si="10"/>
-        <v>779.6</v>
+        <v>701.6400000000001</v>
       </c>
       <c r="D102" s="52">
         <f t="shared" si="11"/>
-        <v>967.375</v>
+        <v>889.98500000000001</v>
       </c>
       <c r="E102" s="52">
         <f t="shared" si="12"/>
-        <v>1156.8000000000002</v>
+        <v>1079.68</v>
       </c>
       <c r="F102" s="52">
         <f t="shared" si="13"/>
-        <v>1350.1250000000002</v>
+        <v>1272.9749999999999</v>
       </c>
       <c r="G102" s="52">
         <f t="shared" si="14"/>
-        <v>1549.6</v>
+        <v>1472.1200000000001</v>
       </c>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
@@ -17289,23 +17285,23 @@
       </c>
       <c r="C103" s="53">
         <f t="shared" si="10"/>
-        <v>873.6</v>
+        <v>786.24</v>
       </c>
       <c r="D103" s="53">
         <f t="shared" si="11"/>
-        <v>1081.125</v>
+        <v>994.63499999999999</v>
       </c>
       <c r="E103" s="53">
         <f t="shared" si="12"/>
-        <v>1288.8000000000002</v>
+        <v>1202.8800000000001</v>
       </c>
       <c r="F103" s="53">
         <f t="shared" si="13"/>
-        <v>1498.875</v>
+        <v>1413.2249999999999</v>
       </c>
       <c r="G103" s="53">
         <f t="shared" si="14"/>
-        <v>1713.6</v>
+        <v>1627.92</v>
       </c>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
@@ -17329,23 +17325,23 @@
       </c>
       <c r="C104" s="52">
         <f t="shared" si="10"/>
-        <v>967.6</v>
+        <v>870.84</v>
       </c>
       <c r="D104" s="52">
         <f t="shared" si="11"/>
-        <v>1194.875</v>
+        <v>1099.2849999999999</v>
       </c>
       <c r="E104" s="52">
         <f t="shared" si="12"/>
-        <v>1420.8000000000002</v>
+        <v>1326.08</v>
       </c>
       <c r="F104" s="52">
         <f t="shared" si="13"/>
-        <v>1647.625</v>
+        <v>1553.4749999999999</v>
       </c>
       <c r="G104" s="52">
         <f t="shared" si="14"/>
-        <v>1877.6</v>
+        <v>1783.7199999999998</v>
       </c>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
@@ -17369,23 +17365,23 @@
       </c>
       <c r="C105" s="53">
         <f t="shared" si="10"/>
-        <v>1061.6000000000001</v>
+        <v>955.44</v>
       </c>
       <c r="D105" s="53">
         <f t="shared" si="11"/>
-        <v>1308.625</v>
+        <v>1203.9349999999999</v>
       </c>
       <c r="E105" s="53">
         <f t="shared" si="12"/>
-        <v>1552.8000000000002</v>
+        <v>1449.2800000000002</v>
       </c>
       <c r="F105" s="53">
         <f t="shared" si="13"/>
-        <v>1796.3750000000002</v>
+        <v>1693.7250000000001</v>
       </c>
       <c r="G105" s="53">
         <f t="shared" si="14"/>
-        <v>2041.6000000000001</v>
+        <v>1939.52</v>
       </c>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
@@ -17409,23 +17405,23 @@
       </c>
       <c r="C106" s="52">
         <f t="shared" si="10"/>
-        <v>1155.5999999999999</v>
+        <v>1040.04</v>
       </c>
       <c r="D106" s="52">
         <f t="shared" si="11"/>
-        <v>1422.375</v>
+        <v>1308.585</v>
       </c>
       <c r="E106" s="52">
         <f t="shared" si="12"/>
-        <v>1684.8</v>
+        <v>1572.48</v>
       </c>
       <c r="F106" s="52">
         <f t="shared" si="13"/>
-        <v>1945.125</v>
+        <v>1833.9749999999999</v>
       </c>
       <c r="G106" s="52">
         <f t="shared" si="14"/>
-        <v>2205.6</v>
+        <v>2095.3199999999997</v>
       </c>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
@@ -17449,23 +17445,23 @@
       </c>
       <c r="C107" s="53">
         <f t="shared" si="10"/>
-        <v>1249.5999999999999</v>
+        <v>1124.6400000000001</v>
       </c>
       <c r="D107" s="53">
         <f t="shared" si="11"/>
-        <v>1536.125</v>
+        <v>1413.2350000000001</v>
       </c>
       <c r="E107" s="53">
         <f t="shared" si="12"/>
-        <v>1816.8000000000002</v>
+        <v>1695.68</v>
       </c>
       <c r="F107" s="53">
         <f t="shared" si="13"/>
-        <v>2093.875</v>
+        <v>1974.2249999999999</v>
       </c>
       <c r="G107" s="53">
         <f t="shared" si="14"/>
-        <v>2369.6</v>
+        <v>2251.12</v>
       </c>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
@@ -17489,23 +17485,23 @@
       </c>
       <c r="C108" s="52">
         <f t="shared" si="10"/>
-        <v>1343.6</v>
+        <v>1209.24</v>
       </c>
       <c r="D108" s="52">
         <f t="shared" si="11"/>
-        <v>1649.875</v>
+        <v>1517.8849999999998</v>
       </c>
       <c r="E108" s="52">
         <f t="shared" si="12"/>
-        <v>1948.7999999999997</v>
+        <v>1818.88</v>
       </c>
       <c r="F108" s="52">
         <f t="shared" si="13"/>
-        <v>2242.625</v>
+        <v>2114.4749999999999</v>
       </c>
       <c r="G108" s="52">
         <f t="shared" si="14"/>
-        <v>2533.6</v>
+        <v>2406.92</v>
       </c>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
@@ -17529,23 +17525,23 @@
       </c>
       <c r="C109" s="53">
         <f t="shared" si="10"/>
-        <v>1437.6</v>
+        <v>1293.8400000000001</v>
       </c>
       <c r="D109" s="53">
         <f t="shared" si="11"/>
-        <v>1763.625</v>
+        <v>1622.5350000000001</v>
       </c>
       <c r="E109" s="53">
         <f t="shared" si="12"/>
-        <v>2080.8000000000002</v>
+        <v>1942.08</v>
       </c>
       <c r="F109" s="53">
         <f t="shared" si="13"/>
-        <v>2391.375</v>
+        <v>2254.7249999999999</v>
       </c>
       <c r="G109" s="53">
         <f t="shared" si="14"/>
-        <v>2697.6</v>
+        <v>2562.7200000000003</v>
       </c>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
@@ -17569,23 +17565,23 @@
       </c>
       <c r="C110" s="52">
         <f t="shared" si="10"/>
-        <v>1531.6000000000001</v>
+        <v>1378.44</v>
       </c>
       <c r="D110" s="52">
         <f t="shared" si="11"/>
-        <v>1877.375</v>
+        <v>1727.1850000000002</v>
       </c>
       <c r="E110" s="52">
         <f t="shared" si="12"/>
-        <v>2212.8000000000002</v>
+        <v>2065.2800000000002</v>
       </c>
       <c r="F110" s="52">
         <f t="shared" si="13"/>
-        <v>2540.125</v>
+        <v>2394.9749999999999</v>
       </c>
       <c r="G110" s="52">
         <f t="shared" si="14"/>
-        <v>2861.6000000000004</v>
+        <v>2718.52</v>
       </c>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
@@ -17609,23 +17605,23 @@
       </c>
       <c r="C111" s="53">
         <f t="shared" si="10"/>
-        <v>1625.6</v>
+        <v>1463.04</v>
       </c>
       <c r="D111" s="53">
         <f t="shared" si="11"/>
-        <v>1991.125</v>
+        <v>1831.835</v>
       </c>
       <c r="E111" s="53">
         <f t="shared" si="12"/>
-        <v>2344.8000000000002</v>
+        <v>2188.48</v>
       </c>
       <c r="F111" s="53">
         <f t="shared" si="13"/>
-        <v>2688.875</v>
+        <v>2535.2249999999999</v>
       </c>
       <c r="G111" s="53">
         <f t="shared" si="14"/>
-        <v>3025.6000000000004</v>
+        <v>2874.32</v>
       </c>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
@@ -17649,23 +17645,23 @@
       </c>
       <c r="C112" s="52">
         <f t="shared" si="10"/>
-        <v>1719.6000000000001</v>
+        <v>1547.64</v>
       </c>
       <c r="D112" s="52">
         <f t="shared" si="11"/>
-        <v>2104.875</v>
+        <v>1936.4850000000001</v>
       </c>
       <c r="E112" s="52">
         <f t="shared" si="12"/>
-        <v>2476.8000000000002</v>
+        <v>2311.6800000000003</v>
       </c>
       <c r="F112" s="52">
         <f t="shared" si="13"/>
-        <v>2837.625</v>
+        <v>2675.4749999999999</v>
       </c>
       <c r="G112" s="52">
         <f t="shared" si="14"/>
-        <v>3189.6000000000004</v>
+        <v>3030.12</v>
       </c>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
@@ -17689,23 +17685,23 @@
       </c>
       <c r="C113" s="53">
         <f t="shared" si="10"/>
-        <v>1813.6</v>
+        <v>1632.24</v>
       </c>
       <c r="D113" s="53">
         <f t="shared" si="11"/>
-        <v>2218.625</v>
+        <v>2041.135</v>
       </c>
       <c r="E113" s="53">
         <f t="shared" si="12"/>
-        <v>2608.7999999999997</v>
+        <v>2434.88</v>
       </c>
       <c r="F113" s="53">
         <f t="shared" si="13"/>
-        <v>2986.375</v>
+        <v>2815.7249999999999</v>
       </c>
       <c r="G113" s="53">
         <f t="shared" si="14"/>
-        <v>3353.5999999999995</v>
+        <v>3185.9199999999996</v>
       </c>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
@@ -17729,23 +17725,23 @@
       </c>
       <c r="C114" s="52">
         <f t="shared" si="10"/>
-        <v>1907.6000000000001</v>
+        <v>1716.84</v>
       </c>
       <c r="D114" s="52">
         <f t="shared" si="11"/>
-        <v>2332.375</v>
+        <v>2145.7849999999999</v>
       </c>
       <c r="E114" s="52">
         <f t="shared" si="12"/>
-        <v>2740.8</v>
+        <v>2558.08</v>
       </c>
       <c r="F114" s="52">
         <f t="shared" si="13"/>
-        <v>3135.125</v>
+        <v>2955.9749999999999</v>
       </c>
       <c r="G114" s="52">
         <f t="shared" si="14"/>
-        <v>3517.6</v>
+        <v>3341.72</v>
       </c>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
@@ -18084,7 +18080,7 @@
       </c>
       <c r="M125" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S125)+(INDEX(Parameters!$J$17:$N$17,1,S125+1)-INDEX(Parameters!$J$17:$N$17,1,S125))*V125,INDEX(Parameters!$D$17:$H$17,1,S125)+(INDEX(Parameters!$D$17:$H$17,1,S125+1)-INDEX(Parameters!$D$17:$H$17,1,S125))*V125)</f>
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="N125" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S125)+(INDEX(Parameters!$J$18:$N$18,1,S125+1)-INDEX(Parameters!$J$18:$N$18,1,S125))*V125,INDEX(Parameters!$D$18:$H$18,1,S125)+(INDEX(Parameters!$D$18:$H$18,1,S125+1)-INDEX(Parameters!$D$18:$H$18,1,S125))*V125)</f>
@@ -18096,7 +18092,7 @@
       </c>
       <c r="P125" s="43">
         <f>M125*O125</f>
-        <v>1880</v>
+        <v>1692</v>
       </c>
       <c r="Q125" s="43">
         <f>MIN(4,MAX(1,INT((1+C125/Parameters!$D$23)*4)+1))</f>
@@ -18170,7 +18166,7 @@
       </c>
       <c r="M126" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="N126" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S126)+(INDEX(Parameters!$J$18:$N$18,1,S126+1)-INDEX(Parameters!$J$18:$N$18,1,S126))*V126,INDEX(Parameters!$D$18:$H$18,1,S126)+(INDEX(Parameters!$D$18:$H$18,1,S126+1)-INDEX(Parameters!$D$18:$H$18,1,S126))*V126)</f>
@@ -18182,7 +18178,7 @@
       </c>
       <c r="P126" s="45">
         <f>M126*O126</f>
-        <v>2275</v>
+        <v>2093</v>
       </c>
       <c r="Q126" s="45">
         <f>MIN(4,MAX(1,INT((1+C126/Parameters!$D$23)*4)+1))</f>
@@ -18256,7 +18252,7 @@
       </c>
       <c r="M127" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S127)+(INDEX(Parameters!$J$17:$N$17,1,S127+1)-INDEX(Parameters!$J$17:$N$17,1,S127))*V127,INDEX(Parameters!$D$17:$H$17,1,S127)+(INDEX(Parameters!$D$17:$H$17,1,S127+1)-INDEX(Parameters!$D$17:$H$17,1,S127))*V127)</f>
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="N127" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S127)+(INDEX(Parameters!$J$18:$N$18,1,S127+1)-INDEX(Parameters!$J$18:$N$18,1,S127))*V127,INDEX(Parameters!$D$18:$H$18,1,S127)+(INDEX(Parameters!$D$18:$H$18,1,S127+1)-INDEX(Parameters!$D$18:$H$18,1,S127))*V127)</f>
@@ -18268,7 +18264,7 @@
       </c>
       <c r="P127" s="43">
         <f>M127*O127</f>
-        <v>2640</v>
+        <v>2464</v>
       </c>
       <c r="Q127" s="43">
         <f>MIN(4,MAX(1,INT((1+C127/Parameters!$D$23)*4)+1))</f>
@@ -18342,7 +18338,7 @@
       </c>
       <c r="M128" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="N128" s="45">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S128)+(INDEX(Parameters!$J$18:$N$18,1,S128+1)-INDEX(Parameters!$J$18:$N$18,1,S128))*V128,INDEX(Parameters!$D$18:$H$18,1,S128)+(INDEX(Parameters!$D$18:$H$18,1,S128+1)-INDEX(Parameters!$D$18:$H$18,1,S128))*V128)</f>
@@ -18354,7 +18350,7 @@
       </c>
       <c r="P128" s="45">
         <f>M128*O128</f>
-        <v>2975</v>
+        <v>2805</v>
       </c>
       <c r="Q128" s="45">
         <f>MIN(4,MAX(1,INT((1+C128/Parameters!$D$23)*4)+1))</f>
@@ -18428,7 +18424,7 @@
       </c>
       <c r="M129" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="N129" s="43">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S129)+(INDEX(Parameters!$J$18:$N$18,1,S129+1)-INDEX(Parameters!$J$18:$N$18,1,S129))*V129,INDEX(Parameters!$D$18:$H$18,1,S129)+(INDEX(Parameters!$D$18:$H$18,1,S129+1)-INDEX(Parameters!$D$18:$H$18,1,S129))*V129)</f>
@@ -18440,7 +18436,7 @@
       </c>
       <c r="P129" s="43">
         <f>M129*O129</f>
-        <v>3280</v>
+        <v>3116</v>
       </c>
       <c r="Q129" s="43">
         <f>MIN(4,MAX(1,INT((1+C129/Parameters!$D$23)*4)+1))</f>
@@ -18672,23 +18668,23 @@
       </c>
       <c r="H135" s="53">
         <f t="shared" si="20"/>
-        <v>-100</v>
+        <v>-90</v>
       </c>
       <c r="I135" s="53">
         <f t="shared" si="21"/>
-        <v>-125</v>
+        <v>-115</v>
       </c>
       <c r="J135" s="53">
         <f t="shared" si="22"/>
-        <v>-150</v>
+        <v>-140</v>
       </c>
       <c r="K135" s="53">
         <f t="shared" si="23"/>
-        <v>-175</v>
+        <v>-165</v>
       </c>
       <c r="L135" s="53">
         <f t="shared" si="24"/>
-        <v>-200</v>
+        <v>-190</v>
       </c>
       <c r="M135" s="4"/>
       <c r="N135" s="4"/>
@@ -18727,23 +18723,23 @@
       </c>
       <c r="H136" s="52">
         <f t="shared" si="20"/>
-        <v>-200</v>
+        <v>-180</v>
       </c>
       <c r="I136" s="52">
         <f t="shared" si="21"/>
-        <v>-250</v>
+        <v>-230</v>
       </c>
       <c r="J136" s="52">
         <f t="shared" si="22"/>
-        <v>-300</v>
+        <v>-280</v>
       </c>
       <c r="K136" s="52">
         <f t="shared" si="23"/>
-        <v>-350</v>
+        <v>-330</v>
       </c>
       <c r="L136" s="52">
         <f t="shared" si="24"/>
-        <v>-400</v>
+        <v>-380</v>
       </c>
       <c r="M136" s="4"/>
       <c r="N136" s="4"/>
@@ -18782,23 +18778,23 @@
       </c>
       <c r="H137" s="53">
         <f t="shared" si="20"/>
-        <v>-300</v>
+        <v>-270</v>
       </c>
       <c r="I137" s="53">
         <f t="shared" si="21"/>
-        <v>-375</v>
+        <v>-345</v>
       </c>
       <c r="J137" s="53">
         <f t="shared" si="22"/>
-        <v>-450</v>
+        <v>-420</v>
       </c>
       <c r="K137" s="53">
         <f t="shared" si="23"/>
-        <v>-525</v>
+        <v>-495</v>
       </c>
       <c r="L137" s="53">
         <f t="shared" si="24"/>
-        <v>-600</v>
+        <v>-570</v>
       </c>
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
@@ -18837,23 +18833,23 @@
       </c>
       <c r="H138" s="52">
         <f t="shared" si="20"/>
-        <v>-400</v>
+        <v>-360</v>
       </c>
       <c r="I138" s="52">
         <f t="shared" si="21"/>
-        <v>-500</v>
+        <v>-460</v>
       </c>
       <c r="J138" s="52">
         <f t="shared" si="22"/>
-        <v>-600</v>
+        <v>-560</v>
       </c>
       <c r="K138" s="52">
         <f t="shared" si="23"/>
-        <v>-700</v>
+        <v>-660</v>
       </c>
       <c r="L138" s="52">
         <f t="shared" si="24"/>
-        <v>-800</v>
+        <v>-760</v>
       </c>
       <c r="M138" s="4"/>
       <c r="N138" s="4"/>
@@ -18892,23 +18888,23 @@
       </c>
       <c r="H139" s="53">
         <f t="shared" si="20"/>
-        <v>-497.59999999999997</v>
+        <v>-447.84</v>
       </c>
       <c r="I139" s="53">
         <f t="shared" si="21"/>
-        <v>-625</v>
+        <v>-575</v>
       </c>
       <c r="J139" s="53">
         <f t="shared" si="22"/>
-        <v>-750</v>
+        <v>-700</v>
       </c>
       <c r="K139" s="53">
         <f t="shared" si="23"/>
-        <v>-875</v>
+        <v>-825</v>
       </c>
       <c r="L139" s="53">
         <f t="shared" si="24"/>
-        <v>-1000</v>
+        <v>-950</v>
       </c>
       <c r="M139" s="4"/>
       <c r="N139" s="4"/>
@@ -18947,23 +18943,23 @@
       </c>
       <c r="H140" s="52">
         <f t="shared" si="20"/>
-        <v>-591.59999999999991</v>
+        <v>-532.43999999999994</v>
       </c>
       <c r="I140" s="52">
         <f t="shared" si="21"/>
-        <v>-739.875</v>
+        <v>-680.68499999999995</v>
       </c>
       <c r="J140" s="52">
         <f t="shared" si="22"/>
-        <v>-892.8</v>
+        <v>-833.28</v>
       </c>
       <c r="K140" s="52">
         <f t="shared" si="23"/>
-        <v>-1050</v>
+        <v>-990</v>
       </c>
       <c r="L140" s="52">
         <f t="shared" si="24"/>
-        <v>-1200</v>
+        <v>-1140</v>
       </c>
       <c r="M140" s="4"/>
       <c r="N140" s="4"/>
@@ -19002,23 +18998,23 @@
       </c>
       <c r="H141" s="53">
         <f t="shared" si="20"/>
-        <v>-685.59999999999991</v>
+        <v>-617.04</v>
       </c>
       <c r="I141" s="53">
         <f t="shared" si="21"/>
-        <v>-853.625</v>
+        <v>-785.33499999999992</v>
       </c>
       <c r="J141" s="53">
         <f t="shared" si="22"/>
-        <v>-1024.8</v>
+        <v>-956.48</v>
       </c>
       <c r="K141" s="53">
         <f t="shared" si="23"/>
-        <v>-1201.375</v>
+        <v>-1132.7249999999999</v>
       </c>
       <c r="L141" s="53">
         <f t="shared" si="24"/>
-        <v>-1385.6</v>
+        <v>-1316.32</v>
       </c>
       <c r="M141" s="4"/>
       <c r="N141" s="4"/>
@@ -19057,23 +19053,23 @@
       </c>
       <c r="H142" s="52">
         <f t="shared" si="20"/>
-        <v>-779.6</v>
+        <v>-701.6400000000001</v>
       </c>
       <c r="I142" s="52">
         <f t="shared" si="21"/>
-        <v>-967.375</v>
+        <v>-889.98500000000001</v>
       </c>
       <c r="J142" s="52">
         <f t="shared" si="22"/>
-        <v>-1156.8000000000002</v>
+        <v>-1079.68</v>
       </c>
       <c r="K142" s="52">
         <f t="shared" si="23"/>
-        <v>-1350.1250000000002</v>
+        <v>-1272.9749999999999</v>
       </c>
       <c r="L142" s="52">
         <f t="shared" si="24"/>
-        <v>-1549.6</v>
+        <v>-1472.1200000000001</v>
       </c>
       <c r="M142" s="4"/>
       <c r="N142" s="4"/>
@@ -19112,23 +19108,23 @@
       </c>
       <c r="H143" s="53">
         <f t="shared" si="20"/>
-        <v>-873.6</v>
+        <v>-786.24</v>
       </c>
       <c r="I143" s="53">
         <f t="shared" si="21"/>
-        <v>-1081.125</v>
+        <v>-994.63499999999999</v>
       </c>
       <c r="J143" s="53">
         <f t="shared" si="22"/>
-        <v>-1288.8000000000002</v>
+        <v>-1202.8800000000001</v>
       </c>
       <c r="K143" s="53">
         <f t="shared" si="23"/>
-        <v>-1498.875</v>
+        <v>-1413.2249999999999</v>
       </c>
       <c r="L143" s="53">
         <f t="shared" si="24"/>
-        <v>-1713.6</v>
+        <v>-1627.92</v>
       </c>
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
@@ -19167,23 +19163,23 @@
       </c>
       <c r="H144" s="52">
         <f t="shared" si="20"/>
-        <v>-967.6</v>
+        <v>-870.84</v>
       </c>
       <c r="I144" s="52">
         <f t="shared" si="21"/>
-        <v>-1194.875</v>
+        <v>-1099.2849999999999</v>
       </c>
       <c r="J144" s="52">
         <f t="shared" si="22"/>
-        <v>-1420.8000000000002</v>
+        <v>-1326.08</v>
       </c>
       <c r="K144" s="52">
         <f t="shared" si="23"/>
-        <v>-1647.625</v>
+        <v>-1553.4749999999999</v>
       </c>
       <c r="L144" s="52">
         <f t="shared" si="24"/>
-        <v>-1877.6</v>
+        <v>-1783.7199999999998</v>
       </c>
       <c r="M144" s="4"/>
       <c r="N144" s="4"/>
@@ -19222,23 +19218,23 @@
       </c>
       <c r="H145" s="53">
         <f t="shared" si="20"/>
-        <v>-1061.6000000000001</v>
+        <v>-955.44</v>
       </c>
       <c r="I145" s="53">
         <f t="shared" si="21"/>
-        <v>-1308.625</v>
+        <v>-1203.9349999999999</v>
       </c>
       <c r="J145" s="53">
         <f t="shared" si="22"/>
-        <v>-1552.8000000000002</v>
+        <v>-1449.2800000000002</v>
       </c>
       <c r="K145" s="53">
         <f t="shared" si="23"/>
-        <v>-1796.3750000000002</v>
+        <v>-1693.7250000000001</v>
       </c>
       <c r="L145" s="53">
         <f t="shared" si="24"/>
-        <v>-2041.6000000000001</v>
+        <v>-1939.52</v>
       </c>
       <c r="M145" s="4"/>
       <c r="N145" s="4"/>
@@ -19277,23 +19273,23 @@
       </c>
       <c r="H146" s="52">
         <f t="shared" si="20"/>
-        <v>-1155.5999999999999</v>
+        <v>-1040.04</v>
       </c>
       <c r="I146" s="52">
         <f t="shared" si="21"/>
-        <v>-1422.375</v>
+        <v>-1308.585</v>
       </c>
       <c r="J146" s="52">
         <f t="shared" si="22"/>
-        <v>-1684.8</v>
+        <v>-1572.48</v>
       </c>
       <c r="K146" s="52">
         <f t="shared" si="23"/>
-        <v>-1945.125</v>
+        <v>-1833.9749999999999</v>
       </c>
       <c r="L146" s="52">
         <f t="shared" si="24"/>
-        <v>-2205.6</v>
+        <v>-2095.3199999999997</v>
       </c>
       <c r="M146" s="4"/>
       <c r="N146" s="4"/>
@@ -19332,23 +19328,23 @@
       </c>
       <c r="H147" s="53">
         <f t="shared" si="20"/>
-        <v>-1249.5999999999999</v>
+        <v>-1124.6400000000001</v>
       </c>
       <c r="I147" s="53">
         <f t="shared" si="21"/>
-        <v>-1536.125</v>
+        <v>-1413.2350000000001</v>
       </c>
       <c r="J147" s="53">
         <f t="shared" si="22"/>
-        <v>-1816.8000000000002</v>
+        <v>-1695.68</v>
       </c>
       <c r="K147" s="53">
         <f t="shared" si="23"/>
-        <v>-2093.875</v>
+        <v>-1974.2249999999999</v>
       </c>
       <c r="L147" s="53">
         <f t="shared" si="24"/>
-        <v>-2369.6</v>
+        <v>-2251.12</v>
       </c>
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
@@ -19387,23 +19383,23 @@
       </c>
       <c r="H148" s="52">
         <f t="shared" si="20"/>
-        <v>-1343.6</v>
+        <v>-1209.24</v>
       </c>
       <c r="I148" s="52">
         <f t="shared" si="21"/>
-        <v>-1649.875</v>
+        <v>-1517.8849999999998</v>
       </c>
       <c r="J148" s="52">
         <f t="shared" si="22"/>
-        <v>-1948.7999999999997</v>
+        <v>-1818.88</v>
       </c>
       <c r="K148" s="52">
         <f t="shared" si="23"/>
-        <v>-2242.625</v>
+        <v>-2114.4749999999999</v>
       </c>
       <c r="L148" s="52">
         <f t="shared" si="24"/>
-        <v>-2533.6</v>
+        <v>-2406.92</v>
       </c>
       <c r="M148" s="4"/>
       <c r="N148" s="4"/>
@@ -19442,23 +19438,23 @@
       </c>
       <c r="H149" s="53">
         <f t="shared" si="20"/>
-        <v>-1437.6</v>
+        <v>-1293.8400000000001</v>
       </c>
       <c r="I149" s="53">
         <f t="shared" si="21"/>
-        <v>-1763.625</v>
+        <v>-1622.5350000000001</v>
       </c>
       <c r="J149" s="53">
         <f t="shared" si="22"/>
-        <v>-2080.8000000000002</v>
+        <v>-1942.08</v>
       </c>
       <c r="K149" s="53">
         <f t="shared" si="23"/>
-        <v>-2391.375</v>
+        <v>-2254.7249999999999</v>
       </c>
       <c r="L149" s="53">
         <f t="shared" si="24"/>
-        <v>-2697.6</v>
+        <v>-2562.7200000000003</v>
       </c>
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
@@ -19497,23 +19493,23 @@
       </c>
       <c r="H150" s="52">
         <f t="shared" si="20"/>
-        <v>-1531.6000000000001</v>
+        <v>-1378.44</v>
       </c>
       <c r="I150" s="52">
         <f t="shared" si="21"/>
-        <v>-1877.375</v>
+        <v>-1727.1850000000002</v>
       </c>
       <c r="J150" s="52">
         <f t="shared" si="22"/>
-        <v>-2212.8000000000002</v>
+        <v>-2065.2800000000002</v>
       </c>
       <c r="K150" s="52">
         <f t="shared" si="23"/>
-        <v>-2540.125</v>
+        <v>-2394.9749999999999</v>
       </c>
       <c r="L150" s="52">
         <f t="shared" si="24"/>
-        <v>-2861.6000000000004</v>
+        <v>-2718.52</v>
       </c>
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
@@ -19552,23 +19548,23 @@
       </c>
       <c r="H151" s="53">
         <f t="shared" si="20"/>
-        <v>-1625.6</v>
+        <v>-1463.04</v>
       </c>
       <c r="I151" s="53">
         <f t="shared" si="21"/>
-        <v>-1991.125</v>
+        <v>-1831.835</v>
       </c>
       <c r="J151" s="53">
         <f t="shared" si="22"/>
-        <v>-2344.8000000000002</v>
+        <v>-2188.48</v>
       </c>
       <c r="K151" s="53">
         <f t="shared" si="23"/>
-        <v>-2688.875</v>
+        <v>-2535.2249999999999</v>
       </c>
       <c r="L151" s="53">
         <f t="shared" si="24"/>
-        <v>-3025.6000000000004</v>
+        <v>-2874.32</v>
       </c>
       <c r="M151" s="4"/>
       <c r="N151" s="4"/>
@@ -19607,23 +19603,23 @@
       </c>
       <c r="H152" s="52">
         <f t="shared" si="20"/>
-        <v>-1719.6000000000001</v>
+        <v>-1547.64</v>
       </c>
       <c r="I152" s="52">
         <f t="shared" si="21"/>
-        <v>-2104.875</v>
+        <v>-1936.4850000000001</v>
       </c>
       <c r="J152" s="52">
         <f t="shared" si="22"/>
-        <v>-2476.8000000000002</v>
+        <v>-2311.6800000000003</v>
       </c>
       <c r="K152" s="52">
         <f t="shared" si="23"/>
-        <v>-2837.625</v>
+        <v>-2675.4749999999999</v>
       </c>
       <c r="L152" s="52">
         <f t="shared" si="24"/>
-        <v>-3189.6000000000004</v>
+        <v>-3030.12</v>
       </c>
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
@@ -19662,23 +19658,23 @@
       </c>
       <c r="H153" s="53">
         <f t="shared" si="20"/>
-        <v>-1813.6</v>
+        <v>-1632.24</v>
       </c>
       <c r="I153" s="53">
         <f t="shared" si="21"/>
-        <v>-2218.625</v>
+        <v>-2041.135</v>
       </c>
       <c r="J153" s="53">
         <f t="shared" si="22"/>
-        <v>-2608.7999999999997</v>
+        <v>-2434.88</v>
       </c>
       <c r="K153" s="53">
         <f t="shared" si="23"/>
-        <v>-2986.375</v>
+        <v>-2815.7249999999999</v>
       </c>
       <c r="L153" s="53">
         <f t="shared" si="24"/>
-        <v>-3353.5999999999995</v>
+        <v>-3185.9199999999996</v>
       </c>
       <c r="M153" s="4"/>
       <c r="N153" s="4"/>
@@ -19717,23 +19713,23 @@
       </c>
       <c r="H154" s="52">
         <f t="shared" si="20"/>
-        <v>-1907.6000000000001</v>
+        <v>-1716.84</v>
       </c>
       <c r="I154" s="52">
         <f t="shared" si="21"/>
-        <v>-2332.375</v>
+        <v>-2145.7849999999999</v>
       </c>
       <c r="J154" s="52">
         <f t="shared" si="22"/>
-        <v>-2740.8</v>
+        <v>-2558.08</v>
       </c>
       <c r="K154" s="52">
         <f t="shared" si="23"/>
-        <v>-3135.125</v>
+        <v>-2955.9749999999999</v>
       </c>
       <c r="L154" s="52">
         <f t="shared" si="24"/>
-        <v>-3517.6</v>
+        <v>-3341.72</v>
       </c>
       <c r="M154" s="4"/>
       <c r="N154" s="4"/>
@@ -19949,7 +19945,7 @@
       </c>
       <c r="M165" s="56">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S165)+(INDEX(Parameters!$J$17:$N$17,1,S165+1)-INDEX(Parameters!$J$17:$N$17,1,S165))*V165,INDEX(Parameters!$D$17:$H$17,1,S165)+(INDEX(Parameters!$D$17:$H$17,1,S165+1)-INDEX(Parameters!$D$17:$H$17,1,S165))*V165)</f>
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="N165" s="56">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S165)+(INDEX(Parameters!$J$18:$N$18,1,S165+1)-INDEX(Parameters!$J$18:$N$18,1,S165))*V165,INDEX(Parameters!$D$18:$H$18,1,S165)+(INDEX(Parameters!$D$18:$H$18,1,S165+1)-INDEX(Parameters!$D$18:$H$18,1,S165))*V165)</f>
@@ -19961,7 +19957,7 @@
       </c>
       <c r="P165" s="56">
         <f>M165*O165</f>
-        <v>2497.6</v>
+        <v>2319.1999999999998</v>
       </c>
       <c r="Q165" s="56">
         <f>MIN(4,MAX(1,INT((1+C165/Parameters!$D$23)*4)+1))</f>

--- a/docs/damping_curve_RAx8.xlsx
+++ b/docs/damping_curve_RAx8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4075A77F-6E09-4DA1-9293-4EC61C2C99DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EB708F-28AE-465D-9553-5A7A13DF5762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -1693,8 +1693,8 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="39" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="96">
@@ -1895,23 +1895,26 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1919,11 +1922,11 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="24" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1931,23 +1934,32 @@
     <xf numFmtId="2" fontId="25" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="42" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="33" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1964,18 +1976,6 @@
     <xf numFmtId="0" fontId="48" fillId="40" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="42" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="51" fillId="43" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1984,7 +1984,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2002,7 +2002,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3092,7 +3092,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4172,7 +4172,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -5245,7 +5245,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -7544,7 +7544,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -7563,19 +7563,19 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="35.1" customHeight="1">
+    <row r="2" spans="1:8" ht="35.15" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" ht="24.95" customHeight="1">
+    <row r="3" spans="1:8" ht="25" customHeight="1">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -7585,7 +7585,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" ht="32.1" customHeight="1">
+    <row r="4" spans="1:8" ht="32.15" customHeight="1">
       <c r="A4" s="6"/>
       <c r="B4" s="16"/>
       <c r="C4" s="6"/>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:8" ht="30.95" customHeight="1">
+    <row r="5" spans="1:8" ht="31" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="16"/>
       <c r="C5" s="6"/>
@@ -7615,9 +7615,9 @@
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" ht="30.95" customHeight="1">
+    <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="83" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="6"/>
@@ -7632,9 +7632,9 @@
       </c>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" ht="30.95" customHeight="1">
+    <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="72"/>
+      <c r="B7" s="83"/>
       <c r="C7" s="6"/>
       <c r="D7" s="10" t="s">
         <v>4</v>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="30.95" customHeight="1">
+    <row r="8" spans="1:8" ht="31" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="65" t="s">
         <v>92</v>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:8" ht="30.95" customHeight="1">
+    <row r="9" spans="1:8" ht="31" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="66" t="s">
         <v>74</v>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" ht="30.95" customHeight="1">
+    <row r="10" spans="1:8" ht="31" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="6"/>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" ht="30.95" customHeight="1">
+    <row r="11" spans="1:8" ht="31" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="6"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" ht="30.95" customHeight="1">
+    <row r="12" spans="1:8" ht="31" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="6"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" ht="30.95" customHeight="1">
+    <row r="13" spans="1:8" ht="31" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="6"/>
@@ -7741,7 +7741,7 @@
       <c r="F13" s="18"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="24.95" customHeight="1">
+    <row r="14" spans="1:8" ht="25" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -7751,37 +7751,37 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" ht="21.95" customHeight="1">
+    <row r="15" spans="1:8" ht="22" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" ht="21.95" customHeight="1">
+    <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" ht="21.95" customHeight="1">
+    <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="80"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="24.95" customHeight="1">
+    <row r="18" spans="1:8" ht="25" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -7791,7 +7791,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="24.95" customHeight="1">
+    <row r="19" spans="1:8" ht="25" customHeight="1">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -7801,7 +7801,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="24.95" customHeight="1">
+    <row r="20" spans="1:8" ht="25" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7811,7 +7811,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="24.95" customHeight="1">
+    <row r="21" spans="1:8" ht="25" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -7840,7 +7840,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -7866,22 +7866,22 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -7902,7 +7902,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -7911,19 +7911,19 @@
         <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="14.1" customHeight="1">
+    <row r="5" spans="1:15" ht="14.15" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -7940,7 +7940,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="32.1" customHeight="1">
+    <row r="6" spans="1:15" ht="32.15" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="22" t="s">
         <v>12</v>
@@ -7950,20 +7950,20 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="27.95" customHeight="1">
+    <row r="7" spans="1:15" ht="28" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="23" t="s">
         <v>14</v>
@@ -7984,7 +7984,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="27.95" customHeight="1">
+    <row r="8" spans="1:15" ht="28" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="20" t="s">
         <v>15</v>
@@ -7994,23 +7994,23 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="75" t="s">
+      <c r="F8" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="77">
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="78">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>2151.6666666666665</v>
       </c>
-      <c r="J8" s="78"/>
+      <c r="J8" s="79"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="27.95" customHeight="1">
+    <row r="9" spans="1:15" ht="28" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="23" t="s">
         <v>17</v>
@@ -8031,7 +8031,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="27.95" customHeight="1">
+    <row r="10" spans="1:15" ht="28" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="22" t="s">
         <v>18</v>
@@ -8041,23 +8041,23 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="75" t="s">
+      <c r="F10" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="77">
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="78">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1467.3359999999998</v>
       </c>
-      <c r="J10" s="78"/>
+      <c r="J10" s="79"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="23.1" customHeight="1">
+    <row r="11" spans="1:15" ht="23.15" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -8074,7 +8074,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="23.1" customHeight="1">
+    <row r="12" spans="1:15" ht="23.15" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -8091,7 +8091,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="32.1" customHeight="1">
+    <row r="13" spans="1:15" ht="32.15" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="22" t="s">
         <v>20</v>
@@ -8102,20 +8102,20 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="73" t="s">
+      <c r="F13" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="75"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="27.95" customHeight="1">
+    <row r="14" spans="1:15" ht="28" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="27" t="s">
         <v>22</v>
@@ -8126,11 +8126,11 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="79" t="s">
+      <c r="F14" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
       <c r="I14" s="29">
         <f>Samples!F165</f>
         <v>3400</v>
@@ -8144,7 +8144,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="27.95" customHeight="1">
+    <row r="15" spans="1:15" ht="28" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="22" t="s">
         <v>25</v>
@@ -8155,11 +8155,11 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="76" t="s">
+      <c r="F15" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
       <c r="I15" s="30">
         <f>Samples!I165</f>
         <v>3173.3333333333335</v>
@@ -8173,17 +8173,17 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="27.95" customHeight="1">
+    <row r="16" spans="1:15" ht="28" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="82" t="s">
+      <c r="F16" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
       <c r="I16" s="29">
         <f>Samples!J165</f>
         <v>1500</v>
@@ -8197,17 +8197,17 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="27.95" customHeight="1">
+    <row r="17" spans="1:15" ht="28" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="81"/>
-      <c r="H17" s="81"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
       <c r="I17" s="30">
         <f>Samples!L165</f>
         <v>4673.3333333333339</v>
@@ -8221,7 +8221,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="27.95" customHeight="1">
+    <row r="18" spans="1:15" ht="28" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="22" t="s">
         <v>29</v>
@@ -8243,17 +8243,17 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="27.95" customHeight="1">
+    <row r="19" spans="1:15" ht="28" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="79" t="s">
+      <c r="F19" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="G19" s="80"/>
-      <c r="H19" s="80"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
       <c r="I19" s="29">
         <f>Samples!M165</f>
         <v>2600</v>
@@ -8267,17 +8267,17 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="27.95" customHeight="1">
+    <row r="20" spans="1:15" ht="28" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="76" t="s">
+      <c r="F20" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
       <c r="I20" s="30">
         <f>Samples!P165</f>
         <v>2319.1999999999998</v>
@@ -8291,7 +8291,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" ht="27.95" customHeight="1">
+    <row r="21" spans="1:15" ht="28" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -8308,17 +8308,17 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="27.95" customHeight="1">
+    <row r="22" spans="1:15" ht="28" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="82" t="s">
+      <c r="F22" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
       <c r="I22" s="32">
         <f>Samples!G165</f>
         <v>0.1</v>
@@ -8332,17 +8332,17 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="27.95" customHeight="1">
+    <row r="23" spans="1:15" ht="28" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="75" t="s">
+      <c r="F23" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
       <c r="I23" s="33">
         <f>Samples!K165</f>
         <v>0.45</v>
@@ -8356,17 +8356,17 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="27.95" customHeight="1">
+    <row r="24" spans="1:15" ht="28" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="79" t="s">
+      <c r="F24" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
       <c r="I24" s="32">
         <f>Samples!N165</f>
         <v>0.27</v>
@@ -8380,7 +8380,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="23.1" customHeight="1">
+    <row r="25" spans="1:15" ht="23.15" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -8397,7 +8397,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="23.1" customHeight="1">
+    <row r="26" spans="1:15" ht="23.15" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -8414,26 +8414,26 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="23.1" customHeight="1">
+    <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="83" t="s">
+      <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="84"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="84"/>
-      <c r="F27" s="84"/>
-      <c r="G27" s="84"/>
-      <c r="H27" s="84"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="84"/>
-      <c r="M27" s="84"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="67"/>
+      <c r="K27" s="67"/>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" ht="23.1" customHeight="1">
+    <row r="28" spans="1:15" ht="23.15" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -8450,7 +8450,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -8467,7 +8467,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="23.1" customHeight="1">
+    <row r="30" spans="1:15" ht="23.15" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -8484,7 +8484,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -8501,7 +8501,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -8518,7 +8518,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -8535,7 +8535,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -8552,7 +8552,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -8569,7 +8569,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -8586,7 +8586,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -8603,7 +8603,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -8620,7 +8620,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -8637,7 +8637,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -8654,7 +8654,7 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -8671,7 +8671,7 @@
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" ht="23.1" customHeight="1">
+    <row r="42" spans="1:15" ht="23.15" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -8690,17 +8690,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -8708,6 +8697,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="74" type="noConversion"/>
   <dataValidations count="5">
@@ -8739,7 +8739,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -8762,22 +8762,22 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -8798,7 +8798,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8807,19 +8807,19 @@
         <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="14.1" customHeight="1">
+    <row r="5" spans="1:15" ht="14.15" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -8836,7 +8836,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="27.95" customHeight="1">
+    <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="22" t="s">
         <v>37</v>
@@ -8845,19 +8845,19 @@
         <v>-10</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="23.1" customHeight="1">
+    <row r="7" spans="1:15" ht="23.15" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -8874,7 +8874,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="23.1" customHeight="1">
+    <row r="8" spans="1:15" ht="23.15" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -8891,7 +8891,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="23.1" customHeight="1">
+    <row r="9" spans="1:15" ht="23.15" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -8908,7 +8908,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="23.1" customHeight="1">
+    <row r="10" spans="1:15" ht="23.15" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -8925,7 +8925,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="23.1" customHeight="1">
+    <row r="11" spans="1:15" ht="23.15" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -8942,7 +8942,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="23.1" customHeight="1">
+    <row r="12" spans="1:15" ht="23.15" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -8959,7 +8959,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="23.1" customHeight="1">
+    <row r="13" spans="1:15" ht="23.15" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -8976,7 +8976,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="23.1" customHeight="1">
+    <row r="14" spans="1:15" ht="23.15" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -8993,7 +8993,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="23.1" customHeight="1">
+    <row r="15" spans="1:15" ht="23.15" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -9010,7 +9010,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="23.1" customHeight="1">
+    <row r="16" spans="1:15" ht="23.15" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -9027,7 +9027,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="23.1" customHeight="1">
+    <row r="17" spans="1:15" ht="23.15" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -9044,7 +9044,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="23.1" customHeight="1">
+    <row r="18" spans="1:15" ht="23.15" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -9061,7 +9061,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="23.1" customHeight="1">
+    <row r="19" spans="1:15" ht="23.15" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -9078,7 +9078,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="23.1" customHeight="1">
+    <row r="20" spans="1:15" ht="23.15" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -9095,7 +9095,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" ht="23.1" customHeight="1">
+    <row r="21" spans="1:15" ht="23.15" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -9112,7 +9112,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="23.1" customHeight="1">
+    <row r="22" spans="1:15" ht="23.15" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -9129,7 +9129,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="23.1" customHeight="1">
+    <row r="23" spans="1:15" ht="23.15" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -9146,7 +9146,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="23.1" customHeight="1">
+    <row r="24" spans="1:15" ht="23.15" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -9163,7 +9163,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="23.1" customHeight="1">
+    <row r="25" spans="1:15" ht="23.15" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -9180,7 +9180,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="23.1" customHeight="1">
+    <row r="26" spans="1:15" ht="23.15" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -9197,7 +9197,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="23.1" customHeight="1">
+    <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -9214,7 +9214,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" ht="23.1" customHeight="1">
+    <row r="28" spans="1:15" ht="23.15" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -9231,7 +9231,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -9248,7 +9248,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="23.1" customHeight="1">
+    <row r="30" spans="1:15" ht="23.15" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -9265,7 +9265,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -9282,7 +9282,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -9299,7 +9299,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -9316,7 +9316,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -9333,7 +9333,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -9350,7 +9350,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -9367,7 +9367,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -9384,7 +9384,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -9401,7 +9401,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -9418,7 +9418,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -9435,24 +9435,24 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
-      <c r="H41" s="68"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="68"/>
-      <c r="M41" s="68"/>
+      <c r="B41" s="84"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="84"/>
+      <c r="J41" s="84"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="84"/>
+      <c r="M41" s="84"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" ht="23.1" customHeight="1">
+    <row r="42" spans="1:15" ht="23.15" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -9497,7 +9497,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -9520,22 +9520,22 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -9556,7 +9556,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -9565,19 +9565,19 @@
         <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="14.1" customHeight="1">
+    <row r="5" spans="1:15" ht="14.15" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -9594,7 +9594,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="27.95" customHeight="1">
+    <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="22" t="s">
         <v>38</v>
@@ -9603,19 +9603,19 @@
         <v>-8</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="23.1" customHeight="1">
+    <row r="7" spans="1:15" ht="23.15" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -9632,7 +9632,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="23.1" customHeight="1">
+    <row r="8" spans="1:15" ht="23.15" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -9649,7 +9649,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="23.1" customHeight="1">
+    <row r="9" spans="1:15" ht="23.15" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -9666,7 +9666,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="23.1" customHeight="1">
+    <row r="10" spans="1:15" ht="23.15" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -9683,7 +9683,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="23.1" customHeight="1">
+    <row r="11" spans="1:15" ht="23.15" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -9700,7 +9700,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="23.1" customHeight="1">
+    <row r="12" spans="1:15" ht="23.15" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -9717,7 +9717,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="23.1" customHeight="1">
+    <row r="13" spans="1:15" ht="23.15" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -9734,7 +9734,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="23.1" customHeight="1">
+    <row r="14" spans="1:15" ht="23.15" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -9751,7 +9751,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="23.1" customHeight="1">
+    <row r="15" spans="1:15" ht="23.15" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -9768,7 +9768,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="23.1" customHeight="1">
+    <row r="16" spans="1:15" ht="23.15" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -9785,7 +9785,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="23.1" customHeight="1">
+    <row r="17" spans="1:15" ht="23.15" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -9802,7 +9802,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="23.1" customHeight="1">
+    <row r="18" spans="1:15" ht="23.15" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -9819,7 +9819,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="23.1" customHeight="1">
+    <row r="19" spans="1:15" ht="23.15" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -9836,7 +9836,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="23.1" customHeight="1">
+    <row r="20" spans="1:15" ht="23.15" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -9853,7 +9853,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" ht="23.1" customHeight="1">
+    <row r="21" spans="1:15" ht="23.15" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -9870,7 +9870,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="23.1" customHeight="1">
+    <row r="22" spans="1:15" ht="23.15" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -9887,7 +9887,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="23.1" customHeight="1">
+    <row r="23" spans="1:15" ht="23.15" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -9904,7 +9904,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="23.1" customHeight="1">
+    <row r="24" spans="1:15" ht="23.15" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -9921,7 +9921,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="23.1" customHeight="1">
+    <row r="25" spans="1:15" ht="23.15" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -9938,7 +9938,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="23.1" customHeight="1">
+    <row r="26" spans="1:15" ht="23.15" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -9955,7 +9955,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="23.1" customHeight="1">
+    <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -9972,7 +9972,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" ht="23.1" customHeight="1">
+    <row r="28" spans="1:15" ht="23.15" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -9989,7 +9989,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -10006,7 +10006,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="23.1" customHeight="1">
+    <row r="30" spans="1:15" ht="23.15" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -10023,7 +10023,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -10040,7 +10040,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -10057,7 +10057,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -10074,7 +10074,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -10091,7 +10091,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -10108,7 +10108,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -10125,7 +10125,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -10142,7 +10142,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -10159,7 +10159,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -10176,7 +10176,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -10193,24 +10193,24 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
-      <c r="H41" s="68"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="68"/>
-      <c r="M41" s="68"/>
+      <c r="B41" s="84"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="84"/>
+      <c r="J41" s="84"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="84"/>
+      <c r="M41" s="84"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" ht="23.1" customHeight="1">
+    <row r="42" spans="1:15" ht="23.15" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -10255,7 +10255,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -10278,22 +10278,22 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -10314,7 +10314,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -10323,19 +10323,19 @@
         <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="14.1" customHeight="1">
+    <row r="5" spans="1:15" ht="14.15" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -10352,24 +10352,24 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="27.95" customHeight="1">
+    <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="23.1" customHeight="1">
+    <row r="7" spans="1:15" ht="23.15" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -10386,7 +10386,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="23.1" customHeight="1">
+    <row r="8" spans="1:15" ht="23.15" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -10403,7 +10403,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="23.1" customHeight="1">
+    <row r="9" spans="1:15" ht="23.15" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -10420,7 +10420,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="23.1" customHeight="1">
+    <row r="10" spans="1:15" ht="23.15" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -10437,7 +10437,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="23.1" customHeight="1">
+    <row r="11" spans="1:15" ht="23.15" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -10454,7 +10454,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="23.1" customHeight="1">
+    <row r="12" spans="1:15" ht="23.15" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -10471,7 +10471,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="23.1" customHeight="1">
+    <row r="13" spans="1:15" ht="23.15" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -10488,7 +10488,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="23.1" customHeight="1">
+    <row r="14" spans="1:15" ht="23.15" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -10505,7 +10505,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="23.1" customHeight="1">
+    <row r="15" spans="1:15" ht="23.15" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -10522,7 +10522,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="23.1" customHeight="1">
+    <row r="16" spans="1:15" ht="23.15" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -10539,7 +10539,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="23.1" customHeight="1">
+    <row r="17" spans="1:15" ht="23.15" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -10556,7 +10556,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="23.1" customHeight="1">
+    <row r="18" spans="1:15" ht="23.15" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -10573,7 +10573,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="23.1" customHeight="1">
+    <row r="19" spans="1:15" ht="23.15" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -10590,7 +10590,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="23.1" customHeight="1">
+    <row r="20" spans="1:15" ht="23.15" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -10607,7 +10607,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" ht="23.1" customHeight="1">
+    <row r="21" spans="1:15" ht="23.15" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -10624,7 +10624,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="23.1" customHeight="1">
+    <row r="22" spans="1:15" ht="23.15" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -10641,7 +10641,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="23.1" customHeight="1">
+    <row r="23" spans="1:15" ht="23.15" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -10658,7 +10658,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="23.1" customHeight="1">
+    <row r="24" spans="1:15" ht="23.15" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -10675,7 +10675,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="23.1" customHeight="1">
+    <row r="25" spans="1:15" ht="23.15" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -10692,7 +10692,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="23.1" customHeight="1">
+    <row r="26" spans="1:15" ht="23.15" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -10709,7 +10709,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="23.1" customHeight="1">
+    <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -10726,7 +10726,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" ht="23.1" customHeight="1">
+    <row r="28" spans="1:15" ht="23.15" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -10743,7 +10743,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -10760,7 +10760,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="23.1" customHeight="1">
+    <row r="30" spans="1:15" ht="23.15" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -10777,7 +10777,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -10794,7 +10794,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -10811,7 +10811,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -10828,7 +10828,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -10845,7 +10845,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -10862,7 +10862,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -10879,7 +10879,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -10896,7 +10896,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -10913,7 +10913,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -10930,7 +10930,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -10947,24 +10947,24 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
-      <c r="H41" s="68"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="68"/>
-      <c r="M41" s="68"/>
+      <c r="B41" s="84"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="84"/>
+      <c r="J41" s="84"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="84"/>
+      <c r="M41" s="84"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" ht="23.1" customHeight="1">
+    <row r="42" spans="1:15" ht="23.15" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -11005,7 +11005,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -11028,22 +11028,22 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -11064,7 +11064,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -11073,19 +11073,19 @@
         <v>39</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="14.1" customHeight="1">
+    <row r="5" spans="1:15" ht="14.15" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -11102,24 +11102,24 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="27.95" customHeight="1">
+    <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="23.1" customHeight="1">
+    <row r="7" spans="1:15" ht="23.15" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -11136,7 +11136,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="23.1" customHeight="1">
+    <row r="8" spans="1:15" ht="23.15" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -11153,7 +11153,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="23.1" customHeight="1">
+    <row r="9" spans="1:15" ht="23.15" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -11170,7 +11170,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="23.1" customHeight="1">
+    <row r="10" spans="1:15" ht="23.15" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -11187,7 +11187,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="23.1" customHeight="1">
+    <row r="11" spans="1:15" ht="23.15" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -11204,7 +11204,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="23.1" customHeight="1">
+    <row r="12" spans="1:15" ht="23.15" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -11221,7 +11221,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="23.1" customHeight="1">
+    <row r="13" spans="1:15" ht="23.15" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -11238,7 +11238,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="23.1" customHeight="1">
+    <row r="14" spans="1:15" ht="23.15" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -11255,7 +11255,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="23.1" customHeight="1">
+    <row r="15" spans="1:15" ht="23.15" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -11272,7 +11272,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="23.1" customHeight="1">
+    <row r="16" spans="1:15" ht="23.15" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -11289,7 +11289,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="23.1" customHeight="1">
+    <row r="17" spans="1:15" ht="23.15" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -11306,7 +11306,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="23.1" customHeight="1">
+    <row r="18" spans="1:15" ht="23.15" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -11323,7 +11323,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="23.1" customHeight="1">
+    <row r="19" spans="1:15" ht="23.15" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -11340,7 +11340,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="23.1" customHeight="1">
+    <row r="20" spans="1:15" ht="23.15" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -11357,7 +11357,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" ht="23.1" customHeight="1">
+    <row r="21" spans="1:15" ht="23.15" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -11374,7 +11374,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="23.1" customHeight="1">
+    <row r="22" spans="1:15" ht="23.15" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -11391,7 +11391,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="23.1" customHeight="1">
+    <row r="23" spans="1:15" ht="23.15" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -11408,7 +11408,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="23.1" customHeight="1">
+    <row r="24" spans="1:15" ht="23.15" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -11425,7 +11425,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="23.1" customHeight="1">
+    <row r="25" spans="1:15" ht="23.15" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -11442,7 +11442,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="23.1" customHeight="1">
+    <row r="26" spans="1:15" ht="23.15" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -11459,7 +11459,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="23.1" customHeight="1">
+    <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -11476,7 +11476,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" ht="23.1" customHeight="1">
+    <row r="28" spans="1:15" ht="23.15" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -11493,7 +11493,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -11510,7 +11510,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="23.1" customHeight="1">
+    <row r="30" spans="1:15" ht="23.15" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -11527,7 +11527,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -11544,7 +11544,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -11561,7 +11561,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -11578,7 +11578,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -11595,7 +11595,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -11612,7 +11612,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -11629,7 +11629,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -11646,7 +11646,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -11663,7 +11663,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -11680,7 +11680,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -11697,24 +11697,24 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
-      <c r="H41" s="68"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="68"/>
-      <c r="M41" s="68"/>
+      <c r="B41" s="84"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="84"/>
+      <c r="J41" s="84"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="84"/>
+      <c r="M41" s="84"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" ht="23.1" customHeight="1">
+    <row r="42" spans="1:15" ht="23.15" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -11755,7 +11755,7 @@
     <tabColor rgb="FFC49A32"/>
   </sheetPr>
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -11782,45 +11782,45 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="76" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -11837,25 +11837,25 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="32.1" customHeight="1">
+    <row r="5" spans="1:15" ht="32.15" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="74" t="s">
+      <c r="D5" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="74" t="s">
+      <c r="J5" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="29.1" customHeight="1">
+    <row r="7" spans="1:15" ht="29.15" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="20" t="s">
         <v>14</v>
@@ -11955,7 +11955,7 @@
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="29.1" customHeight="1">
+    <row r="8" spans="1:15" ht="29.15" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="23" t="s">
         <v>15</v>
@@ -12023,7 +12023,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="29.1" customHeight="1">
+    <row r="10" spans="1:15" ht="29.15" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="20" t="s">
         <v>23</v>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="29.1" customHeight="1">
+    <row r="11" spans="1:15" ht="29.15" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="27" t="s">
         <v>32</v>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="29.1" customHeight="1">
+    <row r="12" spans="1:15" ht="29.15" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="20" t="s">
         <v>44</v>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="29.1" customHeight="1">
+    <row r="13" spans="1:15" ht="29.15" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="27" t="s">
         <v>27</v>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="29.1" customHeight="1">
+    <row r="14" spans="1:15" ht="29.15" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="22" t="s">
         <v>34</v>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="29.1" customHeight="1">
+    <row r="17" spans="1:15" ht="29.15" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="20" t="s">
         <v>30</v>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="29.1" customHeight="1">
+    <row r="18" spans="1:15" ht="29.15" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="23" t="s">
         <v>35</v>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="29.1" customHeight="1">
+    <row r="19" spans="1:15" ht="29.15" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="20" t="s">
         <v>46</v>
@@ -12487,75 +12487,75 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" ht="32.1" customHeight="1">
+    <row r="22" spans="1:15" ht="32.15" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="73" t="s">
+      <c r="B22" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="74"/>
-      <c r="N22" s="74"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="75"/>
+      <c r="L22" s="75"/>
+      <c r="M22" s="75"/>
+      <c r="N22" s="75"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" ht="29.1" customHeight="1">
+    <row r="23" spans="1:15" ht="29.15" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="82" t="s">
+      <c r="B23" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="80"/>
+      <c r="C23" s="69"/>
       <c r="D23" s="26">
         <v>24</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="87" t="s">
+      <c r="F23" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="88"/>
-      <c r="H23" s="88"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="88"/>
-      <c r="K23" s="88"/>
-      <c r="L23" s="88"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="88"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="92"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="92"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="29.1" customHeight="1">
+    <row r="24" spans="1:15" ht="29.15" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="81"/>
+      <c r="C24" s="71"/>
       <c r="D24" s="28">
         <v>20</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="88"/>
-      <c r="K24" s="88"/>
-      <c r="L24" s="88"/>
-      <c r="M24" s="88"/>
-      <c r="N24" s="88"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="92"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="92"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="29.1" customHeight="1">
+    <row r="25" spans="1:15" ht="29.15" customHeight="1">
       <c r="A25" s="2"/>
-      <c r="B25" s="82" t="s">
+      <c r="B25" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="80"/>
+      <c r="C25" s="69"/>
       <c r="D25" s="26">
         <v>40</v>
       </c>
@@ -12571,35 +12571,35 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="29.1" customHeight="1">
+    <row r="26" spans="1:15" ht="29.15" customHeight="1">
       <c r="A26" s="2"/>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="81"/>
+      <c r="C26" s="71"/>
       <c r="D26" s="28">
         <v>40</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="89" t="s">
+      <c r="F26" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="86"/>
-      <c r="M26" s="86"/>
-      <c r="N26" s="86"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="90"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="90"/>
+      <c r="K26" s="90"/>
+      <c r="L26" s="90"/>
+      <c r="M26" s="90"/>
+      <c r="N26" s="90"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="29.1" customHeight="1">
+    <row r="27" spans="1:15" ht="29.15" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="81"/>
+      <c r="C27" s="71"/>
       <c r="D27" s="28">
         <v>10</v>
       </c>
@@ -12617,143 +12617,143 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="91" t="s">
+      <c r="B28" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="92"/>
-      <c r="G28" s="92"/>
-      <c r="H28" s="92"/>
-      <c r="I28" s="92"/>
-      <c r="J28" s="92"/>
-      <c r="K28" s="92"/>
-      <c r="L28" s="92"/>
-      <c r="M28" s="92"/>
-      <c r="N28" s="92"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="87"/>
+      <c r="J28" s="87"/>
+      <c r="K28" s="87"/>
+      <c r="L28" s="87"/>
+      <c r="M28" s="87"/>
+      <c r="N28" s="87"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="2"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="90"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="90"/>
-      <c r="F29" s="90"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="90"/>
-      <c r="I29" s="90"/>
-      <c r="J29" s="90"/>
-      <c r="K29" s="90"/>
-      <c r="L29" s="90"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="90"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+      <c r="G29" s="85"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="85"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="85"/>
+      <c r="N29" s="85"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" ht="30.95" customHeight="1">
+    <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="93"/>
-      <c r="C30" s="93"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="93"/>
-      <c r="H30" s="93"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="93"/>
-      <c r="M30" s="93"/>
-      <c r="N30" s="93"/>
+      <c r="B30" s="88"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="88"/>
+      <c r="I30" s="88"/>
+      <c r="J30" s="88"/>
+      <c r="K30" s="88"/>
+      <c r="L30" s="88"/>
+      <c r="M30" s="88"/>
+      <c r="N30" s="88"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="90"/>
-      <c r="F31" s="90"/>
-      <c r="G31" s="90"/>
-      <c r="H31" s="90"/>
-      <c r="I31" s="90"/>
-      <c r="J31" s="90"/>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90"/>
-      <c r="M31" s="90"/>
-      <c r="N31" s="90"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="2"/>
-      <c r="B32" s="90"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="90"/>
-      <c r="F32" s="90"/>
-      <c r="G32" s="90"/>
-      <c r="H32" s="90"/>
-      <c r="I32" s="90"/>
-      <c r="J32" s="90"/>
-      <c r="K32" s="90"/>
-      <c r="L32" s="90"/>
-      <c r="M32" s="90"/>
-      <c r="N32" s="90"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="85"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="85"/>
+      <c r="G32" s="85"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="85"/>
+      <c r="J32" s="85"/>
+      <c r="K32" s="85"/>
+      <c r="L32" s="85"/>
+      <c r="M32" s="85"/>
+      <c r="N32" s="85"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="90"/>
-      <c r="C33" s="90"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="90"/>
-      <c r="F33" s="90"/>
-      <c r="G33" s="90"/>
-      <c r="H33" s="90"/>
-      <c r="I33" s="90"/>
-      <c r="J33" s="90"/>
-      <c r="K33" s="90"/>
-      <c r="L33" s="90"/>
-      <c r="M33" s="90"/>
-      <c r="N33" s="90"/>
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+      <c r="G33" s="85"/>
+      <c r="H33" s="85"/>
+      <c r="I33" s="85"/>
+      <c r="J33" s="85"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="85"/>
+      <c r="N33" s="85"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="90"/>
-      <c r="C34" s="90"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="90"/>
-      <c r="G34" s="90"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="90"/>
-      <c r="J34" s="90"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="90"/>
-      <c r="M34" s="90"/>
-      <c r="N34" s="90"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="85"/>
+      <c r="G34" s="85"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
+      <c r="K34" s="85"/>
+      <c r="L34" s="85"/>
+      <c r="M34" s="85"/>
+      <c r="N34" s="85"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="2"/>
-      <c r="B35" s="90"/>
-      <c r="C35" s="90"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="90"/>
-      <c r="F35" s="90"/>
-      <c r="G35" s="90"/>
-      <c r="H35" s="90"/>
-      <c r="I35" s="90"/>
-      <c r="J35" s="90"/>
-      <c r="K35" s="90"/>
-      <c r="L35" s="90"/>
-      <c r="M35" s="90"/>
-      <c r="N35" s="90"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="85"/>
+      <c r="D35" s="85"/>
+      <c r="E35" s="85"/>
+      <c r="F35" s="85"/>
+      <c r="G35" s="85"/>
+      <c r="H35" s="85"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="85"/>
+      <c r="K35" s="85"/>
+      <c r="L35" s="85"/>
+      <c r="M35" s="85"/>
+      <c r="N35" s="85"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -12770,7 +12770,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -12787,7 +12787,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -12804,7 +12804,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -12821,7 +12821,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -12838,7 +12838,7 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -12857,14 +12857,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -12877,6 +12869,14 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
   </mergeCells>
   <phoneticPr fontId="74" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12889,31 +12889,31 @@
     <tabColor rgb="FF93A0AC"/>
   </sheetPr>
   <dimension ref="A1:V165"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="22" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="32.1" customHeight="1">
+    <row r="1" spans="1:22" ht="32.15" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
       <c r="P1" s="94"/>
       <c r="Q1" s="94"/>
       <c r="R1" s="94"/>
@@ -12922,7 +12922,7 @@
       <c r="U1" s="94"/>
       <c r="V1" s="94"/>
     </row>
-    <row r="2" spans="1:22" ht="21.95" customHeight="1">
+    <row r="2" spans="1:22" ht="22" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -12946,7 +12946,7 @@
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
     </row>
-    <row r="3" spans="1:22" ht="21.95" customHeight="1">
+    <row r="3" spans="1:22" ht="22" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -12970,7 +12970,7 @@
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
     </row>
-    <row r="4" spans="1:22" ht="44.1" customHeight="1">
+    <row r="4" spans="1:22" ht="44.15" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="38" t="s">
         <v>51</v>
@@ -13036,7 +13036,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="24.95" customHeight="1">
+    <row r="5" spans="1:22" ht="25" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="42" t="str">
         <f>"c "&amp;C5</f>
@@ -13123,7 +13123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="24.95" customHeight="1">
+    <row r="6" spans="1:22" ht="25" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="44" t="str">
         <f>"c "&amp;C6</f>
@@ -13210,7 +13210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="24.95" customHeight="1">
+    <row r="7" spans="1:22" ht="25" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="42" t="str">
         <f>"c "&amp;C7</f>
@@ -13297,7 +13297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="24.95" customHeight="1">
+    <row r="8" spans="1:22" ht="25" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="44" t="str">
         <f>"c "&amp;C8</f>
@@ -13384,7 +13384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="24.95" customHeight="1">
+    <row r="9" spans="1:22" ht="25" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="42" t="str">
         <f>"c "&amp;C9</f>
@@ -13471,7 +13471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="21.95" customHeight="1">
+    <row r="10" spans="1:22" ht="22" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -13495,7 +13495,7 @@
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
     </row>
-    <row r="11" spans="1:22" ht="21.95" customHeight="1">
+    <row r="11" spans="1:22" ht="22" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -13519,7 +13519,7 @@
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
     </row>
-    <row r="12" spans="1:22" ht="21.95" customHeight="1">
+    <row r="12" spans="1:22" ht="22" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -13584,7 +13584,7 @@
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
     </row>
-    <row r="14" spans="1:22" ht="24.95" customHeight="1">
+    <row r="14" spans="1:22" ht="25" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="48">
         <v>0</v>
@@ -13625,7 +13625,7 @@
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
     </row>
-    <row r="15" spans="1:22" ht="24.95" customHeight="1">
+    <row r="15" spans="1:22" ht="25" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="49">
         <v>0.05</v>
@@ -13666,7 +13666,7 @@
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
     </row>
-    <row r="16" spans="1:22" ht="24.95" customHeight="1">
+    <row r="16" spans="1:22" ht="25" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="48">
         <v>0.1</v>
@@ -13707,7 +13707,7 @@
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
     </row>
-    <row r="17" spans="1:22" ht="24.95" customHeight="1">
+    <row r="17" spans="1:22" ht="25" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="49">
         <v>0.15</v>
@@ -13748,7 +13748,7 @@
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
     </row>
-    <row r="18" spans="1:22" ht="24.95" customHeight="1">
+    <row r="18" spans="1:22" ht="25" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="48">
         <v>0.2</v>
@@ -13789,7 +13789,7 @@
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
     </row>
-    <row r="19" spans="1:22" ht="24.95" customHeight="1">
+    <row r="19" spans="1:22" ht="25" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="49">
         <v>0.25</v>
@@ -13830,7 +13830,7 @@
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
     </row>
-    <row r="20" spans="1:22" ht="24.95" customHeight="1">
+    <row r="20" spans="1:22" ht="25" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="48">
         <v>0.3</v>
@@ -13871,7 +13871,7 @@
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
     </row>
-    <row r="21" spans="1:22" ht="24.95" customHeight="1">
+    <row r="21" spans="1:22" ht="25" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="49">
         <v>0.35</v>
@@ -13912,7 +13912,7 @@
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
     </row>
-    <row r="22" spans="1:22" ht="24.95" customHeight="1">
+    <row r="22" spans="1:22" ht="25" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="48">
         <v>0.4</v>
@@ -13953,7 +13953,7 @@
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
     </row>
-    <row r="23" spans="1:22" ht="24.95" customHeight="1">
+    <row r="23" spans="1:22" ht="25" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="49">
         <v>0.45</v>
@@ -13994,7 +13994,7 @@
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
     </row>
-    <row r="24" spans="1:22" ht="24.95" customHeight="1">
+    <row r="24" spans="1:22" ht="25" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="48">
         <v>0.5</v>
@@ -14035,7 +14035,7 @@
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
     </row>
-    <row r="25" spans="1:22" ht="24.95" customHeight="1">
+    <row r="25" spans="1:22" ht="25" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="49">
         <v>0.55000000000000004</v>
@@ -14076,7 +14076,7 @@
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
     </row>
-    <row r="26" spans="1:22" ht="24.95" customHeight="1">
+    <row r="26" spans="1:22" ht="25" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="48">
         <v>0.6</v>
@@ -14117,7 +14117,7 @@
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
     </row>
-    <row r="27" spans="1:22" ht="24.95" customHeight="1">
+    <row r="27" spans="1:22" ht="25" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="49">
         <v>0.65</v>
@@ -14158,7 +14158,7 @@
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
     </row>
-    <row r="28" spans="1:22" ht="24.95" customHeight="1">
+    <row r="28" spans="1:22" ht="25" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="48">
         <v>0.7</v>
@@ -14199,7 +14199,7 @@
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
     </row>
-    <row r="29" spans="1:22" ht="24.95" customHeight="1">
+    <row r="29" spans="1:22" ht="25" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="49">
         <v>0.75</v>
@@ -14240,7 +14240,7 @@
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
     </row>
-    <row r="30" spans="1:22" ht="24.95" customHeight="1">
+    <row r="30" spans="1:22" ht="25" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="48">
         <v>0.8</v>
@@ -14281,7 +14281,7 @@
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
     </row>
-    <row r="31" spans="1:22" ht="24.95" customHeight="1">
+    <row r="31" spans="1:22" ht="25" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="49">
         <v>0.85</v>
@@ -14322,7 +14322,7 @@
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
     </row>
-    <row r="32" spans="1:22" ht="24.95" customHeight="1">
+    <row r="32" spans="1:22" ht="25" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="48">
         <v>0.9</v>
@@ -14363,7 +14363,7 @@
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
     </row>
-    <row r="33" spans="1:22" ht="24.95" customHeight="1">
+    <row r="33" spans="1:22" ht="25" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="49">
         <v>0.95</v>
@@ -14404,7 +14404,7 @@
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
     </row>
-    <row r="34" spans="1:22" ht="24.95" customHeight="1">
+    <row r="34" spans="1:22" ht="25" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="48">
         <v>1</v>
@@ -14445,7 +14445,7 @@
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
     </row>
-    <row r="35" spans="1:22" ht="21.95" customHeight="1">
+    <row r="35" spans="1:22" ht="22" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -14469,7 +14469,7 @@
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
     </row>
-    <row r="36" spans="1:22" ht="21.95" customHeight="1">
+    <row r="36" spans="1:22" ht="22" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -14493,7 +14493,7 @@
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
     </row>
-    <row r="37" spans="1:22" ht="21.95" customHeight="1">
+    <row r="37" spans="1:22" ht="22" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -14517,7 +14517,7 @@
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
     </row>
-    <row r="38" spans="1:22" ht="21.95" customHeight="1">
+    <row r="38" spans="1:22" ht="22" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -14541,7 +14541,7 @@
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
     </row>
-    <row r="39" spans="1:22" ht="21.95" customHeight="1">
+    <row r="39" spans="1:22" ht="22" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -14565,7 +14565,7 @@
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
     </row>
-    <row r="40" spans="1:22" ht="21.95" customHeight="1">
+    <row r="40" spans="1:22" ht="22" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -14589,24 +14589,24 @@
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
     </row>
-    <row r="41" spans="1:22" ht="32.1" customHeight="1">
+    <row r="41" spans="1:22" ht="32.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
+      <c r="I41" s="76"/>
+      <c r="J41" s="76"/>
+      <c r="K41" s="76"/>
+      <c r="L41" s="76"/>
+      <c r="M41" s="76"/>
+      <c r="N41" s="76"/>
+      <c r="O41" s="76"/>
       <c r="P41" s="94"/>
       <c r="Q41" s="94"/>
       <c r="R41" s="94"/>
@@ -14615,7 +14615,7 @@
       <c r="U41" s="94"/>
       <c r="V41" s="94"/>
     </row>
-    <row r="42" spans="1:22" ht="21.95" customHeight="1">
+    <row r="42" spans="1:22" ht="22" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -14639,7 +14639,7 @@
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
     </row>
-    <row r="43" spans="1:22" ht="21.95" customHeight="1">
+    <row r="43" spans="1:22" ht="22" customHeight="1">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -14662,7 +14662,7 @@
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
     </row>
-    <row r="44" spans="1:22" ht="44.1" customHeight="1">
+    <row r="44" spans="1:22" ht="44.15" customHeight="1">
       <c r="B44" s="41" t="s">
         <v>51</v>
       </c>
@@ -14727,7 +14727,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:22" ht="24.95" customHeight="1">
+    <row r="45" spans="1:22" ht="25" customHeight="1">
       <c r="B45" s="43" t="str">
         <f>"C "&amp;D45</f>
         <v>C -20</v>
@@ -14813,7 +14813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="24.95" customHeight="1">
+    <row r="46" spans="1:22" ht="25" customHeight="1">
       <c r="B46" s="45" t="str">
         <f>"C "&amp;D46</f>
         <v>C -15</v>
@@ -14899,7 +14899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="24.95" customHeight="1">
+    <row r="47" spans="1:22" ht="25" customHeight="1">
       <c r="B47" s="43" t="str">
         <f>"C "&amp;D47</f>
         <v>C -10</v>
@@ -14985,7 +14985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:22" ht="24.95" customHeight="1">
+    <row r="48" spans="1:22" ht="25" customHeight="1">
       <c r="B48" s="45" t="str">
         <f>"C "&amp;D48</f>
         <v>C -5</v>
@@ -15071,7 +15071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22" ht="24.95" customHeight="1">
+    <row r="49" spans="2:22" ht="25" customHeight="1">
       <c r="B49" s="43" t="str">
         <f>"C "&amp;D49</f>
         <v>C 0</v>
@@ -15157,7 +15157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:22" ht="21.95" customHeight="1">
+    <row r="50" spans="2:22" ht="22" customHeight="1">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -15180,7 +15180,7 @@
       <c r="U50" s="4"/>
       <c r="V50" s="4"/>
     </row>
-    <row r="51" spans="2:22" ht="21.95" customHeight="1">
+    <row r="51" spans="2:22" ht="22" customHeight="1">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -15203,7 +15203,7 @@
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
     </row>
-    <row r="52" spans="2:22" ht="21.95" customHeight="1">
+    <row r="52" spans="2:22" ht="22" customHeight="1">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -15266,7 +15266,7 @@
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
     </row>
-    <row r="54" spans="2:22" ht="24.95" customHeight="1">
+    <row r="54" spans="2:22" ht="25" customHeight="1">
       <c r="B54" s="52">
         <v>0</v>
       </c>
@@ -15306,7 +15306,7 @@
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
     </row>
-    <row r="55" spans="2:22" ht="24.95" customHeight="1">
+    <row r="55" spans="2:22" ht="25" customHeight="1">
       <c r="B55" s="53">
         <v>0.05</v>
       </c>
@@ -15346,7 +15346,7 @@
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
     </row>
-    <row r="56" spans="2:22" ht="24.95" customHeight="1">
+    <row r="56" spans="2:22" ht="25" customHeight="1">
       <c r="B56" s="52">
         <v>0.1</v>
       </c>
@@ -15386,7 +15386,7 @@
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
     </row>
-    <row r="57" spans="2:22" ht="24.95" customHeight="1">
+    <row r="57" spans="2:22" ht="25" customHeight="1">
       <c r="B57" s="53">
         <v>0.15</v>
       </c>
@@ -15426,7 +15426,7 @@
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
     </row>
-    <row r="58" spans="2:22" ht="24.95" customHeight="1">
+    <row r="58" spans="2:22" ht="25" customHeight="1">
       <c r="B58" s="52">
         <v>0.2</v>
       </c>
@@ -15466,7 +15466,7 @@
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
     </row>
-    <row r="59" spans="2:22" ht="24.95" customHeight="1">
+    <row r="59" spans="2:22" ht="25" customHeight="1">
       <c r="B59" s="53">
         <v>0.25</v>
       </c>
@@ -15506,7 +15506,7 @@
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
     </row>
-    <row r="60" spans="2:22" ht="24.95" customHeight="1">
+    <row r="60" spans="2:22" ht="25" customHeight="1">
       <c r="B60" s="52">
         <v>0.3</v>
       </c>
@@ -15546,7 +15546,7 @@
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
     </row>
-    <row r="61" spans="2:22" ht="24.95" customHeight="1">
+    <row r="61" spans="2:22" ht="25" customHeight="1">
       <c r="B61" s="53">
         <v>0.35</v>
       </c>
@@ -15586,7 +15586,7 @@
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
     </row>
-    <row r="62" spans="2:22" ht="24.95" customHeight="1">
+    <row r="62" spans="2:22" ht="25" customHeight="1">
       <c r="B62" s="52">
         <v>0.4</v>
       </c>
@@ -15626,7 +15626,7 @@
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
     </row>
-    <row r="63" spans="2:22" ht="24.95" customHeight="1">
+    <row r="63" spans="2:22" ht="25" customHeight="1">
       <c r="B63" s="53">
         <v>0.45</v>
       </c>
@@ -15666,7 +15666,7 @@
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
     </row>
-    <row r="64" spans="2:22" ht="24.95" customHeight="1">
+    <row r="64" spans="2:22" ht="25" customHeight="1">
       <c r="B64" s="52">
         <v>0.5</v>
       </c>
@@ -15706,7 +15706,7 @@
       <c r="U64" s="4"/>
       <c r="V64" s="4"/>
     </row>
-    <row r="65" spans="2:22" ht="24.95" customHeight="1">
+    <row r="65" spans="2:22" ht="25" customHeight="1">
       <c r="B65" s="53">
         <v>0.55000000000000004</v>
       </c>
@@ -15746,7 +15746,7 @@
       <c r="U65" s="4"/>
       <c r="V65" s="4"/>
     </row>
-    <row r="66" spans="2:22" ht="24.95" customHeight="1">
+    <row r="66" spans="2:22" ht="25" customHeight="1">
       <c r="B66" s="52">
         <v>0.6</v>
       </c>
@@ -15786,7 +15786,7 @@
       <c r="U66" s="4"/>
       <c r="V66" s="4"/>
     </row>
-    <row r="67" spans="2:22" ht="24.95" customHeight="1">
+    <row r="67" spans="2:22" ht="25" customHeight="1">
       <c r="B67" s="53">
         <v>0.65</v>
       </c>
@@ -15826,7 +15826,7 @@
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
     </row>
-    <row r="68" spans="2:22" ht="24.95" customHeight="1">
+    <row r="68" spans="2:22" ht="25" customHeight="1">
       <c r="B68" s="52">
         <v>0.7</v>
       </c>
@@ -15866,7 +15866,7 @@
       <c r="U68" s="4"/>
       <c r="V68" s="4"/>
     </row>
-    <row r="69" spans="2:22" ht="24.95" customHeight="1">
+    <row r="69" spans="2:22" ht="25" customHeight="1">
       <c r="B69" s="53">
         <v>0.75</v>
       </c>
@@ -15906,7 +15906,7 @@
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
     </row>
-    <row r="70" spans="2:22" ht="24.95" customHeight="1">
+    <row r="70" spans="2:22" ht="25" customHeight="1">
       <c r="B70" s="52">
         <v>0.8</v>
       </c>
@@ -15946,7 +15946,7 @@
       <c r="U70" s="4"/>
       <c r="V70" s="4"/>
     </row>
-    <row r="71" spans="2:22" ht="24.95" customHeight="1">
+    <row r="71" spans="2:22" ht="25" customHeight="1">
       <c r="B71" s="53">
         <v>0.85</v>
       </c>
@@ -15986,7 +15986,7 @@
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
     </row>
-    <row r="72" spans="2:22" ht="24.95" customHeight="1">
+    <row r="72" spans="2:22" ht="25" customHeight="1">
       <c r="B72" s="52">
         <v>0.9</v>
       </c>
@@ -16026,7 +16026,7 @@
       <c r="U72" s="4"/>
       <c r="V72" s="4"/>
     </row>
-    <row r="73" spans="2:22" ht="24.95" customHeight="1">
+    <row r="73" spans="2:22" ht="25" customHeight="1">
       <c r="B73" s="53">
         <v>0.95</v>
       </c>
@@ -16066,7 +16066,7 @@
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
     </row>
-    <row r="74" spans="2:22" ht="24.95" customHeight="1">
+    <row r="74" spans="2:22" ht="25" customHeight="1">
       <c r="B74" s="52">
         <v>1</v>
       </c>
@@ -16106,7 +16106,7 @@
       <c r="U74" s="4"/>
       <c r="V74" s="4"/>
     </row>
-    <row r="75" spans="2:22" ht="21.95" customHeight="1">
+    <row r="75" spans="2:22" ht="22" customHeight="1">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -16129,7 +16129,7 @@
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
     </row>
-    <row r="76" spans="2:22" ht="21.95" customHeight="1">
+    <row r="76" spans="2:22" ht="22" customHeight="1">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -16152,7 +16152,7 @@
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
     </row>
-    <row r="77" spans="2:22" ht="21.95" customHeight="1">
+    <row r="77" spans="2:22" ht="22" customHeight="1">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -16175,7 +16175,7 @@
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
     </row>
-    <row r="78" spans="2:22" ht="21.95" customHeight="1">
+    <row r="78" spans="2:22" ht="22" customHeight="1">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -16198,7 +16198,7 @@
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
     </row>
-    <row r="79" spans="2:22" ht="21.95" customHeight="1">
+    <row r="79" spans="2:22" ht="22" customHeight="1">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -16221,7 +16221,7 @@
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
     </row>
-    <row r="80" spans="2:22" ht="21.95" customHeight="1">
+    <row r="80" spans="2:22" ht="22" customHeight="1">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -16244,7 +16244,7 @@
       <c r="U80" s="4"/>
       <c r="V80" s="4"/>
     </row>
-    <row r="81" spans="2:22" ht="32.1" customHeight="1">
+    <row r="81" spans="2:22" ht="32.15" customHeight="1">
       <c r="B81" s="94" t="s">
         <v>66</v>
       </c>
@@ -16269,7 +16269,7 @@
       <c r="U81" s="94"/>
       <c r="V81" s="94"/>
     </row>
-    <row r="82" spans="2:22" ht="21.95" customHeight="1">
+    <row r="82" spans="2:22" ht="22" customHeight="1">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -16292,7 +16292,7 @@
       <c r="U82" s="4"/>
       <c r="V82" s="4"/>
     </row>
-    <row r="83" spans="2:22" ht="21.95" customHeight="1">
+    <row r="83" spans="2:22" ht="22" customHeight="1">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -16315,7 +16315,7 @@
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
     </row>
-    <row r="84" spans="2:22" ht="44.1" customHeight="1">
+    <row r="84" spans="2:22" ht="44.15" customHeight="1">
       <c r="B84" s="41" t="s">
         <v>51</v>
       </c>
@@ -16380,7 +16380,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="2:22" ht="24.95" customHeight="1">
+    <row r="85" spans="2:22" ht="25" customHeight="1">
       <c r="B85" s="43" t="str">
         <f>"R "&amp;E85</f>
         <v>R -40</v>
@@ -16466,7 +16466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:22" ht="24.95" customHeight="1">
+    <row r="86" spans="2:22" ht="25" customHeight="1">
       <c r="B86" s="45" t="str">
         <f>"R "&amp;E86</f>
         <v>R -30</v>
@@ -16552,7 +16552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:22" ht="24.95" customHeight="1">
+    <row r="87" spans="2:22" ht="25" customHeight="1">
       <c r="B87" s="43" t="str">
         <f>"R "&amp;E87</f>
         <v>R -20</v>
@@ -16638,7 +16638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:22" ht="24.95" customHeight="1">
+    <row r="88" spans="2:22" ht="25" customHeight="1">
       <c r="B88" s="45" t="str">
         <f>"R "&amp;E88</f>
         <v>R -10</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:22" ht="24.95" customHeight="1">
+    <row r="89" spans="2:22" ht="25" customHeight="1">
       <c r="B89" s="43" t="str">
         <f>"R "&amp;E89</f>
         <v>R 0</v>
@@ -16810,7 +16810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:22" ht="21.95" customHeight="1">
+    <row r="90" spans="2:22" ht="22" customHeight="1">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -16833,7 +16833,7 @@
       <c r="U90" s="4"/>
       <c r="V90" s="4"/>
     </row>
-    <row r="91" spans="2:22" ht="21.95" customHeight="1">
+    <row r="91" spans="2:22" ht="22" customHeight="1">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -16856,7 +16856,7 @@
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
     </row>
-    <row r="92" spans="2:22" ht="21.95" customHeight="1">
+    <row r="92" spans="2:22" ht="22" customHeight="1">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -16919,7 +16919,7 @@
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
     </row>
-    <row r="94" spans="2:22" ht="24.95" customHeight="1">
+    <row r="94" spans="2:22" ht="25" customHeight="1">
       <c r="B94" s="52">
         <v>0</v>
       </c>
@@ -16959,7 +16959,7 @@
       <c r="U94" s="4"/>
       <c r="V94" s="4"/>
     </row>
-    <row r="95" spans="2:22" ht="24.95" customHeight="1">
+    <row r="95" spans="2:22" ht="25" customHeight="1">
       <c r="B95" s="53">
         <v>0.05</v>
       </c>
@@ -16999,7 +16999,7 @@
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
     </row>
-    <row r="96" spans="2:22" ht="24.95" customHeight="1">
+    <row r="96" spans="2:22" ht="25" customHeight="1">
       <c r="B96" s="52">
         <v>0.1</v>
       </c>
@@ -17039,7 +17039,7 @@
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
     </row>
-    <row r="97" spans="2:22" ht="24.95" customHeight="1">
+    <row r="97" spans="2:22" ht="25" customHeight="1">
       <c r="B97" s="53">
         <v>0.15</v>
       </c>
@@ -17079,7 +17079,7 @@
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
     </row>
-    <row r="98" spans="2:22" ht="24.95" customHeight="1">
+    <row r="98" spans="2:22" ht="25" customHeight="1">
       <c r="B98" s="52">
         <v>0.2</v>
       </c>
@@ -17119,7 +17119,7 @@
       <c r="U98" s="4"/>
       <c r="V98" s="4"/>
     </row>
-    <row r="99" spans="2:22" ht="24.95" customHeight="1">
+    <row r="99" spans="2:22" ht="25" customHeight="1">
       <c r="B99" s="53">
         <v>0.25</v>
       </c>
@@ -17159,7 +17159,7 @@
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
     </row>
-    <row r="100" spans="2:22" ht="24.95" customHeight="1">
+    <row r="100" spans="2:22" ht="25" customHeight="1">
       <c r="B100" s="52">
         <v>0.3</v>
       </c>
@@ -17199,7 +17199,7 @@
       <c r="U100" s="4"/>
       <c r="V100" s="4"/>
     </row>
-    <row r="101" spans="2:22" ht="24.95" customHeight="1">
+    <row r="101" spans="2:22" ht="25" customHeight="1">
       <c r="B101" s="53">
         <v>0.35</v>
       </c>
@@ -17239,7 +17239,7 @@
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
     </row>
-    <row r="102" spans="2:22" ht="24.95" customHeight="1">
+    <row r="102" spans="2:22" ht="25" customHeight="1">
       <c r="B102" s="52">
         <v>0.4</v>
       </c>
@@ -17279,7 +17279,7 @@
       <c r="U102" s="4"/>
       <c r="V102" s="4"/>
     </row>
-    <row r="103" spans="2:22" ht="24.95" customHeight="1">
+    <row r="103" spans="2:22" ht="25" customHeight="1">
       <c r="B103" s="53">
         <v>0.45</v>
       </c>
@@ -17319,7 +17319,7 @@
       <c r="U103" s="4"/>
       <c r="V103" s="4"/>
     </row>
-    <row r="104" spans="2:22" ht="24.95" customHeight="1">
+    <row r="104" spans="2:22" ht="25" customHeight="1">
       <c r="B104" s="52">
         <v>0.5</v>
       </c>
@@ -17359,7 +17359,7 @@
       <c r="U104" s="4"/>
       <c r="V104" s="4"/>
     </row>
-    <row r="105" spans="2:22" ht="24.95" customHeight="1">
+    <row r="105" spans="2:22" ht="25" customHeight="1">
       <c r="B105" s="53">
         <v>0.55000000000000004</v>
       </c>
@@ -17399,7 +17399,7 @@
       <c r="U105" s="4"/>
       <c r="V105" s="4"/>
     </row>
-    <row r="106" spans="2:22" ht="24.95" customHeight="1">
+    <row r="106" spans="2:22" ht="25" customHeight="1">
       <c r="B106" s="52">
         <v>0.6</v>
       </c>
@@ -17439,7 +17439,7 @@
       <c r="U106" s="4"/>
       <c r="V106" s="4"/>
     </row>
-    <row r="107" spans="2:22" ht="24.95" customHeight="1">
+    <row r="107" spans="2:22" ht="25" customHeight="1">
       <c r="B107" s="53">
         <v>0.65</v>
       </c>
@@ -17479,7 +17479,7 @@
       <c r="U107" s="4"/>
       <c r="V107" s="4"/>
     </row>
-    <row r="108" spans="2:22" ht="24.95" customHeight="1">
+    <row r="108" spans="2:22" ht="25" customHeight="1">
       <c r="B108" s="52">
         <v>0.7</v>
       </c>
@@ -17519,7 +17519,7 @@
       <c r="U108" s="4"/>
       <c r="V108" s="4"/>
     </row>
-    <row r="109" spans="2:22" ht="24.95" customHeight="1">
+    <row r="109" spans="2:22" ht="25" customHeight="1">
       <c r="B109" s="53">
         <v>0.75</v>
       </c>
@@ -17559,7 +17559,7 @@
       <c r="U109" s="4"/>
       <c r="V109" s="4"/>
     </row>
-    <row r="110" spans="2:22" ht="24.95" customHeight="1">
+    <row r="110" spans="2:22" ht="25" customHeight="1">
       <c r="B110" s="52">
         <v>0.8</v>
       </c>
@@ -17599,7 +17599,7 @@
       <c r="U110" s="4"/>
       <c r="V110" s="4"/>
     </row>
-    <row r="111" spans="2:22" ht="24.95" customHeight="1">
+    <row r="111" spans="2:22" ht="25" customHeight="1">
       <c r="B111" s="53">
         <v>0.85</v>
       </c>
@@ -17639,7 +17639,7 @@
       <c r="U111" s="4"/>
       <c r="V111" s="4"/>
     </row>
-    <row r="112" spans="2:22" ht="24.95" customHeight="1">
+    <row r="112" spans="2:22" ht="25" customHeight="1">
       <c r="B112" s="52">
         <v>0.9</v>
       </c>
@@ -17679,7 +17679,7 @@
       <c r="U112" s="4"/>
       <c r="V112" s="4"/>
     </row>
-    <row r="113" spans="2:22" ht="24.95" customHeight="1">
+    <row r="113" spans="2:22" ht="25" customHeight="1">
       <c r="B113" s="53">
         <v>0.95</v>
       </c>
@@ -17719,7 +17719,7 @@
       <c r="U113" s="4"/>
       <c r="V113" s="4"/>
     </row>
-    <row r="114" spans="2:22" ht="24.95" customHeight="1">
+    <row r="114" spans="2:22" ht="25" customHeight="1">
       <c r="B114" s="52">
         <v>1</v>
       </c>
@@ -17759,7 +17759,7 @@
       <c r="U114" s="4"/>
       <c r="V114" s="4"/>
     </row>
-    <row r="115" spans="2:22" ht="21.95" customHeight="1">
+    <row r="115" spans="2:22" ht="22" customHeight="1">
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
@@ -17782,7 +17782,7 @@
       <c r="U115" s="4"/>
       <c r="V115" s="4"/>
     </row>
-    <row r="116" spans="2:22" ht="21.95" customHeight="1">
+    <row r="116" spans="2:22" ht="22" customHeight="1">
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
@@ -17805,7 +17805,7 @@
       <c r="U116" s="4"/>
       <c r="V116" s="4"/>
     </row>
-    <row r="117" spans="2:22" ht="21.95" customHeight="1">
+    <row r="117" spans="2:22" ht="22" customHeight="1">
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
@@ -17828,7 +17828,7 @@
       <c r="U117" s="4"/>
       <c r="V117" s="4"/>
     </row>
-    <row r="118" spans="2:22" ht="21.95" customHeight="1">
+    <row r="118" spans="2:22" ht="22" customHeight="1">
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
@@ -17851,7 +17851,7 @@
       <c r="U118" s="4"/>
       <c r="V118" s="4"/>
     </row>
-    <row r="119" spans="2:22" ht="21.95" customHeight="1">
+    <row r="119" spans="2:22" ht="22" customHeight="1">
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
@@ -17874,7 +17874,7 @@
       <c r="U119" s="4"/>
       <c r="V119" s="4"/>
     </row>
-    <row r="120" spans="2:22" ht="21.95" customHeight="1">
+    <row r="120" spans="2:22" ht="22" customHeight="1">
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
@@ -17897,7 +17897,7 @@
       <c r="U120" s="4"/>
       <c r="V120" s="4"/>
     </row>
-    <row r="121" spans="2:22" ht="32.1" customHeight="1">
+    <row r="121" spans="2:22" ht="32.15" customHeight="1">
       <c r="B121" s="94" t="s">
         <v>67</v>
       </c>
@@ -17922,7 +17922,7 @@
       <c r="U121" s="94"/>
       <c r="V121" s="94"/>
     </row>
-    <row r="122" spans="2:22" ht="21.95" customHeight="1">
+    <row r="122" spans="2:22" ht="22" customHeight="1">
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
@@ -17945,7 +17945,7 @@
       <c r="U122" s="4"/>
       <c r="V122" s="4"/>
     </row>
-    <row r="123" spans="2:22" ht="21.95" customHeight="1">
+    <row r="123" spans="2:22" ht="22" customHeight="1">
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
@@ -17968,7 +17968,7 @@
       <c r="U123" s="4"/>
       <c r="V123" s="4"/>
     </row>
-    <row r="124" spans="2:22" ht="44.1" customHeight="1">
+    <row r="124" spans="2:22" ht="44.15" customHeight="1">
       <c r="B124" s="41" t="s">
         <v>51</v>
       </c>
@@ -18033,7 +18033,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="125" spans="2:22" ht="24.95" customHeight="1">
+    <row r="125" spans="2:22" ht="25" customHeight="1">
       <c r="B125" s="43" t="str">
         <f>"c "&amp;C125&amp;" / C "&amp;D125</f>
         <v>c -24 / C -20</v>
@@ -18119,7 +18119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="2:22" ht="24.95" customHeight="1">
+    <row r="126" spans="2:22" ht="25" customHeight="1">
       <c r="B126" s="45" t="str">
         <f>"c "&amp;C126&amp;" / C "&amp;D126</f>
         <v>c -18 / C -15</v>
@@ -18205,7 +18205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="2:22" ht="24.95" customHeight="1">
+    <row r="127" spans="2:22" ht="25" customHeight="1">
       <c r="B127" s="43" t="str">
         <f>"c "&amp;C127&amp;" / C "&amp;D127</f>
         <v>c -12 / C -10</v>
@@ -18291,7 +18291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="2:22" ht="24.95" customHeight="1">
+    <row r="128" spans="2:22" ht="25" customHeight="1">
       <c r="B128" s="45" t="str">
         <f>"c "&amp;C128&amp;" / C "&amp;D128</f>
         <v>c -6 / C -5</v>
@@ -18377,7 +18377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="2:22" ht="24.95" customHeight="1">
+    <row r="129" spans="2:22" ht="25" customHeight="1">
       <c r="B129" s="43" t="str">
         <f>"c "&amp;C129&amp;" / C "&amp;D129</f>
         <v>c 0 / C 0</v>
@@ -18463,7 +18463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="2:22" ht="21.95" customHeight="1">
+    <row r="130" spans="2:22" ht="22" customHeight="1">
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
@@ -18486,7 +18486,7 @@
       <c r="U130" s="4"/>
       <c r="V130" s="4"/>
     </row>
-    <row r="131" spans="2:22" ht="21.95" customHeight="1">
+    <row r="131" spans="2:22" ht="22" customHeight="1">
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
@@ -18509,7 +18509,7 @@
       <c r="U131" s="4"/>
       <c r="V131" s="4"/>
     </row>
-    <row r="132" spans="2:22" ht="21.95" customHeight="1">
+    <row r="132" spans="2:22" ht="22" customHeight="1">
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
@@ -18587,7 +18587,7 @@
       <c r="U133" s="4"/>
       <c r="V133" s="4"/>
     </row>
-    <row r="134" spans="2:22" ht="24.95" customHeight="1">
+    <row r="134" spans="2:22" ht="25" customHeight="1">
       <c r="B134" s="52">
         <v>0</v>
       </c>
@@ -18642,7 +18642,7 @@
       <c r="U134" s="4"/>
       <c r="V134" s="4"/>
     </row>
-    <row r="135" spans="2:22" ht="24.95" customHeight="1">
+    <row r="135" spans="2:22" ht="25" customHeight="1">
       <c r="B135" s="53">
         <v>0.05</v>
       </c>
@@ -18697,7 +18697,7 @@
       <c r="U135" s="4"/>
       <c r="V135" s="4"/>
     </row>
-    <row r="136" spans="2:22" ht="24.95" customHeight="1">
+    <row r="136" spans="2:22" ht="25" customHeight="1">
       <c r="B136" s="52">
         <v>0.1</v>
       </c>
@@ -18752,7 +18752,7 @@
       <c r="U136" s="4"/>
       <c r="V136" s="4"/>
     </row>
-    <row r="137" spans="2:22" ht="24.95" customHeight="1">
+    <row r="137" spans="2:22" ht="25" customHeight="1">
       <c r="B137" s="53">
         <v>0.15</v>
       </c>
@@ -18807,7 +18807,7 @@
       <c r="U137" s="4"/>
       <c r="V137" s="4"/>
     </row>
-    <row r="138" spans="2:22" ht="24.95" customHeight="1">
+    <row r="138" spans="2:22" ht="25" customHeight="1">
       <c r="B138" s="52">
         <v>0.2</v>
       </c>
@@ -18862,7 +18862,7 @@
       <c r="U138" s="4"/>
       <c r="V138" s="4"/>
     </row>
-    <row r="139" spans="2:22" ht="24.95" customHeight="1">
+    <row r="139" spans="2:22" ht="25" customHeight="1">
       <c r="B139" s="53">
         <v>0.25</v>
       </c>
@@ -18917,7 +18917,7 @@
       <c r="U139" s="4"/>
       <c r="V139" s="4"/>
     </row>
-    <row r="140" spans="2:22" ht="24.95" customHeight="1">
+    <row r="140" spans="2:22" ht="25" customHeight="1">
       <c r="B140" s="52">
         <v>0.3</v>
       </c>
@@ -18972,7 +18972,7 @@
       <c r="U140" s="4"/>
       <c r="V140" s="4"/>
     </row>
-    <row r="141" spans="2:22" ht="24.95" customHeight="1">
+    <row r="141" spans="2:22" ht="25" customHeight="1">
       <c r="B141" s="53">
         <v>0.35</v>
       </c>
@@ -19027,7 +19027,7 @@
       <c r="U141" s="4"/>
       <c r="V141" s="4"/>
     </row>
-    <row r="142" spans="2:22" ht="24.95" customHeight="1">
+    <row r="142" spans="2:22" ht="25" customHeight="1">
       <c r="B142" s="52">
         <v>0.4</v>
       </c>
@@ -19082,7 +19082,7 @@
       <c r="U142" s="4"/>
       <c r="V142" s="4"/>
     </row>
-    <row r="143" spans="2:22" ht="24.95" customHeight="1">
+    <row r="143" spans="2:22" ht="25" customHeight="1">
       <c r="B143" s="53">
         <v>0.45</v>
       </c>
@@ -19137,7 +19137,7 @@
       <c r="U143" s="4"/>
       <c r="V143" s="4"/>
     </row>
-    <row r="144" spans="2:22" ht="24.95" customHeight="1">
+    <row r="144" spans="2:22" ht="25" customHeight="1">
       <c r="B144" s="52">
         <v>0.5</v>
       </c>
@@ -19192,7 +19192,7 @@
       <c r="U144" s="4"/>
       <c r="V144" s="4"/>
     </row>
-    <row r="145" spans="2:22" ht="24.95" customHeight="1">
+    <row r="145" spans="2:22" ht="25" customHeight="1">
       <c r="B145" s="53">
         <v>0.55000000000000004</v>
       </c>
@@ -19247,7 +19247,7 @@
       <c r="U145" s="4"/>
       <c r="V145" s="4"/>
     </row>
-    <row r="146" spans="2:22" ht="24.95" customHeight="1">
+    <row r="146" spans="2:22" ht="25" customHeight="1">
       <c r="B146" s="52">
         <v>0.6</v>
       </c>
@@ -19302,7 +19302,7 @@
       <c r="U146" s="4"/>
       <c r="V146" s="4"/>
     </row>
-    <row r="147" spans="2:22" ht="24.95" customHeight="1">
+    <row r="147" spans="2:22" ht="25" customHeight="1">
       <c r="B147" s="53">
         <v>0.65</v>
       </c>
@@ -19357,7 +19357,7 @@
       <c r="U147" s="4"/>
       <c r="V147" s="4"/>
     </row>
-    <row r="148" spans="2:22" ht="24.95" customHeight="1">
+    <row r="148" spans="2:22" ht="25" customHeight="1">
       <c r="B148" s="52">
         <v>0.7</v>
       </c>
@@ -19412,7 +19412,7 @@
       <c r="U148" s="4"/>
       <c r="V148" s="4"/>
     </row>
-    <row r="149" spans="2:22" ht="24.95" customHeight="1">
+    <row r="149" spans="2:22" ht="25" customHeight="1">
       <c r="B149" s="53">
         <v>0.75</v>
       </c>
@@ -19467,7 +19467,7 @@
       <c r="U149" s="4"/>
       <c r="V149" s="4"/>
     </row>
-    <row r="150" spans="2:22" ht="24.95" customHeight="1">
+    <row r="150" spans="2:22" ht="25" customHeight="1">
       <c r="B150" s="52">
         <v>0.8</v>
       </c>
@@ -19522,7 +19522,7 @@
       <c r="U150" s="4"/>
       <c r="V150" s="4"/>
     </row>
-    <row r="151" spans="2:22" ht="24.95" customHeight="1">
+    <row r="151" spans="2:22" ht="25" customHeight="1">
       <c r="B151" s="53">
         <v>0.85</v>
       </c>
@@ -19577,7 +19577,7 @@
       <c r="U151" s="4"/>
       <c r="V151" s="4"/>
     </row>
-    <row r="152" spans="2:22" ht="24.95" customHeight="1">
+    <row r="152" spans="2:22" ht="25" customHeight="1">
       <c r="B152" s="52">
         <v>0.9</v>
       </c>
@@ -19632,7 +19632,7 @@
       <c r="U152" s="4"/>
       <c r="V152" s="4"/>
     </row>
-    <row r="153" spans="2:22" ht="24.95" customHeight="1">
+    <row r="153" spans="2:22" ht="25" customHeight="1">
       <c r="B153" s="53">
         <v>0.95</v>
       </c>
@@ -19687,7 +19687,7 @@
       <c r="U153" s="4"/>
       <c r="V153" s="4"/>
     </row>
-    <row r="154" spans="2:22" ht="24.95" customHeight="1">
+    <row r="154" spans="2:22" ht="25" customHeight="1">
       <c r="B154" s="52">
         <v>1</v>
       </c>
@@ -19742,7 +19742,7 @@
       <c r="U154" s="4"/>
       <c r="V154" s="4"/>
     </row>
-    <row r="155" spans="2:22" ht="21.95" customHeight="1">
+    <row r="155" spans="2:22" ht="22" customHeight="1">
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
@@ -19765,7 +19765,7 @@
       <c r="U155" s="4"/>
       <c r="V155" s="4"/>
     </row>
-    <row r="156" spans="2:22" ht="21.95" customHeight="1">
+    <row r="156" spans="2:22" ht="22" customHeight="1">
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
@@ -19788,7 +19788,7 @@
       <c r="U156" s="4"/>
       <c r="V156" s="4"/>
     </row>
-    <row r="157" spans="2:22" ht="21.95" customHeight="1">
+    <row r="157" spans="2:22" ht="22" customHeight="1">
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -19811,7 +19811,7 @@
       <c r="U157" s="4"/>
       <c r="V157" s="4"/>
     </row>
-    <row r="161" spans="2:22" ht="32.1" customHeight="1">
+    <row r="161" spans="2:22" ht="32.15" customHeight="1">
       <c r="B161" s="95" t="s">
         <v>68</v>
       </c>
@@ -19836,7 +19836,7 @@
       <c r="U161" s="95"/>
       <c r="V161" s="95"/>
     </row>
-    <row r="164" spans="2:22" ht="44.1" customHeight="1">
+    <row r="164" spans="2:22" ht="44.15" customHeight="1">
       <c r="B164" s="54" t="s">
         <v>51</v>
       </c>
@@ -19901,7 +19901,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="165" spans="2:22" ht="24.95" customHeight="1">
+    <row r="165" spans="2:22" ht="25" customHeight="1">
       <c r="B165" s="57"/>
       <c r="C165" s="56">
         <f>Calculator!C7</f>

--- a/docs/damping_curve_RAx8.xlsx
+++ b/docs/damping_curve_RAx8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\xlsx-locale-20261027\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EB708F-28AE-465D-9553-5A7A13DF5762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9738C9B-05B1-481C-9E92-C3B20E39C534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -20,9 +20,10 @@
     <sheet name="LSR Sweep" sheetId="3" r:id="rId5"/>
     <sheet name="Full Sweep" sheetId="4" r:id="rId6"/>
     <sheet name="Parameters" sheetId="5" r:id="rId7"/>
-    <sheet name="Samples" sheetId="7" r:id="rId8"/>
+    <sheet name="Locale" sheetId="9" state="hidden" r:id="rId8"/>
+    <sheet name="Samples" sheetId="7" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="266">
   <si>
     <t>规格</t>
   </si>
@@ -132,33 +133,18 @@
     <t>输入检查</t>
   </si>
   <si>
-    <t>rebound</t>
-  </si>
-  <si>
     <t>HSrebound</t>
   </si>
   <si>
-    <t>第一 knee</t>
-  </si>
-  <si>
     <t>m/s</t>
   </si>
   <si>
-    <t>第二 knee</t>
-  </si>
-  <si>
     <t>Rebound knee</t>
   </si>
   <si>
     <t>黄色单元格为手动输入。</t>
   </si>
   <si>
-    <t>固定 HSC</t>
-  </si>
-  <si>
-    <t>固定 LSC</t>
-  </si>
-  <si>
     <t>Type-A</t>
   </si>
   <si>
@@ -183,9 +169,6 @@
     <t>HSrebound / rebound</t>
   </si>
   <si>
-    <t>Adjusters · 调节格数</t>
-  </si>
-  <si>
     <t>0 为最硬，负数为退出格数。</t>
   </si>
   <si>
@@ -258,9 +241,6 @@
     <t>RA88</t>
   </si>
   <si>
-    <t>前 215 / 后 190 mm</t>
-  </si>
-  <si>
     <t>3-Way</t>
   </si>
   <si>
@@ -270,9 +250,6 @@
     <t>固定</t>
   </si>
   <si>
-    <t>可调 · 16 clicks</t>
-  </si>
-  <si>
     <t>有</t>
   </si>
   <si>
@@ -300,9 +277,6 @@
     <t>LSC · 全系列</t>
   </si>
   <si>
-    <t>Sweep 使用 RA88 调节格数。</t>
-  </si>
-  <si>
     <t>HSC · RA88</t>
   </si>
   <si>
@@ -316,13 +290,558 @@
   </si>
   <si>
     <t>RA88</t>
-    <phoneticPr fontId="74" type="noConversion"/>
+    <phoneticPr fontId="73" type="noConversion"/>
   </si>
   <si>
     <t>Rally</t>
   </si>
   <si>
     <t>3+1-Way</t>
+  </si>
+  <si>
+    <t>Language / 语言</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>en-US</t>
+  </si>
+  <si>
+    <t>zh-CN</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>chart.rax8CompressionRebound</t>
+  </si>
+  <si>
+    <t>RAx8 · Compression (+) / Rebound (−)</t>
+  </si>
+  <si>
+    <t>RAx8 · 压缩 (+) / 回弹 (−)</t>
+  </si>
+  <si>
+    <t>chart.rax8HscSweep</t>
+  </si>
+  <si>
+    <t>RAx8 · HSC Sweep</t>
+  </si>
+  <si>
+    <t>RAx8 · 高速压缩调节曲线</t>
+  </si>
+  <si>
+    <t>chart.rax8LscSweep</t>
+  </si>
+  <si>
+    <t>RAx8 · LSC Sweep</t>
+  </si>
+  <si>
+    <t>RAx8 · 低速压缩调节曲线</t>
+  </si>
+  <si>
+    <t>chart.rax8LsrSweep</t>
+  </si>
+  <si>
+    <t>RAx8 · LSR Sweep</t>
+  </si>
+  <si>
+    <t>RAx8 · 低速回弹调节曲线</t>
+  </si>
+  <si>
+    <t>label.adjustableSixteenClicks</t>
+  </si>
+  <si>
+    <t>Adjustable · 16 clicks</t>
+  </si>
+  <si>
+    <t>可调 · 16 格</t>
+  </si>
+  <si>
+    <t>label.adjusterClicks</t>
+  </si>
+  <si>
+    <t>Adjusters · Clicks</t>
+  </si>
+  <si>
+    <t>调节格数</t>
+  </si>
+  <si>
+    <t>label.adjusterPosition</t>
+  </si>
+  <si>
+    <t>Adjuster position</t>
+  </si>
+  <si>
+    <t>label.available</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>label.bump2Multiplier</t>
+  </si>
+  <si>
+    <t>bump2 multiplier</t>
+  </si>
+  <si>
+    <t>label.bumpDampingForceN</t>
+  </si>
+  <si>
+    <t>Bump damping force (N)</t>
+  </si>
+  <si>
+    <t>压缩阻尼力 (N)</t>
+  </si>
+  <si>
+    <t>label.cTotalClicks</t>
+  </si>
+  <si>
+    <t>c total clicks</t>
+  </si>
+  <si>
+    <t>label.calculator</t>
+  </si>
+  <si>
+    <t>计算器</t>
+  </si>
+  <si>
+    <t>label.clicks</t>
+  </si>
+  <si>
+    <t>clicks</t>
+  </si>
+  <si>
+    <t>label.compressionForceN</t>
+  </si>
+  <si>
+    <t>Compression force (N)</t>
+  </si>
+  <si>
+    <t>label.curve</t>
+  </si>
+  <si>
+    <t>Curve</t>
+  </si>
+  <si>
+    <t>label.damperModel</t>
+  </si>
+  <si>
+    <t>Damper model</t>
+  </si>
+  <si>
+    <t>label.dampingAdjustment</t>
+  </si>
+  <si>
+    <t>Damping adjustment</t>
+  </si>
+  <si>
+    <t>label.dampingForceN</t>
+  </si>
+  <si>
+    <t>Damping force (N)</t>
+  </si>
+  <si>
+    <t>阻尼力 (N)</t>
+  </si>
+  <si>
+    <t>label.extensionSpeed</t>
+  </si>
+  <si>
+    <t>Extension speed (m/s)</t>
+  </si>
+  <si>
+    <t>伸展速度 (m/s)</t>
+  </si>
+  <si>
+    <t>label.firstKnee</t>
+  </si>
+  <si>
+    <t>First knee</t>
+  </si>
+  <si>
+    <t>第一拐点</t>
+  </si>
+  <si>
+    <t>label.fixed</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>label.fixedHsc</t>
+  </si>
+  <si>
+    <t>Fixed HSC</t>
+  </si>
+  <si>
+    <t>固定高速压缩</t>
+  </si>
+  <si>
+    <t>label.fixedLsc</t>
+  </si>
+  <si>
+    <t>Fixed LSC</t>
+  </si>
+  <si>
+    <t>固定低速压缩</t>
+  </si>
+  <si>
+    <t>label.frontRearTravel</t>
+  </si>
+  <si>
+    <t>Front 215 / Rear 190 mm</t>
+  </si>
+  <si>
+    <t>前轴 215 / 后轴 190 mm</t>
+  </si>
+  <si>
+    <t>label.fullSweep</t>
+  </si>
+  <si>
+    <t>全范围扫描</t>
+  </si>
+  <si>
+    <t>label.highSpeedBumpIncrement</t>
+  </si>
+  <si>
+    <t>HSbump · High-speed increment</t>
+  </si>
+  <si>
+    <t>label.highSpeedCompressionC</t>
+  </si>
+  <si>
+    <t>High-speed compression · C</t>
+  </si>
+  <si>
+    <t>label.hscRange</t>
+  </si>
+  <si>
+    <t>HSC range</t>
+  </si>
+  <si>
+    <t>label.hscRangePosition</t>
+  </si>
+  <si>
+    <t>HSC range position</t>
+  </si>
+  <si>
+    <t>label.hscSweep</t>
+  </si>
+  <si>
+    <t>HSC 扫描</t>
+  </si>
+  <si>
+    <t>label.hscTotalClicks</t>
+  </si>
+  <si>
+    <t>C total clicks</t>
+  </si>
+  <si>
+    <t>label.hsrMultiplier</t>
+  </si>
+  <si>
+    <t>HSR multiplier</t>
+  </si>
+  <si>
+    <t>label.inputCheck</t>
+  </si>
+  <si>
+    <t>Input check</t>
+  </si>
+  <si>
+    <t>label.lowSpeedCompressionC</t>
+  </si>
+  <si>
+    <t>Low-speed compression · c</t>
+  </si>
+  <si>
+    <t>label.lscAllSeries</t>
+  </si>
+  <si>
+    <t>LSC · All series</t>
+  </si>
+  <si>
+    <t>label.lscRange</t>
+  </si>
+  <si>
+    <t>LSC range</t>
+  </si>
+  <si>
+    <t>label.lscRangePosition</t>
+  </si>
+  <si>
+    <t>LSC range position</t>
+  </si>
+  <si>
+    <t>label.lscSweep</t>
+  </si>
+  <si>
+    <t>LSC 扫描</t>
+  </si>
+  <si>
+    <t>label.lsrRange</t>
+  </si>
+  <si>
+    <t>LSR range</t>
+  </si>
+  <si>
+    <t>label.lsrRangePosition</t>
+  </si>
+  <si>
+    <t>LSR range position</t>
+  </si>
+  <si>
+    <t>label.lsrSweep</t>
+  </si>
+  <si>
+    <t>LSR 扫描</t>
+  </si>
+  <si>
+    <t>label.lsrTotalClicks</t>
+  </si>
+  <si>
+    <t>R total clicks</t>
+  </si>
+  <si>
+    <t>label.multiplier</t>
+  </si>
+  <si>
+    <t>Multiplier</t>
+  </si>
+  <si>
+    <t>label.pistonTravel</t>
+  </si>
+  <si>
+    <t>Piston travel</t>
+  </si>
+  <si>
+    <t>label.rally</t>
+  </si>
+  <si>
+    <t>拉力</t>
+  </si>
+  <si>
+    <t>label.rallycross</t>
+  </si>
+  <si>
+    <t>跨界拉力</t>
+  </si>
+  <si>
+    <t>label.ratio</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>label.rebound</t>
+  </si>
+  <si>
+    <t>Rebound</t>
+  </si>
+  <si>
+    <t>回弹</t>
+  </si>
+  <si>
+    <t>label.reboundDampingForceN</t>
+  </si>
+  <si>
+    <t>Rebound damping force (N)</t>
+  </si>
+  <si>
+    <t>回弹阻尼力 (N)</t>
+  </si>
+  <si>
+    <t>label.reboundForceN</t>
+  </si>
+  <si>
+    <t>Rebound force (N)</t>
+  </si>
+  <si>
+    <t>label.reboundKnee</t>
+  </si>
+  <si>
+    <t>回弹拐点</t>
+  </si>
+  <si>
+    <t>label.reboundR</t>
+  </si>
+  <si>
+    <t>Rebound · R</t>
+  </si>
+  <si>
+    <t>label.secondKnee</t>
+  </si>
+  <si>
+    <t>Second knee</t>
+  </si>
+  <si>
+    <t>第二拐点</t>
+  </si>
+  <si>
+    <t>label.shaftSpeedMagnitudeMps</t>
+  </si>
+  <si>
+    <t>Shaft speed magnitude (m/s)</t>
+  </si>
+  <si>
+    <t>轴速大小 (m/s)</t>
+  </si>
+  <si>
+    <t>label.shaftSpeedMps</t>
+  </si>
+  <si>
+    <t>Shaft speed (m/s)</t>
+  </si>
+  <si>
+    <t>label.shaftVelocityMps</t>
+  </si>
+  <si>
+    <t>label.specification</t>
+  </si>
+  <si>
+    <t>Specification</t>
+  </si>
+  <si>
+    <t>label.threePlusOneWay</t>
+  </si>
+  <si>
+    <t>3+1 向调节</t>
+  </si>
+  <si>
+    <t>label.threeWay</t>
+  </si>
+  <si>
+    <t>3 向调节</t>
+  </si>
+  <si>
+    <t>label.totalHighSpeedCoefficient</t>
+  </si>
+  <si>
+    <t>Total high-speed coefficient</t>
+  </si>
+  <si>
+    <t>label.totalHsCoefficient</t>
+  </si>
+  <si>
+    <t>Total HS coefficient</t>
+  </si>
+  <si>
+    <t>label.valving</t>
+  </si>
+  <si>
+    <t>阀系</t>
+  </si>
+  <si>
+    <t>note.adjusterClicks</t>
+  </si>
+  <si>
+    <t>0 is the hardest setting; negative values are clicks out.</t>
+  </si>
+  <si>
+    <t>note.baseDampingCurve</t>
+  </si>
+  <si>
+    <t>Continuous piecewise theoretical curve; base damping only.</t>
+  </si>
+  <si>
+    <t>note.sweepRa88Clicks</t>
+  </si>
+  <si>
+    <t>Sweep uses RA88 adjustment clicks.</t>
+  </si>
+  <si>
+    <t>调节曲线使用 RA88 调节格数。</t>
+  </si>
+  <si>
+    <t>note.yellowInputs</t>
+  </si>
+  <si>
+    <t>Yellow cells are manual inputs.</t>
+  </si>
+  <si>
+    <t>status.checkInput</t>
+  </si>
+  <si>
+    <t>Check input</t>
+  </si>
+  <si>
+    <t>检查输入</t>
+  </si>
+  <si>
+    <t>status.ok</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>title.currentCurveParameters</t>
+  </si>
+  <si>
+    <t>Current curve parameters</t>
+  </si>
+  <si>
+    <t>title.currentDampingForce</t>
+  </si>
+  <si>
+    <t>Current input · damping force magnitude</t>
+  </si>
+  <si>
+    <t>title.rax8DamperCatalog</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx8 · 避震器目录</t>
+  </si>
+  <si>
+    <t>title.rax8DampingCalculator</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx8 · 阻尼计算器</t>
+  </si>
+  <si>
+    <t>title.rax8FullSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx8 · 全范围扫描</t>
+  </si>
+  <si>
+    <t>title.rax8HSCSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx8 · HSC 扫描</t>
+  </si>
+  <si>
+    <t>title.rax8LSCSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx8 · LSC 扫描</t>
+  </si>
+  <si>
+    <t>title.rax8LSRSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx8 · LSR 扫描</t>
+  </si>
+  <si>
+    <t>title.rax8ValvingParameters</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx8 · 阀系参数</t>
+  </si>
+  <si>
+    <t>Type-A</t>
+    <phoneticPr fontId="73" type="noConversion"/>
+  </si>
+  <si>
+    <t>简体中文</t>
+    <phoneticPr fontId="73" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -334,7 +853,7 @@
     <numFmt numFmtId="177" formatCode="0&quot; mm&quot;"/>
     <numFmt numFmtId="178" formatCode="0&quot; clicks&quot;"/>
   </numFmts>
-  <fonts count="75">
+  <fonts count="76">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -580,12 +1099,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF667B91"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF667B91"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -809,8 +1322,21 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="69">
+  <fills count="71">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -955,11 +1481,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F7FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1150,6 +1671,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1548,13 +2082,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FFDCE4EB"/>
       </bottom>
@@ -1690,14 +2217,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1712,25 +2246,25 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="7" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1742,13 +2276,13 @@
     <xf numFmtId="178" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1796,17 +2330,20 @@
     <xf numFmtId="176" fontId="38" fillId="30" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="35" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="44" fillId="36" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="43" fillId="35" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="37" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="43" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="52" fillId="44" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="45" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1818,7 +2355,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="48" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="49" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1830,75 +2367,89 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="52" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="53" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="54" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="62" fillId="54" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="63" fillId="55" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="64" fillId="56" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="64" fillId="56" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="57" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="58" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="66" fillId="58" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="67" fillId="59" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="68" fillId="60" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="69" fillId="61" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="62" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="63" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="64" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="65" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="65" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="1" fontId="1" fillId="66" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="66" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="65" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="67" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="66" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="67" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="66" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="68" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="67" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="68" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="68" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="75" fillId="70" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="33" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1907,32 +2458,26 @@
     <xf numFmtId="0" fontId="23" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="37" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="38" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="39" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="40" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1946,40 +2491,34 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="74" fillId="68" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="69" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="42" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="33" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="38" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="39" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="40" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="43" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="61" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="60" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2008,22 +2547,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx8 · LSC Sweep</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$4</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx8 · 低速压缩调节曲线</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2952,22 +3500,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Bump damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>压缩阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -2980,7 +3537,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -3003,22 +3560,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Shaft speed (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$56</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>轴速 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -3038,7 +3604,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -3061,7 +3627,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -3084,7 +3650,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -3098,22 +3664,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx8 · HSC Sweep</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$3</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx8 · 高速压缩调节曲线</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -4032,22 +4607,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Bump damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>压缩阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -4060,7 +4644,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -4083,22 +4667,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Shaft speed (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$56</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>轴速 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -4118,7 +4711,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -4141,7 +4734,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -4164,7 +4757,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -4178,22 +4771,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx8 · LSR Sweep</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$5</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx8 · 低速回弹调节曲线</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -5112,22 +5714,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Rebound damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$50</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>回弹阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -5140,7 +5751,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -5163,22 +5774,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Extension speed (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>伸展速度 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -5191,7 +5811,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -5214,7 +5834,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -5237,7 +5857,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -5251,22 +5871,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx8 · Compression (+) / Rebound (−)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$2</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx8 · 压缩 (+) / 回弹 (−)</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -7064,22 +7693,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -7092,7 +7730,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -7115,22 +7753,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Shaft speed magnitude (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$55</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>轴速大小 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -7150,7 +7797,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -7173,7 +7820,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -7196,7 +7843,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -7539,7 +8186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FB0FA4-4DD2-4B50-8AA7-32365116ADE5}">
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
@@ -7553,26 +8200,39 @@
     <col min="8" max="8" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="12" customHeight="1">
+    <row r="1" spans="1:8" ht="22" customHeight="1">
       <c r="A1" s="6"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="89" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="89" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="89" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="90" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="90" t="s">
+        <v>86</v>
+      </c>
       <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" ht="35.15" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="81" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
+      <c r="B2" s="86" t="str">
+        <f>VLOOKUP("title.rax8DamperCatalog",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>CTM Racing · RAx8 · 避震器目录</v>
+      </c>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -7589,14 +8249,15 @@
       <c r="A4" s="6"/>
       <c r="B4" s="16"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="8" t="s">
-        <v>0</v>
+      <c r="D4" s="8" t="str">
+        <f>VLOOKUP("label.specification",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>规格</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H4" s="6"/>
     </row>
@@ -7604,11 +8265,13 @@
       <c r="A5" s="6"/>
       <c r="B5" s="16"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="64" t="s">
-        <v>72</v>
+      <c r="D5" s="17" t="str">
+        <f>VLOOKUP("label.pistonTravel",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>活塞行程</v>
+      </c>
+      <c r="E5" s="64" t="str">
+        <f>VLOOKUP("label.frontRearTravel",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>前轴 215 / 后轴 190 mm</v>
       </c>
       <c r="F5" s="13">
         <v>280</v>
@@ -7617,27 +8280,31 @@
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="88" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>93</v>
+      <c r="D6" s="11" t="str">
+        <f>VLOOKUP("label.dampingAdjustment",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>阻尼调节</v>
+      </c>
+      <c r="E6" s="12" t="str">
+        <f>VLOOKUP("label.threeWay",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>3 向调节</v>
+      </c>
+      <c r="F6" s="12" t="str">
+        <f>VLOOKUP("label.threePlusOneWay",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>3+1 向调节</v>
       </c>
       <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="83"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="10" t="s">
-        <v>4</v>
+      <c r="D7" s="10" t="str">
+        <f>VLOOKUP("label.lowSpeedCompressionC",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>低速压缩 · c</v>
       </c>
       <c r="E7" s="14">
         <f>Parameters!D23</f>
@@ -7651,12 +8318,14 @@
     </row>
     <row r="8" spans="1:8" ht="31" customHeight="1">
       <c r="A8" s="6"/>
-      <c r="B8" s="65" t="s">
-        <v>92</v>
+      <c r="B8" s="65" t="str">
+        <f>VLOOKUP("label.rally",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>拉力</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="11" t="s">
-        <v>5</v>
+      <c r="D8" s="11" t="str">
+        <f>VLOOKUP("label.highSpeedCompressionC",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>高速压缩 · C</v>
       </c>
       <c r="E8" s="15">
         <f>Parameters!D27</f>
@@ -7670,12 +8339,14 @@
     </row>
     <row r="9" spans="1:8" ht="31" customHeight="1">
       <c r="A9" s="6"/>
-      <c r="B9" s="66" t="s">
-        <v>74</v>
+      <c r="B9" s="66" t="str">
+        <f>VLOOKUP("label.rallycross",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>跨界拉力</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="10" t="s">
-        <v>6</v>
+      <c r="D9" s="10" t="str">
+        <f>VLOOKUP("label.reboundR",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹 · R</v>
       </c>
       <c r="E9" s="14">
         <f>Parameters!D25</f>
@@ -7694,11 +8365,13 @@
       <c r="D10" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>76</v>
+      <c r="E10" s="12" t="str">
+        <f>VLOOKUP("label.fixed",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>固定</v>
+      </c>
+      <c r="F10" s="12" t="str">
+        <f>VLOOKUP("label.adjustableSixteenClicks",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>可调 · 16 格</v>
       </c>
       <c r="H10" s="6"/>
     </row>
@@ -7710,8 +8383,9 @@
         <v>8</v>
       </c>
       <c r="E11" s="18"/>
-      <c r="F11" s="14" t="s">
-        <v>77</v>
+      <c r="F11" s="14" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>有</v>
       </c>
       <c r="H11" s="6"/>
     </row>
@@ -7722,11 +8396,13 @@
       <c r="D12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>77</v>
+      <c r="E12" s="12" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>有</v>
+      </c>
+      <c r="F12" s="12" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>有</v>
       </c>
       <c r="H12" s="6"/>
     </row>
@@ -7755,30 +8431,30 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="85"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="85"/>
+      <c r="G16" s="85"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="25" customHeight="1">
@@ -7822,20 +8498,28 @@
       <c r="H21" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
   </mergeCells>
-  <phoneticPr fontId="74" type="noConversion"/>
+  <phoneticPr fontId="73" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="E1:G1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"English,简体中文"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A699E724-B1D7-4C60-847B-65AB4F4CC168}">
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
@@ -7868,20 +8552,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="76" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
+      <c r="B2" s="70" t="str">
+        <f>VLOOKUP("title.rax8DampingCalculator",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>CTM Racing · RAx8 · 阻尼计算器</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -7904,22 +8589,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="20" t="s">
-        <v>11</v>
+      <c r="B4" s="20" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>39</v>
+        <v>264</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="91"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -7942,21 +8628,23 @@
     </row>
     <row r="6" spans="1:15" ht="32.15" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="22" t="s">
-        <v>12</v>
+      <c r="B6" s="22" t="str">
+        <f>VLOOKUP("label.damperModel",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>避震器型号</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
+      <c r="F6" s="74" t="str">
+        <f>VLOOKUP("title.currentDampingForce",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>当前输入 · 阻尼力大小</v>
+      </c>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -7994,16 +8682,17 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="73" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="78">
-        <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
+      <c r="F8" s="1" t="str">
+        <f>VLOOKUP("label.compressionForceN",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>压缩力 (N)</v>
+      </c>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="92">
+        <f>IF(C18=VLOOKUP("status.ok",Locale!$A$2:$D$78,4,FALSE),Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),VLOOKUP("status.checkInput",Locale!$A$2:$D$78,4,FALSE))</f>
         <v>2151.6666666666665</v>
       </c>
-      <c r="J8" s="79"/>
+      <c r="J8" s="93"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -8033,24 +8722,26 @@
     </row>
     <row r="10" spans="1:15" ht="28" customHeight="1">
       <c r="A10" s="2"/>
-      <c r="B10" s="22" t="s">
-        <v>18</v>
+      <c r="B10" s="22" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C10" s="25">
         <v>0.6</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="78">
-        <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
+      <c r="F10" s="1" t="str">
+        <f>VLOOKUP("label.reboundForceN",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹力 (N)</v>
+      </c>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="92">
+        <f>IF(C18=VLOOKUP("status.ok",Locale!$A$2:$D$78,4,FALSE),Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),VLOOKUP("status.checkInput",Locale!$A$2:$D$78,4,FALSE))</f>
         <v>1467.3359999999998</v>
       </c>
-      <c r="J10" s="79"/>
+      <c r="J10" s="93"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -8093,8 +8784,9 @@
     </row>
     <row r="13" spans="1:15" ht="32.15" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="22" t="s">
-        <v>20</v>
+      <c r="B13" s="22" t="str">
+        <f>VLOOKUP("label.cTotalClicks",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>c 总格数</v>
       </c>
       <c r="C13" s="26">
         <f>Parameters!D23</f>
@@ -8102,13 +8794,14 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
+      <c r="F13" s="74" t="str">
+        <f>VLOOKUP("title.currentCurveParameters",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>当前曲线参数</v>
+      </c>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -8117,8 +8810,9 @@
     </row>
     <row r="14" spans="1:15" ht="28" customHeight="1">
       <c r="A14" s="2"/>
-      <c r="B14" s="27" t="s">
-        <v>22</v>
+      <c r="B14" s="27" t="str">
+        <f>VLOOKUP("label.hscTotalClicks",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>C 总格数</v>
       </c>
       <c r="C14" s="28">
         <f>IF(C6="RA68",Parameters!D27,Parameters!D24)</f>
@@ -8126,11 +8820,11 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="68" t="s">
+      <c r="F14" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
       <c r="I14" s="29">
         <f>Samples!F165</f>
         <v>3400</v>
@@ -8146,8 +8840,9 @@
     </row>
     <row r="15" spans="1:15" ht="28" customHeight="1">
       <c r="A15" s="2"/>
-      <c r="B15" s="22" t="s">
-        <v>25</v>
+      <c r="B15" s="22" t="str">
+        <f>VLOOKUP("label.lsrTotalClicks",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>R 总格数</v>
       </c>
       <c r="C15" s="26">
         <f>IF(C6="RA88",Parameters!D26,Parameters!D25)</f>
@@ -8155,11 +8850,11 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="70" t="s">
+      <c r="F15" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
       <c r="I15" s="30">
         <f>Samples!I165</f>
         <v>3173.3333333333335</v>
@@ -8179,11 +8874,12 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
+      <c r="F16" s="75" t="str">
+        <f>VLOOKUP("label.highSpeedBumpIncrement",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSbump · 高速增量</v>
+      </c>
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
       <c r="I16" s="29">
         <f>Samples!J165</f>
         <v>1500</v>
@@ -8203,11 +8899,12 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
+      <c r="F17" s="1" t="str">
+        <f>VLOOKUP("label.totalHighSpeedCoefficient",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>总高速系数</v>
+      </c>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
       <c r="I17" s="30">
         <f>Samples!L165</f>
         <v>4673.3333333333339</v>
@@ -8223,12 +8920,13 @@
     </row>
     <row r="18" spans="1:15" ht="28" customHeight="1">
       <c r="A18" s="2"/>
-      <c r="B18" s="22" t="s">
-        <v>29</v>
+      <c r="B18" s="22" t="str">
+        <f>VLOOKUP("label.inputCheck",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>输入检查</v>
       </c>
       <c r="C18" s="31" t="str">
-        <f>IF(AND(OR(C4="Type-A",C4="Type-B"),OR(C6="RA68",C6="RA88"),COUNT(C7:C10)=4,C7&gt;=-C13,C7&lt;=0,C8&gt;=-C14,C8&lt;=0,C9&gt;=-C15,C9&lt;=0,C10&gt;=0,INT(C7)=C7,INT(C8)=C8,INT(C9)=C9),"OK","检查输入")</f>
-        <v>OK</v>
+        <f>IF(AND(OR(C4="Type-A",C4="Type-B"),OR(C6="RA68",C6="RA88"),COUNT(C7:C10)=4,C7&gt;=-C13,C7&lt;=0,C8&gt;=-C14,C8&lt;=0,C9&gt;=-C15,C9&lt;=0,C10&gt;=0,INT(C7)=C7,INT(C8)=C8,INT(C9)=C9),VLOOKUP("status.ok",Locale!$A$2:$D$78,4,FALSE),VLOOKUP("status.checkInput",Locale!$A$2:$D$78,4,FALSE))</f>
+        <v>正常</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -8249,11 +8947,12 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="68" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
+      <c r="F19" s="94" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="G19" s="76"/>
+      <c r="H19" s="76"/>
       <c r="I19" s="29">
         <f>Samples!M165</f>
         <v>2600</v>
@@ -8273,11 +8972,11 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="70" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
+      <c r="F20" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
       <c r="I20" s="30">
         <f>Samples!P165</f>
         <v>2319.1999999999998</v>
@@ -8314,17 +9013,18 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="72" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
+      <c r="F22" s="75" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
       <c r="I22" s="32">
         <f>Samples!G165</f>
         <v>0.1</v>
       </c>
       <c r="J22" s="20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -8338,17 +9038,18 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="73" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
+      <c r="F23" s="1" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
       <c r="I23" s="33">
         <f>Samples!K165</f>
         <v>0.45</v>
       </c>
       <c r="J23" s="23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
@@ -8362,17 +9063,18 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="68" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
+      <c r="F24" s="94" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
       <c r="I24" s="32">
         <f>Samples!N165</f>
         <v>0.27</v>
       </c>
       <c r="J24" s="20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
@@ -8416,20 +9118,21 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="67"/>
-      <c r="M27" s="67"/>
+      <c r="B27" s="70" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="95"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
+      <c r="M27" s="95"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
@@ -8690,6 +9393,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -8697,19 +9411,8 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
   </mergeCells>
-  <phoneticPr fontId="74" type="noConversion"/>
+  <phoneticPr fontId="73" type="noConversion"/>
   <dataValidations count="5">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -8730,11 +9433,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E35C722-0869-4EF5-9E30-018B3FF565DE}">
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
@@ -8764,20 +9468,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="76" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
+      <c r="B2" s="70" t="str">
+        <f>VLOOKUP("title.rax8LSCSweep",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>CTM Racing · RAx8 · LSC 扫描</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -8800,22 +9505,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="20" t="s">
-        <v>11</v>
+      <c r="B4" s="20" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>39</v>
+        <v>264</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="91"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -8838,22 +9544,23 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="22" t="s">
-        <v>37</v>
+      <c r="B6" s="22" t="str">
+        <f>VLOOKUP("label.fixedHsc",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>固定高速压缩</v>
       </c>
       <c r="C6" s="24">
         <v>-10</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -9437,18 +10144,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="84"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="84"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="84"/>
-      <c r="M41" s="84"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -9476,7 +10183,7 @@
     <mergeCell ref="E6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="74" type="noConversion"/>
+  <phoneticPr fontId="73" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -9487,12 +10194,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9873CC8-23D3-43CA-BCB6-F3EE11F2654B}">
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
@@ -9522,20 +10230,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="76" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
+      <c r="B2" s="70" t="str">
+        <f>VLOOKUP("title.rax8HSCSweep",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>CTM Racing · RAx8 · HSC 扫描</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -9558,22 +10267,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="20" t="s">
-        <v>11</v>
+      <c r="B4" s="20" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>39</v>
+        <v>264</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="91"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -9596,22 +10306,23 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="22" t="s">
-        <v>38</v>
+      <c r="B6" s="22" t="str">
+        <f>VLOOKUP("label.fixedLsc",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>固定低速压缩</v>
       </c>
       <c r="C6" s="24">
         <v>-8</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -10195,18 +10906,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="84"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="84"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="84"/>
-      <c r="M41" s="84"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -10234,7 +10945,7 @@
     <mergeCell ref="E6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="74" type="noConversion"/>
+  <phoneticPr fontId="73" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -10245,12 +10956,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85EF75BE-7BBD-401F-B54B-864310A91D47}">
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
@@ -10280,20 +10992,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="76" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
+      <c r="B2" s="70" t="str">
+        <f>VLOOKUP("title.rax8LSRSweep",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>CTM Racing · RAx8 · LSR 扫描</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -10316,22 +11029,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="20" t="s">
-        <v>11</v>
+      <c r="B4" s="20" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>39</v>
+        <v>264</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="91"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -10354,18 +11068,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -10949,18 +11663,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="84"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="84"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="84"/>
-      <c r="M41" s="84"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -10988,19 +11702,20 @@
     <mergeCell ref="B6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="74" type="noConversion"/>
+  <phoneticPr fontId="73" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F75CD3-785E-4443-841F-282AAFF59AF6}">
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
@@ -11030,20 +11745,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
+      <c r="B2" s="70" t="str">
+        <f>VLOOKUP("title.rax8FullSweep",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>CTM Racing · RAx8 · 全范围扫描</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -11066,22 +11782,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="20" t="s">
-        <v>11</v>
+      <c r="B4" s="20" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>39</v>
+        <v>264</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="91"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -11104,18 +11821,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -11699,18 +12416,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="84"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="84"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="84"/>
-      <c r="M41" s="84"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -11738,19 +12455,20 @@
     <mergeCell ref="B6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="74" type="noConversion"/>
+  <phoneticPr fontId="73" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16452F0B-D397-4A4A-868D-8FD96F5F4234}">
   <sheetPr>
     <tabColor rgb="FFC49A32"/>
   </sheetPr>
@@ -11784,40 +12502,42 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="76" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
+      <c r="B2" s="70" t="str">
+        <f>VLOOKUP("title.rax8ValvingParameters",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>CTM Racing · RAx8 · 阀系参数</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="89" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
+      <c r="B3" s="71" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -11841,30 +12561,32 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="75" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
+      <c r="D5" s="73" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="75" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
+      <c r="J5" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>42</v>
+      <c r="B6" s="34" t="str">
+        <f>VLOOKUP("label.adjusterPosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>调节位置</v>
+      </c>
+      <c r="C6" s="34" t="str">
+        <f>VLOOKUP("label.ratio",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>比例</v>
       </c>
       <c r="D6" s="35">
         <v>0</v>
@@ -11909,8 +12631,9 @@
       <c r="B7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>43</v>
+      <c r="C7" s="22" t="str">
+        <f>VLOOKUP("label.clicks",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>格</v>
       </c>
       <c r="D7" s="26">
         <f>(D$6-1)*$D$23</f>
@@ -11960,8 +12683,9 @@
       <c r="B8" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>43</v>
+      <c r="C8" s="27" t="str">
+        <f>VLOOKUP("label.clicks",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>格</v>
       </c>
       <c r="D8" s="28">
         <f>(D$6-1)*$D$24</f>
@@ -12070,11 +12794,12 @@
     </row>
     <row r="11" spans="1:15" ht="29.15" customHeight="1">
       <c r="A11" s="2"/>
-      <c r="B11" s="27" t="s">
-        <v>32</v>
+      <c r="B11" s="27" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第一拐点</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D11" s="60">
         <v>0.1</v>
@@ -12116,10 +12841,11 @@
     <row r="12" spans="1:15" ht="29.15" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+      <c r="C12" s="22" t="str">
+        <f>VLOOKUP("label.multiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>倍率</v>
       </c>
       <c r="D12" s="60">
         <v>1</v>
@@ -12160,8 +12886,9 @@
     </row>
     <row r="13" spans="1:15" ht="29.15" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="27" t="s">
-        <v>27</v>
+      <c r="B13" s="27" t="str">
+        <f>VLOOKUP("label.highSpeedBumpIncrement",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSbump · 高速增量</v>
       </c>
       <c r="C13" s="23" t="s">
         <v>24</v>
@@ -12205,11 +12932,12 @@
     </row>
     <row r="14" spans="1:15" ht="29.15" customHeight="1">
       <c r="A14" s="2"/>
-      <c r="B14" s="22" t="s">
-        <v>34</v>
+      <c r="B14" s="22" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第二拐点</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D14" s="60">
         <v>0.44</v>
@@ -12270,10 +12998,11 @@
     <row r="16" spans="1:15" ht="30" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>43</v>
+        <v>76</v>
+      </c>
+      <c r="C16" s="34" t="str">
+        <f>VLOOKUP("label.clicks",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>格</v>
       </c>
       <c r="D16" s="36">
         <f>(D$6-1)*$D$26</f>
@@ -12320,8 +13049,9 @@
     </row>
     <row r="17" spans="1:15" ht="29.15" customHeight="1">
       <c r="A17" s="2"/>
-      <c r="B17" s="20" t="s">
-        <v>30</v>
+      <c r="B17" s="20" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>24</v>
@@ -12365,11 +13095,12 @@
     </row>
     <row r="18" spans="1:15" ht="29.15" customHeight="1">
       <c r="A18" s="2"/>
-      <c r="B18" s="23" t="s">
-        <v>35</v>
+      <c r="B18" s="23" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹拐点</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D18" s="60">
         <v>0.23</v>
@@ -12411,10 +13142,11 @@
     <row r="19" spans="1:15" ht="29.15" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="C19" s="22" t="str">
+        <f>VLOOKUP("label.multiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>倍率</v>
       </c>
       <c r="D19" s="60">
         <v>0.94</v>
@@ -12489,73 +13221,76 @@
     </row>
     <row r="22" spans="1:15" ht="32.15" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="74" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="75"/>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
-      <c r="M22" s="75"/>
-      <c r="N22" s="75"/>
+      <c r="B22" s="74" t="str">
+        <f>VLOOKUP("label.adjusterClicks",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>调节格数</v>
+      </c>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="73"/>
       <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:15" ht="29.15" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="72" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="69"/>
+      <c r="B23" s="75" t="str">
+        <f>VLOOKUP("label.lscAllSeries",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC · 全系列</v>
+      </c>
+      <c r="C23" s="76"/>
       <c r="D23" s="26">
         <v>24</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="91" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="92"/>
-      <c r="M23" s="92"/>
-      <c r="N23" s="92"/>
+      <c r="F23" s="78" t="str">
+        <f>VLOOKUP("note.sweepRa88Clicks",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>调节曲线使用 RA88 调节格数。</v>
+      </c>
+      <c r="G23" s="79"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="79"/>
+      <c r="K23" s="79"/>
+      <c r="L23" s="79"/>
+      <c r="M23" s="79"/>
+      <c r="N23" s="79"/>
       <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:15" ht="29.15" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="73" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" s="71"/>
+      <c r="B24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="69"/>
       <c r="D24" s="28">
         <v>20</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="92"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="92"/>
-      <c r="I24" s="92"/>
-      <c r="J24" s="92"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="92"/>
-      <c r="N24" s="92"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="79"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="79"/>
       <c r="O24" s="2"/>
     </row>
     <row r="25" spans="1:15" ht="29.15" customHeight="1">
       <c r="A25" s="2"/>
-      <c r="B25" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" s="69"/>
+      <c r="B25" s="75" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="76"/>
       <c r="D25" s="26">
         <v>40</v>
       </c>
@@ -12573,33 +13308,34 @@
     </row>
     <row r="26" spans="1:15" ht="29.15" customHeight="1">
       <c r="A26" s="2"/>
-      <c r="B26" s="70" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="71"/>
+      <c r="B26" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="69"/>
       <c r="D26" s="28">
         <v>40</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="93" t="s">
-        <v>48</v>
-      </c>
-      <c r="G26" s="90"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="90"/>
-      <c r="J26" s="90"/>
-      <c r="K26" s="90"/>
-      <c r="L26" s="90"/>
-      <c r="M26" s="90"/>
-      <c r="N26" s="90"/>
+      <c r="F26" s="80" t="str">
+        <f>VLOOKUP("note.adjusterClicks",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>0 为最硬，负数为退出格数。</v>
+      </c>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
       <c r="O26" s="2"/>
     </row>
     <row r="27" spans="1:15" ht="29.15" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="71"/>
+      <c r="B27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="69"/>
       <c r="D27" s="28">
         <v>10</v>
       </c>
@@ -12617,140 +13353,141 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="86" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="87"/>
-      <c r="D28" s="87"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="87"/>
-      <c r="G28" s="87"/>
-      <c r="H28" s="87"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="K28" s="87"/>
-      <c r="L28" s="87"/>
-      <c r="M28" s="87"/>
-      <c r="N28" s="87"/>
+      <c r="B28" s="82" t="str">
+        <f>VLOOKUP("note.baseDampingCurve",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>连续分段理论曲线，仅基础阻尼。</v>
+      </c>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83"/>
+      <c r="N28" s="83"/>
       <c r="O28" s="2"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="2"/>
-      <c r="B29" s="85"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="85"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
+      <c r="M29" s="81"/>
+      <c r="N29" s="81"/>
       <c r="O29" s="2"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="88"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="88"/>
-      <c r="H30" s="88"/>
-      <c r="I30" s="88"/>
-      <c r="J30" s="88"/>
-      <c r="K30" s="88"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="88"/>
-      <c r="N30" s="88"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="84"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="84"/>
       <c r="O30" s="2"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="85"/>
-      <c r="D31" s="85"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="85"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="85"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="81"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="81"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="81"/>
+      <c r="M31" s="81"/>
+      <c r="N31" s="81"/>
       <c r="O31" s="2"/>
     </row>
     <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="2"/>
-      <c r="B32" s="85"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="85"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="85"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="85"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="81"/>
+      <c r="K32" s="81"/>
+      <c r="L32" s="81"/>
+      <c r="M32" s="81"/>
+      <c r="N32" s="81"/>
       <c r="O32" s="2"/>
     </row>
     <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="85"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="85"/>
-      <c r="E33" s="85"/>
-      <c r="F33" s="85"/>
-      <c r="G33" s="85"/>
-      <c r="H33" s="85"/>
-      <c r="I33" s="85"/>
-      <c r="J33" s="85"/>
-      <c r="K33" s="85"/>
-      <c r="L33" s="85"/>
-      <c r="M33" s="85"/>
-      <c r="N33" s="85"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
+      <c r="M33" s="81"/>
+      <c r="N33" s="81"/>
       <c r="O33" s="2"/>
     </row>
     <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="85"/>
-      <c r="E34" s="85"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="85"/>
-      <c r="H34" s="85"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="85"/>
-      <c r="K34" s="85"/>
-      <c r="L34" s="85"/>
-      <c r="M34" s="85"/>
-      <c r="N34" s="85"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="81"/>
+      <c r="L34" s="81"/>
+      <c r="M34" s="81"/>
+      <c r="N34" s="81"/>
       <c r="O34" s="2"/>
     </row>
     <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="2"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="85"/>
-      <c r="D35" s="85"/>
-      <c r="E35" s="85"/>
-      <c r="F35" s="85"/>
-      <c r="G35" s="85"/>
-      <c r="H35" s="85"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="85"/>
-      <c r="K35" s="85"/>
-      <c r="L35" s="85"/>
-      <c r="M35" s="85"/>
-      <c r="N35" s="85"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="81"/>
+      <c r="K35" s="81"/>
+      <c r="L35" s="81"/>
+      <c r="M35" s="81"/>
+      <c r="N35" s="81"/>
       <c r="O35" s="2"/>
     </row>
     <row r="36" spans="1:15" ht="23.15" customHeight="1">
@@ -12857,6 +13594,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -12869,22 +13614,1195 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
   </mergeCells>
-  <phoneticPr fontId="74" type="noConversion"/>
+  <phoneticPr fontId="73" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4F4E53-CC2B-4C83-8B3D-A6BCF903E527}">
+  <dimension ref="A1:D78"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B2,C2)</f>
+        <v>RAx8 · 压缩 (+) / 回弹 (−)</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="67" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B3,C3)</f>
+        <v>RAx8 · 高速压缩调节曲线</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="67" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="67" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B4,C4)</f>
+        <v>RAx8 · 低速压缩调节曲线</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B5,C5)</f>
+        <v>RAx8 · 低速回弹调节曲线</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B6,C6)</f>
+        <v>可调 · 16 格</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B7,C7)</f>
+        <v>调节格数</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="67" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B8,C8)</f>
+        <v>调节位置</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B9,C9)</f>
+        <v>有</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="67" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B10,C10)</f>
+        <v>bump2 倍率</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B11,C11)</f>
+        <v>压缩阻尼力 (N)</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B12,C12)</f>
+        <v>c 总格数</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="67" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="67" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B13,C13)</f>
+        <v>计算器</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B14,C14)</f>
+        <v>格</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B15,C15)</f>
+        <v>压缩力 (N)</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B16,C16)</f>
+        <v>曲线</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B17,C17)</f>
+        <v>避震器型号</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B18,C18)</f>
+        <v>阻尼调节</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="67" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="67" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B19,C19)</f>
+        <v>阻尼力 (N)</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B20,C20)</f>
+        <v>伸展速度 (m/s)</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="67" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="67" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B21,C21)</f>
+        <v>第一拐点</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="67" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B22,C22)</f>
+        <v>固定</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="D23" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B23,C23)</f>
+        <v>固定高速压缩</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B24,C24)</f>
+        <v>固定低速压缩</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="67" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="67" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B25,C25)</f>
+        <v>前轴 215 / 后轴 190 mm</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="67" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="67" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B26,C26)</f>
+        <v>全范围扫描</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B27,C27)</f>
+        <v>HSbump · 高速增量</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="67" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" s="67" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B28,C28)</f>
+        <v>高速压缩 · C</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" s="67" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B29,C29)</f>
+        <v>HSC 区间</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B30,C30)</f>
+        <v>HSC 区间位置</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="67" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" s="67" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B31,C31)</f>
+        <v>HSC 扫描</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" s="67" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B32,C32)</f>
+        <v>C 总格数</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="C33" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B33,C33)</f>
+        <v>HSR 倍率</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="67" t="s">
+        <v>168</v>
+      </c>
+      <c r="B34" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="C34" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B34,C34)</f>
+        <v>输入检查</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="C35" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B35,C35)</f>
+        <v>低速压缩 · c</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="B36" s="67" t="s">
+        <v>173</v>
+      </c>
+      <c r="C36" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B36,C36)</f>
+        <v>LSC · 全系列</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" s="67" t="s">
+        <v>175</v>
+      </c>
+      <c r="C37" s="67" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B37,C37)</f>
+        <v>LSC 区间</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="B38" s="67" t="s">
+        <v>177</v>
+      </c>
+      <c r="C38" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B38,C38)</f>
+        <v>LSC 区间位置</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="67" t="s">
+        <v>178</v>
+      </c>
+      <c r="B39" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="67" t="s">
+        <v>179</v>
+      </c>
+      <c r="D39" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B39,C39)</f>
+        <v>LSC 扫描</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="67" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" s="67" t="s">
+        <v>181</v>
+      </c>
+      <c r="C40" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B40,C40)</f>
+        <v>LSR 区间</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="67" t="s">
+        <v>182</v>
+      </c>
+      <c r="B41" s="67" t="s">
+        <v>183</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B41,C41)</f>
+        <v>LSR 区间位置</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="67" t="s">
+        <v>185</v>
+      </c>
+      <c r="D42" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B42,C42)</f>
+        <v>LSR 扫描</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="67" t="s">
+        <v>186</v>
+      </c>
+      <c r="B43" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="C43" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B43,C43)</f>
+        <v>R 总格数</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="C44" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B44,C44)</f>
+        <v>倍率</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="67" t="s">
+        <v>190</v>
+      </c>
+      <c r="B45" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="C45" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B45,C45)</f>
+        <v>活塞行程</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="67" t="s">
+        <v>192</v>
+      </c>
+      <c r="B46" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="D46" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B46,C46)</f>
+        <v>拉力</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="B47" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="67" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B47,C47)</f>
+        <v>跨界拉力</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="67" t="s">
+        <v>196</v>
+      </c>
+      <c r="B48" s="67" t="s">
+        <v>197</v>
+      </c>
+      <c r="C48" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B48,C48)</f>
+        <v>比例</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="67" t="s">
+        <v>198</v>
+      </c>
+      <c r="B49" s="67" t="s">
+        <v>199</v>
+      </c>
+      <c r="C49" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D49" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B49,C49)</f>
+        <v>回弹</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="B50" s="67" t="s">
+        <v>202</v>
+      </c>
+      <c r="C50" s="67" t="s">
+        <v>203</v>
+      </c>
+      <c r="D50" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B50,C50)</f>
+        <v>回弹阻尼力 (N)</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="67" t="s">
+        <v>204</v>
+      </c>
+      <c r="B51" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="C51" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B51,C51)</f>
+        <v>回弹力 (N)</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="67" t="s">
+        <v>206</v>
+      </c>
+      <c r="B52" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="67" t="s">
+        <v>207</v>
+      </c>
+      <c r="D52" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B52,C52)</f>
+        <v>回弹拐点</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="67" t="s">
+        <v>208</v>
+      </c>
+      <c r="B53" s="67" t="s">
+        <v>209</v>
+      </c>
+      <c r="C53" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B53,C53)</f>
+        <v>回弹 · R</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="67" t="s">
+        <v>210</v>
+      </c>
+      <c r="B54" s="67" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="67" t="s">
+        <v>212</v>
+      </c>
+      <c r="D54" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B54,C54)</f>
+        <v>第二拐点</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="67" t="s">
+        <v>213</v>
+      </c>
+      <c r="B55" s="67" t="s">
+        <v>214</v>
+      </c>
+      <c r="C55" s="67" t="s">
+        <v>215</v>
+      </c>
+      <c r="D55" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B55,C55)</f>
+        <v>轴速大小 (m/s)</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="67" t="s">
+        <v>216</v>
+      </c>
+      <c r="B56" s="67" t="s">
+        <v>217</v>
+      </c>
+      <c r="C56" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B56,C56)</f>
+        <v>轴速 (m/s)</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="67" t="s">
+        <v>218</v>
+      </c>
+      <c r="B57" s="67" t="s">
+        <v>217</v>
+      </c>
+      <c r="C57" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B57,C57)</f>
+        <v>轴速 (m/s)</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="67" t="s">
+        <v>219</v>
+      </c>
+      <c r="B58" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="C58" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="D58" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B58,C58)</f>
+        <v>规格</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="67" t="s">
+        <v>221</v>
+      </c>
+      <c r="B59" s="67" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="67" t="s">
+        <v>222</v>
+      </c>
+      <c r="D59" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B59,C59)</f>
+        <v>3+1 向调节</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="B60" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" s="67" t="s">
+        <v>224</v>
+      </c>
+      <c r="D60" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B60,C60)</f>
+        <v>3 向调节</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="B61" s="67" t="s">
+        <v>226</v>
+      </c>
+      <c r="C61" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B61,C61)</f>
+        <v>总高速系数</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="67" t="s">
+        <v>227</v>
+      </c>
+      <c r="B62" s="67" t="s">
+        <v>228</v>
+      </c>
+      <c r="C62" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="D62" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B62,C62)</f>
+        <v>总 HS 系数</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="B63" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="67" t="s">
+        <v>230</v>
+      </c>
+      <c r="D63" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B63,C63)</f>
+        <v>阀系</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="67" t="s">
+        <v>231</v>
+      </c>
+      <c r="B64" s="67" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64" s="67" t="s">
+        <v>42</v>
+      </c>
+      <c r="D64" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B64,C64)</f>
+        <v>0 为最硬，负数为退出格数。</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="67" t="s">
+        <v>233</v>
+      </c>
+      <c r="B65" s="67" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="D65" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B65,C65)</f>
+        <v>连续分段理论曲线，仅基础阻尼。</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="67" t="s">
+        <v>235</v>
+      </c>
+      <c r="B66" s="67" t="s">
+        <v>236</v>
+      </c>
+      <c r="C66" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="D66" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B66,C66)</f>
+        <v>调节曲线使用 RA88 调节格数。</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="67" t="s">
+        <v>238</v>
+      </c>
+      <c r="B67" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="C67" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B67,C67)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="67" t="s">
+        <v>240</v>
+      </c>
+      <c r="B68" s="67" t="s">
+        <v>241</v>
+      </c>
+      <c r="C68" s="67" t="s">
+        <v>242</v>
+      </c>
+      <c r="D68" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B68,C68)</f>
+        <v>检查输入</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="67" t="s">
+        <v>243</v>
+      </c>
+      <c r="B69" s="67" t="s">
+        <v>244</v>
+      </c>
+      <c r="C69" s="67" t="s">
+        <v>245</v>
+      </c>
+      <c r="D69" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B69,C69)</f>
+        <v>正常</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="67" t="s">
+        <v>246</v>
+      </c>
+      <c r="B70" s="67" t="s">
+        <v>247</v>
+      </c>
+      <c r="C70" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B70,C70)</f>
+        <v>当前曲线参数</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="B71" s="67" t="s">
+        <v>249</v>
+      </c>
+      <c r="C71" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B71,C71)</f>
+        <v>当前输入 · 阻尼力大小</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="67" t="s">
+        <v>250</v>
+      </c>
+      <c r="B72" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="C72" s="67" t="s">
+        <v>251</v>
+      </c>
+      <c r="D72" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B72,C72)</f>
+        <v>CTM Racing · RAx8 · 避震器目录</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="67" t="s">
+        <v>252</v>
+      </c>
+      <c r="B73" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="C73" s="67" t="s">
+        <v>253</v>
+      </c>
+      <c r="D73" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B73,C73)</f>
+        <v>CTM Racing · RAx8 · 阻尼计算器</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="67" t="s">
+        <v>254</v>
+      </c>
+      <c r="B74" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="C74" s="67" t="s">
+        <v>255</v>
+      </c>
+      <c r="D74" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B74,C74)</f>
+        <v>CTM Racing · RAx8 · 全范围扫描</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="67" t="s">
+        <v>256</v>
+      </c>
+      <c r="B75" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="C75" s="67" t="s">
+        <v>257</v>
+      </c>
+      <c r="D75" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B75,C75)</f>
+        <v>CTM Racing · RAx8 · HSC 扫描</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="B76" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="C76" s="67" t="s">
+        <v>259</v>
+      </c>
+      <c r="D76" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B76,C76)</f>
+        <v>CTM Racing · RAx8 · LSC 扫描</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="67" t="s">
+        <v>260</v>
+      </c>
+      <c r="B77" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C77" s="67" t="s">
+        <v>261</v>
+      </c>
+      <c r="D77" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B77,C77)</f>
+        <v>CTM Racing · RAx8 · LSR 扫描</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="67" t="s">
+        <v>262</v>
+      </c>
+      <c r="B78" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="C78" s="67" t="s">
+        <v>263</v>
+      </c>
+      <c r="D78" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B78,C78)</f>
+        <v>CTM Racing · RAx8 · 阀系参数</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="73" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B13A58C-8166-4CD0-9A95-0679512CED5E}">
   <sheetPr>
     <tabColor rgb="FF93A0AC"/>
   </sheetPr>
@@ -12898,29 +14816,30 @@
   <sheetData>
     <row r="1" spans="1:22" ht="32.15" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="76" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
-      <c r="U1" s="94"/>
-      <c r="V1" s="94"/>
+      <c r="B1" s="70" t="str">
+        <f>VLOOKUP("label.lscSweep",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC 扫描</v>
+      </c>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="97"/>
     </row>
     <row r="2" spans="1:22" ht="22" customHeight="1">
       <c r="A2" s="2"/>
@@ -12972,68 +14891,82 @@
     </row>
     <row r="4" spans="1:22" ht="44.15" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="38" t="s">
-        <v>51</v>
+      <c r="B4" s="38" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>曲线</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F4" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="38" t="s">
-        <v>55</v>
+      <c r="G4" s="38" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H4" s="38" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>bump2 倍率</v>
       </c>
       <c r="I4" s="39" t="s">
         <v>26</v>
       </c>
       <c r="J4" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="K4" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="M4" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="38" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L4" s="38" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M4" s="39" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N4" s="39" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O4" s="38" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P4" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="P4" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="R4" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="S4" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="T4" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="U4" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="V4" s="41" t="s">
-        <v>64</v>
+      <c r="Q4" s="41" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R4" s="41" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S4" s="41" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T4" s="41" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U4" s="41" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V4" s="41" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="25" customHeight="1">
@@ -13545,8 +15478,9 @@
     </row>
     <row r="13" spans="1:22" ht="30" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="46" t="s">
-        <v>18</v>
+      <c r="B13" s="46" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C13" s="47" t="str">
         <f>B5</f>
@@ -14591,29 +16525,30 @@
     </row>
     <row r="41" spans="1:22" ht="32.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="76" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="76"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
-      <c r="I41" s="76"/>
-      <c r="J41" s="76"/>
-      <c r="K41" s="76"/>
-      <c r="L41" s="76"/>
-      <c r="M41" s="76"/>
-      <c r="N41" s="76"/>
-      <c r="O41" s="76"/>
-      <c r="P41" s="94"/>
-      <c r="Q41" s="94"/>
-      <c r="R41" s="94"/>
-      <c r="S41" s="94"/>
-      <c r="T41" s="94"/>
-      <c r="U41" s="94"/>
-      <c r="V41" s="94"/>
+      <c r="B41" s="70" t="str">
+        <f>VLOOKUP("label.hscSweep",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSC 扫描</v>
+      </c>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
+      <c r="N41" s="70"/>
+      <c r="O41" s="70"/>
+      <c r="P41" s="97"/>
+      <c r="Q41" s="97"/>
+      <c r="R41" s="97"/>
+      <c r="S41" s="97"/>
+      <c r="T41" s="97"/>
+      <c r="U41" s="97"/>
+      <c r="V41" s="97"/>
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1">
       <c r="A42" s="2"/>
@@ -14663,68 +16598,82 @@
       <c r="V43" s="4"/>
     </row>
     <row r="44" spans="1:22" ht="44.15" customHeight="1">
-      <c r="B44" s="41" t="s">
-        <v>51</v>
+      <c r="B44" s="41" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>曲线</v>
       </c>
       <c r="C44" s="40" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F44" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="G44" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H44" s="41" t="s">
-        <v>55</v>
+      <c r="G44" s="41" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H44" s="41" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>bump2 倍率</v>
       </c>
       <c r="I44" s="40" t="s">
         <v>26</v>
       </c>
       <c r="J44" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="K44" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="L44" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="M44" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="K44" s="41" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L44" s="41" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M44" s="40" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N44" s="40" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O44" s="41" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P44" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="N44" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="O44" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="P44" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q44" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="R44" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="S44" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="T44" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="U44" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="V44" s="41" t="s">
-        <v>64</v>
+      <c r="Q44" s="41" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R44" s="41" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S44" s="41" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T44" s="41" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U44" s="41" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V44" s="41" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="25" customHeight="1">
@@ -15227,8 +17176,9 @@
       <c r="V52" s="4"/>
     </row>
     <row r="53" spans="2:22" ht="30" customHeight="1">
-      <c r="B53" s="50" t="s">
-        <v>18</v>
+      <c r="B53" s="50" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C53" s="51" t="str">
         <f>B45</f>
@@ -16245,29 +18195,30 @@
       <c r="V80" s="4"/>
     </row>
     <row r="81" spans="2:22" ht="32.15" customHeight="1">
-      <c r="B81" s="94" t="s">
-        <v>66</v>
-      </c>
-      <c r="C81" s="94"/>
-      <c r="D81" s="94"/>
-      <c r="E81" s="94"/>
-      <c r="F81" s="94"/>
-      <c r="G81" s="94"/>
-      <c r="H81" s="94"/>
-      <c r="I81" s="94"/>
-      <c r="J81" s="94"/>
-      <c r="K81" s="94"/>
-      <c r="L81" s="94"/>
-      <c r="M81" s="94"/>
-      <c r="N81" s="94"/>
-      <c r="O81" s="94"/>
-      <c r="P81" s="94"/>
-      <c r="Q81" s="94"/>
-      <c r="R81" s="94"/>
-      <c r="S81" s="94"/>
-      <c r="T81" s="94"/>
-      <c r="U81" s="94"/>
-      <c r="V81" s="94"/>
+      <c r="B81" s="97" t="str">
+        <f>VLOOKUP("label.lsrSweep",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSR 扫描</v>
+      </c>
+      <c r="C81" s="97"/>
+      <c r="D81" s="97"/>
+      <c r="E81" s="97"/>
+      <c r="F81" s="97"/>
+      <c r="G81" s="97"/>
+      <c r="H81" s="97"/>
+      <c r="I81" s="97"/>
+      <c r="J81" s="97"/>
+      <c r="K81" s="97"/>
+      <c r="L81" s="97"/>
+      <c r="M81" s="97"/>
+      <c r="N81" s="97"/>
+      <c r="O81" s="97"/>
+      <c r="P81" s="97"/>
+      <c r="Q81" s="97"/>
+      <c r="R81" s="97"/>
+      <c r="S81" s="97"/>
+      <c r="T81" s="97"/>
+      <c r="U81" s="97"/>
+      <c r="V81" s="97"/>
     </row>
     <row r="82" spans="2:22" ht="22" customHeight="1">
       <c r="B82" s="4"/>
@@ -16316,68 +18267,82 @@
       <c r="V83" s="4"/>
     </row>
     <row r="84" spans="2:22" ht="44.15" customHeight="1">
-      <c r="B84" s="41" t="s">
-        <v>51</v>
+      <c r="B84" s="41" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>曲线</v>
       </c>
       <c r="C84" s="40" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F84" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="G84" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H84" s="41" t="s">
-        <v>55</v>
+      <c r="G84" s="41" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H84" s="41" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>bump2 倍率</v>
       </c>
       <c r="I84" s="40" t="s">
         <v>26</v>
       </c>
       <c r="J84" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="K84" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="L84" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="M84" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="K84" s="41" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L84" s="41" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M84" s="40" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N84" s="40" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O84" s="41" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P84" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="N84" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="O84" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="P84" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q84" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="R84" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="S84" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="T84" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="U84" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="V84" s="41" t="s">
-        <v>64</v>
+      <c r="Q84" s="41" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R84" s="41" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S84" s="41" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T84" s="41" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U84" s="41" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V84" s="41" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="85" spans="2:22" ht="25" customHeight="1">
@@ -16880,8 +18845,9 @@
       <c r="V92" s="4"/>
     </row>
     <row r="93" spans="2:22" ht="30" customHeight="1">
-      <c r="B93" s="50" t="s">
-        <v>18</v>
+      <c r="B93" s="50" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C93" s="51" t="str">
         <f>B85</f>
@@ -17898,29 +19864,30 @@
       <c r="V120" s="4"/>
     </row>
     <row r="121" spans="2:22" ht="32.15" customHeight="1">
-      <c r="B121" s="94" t="s">
-        <v>67</v>
-      </c>
-      <c r="C121" s="94"/>
-      <c r="D121" s="94"/>
-      <c r="E121" s="94"/>
-      <c r="F121" s="94"/>
-      <c r="G121" s="94"/>
-      <c r="H121" s="94"/>
-      <c r="I121" s="94"/>
-      <c r="J121" s="94"/>
-      <c r="K121" s="94"/>
-      <c r="L121" s="94"/>
-      <c r="M121" s="94"/>
-      <c r="N121" s="94"/>
-      <c r="O121" s="94"/>
-      <c r="P121" s="94"/>
-      <c r="Q121" s="94"/>
-      <c r="R121" s="94"/>
-      <c r="S121" s="94"/>
-      <c r="T121" s="94"/>
-      <c r="U121" s="94"/>
-      <c r="V121" s="94"/>
+      <c r="B121" s="97" t="str">
+        <f>VLOOKUP("label.fullSweep",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>全范围扫描</v>
+      </c>
+      <c r="C121" s="97"/>
+      <c r="D121" s="97"/>
+      <c r="E121" s="97"/>
+      <c r="F121" s="97"/>
+      <c r="G121" s="97"/>
+      <c r="H121" s="97"/>
+      <c r="I121" s="97"/>
+      <c r="J121" s="97"/>
+      <c r="K121" s="97"/>
+      <c r="L121" s="97"/>
+      <c r="M121" s="97"/>
+      <c r="N121" s="97"/>
+      <c r="O121" s="97"/>
+      <c r="P121" s="97"/>
+      <c r="Q121" s="97"/>
+      <c r="R121" s="97"/>
+      <c r="S121" s="97"/>
+      <c r="T121" s="97"/>
+      <c r="U121" s="97"/>
+      <c r="V121" s="97"/>
     </row>
     <row r="122" spans="2:22" ht="22" customHeight="1">
       <c r="B122" s="4"/>
@@ -17969,68 +19936,82 @@
       <c r="V123" s="4"/>
     </row>
     <row r="124" spans="2:22" ht="44.15" customHeight="1">
-      <c r="B124" s="41" t="s">
-        <v>51</v>
+      <c r="B124" s="41" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>曲线</v>
       </c>
       <c r="C124" s="40" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D124" s="40" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E124" s="40" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F124" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="G124" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H124" s="41" t="s">
-        <v>55</v>
+      <c r="G124" s="41" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H124" s="41" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>bump2 倍率</v>
       </c>
       <c r="I124" s="40" t="s">
         <v>26</v>
       </c>
       <c r="J124" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="K124" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="L124" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="M124" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="K124" s="41" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L124" s="41" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M124" s="40" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N124" s="40" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O124" s="41" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P124" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="N124" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="O124" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="P124" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q124" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="R124" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="S124" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="T124" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="U124" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="V124" s="41" t="s">
-        <v>64</v>
+      <c r="Q124" s="41" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R124" s="41" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S124" s="41" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T124" s="41" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U124" s="41" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V124" s="41" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="125" spans="2:22" ht="25" customHeight="1">
@@ -18533,8 +20514,9 @@
       <c r="V132" s="4"/>
     </row>
     <row r="133" spans="2:22" ht="30" customHeight="1">
-      <c r="B133" s="50" t="s">
-        <v>18</v>
+      <c r="B133" s="50" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C133" s="51" t="str">
         <f>B125</f>
@@ -19812,93 +21794,108 @@
       <c r="V157" s="4"/>
     </row>
     <row r="161" spans="2:22" ht="32.15" customHeight="1">
-      <c r="B161" s="95" t="s">
-        <v>68</v>
-      </c>
-      <c r="C161" s="95"/>
-      <c r="D161" s="95"/>
-      <c r="E161" s="95"/>
-      <c r="F161" s="95"/>
-      <c r="G161" s="95"/>
-      <c r="H161" s="95"/>
-      <c r="I161" s="95"/>
-      <c r="J161" s="95"/>
-      <c r="K161" s="95"/>
-      <c r="L161" s="95"/>
-      <c r="M161" s="95"/>
-      <c r="N161" s="95"/>
-      <c r="O161" s="95"/>
-      <c r="P161" s="95"/>
-      <c r="Q161" s="95"/>
-      <c r="R161" s="95"/>
-      <c r="S161" s="95"/>
-      <c r="T161" s="95"/>
-      <c r="U161" s="95"/>
-      <c r="V161" s="95"/>
+      <c r="B161" s="98" t="str">
+        <f>VLOOKUP("label.calculator",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>计算器</v>
+      </c>
+      <c r="C161" s="98"/>
+      <c r="D161" s="98"/>
+      <c r="E161" s="98"/>
+      <c r="F161" s="98"/>
+      <c r="G161" s="98"/>
+      <c r="H161" s="98"/>
+      <c r="I161" s="98"/>
+      <c r="J161" s="98"/>
+      <c r="K161" s="98"/>
+      <c r="L161" s="98"/>
+      <c r="M161" s="98"/>
+      <c r="N161" s="98"/>
+      <c r="O161" s="98"/>
+      <c r="P161" s="98"/>
+      <c r="Q161" s="98"/>
+      <c r="R161" s="98"/>
+      <c r="S161" s="98"/>
+      <c r="T161" s="98"/>
+      <c r="U161" s="98"/>
+      <c r="V161" s="98"/>
     </row>
     <row r="164" spans="2:22" ht="44.15" customHeight="1">
-      <c r="B164" s="54" t="s">
-        <v>51</v>
+      <c r="B164" s="54" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>曲线</v>
       </c>
       <c r="C164" s="55" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D164" s="55" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E164" s="55" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F164" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G164" s="54" t="s">
-        <v>32</v>
-      </c>
-      <c r="H164" s="54" t="s">
-        <v>55</v>
+      <c r="G164" s="54" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H164" s="54" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>bump2 倍率</v>
       </c>
       <c r="I164" s="55" t="s">
         <v>26</v>
       </c>
       <c r="J164" s="55" t="s">
-        <v>56</v>
-      </c>
-      <c r="K164" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="L164" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="M164" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K164" s="54" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L164" s="54" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M164" s="55" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N164" s="55" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O164" s="54" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P164" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="N164" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="O164" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="P164" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q164" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="R164" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="S164" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="T164" s="54" t="s">
-        <v>62</v>
-      </c>
-      <c r="U164" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="V164" s="54" t="s">
-        <v>64</v>
+      <c r="Q164" s="54" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R164" s="54" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S164" s="54" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T164" s="54" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U164" s="54" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V164" s="54" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="165" spans="2:22" ht="25" customHeight="1">
@@ -19992,7 +21989,8 @@
     <mergeCell ref="B121:V121"/>
     <mergeCell ref="B161:V161"/>
   </mergeCells>
-  <phoneticPr fontId="74" type="noConversion"/>
+  <phoneticPr fontId="73" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/damping_curve_RAx8.xlsx
+++ b/docs/damping_curve_RAx8.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\xlsx-locale-20261027\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9738C9B-05B1-481C-9E92-C3B20E39C534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E491ADC5-F862-4705-9401-3F66287E1DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -290,7 +290,7 @@
   </si>
   <si>
     <t>RA88</t>
-    <phoneticPr fontId="73" type="noConversion"/>
+    <phoneticPr fontId="72" type="noConversion"/>
   </si>
   <si>
     <t>Rally</t>
@@ -837,11 +837,11 @@
   </si>
   <si>
     <t>Type-A</t>
-    <phoneticPr fontId="73" type="noConversion"/>
+    <phoneticPr fontId="72" type="noConversion"/>
   </si>
   <si>
     <t>简体中文</t>
-    <phoneticPr fontId="73" type="noConversion"/>
+    <phoneticPr fontId="72" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -853,7 +853,7 @@
     <numFmt numFmtId="177" formatCode="0&quot; mm&quot;"/>
     <numFmt numFmtId="178" formatCode="0&quot; clicks&quot;"/>
   </numFmts>
-  <fonts count="76">
+  <fonts count="75">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -990,12 +990,6 @@
       <sz val="11"/>
       <color rgb="FF195DB1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF667B91"/>
-      <name val="微软雅黑"/>
       <family val="2"/>
     </font>
     <font>
@@ -1336,7 +1330,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="71">
+  <fills count="70">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1401,11 +1395,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1687,7 +1676,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="66">
+  <borders count="65">
     <border>
       <left/>
       <right/>
@@ -1790,15 +1779,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFDCE4EB"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2227,11 +2207,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2303,44 +2283,47 @@
     <xf numFmtId="1" fontId="21" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="26" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="25" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="31" fillId="23" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="32" fillId="24" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="33" fillId="25" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="34" fillId="26" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="36" fillId="28" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="37" fillId="29" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="38" fillId="30" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="33" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="43" fillId="35" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="42" fillId="34" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="36" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="35" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="42" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="51" fillId="43" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="44" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2352,7 +2335,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="47" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="48" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2364,60 +2347,57 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="51" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="52" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="53" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="61" fillId="53" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="62" fillId="54" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="63" fillId="55" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="56" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="65" fillId="57" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="66" fillId="58" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="67" fillId="59" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="68" fillId="60" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="61" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="62" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="63" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="64" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="64" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="65" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="65" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="66" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="65" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="67" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="64" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="66" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="67" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="65" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="66" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2429,33 +2409,87 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="68" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="75" fillId="70" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="67" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="74" fillId="69" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="59" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="67" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="68" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="23" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="39" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="40" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="33" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="37" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2463,63 +2497,6 @@
     </xf>
     <xf numFmtId="0" fontId="46" fillId="38" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="39" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="40" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="41" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="68" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="69" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="42" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="60" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8202,37 +8179,37 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1">
       <c r="A1" s="6"/>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="89" t="s">
+      <c r="C1" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="89" t="s">
+      <c r="D1" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="90" t="s">
+      <c r="E1" s="72" t="s">
         <v>265</v>
       </c>
-      <c r="F1" s="90" t="s">
+      <c r="F1" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="90" t="s">
+      <c r="G1" s="72" t="s">
         <v>86</v>
       </c>
       <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" ht="35.15" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="86" t="str">
+      <c r="B2" s="74" t="str">
         <f>VLOOKUP("title.rax8DamperCatalog",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>CTM Racing · RAx8 · 避震器目录</v>
       </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -8280,7 +8257,7 @@
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="88" t="s">
+      <c r="B6" s="76" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="6"/>
@@ -8300,7 +8277,7 @@
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="88"/>
+      <c r="B7" s="76"/>
       <c r="C7" s="6"/>
       <c r="D7" s="10" t="str">
         <f>VLOOKUP("label.lowSpeedCompressionC",Locale!$A$2:$D$78,4,FALSE)</f>
@@ -8431,30 +8408,30 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="85"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="85"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="25" customHeight="1">
@@ -8507,7 +8484,7 @@
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
   </mergeCells>
-  <phoneticPr fontId="73" type="noConversion"/>
+  <phoneticPr fontId="72" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="E1:G1" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"English,简体中文"</formula1>
@@ -8552,21 +8529,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="70" t="str">
+      <c r="B2" s="1" t="str">
         <f>VLOOKUP("title.rax8DampingCalculator",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>CTM Racing · RAx8 · 阻尼计算器</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -8597,15 +8574,15 @@
         <v>264</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -8637,14 +8614,14 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="74" t="str">
+      <c r="F6" s="83" t="str">
         <f>VLOOKUP("title.currentDampingForce",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>当前输入 · 阻尼力大小</v>
       </c>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -8686,13 +8663,13 @@
         <f>VLOOKUP("label.compressionForceN",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>压缩力 (N)</v>
       </c>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="92">
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="86">
         <f>IF(C18=VLOOKUP("status.ok",Locale!$A$2:$D$78,4,FALSE),Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),VLOOKUP("status.checkInput",Locale!$A$2:$D$78,4,FALSE))</f>
         <v>2151.6666666666665</v>
       </c>
-      <c r="J8" s="93"/>
+      <c r="J8" s="87"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -8735,13 +8712,13 @@
         <f>VLOOKUP("label.reboundForceN",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>回弹力 (N)</v>
       </c>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="92">
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="86">
         <f>IF(C18=VLOOKUP("status.ok",Locale!$A$2:$D$78,4,FALSE),Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),VLOOKUP("status.checkInput",Locale!$A$2:$D$78,4,FALSE))</f>
         <v>1467.3359999999998</v>
       </c>
-      <c r="J10" s="93"/>
+      <c r="J10" s="87"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -8794,14 +8771,14 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="74" t="str">
+      <c r="F13" s="83" t="str">
         <f>VLOOKUP("title.currentCurveParameters",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>当前曲线参数</v>
       </c>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="73"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="84"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -8820,11 +8797,11 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="94" t="s">
+      <c r="F14" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
       <c r="I14" s="29">
         <f>Samples!F165</f>
         <v>3400</v>
@@ -8850,11 +8827,11 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="77" t="s">
+      <c r="F15" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
       <c r="I15" s="30">
         <f>Samples!I165</f>
         <v>3173.3333333333335</v>
@@ -8874,12 +8851,12 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="75" t="str">
+      <c r="F16" s="82" t="str">
         <f>VLOOKUP("label.highSpeedBumpIncrement",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>HSbump · 高速增量</v>
       </c>
-      <c r="G16" s="76"/>
-      <c r="H16" s="76"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="79"/>
       <c r="I16" s="29">
         <f>Samples!J165</f>
         <v>1500</v>
@@ -8903,8 +8880,8 @@
         <f>VLOOKUP("label.totalHighSpeedCoefficient",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>总高速系数</v>
       </c>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
       <c r="I17" s="30">
         <f>Samples!L165</f>
         <v>4673.3333333333339</v>
@@ -8947,12 +8924,12 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="94" t="str">
+      <c r="F19" s="78" t="str">
         <f>VLOOKUP("label.rebound",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>回弹</v>
       </c>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="79"/>
       <c r="I19" s="29">
         <f>Samples!M165</f>
         <v>2600</v>
@@ -8972,11 +8949,11 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="77" t="s">
+      <c r="F20" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
       <c r="I20" s="30">
         <f>Samples!P165</f>
         <v>2319.1999999999998</v>
@@ -9013,12 +8990,12 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="75" t="str">
+      <c r="F22" s="82" t="str">
         <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>第一拐点</v>
       </c>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
       <c r="I22" s="32">
         <f>Samples!G165</f>
         <v>0.1</v>
@@ -9042,8 +9019,8 @@
         <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>第二拐点</v>
       </c>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
       <c r="I23" s="33">
         <f>Samples!K165</f>
         <v>0.45</v>
@@ -9063,12 +9040,12 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="94" t="str">
+      <c r="F24" s="78" t="str">
         <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>回弹拐点</v>
       </c>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="79"/>
       <c r="I24" s="32">
         <f>Samples!N165</f>
         <v>0.27</v>
@@ -9118,21 +9095,21 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="70" t="str">
+      <c r="B27" s="1" t="str">
         <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>黄色单元格为手动输入。</v>
       </c>
-      <c r="C27" s="95"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="95"/>
-      <c r="G27" s="95"/>
-      <c r="H27" s="95"/>
-      <c r="I27" s="95"/>
-      <c r="J27" s="95"/>
-      <c r="K27" s="95"/>
-      <c r="L27" s="95"/>
-      <c r="M27" s="95"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="77"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="77"/>
+      <c r="K27" s="77"/>
+      <c r="L27" s="77"/>
+      <c r="M27" s="77"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
@@ -9393,17 +9370,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -9411,8 +9377,19 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
-  <phoneticPr fontId="73" type="noConversion"/>
+  <phoneticPr fontId="72" type="noConversion"/>
   <dataValidations count="5">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -9468,21 +9445,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="70" t="str">
+      <c r="B2" s="1" t="str">
         <f>VLOOKUP("title.rax8LSCSweep",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>CTM Racing · RAx8 · LSC 扫描</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -9513,15 +9490,15 @@
         <v>264</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -9552,15 +9529,15 @@
         <v>-10</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -10144,18 +10121,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="96"/>
-      <c r="C41" s="96"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="96"/>
-      <c r="F41" s="96"/>
-      <c r="G41" s="96"/>
-      <c r="H41" s="96"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="96"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="96"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="88"/>
+      <c r="J41" s="88"/>
+      <c r="K41" s="88"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="88"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -10183,7 +10160,7 @@
     <mergeCell ref="E6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="73" type="noConversion"/>
+  <phoneticPr fontId="72" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -10230,21 +10207,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="70" t="str">
+      <c r="B2" s="1" t="str">
         <f>VLOOKUP("title.rax8HSCSweep",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>CTM Racing · RAx8 · HSC 扫描</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -10275,15 +10252,15 @@
         <v>264</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -10314,15 +10291,15 @@
         <v>-8</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -10906,18 +10883,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="96"/>
-      <c r="C41" s="96"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="96"/>
-      <c r="F41" s="96"/>
-      <c r="G41" s="96"/>
-      <c r="H41" s="96"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="96"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="96"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="88"/>
+      <c r="J41" s="88"/>
+      <c r="K41" s="88"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="88"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -10945,7 +10922,7 @@
     <mergeCell ref="E6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="73" type="noConversion"/>
+  <phoneticPr fontId="72" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -10992,21 +10969,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="70" t="str">
+      <c r="B2" s="1" t="str">
         <f>VLOOKUP("title.rax8LSRSweep",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>CTM Racing · RAx8 · LSR 扫描</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -11037,15 +11014,15 @@
         <v>264</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -11068,18 +11045,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -11663,18 +11640,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="96"/>
-      <c r="C41" s="96"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="96"/>
-      <c r="F41" s="96"/>
-      <c r="G41" s="96"/>
-      <c r="H41" s="96"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="96"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="96"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="88"/>
+      <c r="J41" s="88"/>
+      <c r="K41" s="88"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="88"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -11702,7 +11679,7 @@
     <mergeCell ref="B6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="73" type="noConversion"/>
+  <phoneticPr fontId="72" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -11745,21 +11722,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="70" t="str">
+      <c r="B2" s="1" t="str">
         <f>VLOOKUP("title.rax8FullSweep",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>CTM Racing · RAx8 · 全范围扫描</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="19"/>
       <c r="O2" s="2"/>
     </row>
@@ -11790,15 +11767,15 @@
         <v>264</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
@@ -11821,18 +11798,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
@@ -12416,18 +12393,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="96"/>
-      <c r="C41" s="96"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="96"/>
-      <c r="F41" s="96"/>
-      <c r="G41" s="96"/>
-      <c r="H41" s="96"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="96"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="96"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="88"/>
+      <c r="J41" s="88"/>
+      <c r="K41" s="88"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="88"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
@@ -12455,7 +12432,7 @@
     <mergeCell ref="B6:M6"/>
     <mergeCell ref="B41:M41"/>
   </mergeCells>
-  <phoneticPr fontId="73" type="noConversion"/>
+  <phoneticPr fontId="72" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C4" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Type-A,Type-B"</formula1>
@@ -12502,42 +12479,42 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="70" t="str">
+      <c r="B2" s="1" t="str">
         <f>VLOOKUP("title.rax8ValvingParameters",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>CTM Racing · RAx8 · 阀系参数</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="71" t="str">
+      <c r="B3" s="93" t="str">
         <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>黄色单元格为手动输入。</v>
       </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -12561,21 +12538,21 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="73" t="s">
+      <c r="D5" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="73" t="s">
+      <c r="J5" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="73"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -13221,47 +13198,47 @@
     </row>
     <row r="22" spans="1:15" ht="32.15" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="74" t="str">
+      <c r="B22" s="83" t="str">
         <f>VLOOKUP("label.adjusterClicks",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>调节格数</v>
       </c>
-      <c r="C22" s="73"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
-      <c r="K22" s="73"/>
-      <c r="L22" s="73"/>
-      <c r="M22" s="73"/>
-      <c r="N22" s="73"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
       <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:15" ht="29.15" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="75" t="str">
+      <c r="B23" s="82" t="str">
         <f>VLOOKUP("label.lscAllSeries",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>LSC · 全系列</v>
       </c>
-      <c r="C23" s="76"/>
+      <c r="C23" s="79"/>
       <c r="D23" s="26">
         <v>24</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="78" t="str">
+      <c r="F23" s="95" t="str">
         <f>VLOOKUP("note.sweepRa88Clicks",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>调节曲线使用 RA88 调节格数。</v>
       </c>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="79"/>
-      <c r="K23" s="79"/>
-      <c r="L23" s="79"/>
-      <c r="M23" s="79"/>
-      <c r="N23" s="79"/>
+      <c r="G23" s="96"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="96"/>
+      <c r="L23" s="96"/>
+      <c r="M23" s="96"/>
+      <c r="N23" s="96"/>
       <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:15" ht="29.15" customHeight="1">
@@ -13269,28 +13246,28 @@
       <c r="B24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="69"/>
+      <c r="C24" s="81"/>
       <c r="D24" s="28">
         <v>20</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="79"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="79"/>
-      <c r="K24" s="79"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="79"/>
-      <c r="N24" s="79"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="96"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="96"/>
+      <c r="L24" s="96"/>
+      <c r="M24" s="96"/>
+      <c r="N24" s="96"/>
       <c r="O24" s="2"/>
     </row>
     <row r="25" spans="1:15" ht="29.15" customHeight="1">
       <c r="A25" s="2"/>
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="76"/>
+      <c r="C25" s="79"/>
       <c r="D25" s="26">
         <v>40</v>
       </c>
@@ -13308,26 +13285,26 @@
     </row>
     <row r="26" spans="1:15" ht="29.15" customHeight="1">
       <c r="A26" s="2"/>
-      <c r="B26" s="77" t="s">
+      <c r="B26" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="69"/>
+      <c r="C26" s="81"/>
       <c r="D26" s="28">
         <v>40</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="80" t="str">
+      <c r="F26" s="97" t="str">
         <f>VLOOKUP("note.adjusterClicks",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>0 为最硬，负数为退出格数。</v>
       </c>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="72"/>
+      <c r="G26" s="94"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="94"/>
+      <c r="J26" s="94"/>
+      <c r="K26" s="94"/>
+      <c r="L26" s="94"/>
+      <c r="M26" s="94"/>
+      <c r="N26" s="94"/>
       <c r="O26" s="2"/>
     </row>
     <row r="27" spans="1:15" ht="29.15" customHeight="1">
@@ -13335,7 +13312,7 @@
       <c r="B27" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="69"/>
+      <c r="C27" s="81"/>
       <c r="D27" s="28">
         <v>10</v>
       </c>
@@ -13353,141 +13330,141 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="82" t="str">
+      <c r="B28" s="90" t="str">
         <f>VLOOKUP("note.baseDampingCurve",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>连续分段理论曲线，仅基础阻尼。</v>
       </c>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="83"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="91"/>
+      <c r="H28" s="91"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="91"/>
+      <c r="K28" s="91"/>
+      <c r="L28" s="91"/>
+      <c r="M28" s="91"/>
+      <c r="N28" s="91"/>
       <c r="O28" s="2"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="2"/>
-      <c r="B29" s="81"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="81"/>
-      <c r="K29" s="81"/>
-      <c r="L29" s="81"/>
-      <c r="M29" s="81"/>
-      <c r="N29" s="81"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="89"/>
+      <c r="N29" s="89"/>
       <c r="O29" s="2"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="84"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="84"/>
-      <c r="K30" s="84"/>
-      <c r="L30" s="84"/>
-      <c r="M30" s="84"/>
-      <c r="N30" s="84"/>
+      <c r="B30" s="92"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="92"/>
+      <c r="G30" s="92"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="92"/>
+      <c r="J30" s="92"/>
+      <c r="K30" s="92"/>
+      <c r="L30" s="92"/>
+      <c r="M30" s="92"/>
+      <c r="N30" s="92"/>
       <c r="O30" s="2"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="81"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="81"/>
-      <c r="K31" s="81"/>
-      <c r="L31" s="81"/>
-      <c r="M31" s="81"/>
-      <c r="N31" s="81"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="89"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
+      <c r="L31" s="89"/>
+      <c r="M31" s="89"/>
+      <c r="N31" s="89"/>
       <c r="O31" s="2"/>
     </row>
     <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="2"/>
-      <c r="B32" s="81"/>
-      <c r="C32" s="81"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="81"/>
-      <c r="L32" s="81"/>
-      <c r="M32" s="81"/>
-      <c r="N32" s="81"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="89"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="89"/>
+      <c r="J32" s="89"/>
+      <c r="K32" s="89"/>
+      <c r="L32" s="89"/>
+      <c r="M32" s="89"/>
+      <c r="N32" s="89"/>
       <c r="O32" s="2"/>
     </row>
     <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="81"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="81"/>
-      <c r="K33" s="81"/>
-      <c r="L33" s="81"/>
-      <c r="M33" s="81"/>
-      <c r="N33" s="81"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="89"/>
+      <c r="D33" s="89"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="89"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="89"/>
+      <c r="J33" s="89"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="89"/>
+      <c r="M33" s="89"/>
+      <c r="N33" s="89"/>
       <c r="O33" s="2"/>
     </row>
     <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="81"/>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="81"/>
-      <c r="K34" s="81"/>
-      <c r="L34" s="81"/>
-      <c r="M34" s="81"/>
-      <c r="N34" s="81"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="89"/>
+      <c r="G34" s="89"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="89"/>
+      <c r="J34" s="89"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="89"/>
+      <c r="M34" s="89"/>
+      <c r="N34" s="89"/>
       <c r="O34" s="2"/>
     </row>
     <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="2"/>
-      <c r="B35" s="81"/>
-      <c r="C35" s="81"/>
-      <c r="D35" s="81"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="81"/>
-      <c r="K35" s="81"/>
-      <c r="L35" s="81"/>
-      <c r="M35" s="81"/>
-      <c r="N35" s="81"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="89"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="89"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="89"/>
+      <c r="H35" s="89"/>
+      <c r="I35" s="89"/>
+      <c r="J35" s="89"/>
+      <c r="K35" s="89"/>
+      <c r="L35" s="89"/>
+      <c r="M35" s="89"/>
+      <c r="N35" s="89"/>
       <c r="O35" s="2"/>
     </row>
     <row r="36" spans="1:15" ht="23.15" customHeight="1">
@@ -13594,14 +13571,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -13614,8 +13583,16 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
   </mergeCells>
-  <phoneticPr fontId="73" type="noConversion"/>
+  <phoneticPr fontId="72" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -14796,7 +14773,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="73" type="noConversion"/>
+  <phoneticPr fontId="72" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14816,30 +14793,30 @@
   <sheetData>
     <row r="1" spans="1:22" ht="32.15" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="70" t="str">
+      <c r="B1" s="1" t="str">
         <f>VLOOKUP("label.lscSweep",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>LSC 扫描</v>
       </c>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
     </row>
     <row r="2" spans="1:22" ht="22" customHeight="1">
       <c r="A2" s="2"/>
@@ -16525,30 +16502,30 @@
     </row>
     <row r="41" spans="1:22" ht="32.15" customHeight="1">
       <c r="A41" s="2"/>
-      <c r="B41" s="70" t="str">
+      <c r="B41" s="1" t="str">
         <f>VLOOKUP("label.hscSweep",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>HSC 扫描</v>
       </c>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="70"/>
-      <c r="N41" s="70"/>
-      <c r="O41" s="70"/>
-      <c r="P41" s="97"/>
-      <c r="Q41" s="97"/>
-      <c r="R41" s="97"/>
-      <c r="S41" s="97"/>
-      <c r="T41" s="97"/>
-      <c r="U41" s="97"/>
-      <c r="V41" s="97"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="69"/>
+      <c r="Q41" s="69"/>
+      <c r="R41" s="69"/>
+      <c r="S41" s="69"/>
+      <c r="T41" s="69"/>
+      <c r="U41" s="69"/>
+      <c r="V41" s="69"/>
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1">
       <c r="A42" s="2"/>
@@ -18195,30 +18172,30 @@
       <c r="V80" s="4"/>
     </row>
     <row r="81" spans="2:22" ht="32.15" customHeight="1">
-      <c r="B81" s="97" t="str">
+      <c r="B81" s="69" t="str">
         <f>VLOOKUP("label.lsrSweep",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>LSR 扫描</v>
       </c>
-      <c r="C81" s="97"/>
-      <c r="D81" s="97"/>
-      <c r="E81" s="97"/>
-      <c r="F81" s="97"/>
-      <c r="G81" s="97"/>
-      <c r="H81" s="97"/>
-      <c r="I81" s="97"/>
-      <c r="J81" s="97"/>
-      <c r="K81" s="97"/>
-      <c r="L81" s="97"/>
-      <c r="M81" s="97"/>
-      <c r="N81" s="97"/>
-      <c r="O81" s="97"/>
-      <c r="P81" s="97"/>
-      <c r="Q81" s="97"/>
-      <c r="R81" s="97"/>
-      <c r="S81" s="97"/>
-      <c r="T81" s="97"/>
-      <c r="U81" s="97"/>
-      <c r="V81" s="97"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="69"/>
+      <c r="E81" s="69"/>
+      <c r="F81" s="69"/>
+      <c r="G81" s="69"/>
+      <c r="H81" s="69"/>
+      <c r="I81" s="69"/>
+      <c r="J81" s="69"/>
+      <c r="K81" s="69"/>
+      <c r="L81" s="69"/>
+      <c r="M81" s="69"/>
+      <c r="N81" s="69"/>
+      <c r="O81" s="69"/>
+      <c r="P81" s="69"/>
+      <c r="Q81" s="69"/>
+      <c r="R81" s="69"/>
+      <c r="S81" s="69"/>
+      <c r="T81" s="69"/>
+      <c r="U81" s="69"/>
+      <c r="V81" s="69"/>
     </row>
     <row r="82" spans="2:22" ht="22" customHeight="1">
       <c r="B82" s="4"/>
@@ -19864,30 +19841,30 @@
       <c r="V120" s="4"/>
     </row>
     <row r="121" spans="2:22" ht="32.15" customHeight="1">
-      <c r="B121" s="97" t="str">
+      <c r="B121" s="69" t="str">
         <f>VLOOKUP("label.fullSweep",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>全范围扫描</v>
       </c>
-      <c r="C121" s="97"/>
-      <c r="D121" s="97"/>
-      <c r="E121" s="97"/>
-      <c r="F121" s="97"/>
-      <c r="G121" s="97"/>
-      <c r="H121" s="97"/>
-      <c r="I121" s="97"/>
-      <c r="J121" s="97"/>
-      <c r="K121" s="97"/>
-      <c r="L121" s="97"/>
-      <c r="M121" s="97"/>
-      <c r="N121" s="97"/>
-      <c r="O121" s="97"/>
-      <c r="P121" s="97"/>
-      <c r="Q121" s="97"/>
-      <c r="R121" s="97"/>
-      <c r="S121" s="97"/>
-      <c r="T121" s="97"/>
-      <c r="U121" s="97"/>
-      <c r="V121" s="97"/>
+      <c r="C121" s="69"/>
+      <c r="D121" s="69"/>
+      <c r="E121" s="69"/>
+      <c r="F121" s="69"/>
+      <c r="G121" s="69"/>
+      <c r="H121" s="69"/>
+      <c r="I121" s="69"/>
+      <c r="J121" s="69"/>
+      <c r="K121" s="69"/>
+      <c r="L121" s="69"/>
+      <c r="M121" s="69"/>
+      <c r="N121" s="69"/>
+      <c r="O121" s="69"/>
+      <c r="P121" s="69"/>
+      <c r="Q121" s="69"/>
+      <c r="R121" s="69"/>
+      <c r="S121" s="69"/>
+      <c r="T121" s="69"/>
+      <c r="U121" s="69"/>
+      <c r="V121" s="69"/>
     </row>
     <row r="122" spans="2:22" ht="22" customHeight="1">
       <c r="B122" s="4"/>
@@ -21794,30 +21771,30 @@
       <c r="V157" s="4"/>
     </row>
     <row r="161" spans="2:22" ht="32.15" customHeight="1">
-      <c r="B161" s="98" t="str">
+      <c r="B161" s="70" t="str">
         <f>VLOOKUP("label.calculator",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>计算器</v>
       </c>
-      <c r="C161" s="98"/>
-      <c r="D161" s="98"/>
-      <c r="E161" s="98"/>
-      <c r="F161" s="98"/>
-      <c r="G161" s="98"/>
-      <c r="H161" s="98"/>
-      <c r="I161" s="98"/>
-      <c r="J161" s="98"/>
-      <c r="K161" s="98"/>
-      <c r="L161" s="98"/>
-      <c r="M161" s="98"/>
-      <c r="N161" s="98"/>
-      <c r="O161" s="98"/>
-      <c r="P161" s="98"/>
-      <c r="Q161" s="98"/>
-      <c r="R161" s="98"/>
-      <c r="S161" s="98"/>
-      <c r="T161" s="98"/>
-      <c r="U161" s="98"/>
-      <c r="V161" s="98"/>
+      <c r="C161" s="70"/>
+      <c r="D161" s="70"/>
+      <c r="E161" s="70"/>
+      <c r="F161" s="70"/>
+      <c r="G161" s="70"/>
+      <c r="H161" s="70"/>
+      <c r="I161" s="70"/>
+      <c r="J161" s="70"/>
+      <c r="K161" s="70"/>
+      <c r="L161" s="70"/>
+      <c r="M161" s="70"/>
+      <c r="N161" s="70"/>
+      <c r="O161" s="70"/>
+      <c r="P161" s="70"/>
+      <c r="Q161" s="70"/>
+      <c r="R161" s="70"/>
+      <c r="S161" s="70"/>
+      <c r="T161" s="70"/>
+      <c r="U161" s="70"/>
+      <c r="V161" s="70"/>
     </row>
     <row r="164" spans="2:22" ht="44.15" customHeight="1">
       <c r="B164" s="54" t="str">
@@ -21989,7 +21966,7 @@
     <mergeCell ref="B121:V121"/>
     <mergeCell ref="B161:V161"/>
   </mergeCells>
-  <phoneticPr fontId="73" type="noConversion"/>
+  <phoneticPr fontId="72" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
